--- a/data/LTMC.MI.xlsx
+++ b/data/LTMC.MI.xlsx
@@ -19991,6 +19991,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="854">
+      <c r="A854" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B854" t="n">
+        <v>875424</v>
+      </c>
+      <c r="C854" t="n">
+        <v>27.7600002288818</v>
+      </c>
+      <c r="D854" t="n">
+        <v>27.0599994659424</v>
+      </c>
+      <c r="E854" t="n">
+        <v>27.4300003051758</v>
+      </c>
+      <c r="F854" t="n">
+        <v>27.2000007629395</v>
+      </c>
+      <c r="G854" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LTMC.MI.xlsx
+++ b/data/LTMC.MI.xlsx
@@ -20014,6 +20014,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="855">
+      <c r="A855" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B855" t="n">
+        <v>869268</v>
+      </c>
+      <c r="C855" t="n">
+        <v>27.2700004577637</v>
+      </c>
+      <c r="D855" t="n">
+        <v>26.5300006866455</v>
+      </c>
+      <c r="E855" t="n">
+        <v>27.0799999237061</v>
+      </c>
+      <c r="F855" t="n">
+        <v>26.8500003814697</v>
+      </c>
+      <c r="G855" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LTMC.MI.xlsx
+++ b/data/LTMC.MI.xlsx
@@ -20037,6 +20037,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="856">
+      <c r="A856" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B856" t="n">
+        <v>974220</v>
+      </c>
+      <c r="C856" t="n">
+        <v>27.5900001525879</v>
+      </c>
+      <c r="D856" t="n">
+        <v>26.6299991607666</v>
+      </c>
+      <c r="E856" t="n">
+        <v>26.8099994659424</v>
+      </c>
+      <c r="F856" t="n">
+        <v>27.5900001525879</v>
+      </c>
+      <c r="G856" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LTMC.MI.xlsx
+++ b/data/LTMC.MI.xlsx
@@ -20060,6 +20060,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="857">
+      <c r="A857" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B857" t="n">
+        <v>713829</v>
+      </c>
+      <c r="C857" t="n">
+        <v>28.0300006866455</v>
+      </c>
+      <c r="D857" t="n">
+        <v>27.4599990844727</v>
+      </c>
+      <c r="E857" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="F857" t="n">
+        <v>27.5799999237061</v>
+      </c>
+      <c r="G857" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LTMC.MI.xlsx
+++ b/data/LTMC.MI.xlsx
@@ -19901,22 +19901,22 @@
     </row>
     <row r="850">
       <c r="A850" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B850" t="n">
-        <v>1764284</v>
+        <v>2666871</v>
       </c>
       <c r="C850" t="n">
-        <v>26.6700000762939</v>
+        <v>26.5900001525879</v>
       </c>
       <c r="D850" t="n">
-        <v>25.8500003814697</v>
+        <v>24.2800006866455</v>
       </c>
       <c r="E850" t="n">
-        <v>26.2999992370605</v>
+        <v>24.3099994659424</v>
       </c>
       <c r="F850" t="n">
-        <v>26.1299991607666</v>
+        <v>26.1399993896484</v>
       </c>
       <c r="G850" t="s">
         <v>7</v>
@@ -19924,22 +19924,22 @@
     </row>
     <row r="851">
       <c r="A851" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B851" t="n">
-        <v>1281916</v>
+        <v>1764284</v>
       </c>
       <c r="C851" t="n">
-        <v>26.4699993133545</v>
+        <v>26.6700000762939</v>
       </c>
       <c r="D851" t="n">
-        <v>25.4599990844727</v>
+        <v>25.8500003814697</v>
       </c>
       <c r="E851" t="n">
-        <v>26.0699996948242</v>
+        <v>26.2999992370605</v>
       </c>
       <c r="F851" t="n">
-        <v>26.0799999237061</v>
+        <v>26.1299991607666</v>
       </c>
       <c r="G851" t="s">
         <v>7</v>
@@ -19947,22 +19947,22 @@
     </row>
     <row r="852">
       <c r="A852" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B852" t="n">
-        <v>2547402</v>
+        <v>1281916</v>
       </c>
       <c r="C852" t="n">
-        <v>27.5799999237061</v>
+        <v>26.4699993133545</v>
       </c>
       <c r="D852" t="n">
-        <v>26.0400009155273</v>
+        <v>25.4599990844727</v>
       </c>
       <c r="E852" t="n">
-        <v>26.1399993896484</v>
+        <v>26.0699996948242</v>
       </c>
       <c r="F852" t="n">
-        <v>27.5</v>
+        <v>26.0799999237061</v>
       </c>
       <c r="G852" t="s">
         <v>7</v>
@@ -19970,22 +19970,22 @@
     </row>
     <row r="853">
       <c r="A853" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B853" t="n">
-        <v>1432651</v>
+        <v>2547402</v>
       </c>
       <c r="C853" t="n">
-        <v>27.6800003051758</v>
+        <v>27.5799999237061</v>
       </c>
       <c r="D853" t="n">
-        <v>27.2299995422363</v>
+        <v>26.0400009155273</v>
       </c>
       <c r="E853" t="n">
-        <v>27.4599990844727</v>
+        <v>26.1399993896484</v>
       </c>
       <c r="F853" t="n">
-        <v>27.3299999237061</v>
+        <v>27.5</v>
       </c>
       <c r="G853" t="s">
         <v>7</v>
@@ -19993,22 +19993,22 @@
     </row>
     <row r="854">
       <c r="A854" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B854" t="n">
-        <v>875424</v>
+        <v>1432651</v>
       </c>
       <c r="C854" t="n">
-        <v>27.7600002288818</v>
+        <v>27.6800003051758</v>
       </c>
       <c r="D854" t="n">
-        <v>27.0599994659424</v>
+        <v>27.2299995422363</v>
       </c>
       <c r="E854" t="n">
-        <v>27.4300003051758</v>
+        <v>27.4599990844727</v>
       </c>
       <c r="F854" t="n">
-        <v>27.2000007629395</v>
+        <v>27.3299999237061</v>
       </c>
       <c r="G854" t="s">
         <v>7</v>
@@ -20016,22 +20016,22 @@
     </row>
     <row r="855">
       <c r="A855" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B855" t="n">
-        <v>869268</v>
+        <v>875424</v>
       </c>
       <c r="C855" t="n">
-        <v>27.2700004577637</v>
+        <v>27.7600002288818</v>
       </c>
       <c r="D855" t="n">
-        <v>26.5300006866455</v>
+        <v>27.0599994659424</v>
       </c>
       <c r="E855" t="n">
-        <v>27.0799999237061</v>
+        <v>27.4300003051758</v>
       </c>
       <c r="F855" t="n">
-        <v>26.8500003814697</v>
+        <v>27.2000007629395</v>
       </c>
       <c r="G855" t="s">
         <v>7</v>
@@ -20039,22 +20039,22 @@
     </row>
     <row r="856">
       <c r="A856" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B856" t="n">
-        <v>974220</v>
+        <v>869268</v>
       </c>
       <c r="C856" t="n">
-        <v>27.5900001525879</v>
+        <v>27.2700004577637</v>
       </c>
       <c r="D856" t="n">
-        <v>26.6299991607666</v>
+        <v>26.5300006866455</v>
       </c>
       <c r="E856" t="n">
-        <v>26.8099994659424</v>
+        <v>27.0799999237061</v>
       </c>
       <c r="F856" t="n">
-        <v>27.5900001525879</v>
+        <v>26.8500003814697</v>
       </c>
       <c r="G856" t="s">
         <v>7</v>
@@ -20062,24 +20062,47 @@
     </row>
     <row r="857">
       <c r="A857" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B857" t="n">
-        <v>713829</v>
+        <v>974220</v>
       </c>
       <c r="C857" t="n">
-        <v>28.0300006866455</v>
+        <v>27.5900001525879</v>
       </c>
       <c r="D857" t="n">
-        <v>27.4599990844727</v>
+        <v>26.6299991607666</v>
       </c>
       <c r="E857" t="n">
-        <v>27.75</v>
+        <v>26.8099994659424</v>
       </c>
       <c r="F857" t="n">
-        <v>27.5799999237061</v>
+        <v>27.5900001525879</v>
       </c>
       <c r="G857" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B858" t="n">
+        <v>1705118</v>
+      </c>
+      <c r="C858" t="n">
+        <v>27.5599994659424</v>
+      </c>
+      <c r="D858" t="n">
+        <v>26.9799995422363</v>
+      </c>
+      <c r="E858" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F858" t="n">
+        <v>27.0900001525879</v>
+      </c>
+      <c r="G858" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LTMC.MI.xlsx
+++ b/data/LTMC.MI.xlsx
@@ -421,7 +421,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2" t="n">
-        <v>7.75911998748779</v>
+        <v>7.75911951065063</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G3" t="n">
-        <v>7.82535696029663</v>
+        <v>7.82535743713379</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>8.44600009918213</v>
       </c>
       <c r="G4" t="n">
-        <v>7.99189424514771</v>
+        <v>7.99189376831055</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G7" t="n">
-        <v>7.92944240570068</v>
+        <v>7.92944288253784</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>7.98600006103516</v>
       </c>
       <c r="G8" t="n">
-        <v>7.55662631988525</v>
+        <v>7.5566258430481</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G10" t="n">
-        <v>7.99567890167236</v>
+        <v>7.99567842483521</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>7.72300004959106</v>
       </c>
       <c r="G17" t="n">
-        <v>7.30776643753052</v>
+        <v>7.30776596069336</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>7.80100011825562</v>
       </c>
       <c r="G20" t="n">
-        <v>7.38157224655151</v>
+        <v>7.38157272338867</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>7.50699996948242</v>
       </c>
       <c r="G23" t="n">
-        <v>7.10338020324707</v>
+        <v>7.10337972640991</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G25" t="n">
-        <v>7.28600263595581</v>
+        <v>7.28600215911865</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>8.23200035095215</v>
       </c>
       <c r="G31" t="n">
-        <v>7.78939962387085</v>
+        <v>7.78940010070801</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>8.16199970245361</v>
       </c>
       <c r="G32" t="n">
-        <v>7.72316312789917</v>
+        <v>7.72316265106201</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>8.41300010681152</v>
       </c>
       <c r="G34" t="n">
-        <v>7.96066761016846</v>
+        <v>7.96066808700562</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G37" t="n">
-        <v>7.92944240570068</v>
+        <v>7.92944288253784</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>8.4379997253418</v>
       </c>
       <c r="G38" t="n">
-        <v>7.98432350158691</v>
+        <v>7.98432397842407</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>8.43299961090088</v>
       </c>
       <c r="G39" t="n">
-        <v>7.97959184646606</v>
+        <v>7.97959136962891</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>8.43599987030029</v>
       </c>
       <c r="G40" t="n">
-        <v>7.98243093490601</v>
+        <v>7.98243045806885</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G41" t="n">
-        <v>7.92944240570068</v>
+        <v>7.92944288253784</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>8.41300010681152</v>
       </c>
       <c r="G42" t="n">
-        <v>7.96066761016846</v>
+        <v>7.96066808700562</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>8.23223686218262</v>
+        <v>8.23223781585693</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>8.5620002746582</v>
       </c>
       <c r="G45" t="n">
-        <v>8.10165691375732</v>
+        <v>8.10165596008301</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>8.69499969482422</v>
       </c>
       <c r="G46" t="n">
-        <v>8.22750568389893</v>
+        <v>8.22750473022461</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G52" t="n">
-        <v>8.7905158996582</v>
+        <v>8.79051494598389</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>9.4689998626709</v>
       </c>
       <c r="G53" t="n">
-        <v>8.9598913192749</v>
+        <v>8.95989036560059</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>9.39500045776367</v>
       </c>
       <c r="G56" t="n">
-        <v>8.88987159729004</v>
+        <v>8.88987064361572</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G58" t="n">
-        <v>8.84728908538818</v>
+        <v>8.8472900390625</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>9.27099990844727</v>
       </c>
       <c r="G59" t="n">
-        <v>8.772536277771</v>
+        <v>8.77253723144531</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>9.37600040435791</v>
       </c>
       <c r="G60" t="n">
-        <v>8.87189197540283</v>
+        <v>8.87189292907715</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G65" t="n">
-        <v>8.94191265106201</v>
+        <v>8.94191360473633</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G68" t="n">
-        <v>8.84728908538818</v>
+        <v>8.8472900390625</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G70" t="n">
-        <v>8.87567710876465</v>
+        <v>8.87567615509033</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>9.31900024414062</v>
       </c>
       <c r="G72" t="n">
-        <v>8.81795692443848</v>
+        <v>8.81795597076416</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>9.12600040435791</v>
       </c>
       <c r="G77" t="n">
-        <v>8.63533306121826</v>
+        <v>8.63533401489258</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>9.10799980163574</v>
       </c>
       <c r="G79" t="n">
-        <v>8.61830043792725</v>
+        <v>8.61829948425293</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G80" t="n">
-        <v>8.67696762084961</v>
+        <v>8.67696666717529</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G83" t="n">
-        <v>8.91352653503418</v>
+        <v>8.91352558135986</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G85" t="n">
-        <v>8.91352653503418</v>
+        <v>8.91352558135986</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>9.10799980163574</v>
       </c>
       <c r="G88" t="n">
-        <v>8.61830043792725</v>
+        <v>8.61829948425293</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G89" t="n">
-        <v>8.74320316314697</v>
+        <v>8.74320411682129</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.22700023651123</v>
       </c>
       <c r="G93" t="n">
-        <v>8.73090267181396</v>
+        <v>8.73090362548828</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.02299976348877</v>
       </c>
       <c r="G94" t="n">
-        <v>8.53786945343018</v>
+        <v>8.53787040710449</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>8.67696762084961</v>
+        <v>8.67696666717529</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9.01900005340576</v>
       </c>
       <c r="G101" t="n">
-        <v>8.53408622741699</v>
+        <v>8.53408527374268</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>8.89700031280518</v>
       </c>
       <c r="G102" t="n">
-        <v>8.41864490509033</v>
+        <v>8.41864585876465</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>8.53899955749512</v>
       </c>
       <c r="G105" t="n">
-        <v>8.0798921585083</v>
+        <v>8.07989311218262</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>8.56900024414062</v>
       </c>
       <c r="G112" t="n">
-        <v>8.10828113555908</v>
+        <v>8.10828018188477</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G114" t="n">
-        <v>8.13761329650879</v>
+        <v>8.13761425018311</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G118" t="n">
-        <v>8.23223686218262</v>
+        <v>8.23223781585693</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>8.7209997177124</v>
       </c>
       <c r="G119" t="n">
-        <v>8.25210857391357</v>
+        <v>8.25210762023926</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>8.82600021362305</v>
       </c>
       <c r="G121" t="n">
-        <v>8.35146236419678</v>
+        <v>8.35146331787109</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G126" t="n">
-        <v>8.36470985412598</v>
+        <v>8.36470890045166</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>8.82100009918213</v>
       </c>
       <c r="G128" t="n">
-        <v>8.3467321395874</v>
+        <v>8.34673118591309</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.05300045013428</v>
       </c>
       <c r="G134" t="n">
-        <v>8.56625843048096</v>
+        <v>8.56625747680664</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G135" t="n">
-        <v>8.612624168396</v>
+        <v>8.61262321472168</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G137" t="n">
-        <v>8.612624168396</v>
+        <v>8.61262321472168</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>9.02799987792969</v>
       </c>
       <c r="G138" t="n">
-        <v>8.5426025390625</v>
+        <v>8.54260158538818</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G141" t="n">
-        <v>8.59180641174316</v>
+        <v>8.59180545806885</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>9.39299964904785</v>
       </c>
       <c r="G144" t="n">
-        <v>8.88797760009766</v>
+        <v>8.88797664642334</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>9.26200008392334</v>
       </c>
       <c r="G147" t="n">
-        <v>8.76401996612549</v>
+        <v>8.7640209197998</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>9.36699962615967</v>
       </c>
       <c r="G148" t="n">
-        <v>8.86337471008301</v>
+        <v>8.86337375640869</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G149" t="n">
-        <v>8.84728908538818</v>
+        <v>8.8472900390625</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G154" t="n">
-        <v>8.96083831787109</v>
+        <v>8.96083736419678</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>9.51799964904785</v>
       </c>
       <c r="G159" t="n">
-        <v>9.00625610351562</v>
+        <v>9.00625705718994</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>9.58500003814697</v>
       </c>
       <c r="G160" t="n">
-        <v>9.06965351104736</v>
+        <v>9.06965446472168</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G161" t="n">
-        <v>8.94191265106201</v>
+        <v>8.94191360473633</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>9.79300022125244</v>
       </c>
       <c r="G163" t="n">
-        <v>9.26647090911865</v>
+        <v>9.26646995544434</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>9.80599975585938</v>
       </c>
       <c r="G165" t="n">
-        <v>9.27877235412598</v>
+        <v>9.27877140045166</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>9.84700012207031</v>
       </c>
       <c r="G169" t="n">
-        <v>9.31756687164307</v>
+        <v>9.31756782531738</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>9.26363277435303</v>
+        <v>9.26363182067871</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>9.6230001449585</v>
       </c>
       <c r="G174" t="n">
-        <v>9.10561084747314</v>
+        <v>9.10561180114746</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>10.4580001831055</v>
       </c>
       <c r="G183" t="n">
-        <v>9.89571666717529</v>
+        <v>9.89571762084961</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G185" t="n">
-        <v>10.0395441055298</v>
+        <v>10.0395450592041</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>10.7720003128052</v>
       </c>
       <c r="G192" t="n">
-        <v>10.1928339004517</v>
+        <v>10.192834854126</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>10.7740001678467</v>
       </c>
       <c r="G195" t="n">
-        <v>10.1947259902954</v>
+        <v>10.1947269439697</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G198" t="n">
-        <v>10.4842748641968</v>
+        <v>10.4842739105225</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>11.1260004043579</v>
       </c>
       <c r="G199" t="n">
-        <v>10.5278024673462</v>
+        <v>10.5278015136719</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G201" t="n">
-        <v>10.5788984298706</v>
+        <v>10.5788974761963</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G203" t="n">
-        <v>10.5978231430054</v>
+        <v>10.5978221893311</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>11.3420000076294</v>
       </c>
       <c r="G205" t="n">
-        <v>10.7321882247925</v>
+        <v>10.7321872711182</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G207" t="n">
-        <v>10.966854095459</v>
+        <v>10.9668531417847</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>11.4820003509521</v>
       </c>
       <c r="G212" t="n">
-        <v>10.8646602630615</v>
+        <v>10.8646612167358</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>11.5019998550415</v>
       </c>
       <c r="G213" t="n">
-        <v>10.8835849761963</v>
+        <v>10.8835859298706</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>10.9619998931885</v>
       </c>
       <c r="G220" t="n">
-        <v>10.3726186752319</v>
+        <v>10.3726196289062</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>11.6719999313354</v>
       </c>
       <c r="G223" t="n">
-        <v>11.0444440841675</v>
+        <v>11.0444450378418</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>11.9340000152588</v>
       </c>
       <c r="G225" t="n">
-        <v>11.2923574447632</v>
+        <v>11.2923583984375</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>11.0279998779297</v>
       </c>
       <c r="G232" t="n">
-        <v>10.4350700378418</v>
+        <v>10.4350690841675</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G234" t="n">
-        <v>10.5126600265503</v>
+        <v>10.5126609802246</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G236" t="n">
-        <v>10.2382526397705</v>
+        <v>10.2382535934448</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G238" t="n">
-        <v>10.2382526397705</v>
+        <v>10.2382535934448</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G240" t="n">
-        <v>10.0395441055298</v>
+        <v>10.0395450592041</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G241" t="n">
-        <v>10.0395441055298</v>
+        <v>10.0395450592041</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G244" t="n">
-        <v>10.0395441055298</v>
+        <v>10.0395450592041</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G245" t="n">
-        <v>9.97330856323242</v>
+        <v>9.97330760955811</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G255" t="n">
-        <v>10.2950286865234</v>
+        <v>10.2950277328491</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G260" t="n">
-        <v>10.2382526397705</v>
+        <v>10.2382535934448</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G262" t="n">
-        <v>10.2382526397705</v>
+        <v>10.2382535934448</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G266" t="n">
-        <v>10.143630027771</v>
+        <v>10.1436309814453</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G268" t="n">
-        <v>10.0982236862183</v>
+        <v>10.0982227325439</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G275" t="n">
-        <v>10.3310356140137</v>
+        <v>10.3310346603394</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G283" t="n">
-        <v>10.6220512390137</v>
+        <v>10.6220502853394</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G285" t="n">
-        <v>10.5638475418091</v>
+        <v>10.5638484954834</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G287" t="n">
-        <v>10.2534303665161</v>
+        <v>10.2534313201904</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G288" t="n">
-        <v>10.311635017395</v>
+        <v>10.3116340637207</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G290" t="n">
-        <v>10.4377422332764</v>
+        <v>10.4377412796021</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G294" t="n">
-        <v>10.8063611984253</v>
+        <v>10.806360244751</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G297" t="n">
-        <v>10.9518671035767</v>
+        <v>10.951868057251</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G298" t="n">
-        <v>10.7578573226929</v>
+        <v>10.7578582763672</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G305" t="n">
-        <v>11.5824003219604</v>
+        <v>11.5823993682861</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G314" t="n">
-        <v>11.3398876190186</v>
+        <v>11.3398866653442</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G317" t="n">
-        <v>11.2525835037231</v>
+        <v>11.2525844573975</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G320" t="n">
-        <v>10.9518671035767</v>
+        <v>10.951868057251</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G322" t="n">
-        <v>10.9712686538696</v>
+        <v>10.9712696075439</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G324" t="n">
-        <v>10.7481565475464</v>
+        <v>10.7481575012207</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>10.7190561294556</v>
+        <v>10.7190551757812</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G328" t="n">
-        <v>10.7578573226929</v>
+        <v>10.7578582763672</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>10.8160610198975</v>
+        <v>10.8160600662231</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G334" t="n">
-        <v>11.136176109314</v>
+        <v>11.1361770629883</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G335" t="n">
-        <v>11.136176109314</v>
+        <v>11.1361770629883</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G341" t="n">
-        <v>11.4077920913696</v>
+        <v>11.4077911376953</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G345" t="n">
-        <v>10.9712686538696</v>
+        <v>10.9712696075439</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G346" t="n">
-        <v>10.9615678787231</v>
+        <v>10.9615688323975</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G347" t="n">
-        <v>11.0003709793091</v>
+        <v>11.0003700256348</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G348" t="n">
-        <v>11.0003709793091</v>
+        <v>11.0003700256348</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G357" t="n">
-        <v>11.058572769165</v>
+        <v>11.0585737228394</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G359" t="n">
-        <v>11.0003709793091</v>
+        <v>11.0003700256348</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>11.25</v>
       </c>
       <c r="G362" t="n">
-        <v>10.9130659103394</v>
+        <v>10.913064956665</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G364" t="n">
-        <v>11.1458768844604</v>
+        <v>11.1458778381348</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>11.058572769165</v>
+        <v>11.0585737228394</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G369" t="n">
-        <v>11.1458768844604</v>
+        <v>11.1458778381348</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G371" t="n">
-        <v>11.136176109314</v>
+        <v>11.1361770629883</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G373" t="n">
-        <v>11.0197715759277</v>
+        <v>11.0197706222534</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G377" t="n">
-        <v>11.0197715759277</v>
+        <v>11.0197706222534</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G383" t="n">
-        <v>11.136176109314</v>
+        <v>11.1361770629883</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G387" t="n">
-        <v>11.1749801635742</v>
+        <v>11.1749792098999</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G389" t="n">
-        <v>11.4465932846069</v>
+        <v>11.4465942382812</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G392" t="n">
-        <v>11.8540143966675</v>
+        <v>11.8540153503418</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G394" t="n">
-        <v>11.6988077163696</v>
+        <v>11.6988067626953</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G398" t="n">
-        <v>11.6309022903442</v>
+        <v>11.6309032440186</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G399" t="n">
-        <v>11.5824003219604</v>
+        <v>11.5823993682861</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G403" t="n">
-        <v>12.193531036377</v>
+        <v>12.1935319900513</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G405" t="n">
-        <v>12.193531036377</v>
+        <v>12.1935319900513</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G407" t="n">
-        <v>12.2226343154907</v>
+        <v>12.2226333618164</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G408" t="n">
-        <v>12.2517356872559</v>
+        <v>12.2517347335815</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G411" t="n">
-        <v>12.4651470184326</v>
+        <v>12.4651460647583</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G412" t="n">
-        <v>12.3875417709351</v>
+        <v>12.3875427246094</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G419" t="n">
-        <v>12.2517356872559</v>
+        <v>12.2517347335815</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G420" t="n">
-        <v>12.2226343154907</v>
+        <v>12.2226333618164</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G422" t="n">
-        <v>12.2129325866699</v>
+        <v>12.2129335403442</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G423" t="n">
-        <v>12.3875417709351</v>
+        <v>12.3875427246094</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G426" t="n">
-        <v>12.5427503585815</v>
+        <v>12.5427513122559</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G427" t="n">
-        <v>12.6300554275513</v>
+        <v>12.630054473877</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>13</v>
       </c>
       <c r="G430" t="n">
-        <v>12.6106538772583</v>
+        <v>12.610652923584</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G432" t="n">
-        <v>12.3972415924072</v>
+        <v>12.3972425460815</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G434" t="n">
-        <v>12.6882572174072</v>
+        <v>12.6882581710815</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G436" t="n">
-        <v>13.1538829803467</v>
+        <v>13.1538820266724</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G445" t="n">
-        <v>13.7844142913818</v>
+        <v>13.7844152450562</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G446" t="n">
-        <v>14.3373422622681</v>
+        <v>14.3373432159424</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G447" t="n">
-        <v>14.4537487030029</v>
+        <v>14.4537496566772</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G448" t="n">
-        <v>14.6671600341797</v>
+        <v>14.667160987854</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G450" t="n">
-        <v>14.8029680252075</v>
+        <v>14.8029670715332</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G457" t="n">
-        <v>16.0446319580078</v>
+        <v>16.0446338653564</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G459" t="n">
-        <v>15.9573278427124</v>
+        <v>15.9573268890381</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G463" t="n">
-        <v>16.0252323150635</v>
+        <v>16.0252304077148</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G464" t="n">
-        <v>15.6857137680054</v>
+        <v>15.6857128143311</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G471" t="n">
-        <v>15.8700227737427</v>
+        <v>15.870023727417</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G474" t="n">
-        <v>16.9273777008057</v>
+        <v>16.9273796081543</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G479" t="n">
-        <v>17.5870113372803</v>
+        <v>17.5870094299316</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G480" t="n">
-        <v>17.5870113372803</v>
+        <v>17.5870094299316</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G482" t="n">
-        <v>17.1601905822754</v>
+        <v>17.1601886749268</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G484" t="n">
-        <v>17.7519207000732</v>
+        <v>17.7519187927246</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G485" t="n">
-        <v>17.7422199249268</v>
+        <v>17.7422218322754</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G488" t="n">
-        <v>17.9071273803711</v>
+        <v>17.9071292877197</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G489" t="n">
-        <v>18.3727512359619</v>
+        <v>18.3727531433105</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>16.8303737640381</v>
+        <v>16.8303718566895</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G494" t="n">
-        <v>17.1601905822754</v>
+        <v>17.1601886749268</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G501" t="n">
-        <v>18.8480758666992</v>
+        <v>18.8480777740479</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>19.4699993133545</v>
       </c>
       <c r="G502" t="n">
-        <v>18.8868770599365</v>
+        <v>18.8868789672852</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G503" t="n">
-        <v>19.0226879119873</v>
+        <v>19.0226860046387</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G505" t="n">
-        <v>19.4786109924316</v>
+        <v>19.478609085083</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G506" t="n">
-        <v>19.4592094421387</v>
+        <v>19.45920753479</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G507" t="n">
-        <v>19.4398078918457</v>
+        <v>19.4398097991943</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G509" t="n">
-        <v>20.3128528594971</v>
+        <v>20.3128547668457</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G510" t="n">
-        <v>20.2352504730225</v>
+        <v>20.2352485656738</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G511" t="n">
-        <v>19.9248332977295</v>
+        <v>19.9248352050781</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>20</v>
       </c>
       <c r="G512" t="n">
-        <v>19.4010047912598</v>
+        <v>19.4010066986084</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>21.6321220397949</v>
+        <v>21.6321201324463</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G517" t="n">
-        <v>22.1171455383301</v>
+        <v>22.1171474456787</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G518" t="n">
-        <v>21.9619388580322</v>
+        <v>21.9619369506836</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -22732,6 +22732,32 @@
         <v>27.3799991607666</v>
       </c>
       <c r="H860" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B861" t="n">
+        <v>1101615</v>
+      </c>
+      <c r="C861" t="n">
+        <v>28.0400009155273</v>
+      </c>
+      <c r="D861" t="n">
+        <v>27.2399997711182</v>
+      </c>
+      <c r="E861" t="n">
+        <v>27.2999992370605</v>
+      </c>
+      <c r="F861" t="n">
+        <v>27.8299999237061</v>
+      </c>
+      <c r="G861" t="n">
+        <v>27.8299999237061</v>
+      </c>
+      <c r="H861" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/LTMC.MI.xlsx
+++ b/data/LTMC.MI.xlsx
@@ -473,7 +473,7 @@
         <v>8.44600009918213</v>
       </c>
       <c r="G4" t="n">
-        <v>7.99189376831055</v>
+        <v>7.99189424514771</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>8.48400020599365</v>
       </c>
       <c r="G5" t="n">
-        <v>8.02785110473633</v>
+        <v>8.02785015106201</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>8.59099960327148</v>
       </c>
       <c r="G6" t="n">
-        <v>8.12909698486328</v>
+        <v>8.1290979385376</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G7" t="n">
-        <v>7.92944288253784</v>
+        <v>7.92944240570068</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>7.98600006103516</v>
       </c>
       <c r="G8" t="n">
-        <v>7.5566258430481</v>
+        <v>7.55662631988525</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>8.25</v>
       </c>
       <c r="G9" t="n">
-        <v>7.80643129348755</v>
+        <v>7.80643224716187</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G10" t="n">
-        <v>7.99567842483521</v>
+        <v>7.99567890167236</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G14" t="n">
-        <v>7.52256107330322</v>
+        <v>7.52256155014038</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G15" t="n">
-        <v>7.24815320968628</v>
+        <v>7.24815368652344</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>7.86899995803833</v>
       </c>
       <c r="G16" t="n">
-        <v>7.44591665267944</v>
+        <v>7.44591617584229</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>7.72300004959106</v>
       </c>
       <c r="G17" t="n">
-        <v>7.30776596069336</v>
+        <v>7.30776643753052</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>7.80100011825562</v>
       </c>
       <c r="G20" t="n">
-        <v>7.38157272338867</v>
+        <v>7.38157320022583</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>7.71199989318848</v>
       </c>
       <c r="G21" t="n">
-        <v>7.29735803604126</v>
+        <v>7.2973575592041</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G25" t="n">
-        <v>7.28600215911865</v>
+        <v>7.28600263595581</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G28" t="n">
-        <v>7.76858234405518</v>
+        <v>7.76858282089233</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G30" t="n">
-        <v>7.93890476226807</v>
+        <v>7.93890380859375</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>8.23200035095215</v>
       </c>
       <c r="G31" t="n">
-        <v>7.78940010070801</v>
+        <v>7.78939962387085</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>8.21399974822998</v>
       </c>
       <c r="G33" t="n">
-        <v>7.77236652374268</v>
+        <v>7.77236747741699</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>8.41300010681152</v>
       </c>
       <c r="G34" t="n">
-        <v>7.96066808700562</v>
+        <v>7.96066761016846</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>8.24600028991699</v>
       </c>
       <c r="G35" t="n">
-        <v>7.80264663696289</v>
+        <v>7.80264759063721</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G36" t="n">
-        <v>7.81116342544556</v>
+        <v>7.81116247177124</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G37" t="n">
-        <v>7.92944288253784</v>
+        <v>7.92944240570068</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>8.43299961090088</v>
       </c>
       <c r="G39" t="n">
-        <v>7.97959136962891</v>
+        <v>7.97959184646606</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>8.43599987030029</v>
       </c>
       <c r="G40" t="n">
-        <v>7.98243045806885</v>
+        <v>7.98243093490601</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G41" t="n">
-        <v>7.92944288253784</v>
+        <v>7.92944240570068</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>8.41300010681152</v>
       </c>
       <c r="G42" t="n">
-        <v>7.96066808700562</v>
+        <v>7.96066761016846</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>8.23223781585693</v>
+        <v>8.23223686218262</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>8.71599960327148</v>
       </c>
       <c r="G44" t="n">
-        <v>8.24737644195557</v>
+        <v>8.24737548828125</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>8.5620002746582</v>
       </c>
       <c r="G45" t="n">
-        <v>8.10165596008301</v>
+        <v>8.10165691375732</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>8.58300018310547</v>
       </c>
       <c r="G47" t="n">
-        <v>8.12152862548828</v>
+        <v>8.12152767181396</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>8.78800010681152</v>
       </c>
       <c r="G49" t="n">
-        <v>8.315505027771</v>
+        <v>8.31550598144531</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G54" t="n">
-        <v>8.97029876708984</v>
+        <v>8.97029972076416</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G58" t="n">
-        <v>8.8472900390625</v>
+        <v>8.84728908538818</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>9.27099990844727</v>
       </c>
       <c r="G59" t="n">
-        <v>8.77253723144531</v>
+        <v>8.772536277771</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>9.37600040435791</v>
       </c>
       <c r="G60" t="n">
-        <v>8.87189292907715</v>
+        <v>8.87189197540283</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>9.17800045013428</v>
       </c>
       <c r="G63" t="n">
-        <v>8.68453788757324</v>
+        <v>8.68453693389893</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G65" t="n">
-        <v>8.94191360473633</v>
+        <v>8.94191265106201</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G68" t="n">
-        <v>8.8472900390625</v>
+        <v>8.84728908538818</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G70" t="n">
-        <v>8.87567615509033</v>
+        <v>8.87567710876465</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G76" t="n">
-        <v>8.75455856323242</v>
+        <v>8.75455760955811</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>9.12600040435791</v>
       </c>
       <c r="G77" t="n">
-        <v>8.63533401489258</v>
+        <v>8.63533306121826</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>9.08300018310547</v>
       </c>
       <c r="G78" t="n">
-        <v>8.59464550018311</v>
+        <v>8.59464454650879</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>9.10799980163574</v>
       </c>
       <c r="G79" t="n">
-        <v>8.61829948425293</v>
+        <v>8.61830043792725</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G86" t="n">
-        <v>8.8378267288208</v>
+        <v>8.83782768249512</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>9</v>
       </c>
       <c r="G87" t="n">
-        <v>8.51610660552979</v>
+        <v>8.5161075592041</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>9.10799980163574</v>
       </c>
       <c r="G88" t="n">
-        <v>8.61829948425293</v>
+        <v>8.61830043792725</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G89" t="n">
-        <v>8.74320411682129</v>
+        <v>8.74320316314697</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>9.08100032806396</v>
       </c>
       <c r="G91" t="n">
-        <v>8.59275245666504</v>
+        <v>8.59275341033936</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>9.17099952697754</v>
       </c>
       <c r="G92" t="n">
-        <v>8.67791271209717</v>
+        <v>8.67791175842285</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.22700023651123</v>
       </c>
       <c r="G93" t="n">
-        <v>8.73090362548828</v>
+        <v>8.73090267181396</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G95" t="n">
-        <v>8.53503322601318</v>
+        <v>8.53503227233887</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9</v>
       </c>
       <c r="G96" t="n">
-        <v>8.51610660552979</v>
+        <v>8.5161075592041</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.08100032806396</v>
       </c>
       <c r="G98" t="n">
-        <v>8.59275245666504</v>
+        <v>8.59275341033936</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>8.9069995880127</v>
       </c>
       <c r="G100" t="n">
-        <v>8.42810821533203</v>
+        <v>8.42810726165771</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9.01900005340576</v>
       </c>
       <c r="G101" t="n">
-        <v>8.53408527374268</v>
+        <v>8.53408622741699</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>8.78400039672852</v>
       </c>
       <c r="G103" t="n">
-        <v>8.3117208480835</v>
+        <v>8.31172180175781</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>8.53899955749512</v>
       </c>
       <c r="G105" t="n">
-        <v>8.07989311218262</v>
+        <v>8.0798921585083</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>8.78400039672852</v>
       </c>
       <c r="G107" t="n">
-        <v>8.3117208480835</v>
+        <v>8.31172180175781</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>8.80700016021729</v>
       </c>
       <c r="G108" t="n">
-        <v>8.3334846496582</v>
+        <v>8.33348369598389</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G109" t="n">
-        <v>8.27008628845215</v>
+        <v>8.27008724212646</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G110" t="n">
-        <v>8.37417221069336</v>
+        <v>8.37417316436768</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G111" t="n">
-        <v>8.17546272277832</v>
+        <v>8.17546367645264</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>8.80099964141846</v>
       </c>
       <c r="G115" t="n">
-        <v>8.32780647277832</v>
+        <v>8.327805519104</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>8.75500011444092</v>
       </c>
       <c r="G116" t="n">
-        <v>8.28428077697754</v>
+        <v>8.28427982330322</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G118" t="n">
-        <v>8.23223781585693</v>
+        <v>8.23223686218262</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>8.75</v>
       </c>
       <c r="G120" t="n">
-        <v>8.27954769134521</v>
+        <v>8.27954864501953</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>8.7810001373291</v>
       </c>
       <c r="G123" t="n">
-        <v>8.30888175964355</v>
+        <v>8.30888271331787</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9</v>
       </c>
       <c r="G124" t="n">
-        <v>8.51610660552979</v>
+        <v>8.5161075592041</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G126" t="n">
-        <v>8.36470890045166</v>
+        <v>8.36470985412598</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G127" t="n">
-        <v>8.37417221069336</v>
+        <v>8.37417316436768</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G129" t="n">
-        <v>8.44987201690674</v>
+        <v>8.44987106323242</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>9.03800010681152</v>
       </c>
       <c r="G131" t="n">
-        <v>8.55206394195557</v>
+        <v>8.55206489562988</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>9.22200012207031</v>
       </c>
       <c r="G133" t="n">
-        <v>8.72617053985596</v>
+        <v>8.72617149353027</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G136" t="n">
-        <v>8.53503322601318</v>
+        <v>8.53503227233887</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>9</v>
       </c>
       <c r="G139" t="n">
-        <v>8.51610660552979</v>
+        <v>8.5161075592041</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>9.08300018310547</v>
       </c>
       <c r="G140" t="n">
-        <v>8.59464550018311</v>
+        <v>8.59464454650879</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G142" t="n">
-        <v>8.6296558380127</v>
+        <v>8.62965488433838</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G146" t="n">
-        <v>8.81890201568604</v>
+        <v>8.81890106201172</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>9.36699962615967</v>
       </c>
       <c r="G148" t="n">
-        <v>8.86337375640869</v>
+        <v>8.86337471008301</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G149" t="n">
-        <v>8.8472900390625</v>
+        <v>8.84728908538818</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G151" t="n">
-        <v>8.82836437225342</v>
+        <v>8.82836532592773</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G156" t="n">
-        <v>9.00815010070801</v>
+        <v>9.00814914703369</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>9.60900020599365</v>
       </c>
       <c r="G157" t="n">
-        <v>9.09236335754395</v>
+        <v>9.09236431121826</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>9.58500003814697</v>
       </c>
       <c r="G160" t="n">
-        <v>9.06965446472168</v>
+        <v>9.06965351104736</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G161" t="n">
-        <v>8.94191360473633</v>
+        <v>8.94191265106201</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>9.79300022125244</v>
       </c>
       <c r="G163" t="n">
-        <v>9.26646995544434</v>
+        <v>9.26647090911865</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G164" t="n">
-        <v>9.27309417724609</v>
+        <v>9.27309513092041</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G167" t="n">
-        <v>9.32040691375732</v>
+        <v>9.32040786743164</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>9.8149995803833</v>
       </c>
       <c r="G168" t="n">
-        <v>9.28728771209717</v>
+        <v>9.28728866577148</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>9.84700012207031</v>
       </c>
       <c r="G169" t="n">
-        <v>9.31756782531738</v>
+        <v>9.3175687789917</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>9.6230001449585</v>
       </c>
       <c r="G174" t="n">
-        <v>9.10561180114746</v>
+        <v>9.10561084747314</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>9.66800022125244</v>
       </c>
       <c r="G176" t="n">
-        <v>9.14819145202637</v>
+        <v>9.14819240570068</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>9.18793296813965</v>
+        <v>9.18793392181396</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>10.4580001831055</v>
       </c>
       <c r="G183" t="n">
-        <v>9.89571762084961</v>
+        <v>9.89571666717529</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G185" t="n">
-        <v>10.0395450592041</v>
+        <v>10.0395441055298</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>10.78600025177</v>
       </c>
       <c r="G186" t="n">
-        <v>10.2060823440552</v>
+        <v>10.2060813903809</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>10.7840003967285</v>
       </c>
       <c r="G189" t="n">
-        <v>10.2041893005371</v>
+        <v>10.2041902542114</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>10.6820001602173</v>
       </c>
       <c r="G191" t="n">
-        <v>10.1076726913452</v>
+        <v>10.1076736450195</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G198" t="n">
-        <v>10.4842739105225</v>
+        <v>10.4842748641968</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G202" t="n">
-        <v>10.5031995773315</v>
+        <v>10.5031986236572</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>11.3420000076294</v>
       </c>
       <c r="G205" t="n">
-        <v>10.7321872711182</v>
+        <v>10.7321882247925</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G207" t="n">
-        <v>10.9668531417847</v>
+        <v>10.966854095459</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G208" t="n">
-        <v>10.9763164520264</v>
+        <v>10.9763174057007</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>11.5579996109009</v>
       </c>
       <c r="G209" t="n">
-        <v>10.9365730285645</v>
+        <v>10.9365739822388</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G210" t="n">
-        <v>10.9195423126221</v>
+        <v>10.9195413589478</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>11.4820003509521</v>
       </c>
       <c r="G212" t="n">
-        <v>10.8646612167358</v>
+        <v>10.8646602630615</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>11.5019998550415</v>
       </c>
       <c r="G213" t="n">
-        <v>10.8835859298706</v>
+        <v>10.8835849761963</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G214" t="n">
-        <v>10.5031995773315</v>
+        <v>10.5031986236572</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G217" t="n">
-        <v>10.4369630813599</v>
+        <v>10.4369621276855</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>10.9619998931885</v>
       </c>
       <c r="G220" t="n">
-        <v>10.3726196289062</v>
+        <v>10.3726186752319</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>11</v>
       </c>
       <c r="G228" t="n">
-        <v>10.4085750579834</v>
+        <v>10.4085760116577</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G229" t="n">
-        <v>10.4558877944946</v>
+        <v>10.4558868408203</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G230" t="n">
-        <v>10.3896503448486</v>
+        <v>10.3896512985229</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>11.0279998779297</v>
       </c>
       <c r="G232" t="n">
-        <v>10.4350690841675</v>
+        <v>10.4350700378418</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>10.5031995773315</v>
+        <v>10.5031986236572</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G234" t="n">
-        <v>10.5126609802246</v>
+        <v>10.5126619338989</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G235" t="n">
-        <v>10.323413848877</v>
+        <v>10.3234148025513</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G240" t="n">
-        <v>10.0395450592041</v>
+        <v>10.0395441055298</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G241" t="n">
-        <v>10.0395450592041</v>
+        <v>10.0395441055298</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G244" t="n">
-        <v>10.0395450592041</v>
+        <v>10.0395441055298</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G252" t="n">
-        <v>9.8124475479126</v>
+        <v>9.81244850158691</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G253" t="n">
-        <v>9.87868404388428</v>
+        <v>9.87868499755859</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G254" t="n">
-        <v>9.99223327636719</v>
+        <v>9.99223232269287</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G255" t="n">
-        <v>10.2950277328491</v>
+        <v>10.2950267791748</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G256" t="n">
-        <v>10.3896503448486</v>
+        <v>10.3896512985229</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>10.8299999237061</v>
       </c>
       <c r="G259" t="n">
-        <v>10.2477159500122</v>
+        <v>10.2477149963379</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G266" t="n">
-        <v>10.1436309814453</v>
+        <v>10.143630027771</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G267" t="n">
-        <v>10.020619392395</v>
+        <v>10.0206203460693</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -22758,6 +22758,32 @@
         <v>27.8299999237061</v>
       </c>
       <c r="H861" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B862" t="n">
+        <v>1155069</v>
+      </c>
+      <c r="C862" t="n">
+        <v>28.1299991607666</v>
+      </c>
+      <c r="D862" t="n">
+        <v>27.2000007629395</v>
+      </c>
+      <c r="E862" t="n">
+        <v>27.8899993896484</v>
+      </c>
+      <c r="F862" t="n">
+        <v>27.4400005340576</v>
+      </c>
+      <c r="G862" t="n">
+        <v>27.4400005340576</v>
+      </c>
+      <c r="H862" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/LTMC.MI.xlsx
+++ b/data/LTMC.MI.xlsx
@@ -473,7 +473,7 @@
         <v>8.44600009918213</v>
       </c>
       <c r="G4" t="n">
-        <v>7.99189424514771</v>
+        <v>7.99189376831055</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>8.48400020599365</v>
       </c>
       <c r="G5" t="n">
-        <v>8.02785015106201</v>
+        <v>8.02785110473633</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>8.59099960327148</v>
       </c>
       <c r="G6" t="n">
-        <v>8.1290979385376</v>
+        <v>8.12909698486328</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G7" t="n">
-        <v>7.92944240570068</v>
+        <v>7.92944288253784</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>7.98600006103516</v>
       </c>
       <c r="G8" t="n">
-        <v>7.55662631988525</v>
+        <v>7.5566258430481</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>8.25</v>
       </c>
       <c r="G9" t="n">
-        <v>7.80643224716187</v>
+        <v>7.80643129348755</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G10" t="n">
-        <v>7.99567890167236</v>
+        <v>7.99567842483521</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G14" t="n">
-        <v>7.52256155014038</v>
+        <v>7.52256107330322</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G15" t="n">
-        <v>7.24815368652344</v>
+        <v>7.24815320968628</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>7.86899995803833</v>
       </c>
       <c r="G16" t="n">
-        <v>7.44591617584229</v>
+        <v>7.44591665267944</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>7.72300004959106</v>
       </c>
       <c r="G17" t="n">
-        <v>7.30776643753052</v>
+        <v>7.30776596069336</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>7.80100011825562</v>
       </c>
       <c r="G20" t="n">
-        <v>7.38157320022583</v>
+        <v>7.38157272338867</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>7.71199989318848</v>
       </c>
       <c r="G21" t="n">
-        <v>7.2973575592041</v>
+        <v>7.29735803604126</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G25" t="n">
-        <v>7.28600263595581</v>
+        <v>7.28600215911865</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G28" t="n">
-        <v>7.76858282089233</v>
+        <v>7.76858234405518</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G30" t="n">
-        <v>7.93890380859375</v>
+        <v>7.93890476226807</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>8.23200035095215</v>
       </c>
       <c r="G31" t="n">
-        <v>7.78939962387085</v>
+        <v>7.78940010070801</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>8.21399974822998</v>
       </c>
       <c r="G33" t="n">
-        <v>7.77236747741699</v>
+        <v>7.77236652374268</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>8.41300010681152</v>
       </c>
       <c r="G34" t="n">
-        <v>7.96066761016846</v>
+        <v>7.96066808700562</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>8.24600028991699</v>
       </c>
       <c r="G35" t="n">
-        <v>7.80264759063721</v>
+        <v>7.80264663696289</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G36" t="n">
-        <v>7.81116247177124</v>
+        <v>7.81116342544556</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G37" t="n">
-        <v>7.92944240570068</v>
+        <v>7.92944288253784</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>8.43299961090088</v>
       </c>
       <c r="G39" t="n">
-        <v>7.97959184646606</v>
+        <v>7.97959136962891</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>8.43599987030029</v>
       </c>
       <c r="G40" t="n">
-        <v>7.98243093490601</v>
+        <v>7.98243045806885</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G41" t="n">
-        <v>7.92944240570068</v>
+        <v>7.92944288253784</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>8.41300010681152</v>
       </c>
       <c r="G42" t="n">
-        <v>7.96066761016846</v>
+        <v>7.96066808700562</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>8.23223686218262</v>
+        <v>8.23223781585693</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>8.71599960327148</v>
       </c>
       <c r="G44" t="n">
-        <v>8.24737548828125</v>
+        <v>8.24737644195557</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>8.5620002746582</v>
       </c>
       <c r="G45" t="n">
-        <v>8.10165691375732</v>
+        <v>8.10165596008301</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>8.58300018310547</v>
       </c>
       <c r="G47" t="n">
-        <v>8.12152767181396</v>
+        <v>8.12152862548828</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>8.78800010681152</v>
       </c>
       <c r="G49" t="n">
-        <v>8.31550598144531</v>
+        <v>8.315505027771</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G54" t="n">
-        <v>8.97029972076416</v>
+        <v>8.97029876708984</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G58" t="n">
-        <v>8.84728908538818</v>
+        <v>8.8472900390625</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>9.27099990844727</v>
       </c>
       <c r="G59" t="n">
-        <v>8.772536277771</v>
+        <v>8.77253723144531</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>9.37600040435791</v>
       </c>
       <c r="G60" t="n">
-        <v>8.87189197540283</v>
+        <v>8.87189292907715</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>9.17800045013428</v>
       </c>
       <c r="G63" t="n">
-        <v>8.68453693389893</v>
+        <v>8.68453788757324</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G65" t="n">
-        <v>8.94191265106201</v>
+        <v>8.94191360473633</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G68" t="n">
-        <v>8.84728908538818</v>
+        <v>8.8472900390625</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G70" t="n">
-        <v>8.87567710876465</v>
+        <v>8.87567615509033</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G76" t="n">
-        <v>8.75455760955811</v>
+        <v>8.75455856323242</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>9.12600040435791</v>
       </c>
       <c r="G77" t="n">
-        <v>8.63533306121826</v>
+        <v>8.63533401489258</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>9.08300018310547</v>
       </c>
       <c r="G78" t="n">
-        <v>8.59464454650879</v>
+        <v>8.59464550018311</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>9.10799980163574</v>
       </c>
       <c r="G79" t="n">
-        <v>8.61830043792725</v>
+        <v>8.61829948425293</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G86" t="n">
-        <v>8.83782768249512</v>
+        <v>8.8378267288208</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>9</v>
       </c>
       <c r="G87" t="n">
-        <v>8.5161075592041</v>
+        <v>8.51610660552979</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>9.10799980163574</v>
       </c>
       <c r="G88" t="n">
-        <v>8.61830043792725</v>
+        <v>8.61829948425293</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G89" t="n">
-        <v>8.74320316314697</v>
+        <v>8.74320411682129</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>9.08100032806396</v>
       </c>
       <c r="G91" t="n">
-        <v>8.59275341033936</v>
+        <v>8.59275245666504</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>9.17099952697754</v>
       </c>
       <c r="G92" t="n">
-        <v>8.67791175842285</v>
+        <v>8.67791271209717</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.22700023651123</v>
       </c>
       <c r="G93" t="n">
-        <v>8.73090267181396</v>
+        <v>8.73090362548828</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G95" t="n">
-        <v>8.53503227233887</v>
+        <v>8.53503322601318</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9</v>
       </c>
       <c r="G96" t="n">
-        <v>8.5161075592041</v>
+        <v>8.51610660552979</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.08100032806396</v>
       </c>
       <c r="G98" t="n">
-        <v>8.59275341033936</v>
+        <v>8.59275245666504</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>8.9069995880127</v>
       </c>
       <c r="G100" t="n">
-        <v>8.42810726165771</v>
+        <v>8.42810821533203</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9.01900005340576</v>
       </c>
       <c r="G101" t="n">
-        <v>8.53408622741699</v>
+        <v>8.53408527374268</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>8.78400039672852</v>
       </c>
       <c r="G103" t="n">
-        <v>8.31172180175781</v>
+        <v>8.3117208480835</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>8.53899955749512</v>
       </c>
       <c r="G105" t="n">
-        <v>8.0798921585083</v>
+        <v>8.07989311218262</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>8.78400039672852</v>
       </c>
       <c r="G107" t="n">
-        <v>8.31172180175781</v>
+        <v>8.3117208480835</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>8.80700016021729</v>
       </c>
       <c r="G108" t="n">
-        <v>8.33348369598389</v>
+        <v>8.3334846496582</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G109" t="n">
-        <v>8.27008724212646</v>
+        <v>8.27008628845215</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G110" t="n">
-        <v>8.37417316436768</v>
+        <v>8.37417221069336</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G111" t="n">
-        <v>8.17546367645264</v>
+        <v>8.17546272277832</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>8.80099964141846</v>
       </c>
       <c r="G115" t="n">
-        <v>8.327805519104</v>
+        <v>8.32780647277832</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>8.75500011444092</v>
       </c>
       <c r="G116" t="n">
-        <v>8.28427982330322</v>
+        <v>8.28428077697754</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G118" t="n">
-        <v>8.23223686218262</v>
+        <v>8.23223781585693</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>8.75</v>
       </c>
       <c r="G120" t="n">
-        <v>8.27954864501953</v>
+        <v>8.27954769134521</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>8.7810001373291</v>
       </c>
       <c r="G123" t="n">
-        <v>8.30888271331787</v>
+        <v>8.30888175964355</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9</v>
       </c>
       <c r="G124" t="n">
-        <v>8.5161075592041</v>
+        <v>8.51610660552979</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G126" t="n">
-        <v>8.36470985412598</v>
+        <v>8.36470890045166</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G127" t="n">
-        <v>8.37417316436768</v>
+        <v>8.37417221069336</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G129" t="n">
-        <v>8.44987106323242</v>
+        <v>8.44987201690674</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>9.03800010681152</v>
       </c>
       <c r="G131" t="n">
-        <v>8.55206489562988</v>
+        <v>8.55206394195557</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>9.22200012207031</v>
       </c>
       <c r="G133" t="n">
-        <v>8.72617149353027</v>
+        <v>8.72617053985596</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G136" t="n">
-        <v>8.53503227233887</v>
+        <v>8.53503322601318</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>9</v>
       </c>
       <c r="G139" t="n">
-        <v>8.5161075592041</v>
+        <v>8.51610660552979</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>9.08300018310547</v>
       </c>
       <c r="G140" t="n">
-        <v>8.59464454650879</v>
+        <v>8.59464550018311</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G142" t="n">
-        <v>8.62965488433838</v>
+        <v>8.6296558380127</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G146" t="n">
-        <v>8.81890106201172</v>
+        <v>8.81890201568604</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>9.36699962615967</v>
       </c>
       <c r="G148" t="n">
-        <v>8.86337471008301</v>
+        <v>8.86337375640869</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G149" t="n">
-        <v>8.84728908538818</v>
+        <v>8.8472900390625</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G151" t="n">
-        <v>8.82836532592773</v>
+        <v>8.82836437225342</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G156" t="n">
-        <v>9.00814914703369</v>
+        <v>9.00815010070801</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>9.60900020599365</v>
       </c>
       <c r="G157" t="n">
-        <v>9.09236431121826</v>
+        <v>9.09236335754395</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>9.58500003814697</v>
       </c>
       <c r="G160" t="n">
-        <v>9.06965351104736</v>
+        <v>9.06965446472168</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G161" t="n">
-        <v>8.94191265106201</v>
+        <v>8.94191360473633</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>9.79300022125244</v>
       </c>
       <c r="G163" t="n">
-        <v>9.26647090911865</v>
+        <v>9.26646995544434</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G164" t="n">
-        <v>9.27309513092041</v>
+        <v>9.27309417724609</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G167" t="n">
-        <v>9.32040786743164</v>
+        <v>9.32040691375732</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>9.8149995803833</v>
       </c>
       <c r="G168" t="n">
-        <v>9.28728866577148</v>
+        <v>9.28728771209717</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>9.84700012207031</v>
       </c>
       <c r="G169" t="n">
-        <v>9.3175687789917</v>
+        <v>9.31756782531738</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>9.6230001449585</v>
       </c>
       <c r="G174" t="n">
-        <v>9.10561084747314</v>
+        <v>9.10561180114746</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>9.66800022125244</v>
       </c>
       <c r="G176" t="n">
-        <v>9.14819240570068</v>
+        <v>9.14819145202637</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>9.18793392181396</v>
+        <v>9.18793296813965</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>10.4580001831055</v>
       </c>
       <c r="G183" t="n">
-        <v>9.89571666717529</v>
+        <v>9.89571762084961</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G185" t="n">
-        <v>10.0395441055298</v>
+        <v>10.0395450592041</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>10.78600025177</v>
       </c>
       <c r="G186" t="n">
-        <v>10.2060813903809</v>
+        <v>10.2060823440552</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>10.7840003967285</v>
       </c>
       <c r="G189" t="n">
-        <v>10.2041902542114</v>
+        <v>10.2041893005371</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>10.6820001602173</v>
       </c>
       <c r="G191" t="n">
-        <v>10.1076736450195</v>
+        <v>10.1076726913452</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G198" t="n">
-        <v>10.4842748641968</v>
+        <v>10.4842739105225</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G202" t="n">
-        <v>10.5031986236572</v>
+        <v>10.5031995773315</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>11.3420000076294</v>
       </c>
       <c r="G205" t="n">
-        <v>10.7321882247925</v>
+        <v>10.7321872711182</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G207" t="n">
-        <v>10.966854095459</v>
+        <v>10.9668531417847</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G208" t="n">
-        <v>10.9763174057007</v>
+        <v>10.9763164520264</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>11.5579996109009</v>
       </c>
       <c r="G209" t="n">
-        <v>10.9365739822388</v>
+        <v>10.9365730285645</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G210" t="n">
-        <v>10.9195413589478</v>
+        <v>10.9195423126221</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>11.4820003509521</v>
       </c>
       <c r="G212" t="n">
-        <v>10.8646602630615</v>
+        <v>10.8646612167358</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>11.5019998550415</v>
       </c>
       <c r="G213" t="n">
-        <v>10.8835849761963</v>
+        <v>10.8835859298706</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G214" t="n">
-        <v>10.5031986236572</v>
+        <v>10.5031995773315</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G217" t="n">
-        <v>10.4369621276855</v>
+        <v>10.4369630813599</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>10.9619998931885</v>
       </c>
       <c r="G220" t="n">
-        <v>10.3726186752319</v>
+        <v>10.3726196289062</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>11</v>
       </c>
       <c r="G228" t="n">
-        <v>10.4085760116577</v>
+        <v>10.4085750579834</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G229" t="n">
-        <v>10.4558868408203</v>
+        <v>10.4558877944946</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G230" t="n">
-        <v>10.3896512985229</v>
+        <v>10.3896503448486</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>11.0279998779297</v>
       </c>
       <c r="G232" t="n">
-        <v>10.4350700378418</v>
+        <v>10.4350690841675</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>10.5031986236572</v>
+        <v>10.5031995773315</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G234" t="n">
-        <v>10.5126619338989</v>
+        <v>10.5126609802246</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G235" t="n">
-        <v>10.3234148025513</v>
+        <v>10.323413848877</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G240" t="n">
-        <v>10.0395441055298</v>
+        <v>10.0395450592041</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G241" t="n">
-        <v>10.0395441055298</v>
+        <v>10.0395450592041</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G244" t="n">
-        <v>10.0395441055298</v>
+        <v>10.0395450592041</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G252" t="n">
-        <v>9.81244850158691</v>
+        <v>9.8124475479126</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G253" t="n">
-        <v>9.87868499755859</v>
+        <v>9.87868404388428</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G254" t="n">
-        <v>9.99223232269287</v>
+        <v>9.99223327636719</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G255" t="n">
-        <v>10.2950267791748</v>
+        <v>10.2950277328491</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G256" t="n">
-        <v>10.3896512985229</v>
+        <v>10.3896503448486</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>10.8299999237061</v>
       </c>
       <c r="G259" t="n">
-        <v>10.2477149963379</v>
+        <v>10.2477159500122</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G266" t="n">
-        <v>10.143630027771</v>
+        <v>10.1436309814453</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G267" t="n">
-        <v>10.0206203460693</v>
+        <v>10.020619392395</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -22784,6 +22784,32 @@
         <v>27.4400005340576</v>
       </c>
       <c r="H862" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B863" t="n">
+        <v>1254580</v>
+      </c>
+      <c r="C863" t="n">
+        <v>27.3899993896484</v>
+      </c>
+      <c r="D863" t="n">
+        <v>26.3899993896484</v>
+      </c>
+      <c r="E863" t="n">
+        <v>27.3099994659424</v>
+      </c>
+      <c r="F863" t="n">
+        <v>26.5900001525879</v>
+      </c>
+      <c r="G863" t="n">
+        <v>26.5900001525879</v>
+      </c>
+      <c r="H863" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/LTMC.MI.xlsx
+++ b/data/LTMC.MI.xlsx
@@ -447,7 +447,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G3" t="n">
-        <v>7.82535743713379</v>
+        <v>7.82535696029663</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>8.59099960327148</v>
       </c>
       <c r="G6" t="n">
-        <v>8.12909698486328</v>
+        <v>8.1290979385376</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>8.25</v>
       </c>
       <c r="G9" t="n">
-        <v>7.80643129348755</v>
+        <v>7.80643177032471</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G14" t="n">
-        <v>7.52256107330322</v>
+        <v>7.52256155014038</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>7.72300004959106</v>
       </c>
       <c r="G17" t="n">
-        <v>7.30776596069336</v>
+        <v>7.30776643753052</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>7.71199989318848</v>
       </c>
       <c r="G21" t="n">
-        <v>7.29735803604126</v>
+        <v>7.2973575592041</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G25" t="n">
-        <v>7.28600215911865</v>
+        <v>7.28600263595581</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>7.86800003051758</v>
       </c>
       <c r="G26" t="n">
-        <v>7.44497013092041</v>
+        <v>7.44497060775757</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G28" t="n">
-        <v>7.76858234405518</v>
+        <v>7.76858282089233</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>8.21399974822998</v>
       </c>
       <c r="G33" t="n">
-        <v>7.77236652374268</v>
+        <v>7.77236747741699</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>8.41300010681152</v>
       </c>
       <c r="G34" t="n">
-        <v>7.96066808700562</v>
+        <v>7.9606671333313</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>8.24600028991699</v>
       </c>
       <c r="G35" t="n">
-        <v>7.80264663696289</v>
+        <v>7.80264759063721</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G36" t="n">
-        <v>7.81116342544556</v>
+        <v>7.8111629486084</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>8.41300010681152</v>
       </c>
       <c r="G42" t="n">
-        <v>7.96066808700562</v>
+        <v>7.9606671333313</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>8.23223781585693</v>
+        <v>8.23223686218262</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>8.71599960327148</v>
       </c>
       <c r="G44" t="n">
-        <v>8.24737644195557</v>
+        <v>8.24737548828125</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>8.5620002746582</v>
       </c>
       <c r="G45" t="n">
-        <v>8.10165596008301</v>
+        <v>8.10165691375732</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>8.69499969482422</v>
       </c>
       <c r="G46" t="n">
-        <v>8.22750473022461</v>
+        <v>8.22750568389893</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>8.78800010681152</v>
       </c>
       <c r="G49" t="n">
-        <v>8.315505027771</v>
+        <v>8.31550598144531</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G50" t="n">
-        <v>8.49718189239502</v>
+        <v>8.49718284606934</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>9.37600040435791</v>
       </c>
       <c r="G60" t="n">
-        <v>8.87189292907715</v>
+        <v>8.87189197540283</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G86" t="n">
-        <v>8.8378267288208</v>
+        <v>8.83782768249512</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G89" t="n">
-        <v>8.74320411682129</v>
+        <v>8.74320316314697</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>9.17899990081787</v>
       </c>
       <c r="G90" t="n">
-        <v>8.6854829788208</v>
+        <v>8.68548202514648</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.22700023651123</v>
       </c>
       <c r="G93" t="n">
-        <v>8.73090362548828</v>
+        <v>8.73090267181396</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G95" t="n">
-        <v>8.53503322601318</v>
+        <v>8.53503227233887</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>8.9069995880127</v>
       </c>
       <c r="G100" t="n">
-        <v>8.42810821533203</v>
+        <v>8.42810726165771</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9.01900005340576</v>
       </c>
       <c r="G101" t="n">
-        <v>8.53408527374268</v>
+        <v>8.53408622741699</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G109" t="n">
-        <v>8.27008628845215</v>
+        <v>8.27008724212646</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G110" t="n">
-        <v>8.37417221069336</v>
+        <v>8.37417316436768</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>8.75500011444092</v>
       </c>
       <c r="G116" t="n">
-        <v>8.28428077697754</v>
+        <v>8.28427982330322</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G118" t="n">
-        <v>8.23223781585693</v>
+        <v>8.23223686218262</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>8.75</v>
       </c>
       <c r="G120" t="n">
-        <v>8.27954769134521</v>
+        <v>8.27954864501953</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G126" t="n">
-        <v>8.36470890045166</v>
+        <v>8.36470985412598</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G127" t="n">
-        <v>8.37417221069336</v>
+        <v>8.37417316436768</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G129" t="n">
-        <v>8.44987201690674</v>
+        <v>8.44987106323242</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>9.03800010681152</v>
       </c>
       <c r="G131" t="n">
-        <v>8.55206394195557</v>
+        <v>8.55206489562988</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G136" t="n">
-        <v>8.53503322601318</v>
+        <v>8.53503227233887</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G142" t="n">
-        <v>8.6296558380127</v>
+        <v>8.62965488433838</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G156" t="n">
-        <v>9.00815010070801</v>
+        <v>9.00814914703369</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>9.60900020599365</v>
       </c>
       <c r="G157" t="n">
-        <v>9.09236335754395</v>
+        <v>9.09236431121826</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G162" t="n">
-        <v>9.1122350692749</v>
+        <v>9.11223411560059</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>9.79300022125244</v>
       </c>
       <c r="G163" t="n">
-        <v>9.26646995544434</v>
+        <v>9.26647090911865</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G164" t="n">
-        <v>9.27309417724609</v>
+        <v>9.27309513092041</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>9.7819995880127</v>
       </c>
       <c r="G170" t="n">
-        <v>9.25606250762939</v>
+        <v>9.25606155395508</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>9.57100009918213</v>
       </c>
       <c r="G173" t="n">
-        <v>9.05640697479248</v>
+        <v>9.05640602111816</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>9.1122350692749</v>
+        <v>9.11223411560059</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>10.4580001831055</v>
       </c>
       <c r="G183" t="n">
-        <v>9.89571762084961</v>
+        <v>9.89571666717529</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G185" t="n">
-        <v>10.0395450592041</v>
+        <v>10.0395441055298</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>10.6820001602173</v>
       </c>
       <c r="G191" t="n">
-        <v>10.1076726913452</v>
+        <v>10.1076736450195</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G194" t="n">
-        <v>10.1909418106079</v>
+        <v>10.1909427642822</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G207" t="n">
-        <v>10.9668531417847</v>
+        <v>10.966854095459</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G208" t="n">
-        <v>10.9763164520264</v>
+        <v>10.9763174057007</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>11.5579996109009</v>
       </c>
       <c r="G209" t="n">
-        <v>10.9365730285645</v>
+        <v>10.9365739822388</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G210" t="n">
-        <v>10.9195423126221</v>
+        <v>10.9195413589478</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>11.4820003509521</v>
       </c>
       <c r="G212" t="n">
-        <v>10.8646612167358</v>
+        <v>10.8646602630615</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G217" t="n">
-        <v>10.4369630813599</v>
+        <v>10.4369621276855</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>10.8739995956421</v>
       </c>
       <c r="G218" t="n">
-        <v>10.2893495559692</v>
+        <v>10.2893505096436</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>10.9619998931885</v>
       </c>
       <c r="G220" t="n">
-        <v>10.3726196289062</v>
+        <v>10.3726186752319</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>11.9340000152588</v>
       </c>
       <c r="G225" t="n">
-        <v>11.2923583984375</v>
+        <v>11.2923593521118</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>11</v>
       </c>
       <c r="G228" t="n">
-        <v>10.4085750579834</v>
+        <v>10.4085760116577</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G229" t="n">
-        <v>10.4558877944946</v>
+        <v>10.4558868408203</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G230" t="n">
-        <v>10.3896503448486</v>
+        <v>10.3896512985229</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>11.0279998779297</v>
       </c>
       <c r="G232" t="n">
-        <v>10.4350690841675</v>
+        <v>10.4350700378418</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G234" t="n">
-        <v>10.5126609802246</v>
+        <v>10.5126619338989</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G240" t="n">
-        <v>10.0395450592041</v>
+        <v>10.0395441055298</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G241" t="n">
-        <v>10.0395450592041</v>
+        <v>10.0395441055298</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G244" t="n">
-        <v>10.0395450592041</v>
+        <v>10.0395441055298</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G254" t="n">
-        <v>9.99223327636719</v>
+        <v>9.99223232269287</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G256" t="n">
-        <v>10.3896503448486</v>
+        <v>10.3896512985229</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>10.8299999237061</v>
       </c>
       <c r="G259" t="n">
-        <v>10.2477159500122</v>
+        <v>10.2477149963379</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G266" t="n">
-        <v>10.1436309814453</v>
+        <v>10.143630027771</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -22810,6 +22810,32 @@
         <v>26.5900001525879</v>
       </c>
       <c r="H863" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B864" t="n">
+        <v>844329</v>
+      </c>
+      <c r="C864" t="n">
+        <v>27.1599998474121</v>
+      </c>
+      <c r="D864" t="n">
+        <v>26.3099994659424</v>
+      </c>
+      <c r="E864" t="n">
+        <v>27</v>
+      </c>
+      <c r="F864" t="n">
+        <v>26.5400009155273</v>
+      </c>
+      <c r="G864" t="n">
+        <v>26.5400009155273</v>
+      </c>
+      <c r="H864" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/LTMC.MI.xlsx
+++ b/data/LTMC.MI.xlsx
@@ -421,7 +421,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2" t="n">
-        <v>7.75912046432495</v>
+        <v>7.75911998748779</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>8.59099960327148</v>
       </c>
       <c r="G6" t="n">
-        <v>8.12909698486328</v>
+        <v>8.1290979385376</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>8.25</v>
       </c>
       <c r="G9" t="n">
-        <v>7.80643177032471</v>
+        <v>7.80643224716187</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G10" t="n">
-        <v>7.99567794799805</v>
+        <v>7.99567890167236</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>7.86899995803833</v>
       </c>
       <c r="G16" t="n">
-        <v>7.44591665267944</v>
+        <v>7.44591617584229</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>7.80100011825562</v>
       </c>
       <c r="G20" t="n">
-        <v>7.38157224655151</v>
+        <v>7.38157272338867</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G22" t="n">
-        <v>7.03525066375732</v>
+        <v>7.03525114059448</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G25" t="n">
-        <v>7.28600311279297</v>
+        <v>7.28600263595581</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>8.52200031280518</v>
       </c>
       <c r="G29" t="n">
-        <v>8.06380748748779</v>
+        <v>8.06380844116211</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>8.23200035095215</v>
       </c>
       <c r="G31" t="n">
-        <v>7.78939962387085</v>
+        <v>7.78940010070801</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>8.16199970245361</v>
       </c>
       <c r="G32" t="n">
-        <v>7.72316360473633</v>
+        <v>7.72316312789917</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G36" t="n">
-        <v>7.8111629486084</v>
+        <v>7.81116247177124</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>8.4379997253418</v>
       </c>
       <c r="G38" t="n">
-        <v>7.98432350158691</v>
+        <v>7.98432397842407</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>8.69499969482422</v>
       </c>
       <c r="G46" t="n">
-        <v>8.22750663757324</v>
+        <v>8.22750568389893</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>8.58300018310547</v>
       </c>
       <c r="G47" t="n">
-        <v>8.12152862548828</v>
+        <v>8.12152767181396</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G48" t="n">
-        <v>7.9436354637146</v>
+        <v>7.94363641738892</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G50" t="n">
-        <v>8.49718284606934</v>
+        <v>8.49718189239502</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G52" t="n">
-        <v>8.7905158996582</v>
+        <v>8.79051494598389</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>9.4689998626709</v>
       </c>
       <c r="G53" t="n">
-        <v>8.9598913192749</v>
+        <v>8.95989036560059</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>9.27099990844727</v>
       </c>
       <c r="G59" t="n">
-        <v>8.772536277771</v>
+        <v>8.77253723144531</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G62" t="n">
-        <v>8.65804195404053</v>
+        <v>8.65804290771484</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>9.17800045013428</v>
       </c>
       <c r="G63" t="n">
-        <v>8.68453788757324</v>
+        <v>8.68453693389893</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G65" t="n">
-        <v>8.9419116973877</v>
+        <v>8.94191265106201</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G67" t="n">
-        <v>8.82363319396973</v>
+        <v>8.82363224029541</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G70" t="n">
-        <v>8.87567710876465</v>
+        <v>8.87567615509033</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>9.31900024414062</v>
       </c>
       <c r="G72" t="n">
-        <v>8.81795692443848</v>
+        <v>8.81795597076416</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>9.14700031280518</v>
       </c>
       <c r="G74" t="n">
-        <v>8.65520286560059</v>
+        <v>8.6552038192749</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G80" t="n">
-        <v>8.67696762084961</v>
+        <v>8.67696666717529</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>9.39200019836426</v>
       </c>
       <c r="G84" t="n">
-        <v>8.88703155517578</v>
+        <v>8.88703060150146</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>9.17899990081787</v>
       </c>
       <c r="G90" t="n">
-        <v>8.6854829788208</v>
+        <v>8.68548393249512</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G95" t="n">
-        <v>8.53503322601318</v>
+        <v>8.53503227233887</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>8.67696762084961</v>
+        <v>8.67696666717529</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9.01900005340576</v>
       </c>
       <c r="G101" t="n">
-        <v>8.53408622741699</v>
+        <v>8.53408527374268</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>8.89700031280518</v>
       </c>
       <c r="G102" t="n">
-        <v>8.41864490509033</v>
+        <v>8.41864585876465</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G109" t="n">
-        <v>8.27008628845215</v>
+        <v>8.27008724212646</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G110" t="n">
-        <v>8.37417221069336</v>
+        <v>8.37417316436768</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>8.85400009155273</v>
       </c>
       <c r="G117" t="n">
-        <v>8.37795734405518</v>
+        <v>8.37795829772949</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>8.7209997177124</v>
       </c>
       <c r="G119" t="n">
-        <v>8.25210857391357</v>
+        <v>8.25210762023926</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>8.75</v>
       </c>
       <c r="G120" t="n">
-        <v>8.27954864501953</v>
+        <v>8.27954959869385</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G127" t="n">
-        <v>8.37417221069336</v>
+        <v>8.37417316436768</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>8.82100009918213</v>
       </c>
       <c r="G128" t="n">
-        <v>8.3467321395874</v>
+        <v>8.34673118591309</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>8.93599987030029</v>
       </c>
       <c r="G130" t="n">
-        <v>8.45554733276367</v>
+        <v>8.45554828643799</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>9.03800010681152</v>
       </c>
       <c r="G131" t="n">
-        <v>8.55206394195557</v>
+        <v>8.55206489562988</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>9.22200012207031</v>
       </c>
       <c r="G133" t="n">
-        <v>8.72617053985596</v>
+        <v>8.72617149353027</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G135" t="n">
-        <v>8.612624168396</v>
+        <v>8.61262321472168</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G136" t="n">
-        <v>8.53503322601318</v>
+        <v>8.53503227233887</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G137" t="n">
-        <v>8.612624168396</v>
+        <v>8.61262321472168</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G146" t="n">
-        <v>8.81890296936035</v>
+        <v>8.81890201568604</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>9.45199966430664</v>
       </c>
       <c r="G150" t="n">
-        <v>8.94380474090576</v>
+        <v>8.94380569458008</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G154" t="n">
-        <v>8.96083736419678</v>
+        <v>8.96083641052246</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>9.60900020599365</v>
       </c>
       <c r="G157" t="n">
-        <v>9.09236335754395</v>
+        <v>9.09236431121826</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G161" t="n">
-        <v>8.9419116973877</v>
+        <v>8.94191265106201</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>9.80599975585938</v>
       </c>
       <c r="G165" t="n">
-        <v>9.27877235412598</v>
+        <v>9.27877140045166</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G167" t="n">
-        <v>9.32040691375732</v>
+        <v>9.32040786743164</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>9.84700012207031</v>
       </c>
       <c r="G169" t="n">
-        <v>9.31756687164307</v>
+        <v>9.31756782531738</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>9.7819995880127</v>
       </c>
       <c r="G170" t="n">
-        <v>9.25606250762939</v>
+        <v>9.25606155395508</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>9.6230001449585</v>
       </c>
       <c r="G174" t="n">
-        <v>9.10561180114746</v>
+        <v>9.10561084747314</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>10.4580001831055</v>
       </c>
       <c r="G183" t="n">
-        <v>9.89571666717529</v>
+        <v>9.89571762084961</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>10.1619997024536</v>
       </c>
       <c r="G184" t="n">
-        <v>9.61563014984131</v>
+        <v>9.61563110351562</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>10.6339998245239</v>
       </c>
       <c r="G187" t="n">
-        <v>10.0622529983521</v>
+        <v>10.0622539520264</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>10.7720003128052</v>
       </c>
       <c r="G192" t="n">
-        <v>10.192834854126</v>
+        <v>10.1928339004517</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>10.7440004348755</v>
       </c>
       <c r="G193" t="n">
-        <v>10.1663398742676</v>
+        <v>10.1663408279419</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>11.0480003356934</v>
       </c>
       <c r="G197" t="n">
-        <v>10.4539947509766</v>
+        <v>10.4539957046509</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G198" t="n">
-        <v>10.4842748641968</v>
+        <v>10.4842739105225</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G201" t="n">
-        <v>10.5788984298706</v>
+        <v>10.5788974761963</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>11.2040004730225</v>
       </c>
       <c r="G204" t="n">
-        <v>10.6016082763672</v>
+        <v>10.6016073226929</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>11.5579996109009</v>
       </c>
       <c r="G209" t="n">
-        <v>10.9365739822388</v>
+        <v>10.9365749359131</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G215" t="n">
-        <v>10.7870693206787</v>
+        <v>10.7870683670044</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G217" t="n">
-        <v>10.4369630813599</v>
+        <v>10.4369621276855</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>10.8739995956421</v>
       </c>
       <c r="G218" t="n">
-        <v>10.2893505096436</v>
+        <v>10.2893495559692</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G219" t="n">
-        <v>10.266640663147</v>
+        <v>10.2666416168213</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>10.9619998931885</v>
       </c>
       <c r="G220" t="n">
-        <v>10.3726186752319</v>
+        <v>10.3726196289062</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>11.2340002059937</v>
       </c>
       <c r="G222" t="n">
-        <v>10.6299934387207</v>
+        <v>10.629994392395</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>11.2128744125366</v>
+        <v>11.2128753662109</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>11.9340000152588</v>
       </c>
       <c r="G225" t="n">
-        <v>11.2923574447632</v>
+        <v>11.2923583984375</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G230" t="n">
-        <v>10.3896512985229</v>
+        <v>10.3896503448486</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>10.96399974823</v>
       </c>
       <c r="G231" t="n">
-        <v>10.3745107650757</v>
+        <v>10.37451171875</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G234" t="n">
-        <v>10.5126600265503</v>
+        <v>10.5126609802246</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G236" t="n">
-        <v>10.2382526397705</v>
+        <v>10.2382535934448</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>10.266640663147</v>
+        <v>10.2666416168213</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G238" t="n">
-        <v>10.2382526397705</v>
+        <v>10.2382535934448</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G242" t="n">
-        <v>10.1057815551758</v>
+        <v>10.1057806015015</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G251" t="n">
-        <v>9.89760875701904</v>
+        <v>9.89760971069336</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G253" t="n">
-        <v>9.87868404388428</v>
+        <v>9.87868499755859</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G254" t="n">
-        <v>9.99223232269287</v>
+        <v>9.99223327636719</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G255" t="n">
-        <v>10.2950277328491</v>
+        <v>10.2950267791748</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G256" t="n">
-        <v>10.3896512985229</v>
+        <v>10.3896503448486</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G257" t="n">
-        <v>10.266640663147</v>
+        <v>10.2666416168213</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G258" t="n">
-        <v>10.266640663147</v>
+        <v>10.2666416168213</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G260" t="n">
-        <v>10.2382526397705</v>
+        <v>10.2382535934448</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G261" t="n">
-        <v>10.1814794540405</v>
+        <v>10.1814804077148</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G262" t="n">
-        <v>10.2382526397705</v>
+        <v>10.2382535934448</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G263" t="n">
-        <v>10.1814794540405</v>
+        <v>10.1814804077148</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -22888,6 +22888,32 @@
         <v>25.6900005340576</v>
       </c>
       <c r="H866" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B867" t="n">
+        <v>883515</v>
+      </c>
+      <c r="C867" t="n">
+        <v>26</v>
+      </c>
+      <c r="D867" t="n">
+        <v>25.3199996948242</v>
+      </c>
+      <c r="E867" t="n">
+        <v>25.7000007629395</v>
+      </c>
+      <c r="F867" t="n">
+        <v>25.5300006866455</v>
+      </c>
+      <c r="G867" t="n">
+        <v>25.5300006866455</v>
+      </c>
+      <c r="H867" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/LTMC.MI.xlsx
+++ b/data/LTMC.MI.xlsx
@@ -20375,8 +20375,31 @@
       <c r="E870" t="n">
         <v>25.3700008392334</v>
       </c>
-      <c r="F870"/>
+      <c r="F870" t="n">
+        <v>24.9500007629395</v>
+      </c>
       <c r="G870" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B871" t="n">
+        <v>954397</v>
+      </c>
+      <c r="C871" t="n">
+        <v>25.3400001525879</v>
+      </c>
+      <c r="D871" t="n">
+        <v>24.7399997711182</v>
+      </c>
+      <c r="E871" t="n">
+        <v>25</v>
+      </c>
+      <c r="F871"/>
+      <c r="G871" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LTMC.MI.xlsx
+++ b/data/LTMC.MI.xlsx
@@ -20398,8 +20398,31 @@
       <c r="E871" t="n">
         <v>25</v>
       </c>
-      <c r="F871"/>
+      <c r="F871" t="n">
+        <v>24.9400005340576</v>
+      </c>
       <c r="G871" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B872" t="n">
+        <v>1069105</v>
+      </c>
+      <c r="C872" t="n">
+        <v>24.9400005340576</v>
+      </c>
+      <c r="D872" t="n">
+        <v>24.1800003051758</v>
+      </c>
+      <c r="E872" t="n">
+        <v>24.7600002288818</v>
+      </c>
+      <c r="F872"/>
+      <c r="G872" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LTMC.MI.xlsx
+++ b/data/LTMC.MI.xlsx
@@ -20421,8 +20421,31 @@
       <c r="E872" t="n">
         <v>24.7600002288818</v>
       </c>
-      <c r="F872"/>
+      <c r="F872" t="n">
+        <v>24.3099994659424</v>
+      </c>
       <c r="G872" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B873" t="n">
+        <v>831603</v>
+      </c>
+      <c r="C873" t="n">
+        <v>24.6000003814697</v>
+      </c>
+      <c r="D873" t="n">
+        <v>24.0799999237061</v>
+      </c>
+      <c r="E873" t="n">
+        <v>24.2199993133545</v>
+      </c>
+      <c r="F873"/>
+      <c r="G873" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LTMC.MI.xlsx
+++ b/data/LTMC.MI.xlsx
@@ -20444,8 +20444,31 @@
       <c r="E873" t="n">
         <v>24.2199993133545</v>
       </c>
-      <c r="F873"/>
+      <c r="F873" t="n">
+        <v>24.4099998474121</v>
+      </c>
       <c r="G873" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B874" t="n">
+        <v>623903</v>
+      </c>
+      <c r="C874" t="n">
+        <v>24.9200000762939</v>
+      </c>
+      <c r="D874" t="n">
+        <v>24.4500007629395</v>
+      </c>
+      <c r="E874" t="n">
+        <v>24.6000003814697</v>
+      </c>
+      <c r="F874"/>
+      <c r="G874" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LTMC.MI.xlsx
+++ b/data/LTMC.MI.xlsx
@@ -20474,6 +20474,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="875">
+      <c r="A875" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B875" t="n">
+        <v>737475</v>
+      </c>
+      <c r="C875" t="n">
+        <v>24.7199993133545</v>
+      </c>
+      <c r="D875" t="n">
+        <v>24.2600002288818</v>
+      </c>
+      <c r="E875" t="n">
+        <v>24.7199993133545</v>
+      </c>
+      <c r="F875" t="n">
+        <v>24.3600006103516</v>
+      </c>
+      <c r="G875" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LTMC.MI.xlsx
+++ b/data/LTMC.MI.xlsx
@@ -421,7 +421,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2" t="n">
-        <v>7.75911951065063</v>
+        <v>7.75912046432495</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G3" t="n">
-        <v>7.82535743713379</v>
+        <v>7.82535648345947</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>8.48400020599365</v>
       </c>
       <c r="G5" t="n">
-        <v>8.02785015106201</v>
+        <v>8.02785110473633</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>8.59099960327148</v>
       </c>
       <c r="G6" t="n">
-        <v>8.1290979385376</v>
+        <v>8.12909698486328</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>7.98600006103516</v>
       </c>
       <c r="G8" t="n">
-        <v>7.55662631988525</v>
+        <v>7.5566258430481</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>8.25</v>
       </c>
       <c r="G9" t="n">
-        <v>7.80643224716187</v>
+        <v>7.80643177032471</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G10" t="n">
-        <v>7.99567890167236</v>
+        <v>7.99567794799805</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G14" t="n">
-        <v>7.52256155014038</v>
+        <v>7.52256107330322</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G15" t="n">
-        <v>7.24815368652344</v>
+        <v>7.24815320968628</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>7.86899995803833</v>
       </c>
       <c r="G16" t="n">
-        <v>7.44591617584229</v>
+        <v>7.44591665267944</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G18" t="n">
-        <v>7.26707792282104</v>
+        <v>7.2670783996582</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>7.80100011825562</v>
       </c>
       <c r="G20" t="n">
-        <v>7.38157320022583</v>
+        <v>7.38157224655151</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G25" t="n">
-        <v>7.28600263595581</v>
+        <v>7.28600311279297</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>8.12600040435791</v>
       </c>
       <c r="G27" t="n">
-        <v>7.68909883499146</v>
+        <v>7.68909931182861</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G30" t="n">
-        <v>7.93890380859375</v>
+        <v>7.93890476226807</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>8.16199970245361</v>
       </c>
       <c r="G32" t="n">
-        <v>7.72316265106201</v>
+        <v>7.72316360473633</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>8.21399974822998</v>
       </c>
       <c r="G33" t="n">
-        <v>7.77236747741699</v>
+        <v>7.77236700057983</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>8.24600028991699</v>
       </c>
       <c r="G35" t="n">
-        <v>7.80264759063721</v>
+        <v>7.80264663696289</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G36" t="n">
-        <v>7.81116247177124</v>
+        <v>7.8111629486084</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>8.4379997253418</v>
       </c>
       <c r="G38" t="n">
-        <v>7.98432397842407</v>
+        <v>7.98432350158691</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>8.71599960327148</v>
       </c>
       <c r="G44" t="n">
-        <v>8.24737548828125</v>
+        <v>8.24737644195557</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>8.69499969482422</v>
       </c>
       <c r="G46" t="n">
-        <v>8.22750473022461</v>
+        <v>8.22750663757324</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>8.58300018310547</v>
       </c>
       <c r="G47" t="n">
-        <v>8.12152767181396</v>
+        <v>8.12152862548828</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G48" t="n">
-        <v>7.94363641738892</v>
+        <v>7.9436354637146</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G50" t="n">
-        <v>8.49718189239502</v>
+        <v>8.49718284606934</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G52" t="n">
-        <v>8.79051494598389</v>
+        <v>8.7905158996582</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>9.4689998626709</v>
       </c>
       <c r="G53" t="n">
-        <v>8.95989036560059</v>
+        <v>8.9598913192749</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>9.38399982452393</v>
       </c>
       <c r="G57" t="n">
-        <v>8.87946128845215</v>
+        <v>8.87946033477783</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G58" t="n">
-        <v>8.84728908538818</v>
+        <v>8.8472900390625</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>9.17800045013428</v>
       </c>
       <c r="G63" t="n">
-        <v>8.68453693389893</v>
+        <v>8.68453788757324</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G64" t="n">
-        <v>8.79997730255127</v>
+        <v>8.79997825622559</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G65" t="n">
-        <v>8.94191265106201</v>
+        <v>8.9419116973877</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G68" t="n">
-        <v>8.84728908538818</v>
+        <v>8.8472900390625</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>9.30300045013428</v>
       </c>
       <c r="G69" t="n">
-        <v>8.80281639099121</v>
+        <v>8.80281734466553</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>9.30300045013428</v>
       </c>
       <c r="G71" t="n">
-        <v>8.80281639099121</v>
+        <v>8.80281734466553</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>9.31900024414062</v>
       </c>
       <c r="G72" t="n">
-        <v>8.81795597076416</v>
+        <v>8.81795692443848</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G73" t="n">
-        <v>8.79997730255127</v>
+        <v>8.79997825622559</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>9.14700031280518</v>
       </c>
       <c r="G74" t="n">
-        <v>8.6552038192749</v>
+        <v>8.65520286560059</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G76" t="n">
-        <v>8.75455760955811</v>
+        <v>8.75455856323242</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>9.08300018310547</v>
       </c>
       <c r="G78" t="n">
-        <v>8.59464454650879</v>
+        <v>8.59464550018311</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G80" t="n">
-        <v>8.67696666717529</v>
+        <v>8.67696762084961</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>9.08100032806396</v>
       </c>
       <c r="G91" t="n">
-        <v>8.59275341033936</v>
+        <v>8.59275245666504</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>9.17099952697754</v>
       </c>
       <c r="G92" t="n">
-        <v>8.67791175842285</v>
+        <v>8.67791271209717</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.02299976348877</v>
       </c>
       <c r="G94" t="n">
-        <v>8.53787040710449</v>
+        <v>8.53786945343018</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G95" t="n">
-        <v>8.53503227233887</v>
+        <v>8.53503322601318</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>8.67696666717529</v>
+        <v>8.67696762084961</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>9.08100032806396</v>
       </c>
       <c r="G98" t="n">
-        <v>8.59275341033936</v>
+        <v>8.59275245666504</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>8.89700031280518</v>
       </c>
       <c r="G102" t="n">
-        <v>8.41864585876465</v>
+        <v>8.41864490509033</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>8.78400039672852</v>
       </c>
       <c r="G103" t="n">
-        <v>8.31172180175781</v>
+        <v>8.3117208480835</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>8.78400039672852</v>
       </c>
       <c r="G107" t="n">
-        <v>8.31172180175781</v>
+        <v>8.3117208480835</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>8.80700016021729</v>
       </c>
       <c r="G108" t="n">
-        <v>8.33348369598389</v>
+        <v>8.3334846496582</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G109" t="n">
-        <v>8.27008724212646</v>
+        <v>8.27008628845215</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G110" t="n">
-        <v>8.37417316436768</v>
+        <v>8.37417221069336</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>8.80099964141846</v>
       </c>
       <c r="G115" t="n">
-        <v>8.327805519104</v>
+        <v>8.32780647277832</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>8.7209997177124</v>
       </c>
       <c r="G119" t="n">
-        <v>8.25210762023926</v>
+        <v>8.25210857391357</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G127" t="n">
-        <v>8.37417316436768</v>
+        <v>8.37417221069336</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>8.82100009918213</v>
       </c>
       <c r="G128" t="n">
-        <v>8.34673118591309</v>
+        <v>8.3467321395874</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G129" t="n">
-        <v>8.44987106323242</v>
+        <v>8.44987201690674</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>8.93599987030029</v>
       </c>
       <c r="G130" t="n">
-        <v>8.45554828643799</v>
+        <v>8.45554733276367</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>9.03800010681152</v>
       </c>
       <c r="G131" t="n">
-        <v>8.55206489562988</v>
+        <v>8.55206394195557</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>9.22200012207031</v>
       </c>
       <c r="G133" t="n">
-        <v>8.72617149353027</v>
+        <v>8.72617053985596</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.05300045013428</v>
       </c>
       <c r="G134" t="n">
-        <v>8.56625747680664</v>
+        <v>8.56625843048096</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G135" t="n">
-        <v>8.61262321472168</v>
+        <v>8.612624168396</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G136" t="n">
-        <v>8.53503227233887</v>
+        <v>8.53503322601318</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G137" t="n">
-        <v>8.61262321472168</v>
+        <v>8.612624168396</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>9.08300018310547</v>
       </c>
       <c r="G140" t="n">
-        <v>8.59464454650879</v>
+        <v>8.59464550018311</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G142" t="n">
-        <v>8.62965488433838</v>
+        <v>8.6296558380127</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G146" t="n">
-        <v>8.81890106201172</v>
+        <v>8.81890296936035</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>9.36699962615967</v>
       </c>
       <c r="G148" t="n">
-        <v>8.86337471008301</v>
+        <v>8.86337566375732</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G149" t="n">
-        <v>8.84728908538818</v>
+        <v>8.8472900390625</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>9.42599964141846</v>
       </c>
       <c r="G155" t="n">
-        <v>8.91920185089111</v>
+        <v>8.91920280456543</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G156" t="n">
-        <v>9.00814914703369</v>
+        <v>9.00815010070801</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>9.60900020599365</v>
       </c>
       <c r="G157" t="n">
-        <v>9.09236431121826</v>
+        <v>9.09236335754395</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>9.58500003814697</v>
       </c>
       <c r="G160" t="n">
-        <v>9.06965351104736</v>
+        <v>9.06965446472168</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G161" t="n">
-        <v>8.94191265106201</v>
+        <v>8.9419116973877</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>9.79300022125244</v>
       </c>
       <c r="G163" t="n">
-        <v>9.26647090911865</v>
+        <v>9.26647186279297</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G164" t="n">
-        <v>9.27309513092041</v>
+        <v>9.27309417724609</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>9.80599975585938</v>
       </c>
       <c r="G165" t="n">
-        <v>9.27877140045166</v>
+        <v>9.27877235412598</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G167" t="n">
-        <v>9.32040786743164</v>
+        <v>9.32040691375732</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>9.8149995803833</v>
       </c>
       <c r="G168" t="n">
-        <v>9.28728866577148</v>
+        <v>9.28728771209717</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>9.84700012207031</v>
       </c>
       <c r="G169" t="n">
-        <v>9.3175687789917</v>
+        <v>9.31756687164307</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>9.6230001449585</v>
       </c>
       <c r="G174" t="n">
-        <v>9.10561084747314</v>
+        <v>9.10561180114746</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>9.66800022125244</v>
       </c>
       <c r="G176" t="n">
-        <v>9.14819240570068</v>
+        <v>9.14819145202637</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>10.1619997024536</v>
       </c>
       <c r="G184" t="n">
-        <v>9.61563110351562</v>
+        <v>9.61563014984131</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>10.6339998245239</v>
       </c>
       <c r="G187" t="n">
-        <v>10.0622539520264</v>
+        <v>10.0622529983521</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>10.7840003967285</v>
       </c>
       <c r="G189" t="n">
-        <v>10.2041902542114</v>
+        <v>10.2041893005371</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>10.6820001602173</v>
       </c>
       <c r="G191" t="n">
-        <v>10.1076736450195</v>
+        <v>10.1076726913452</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>11.0480003356934</v>
       </c>
       <c r="G197" t="n">
-        <v>10.4539957046509</v>
+        <v>10.4539947509766</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G201" t="n">
-        <v>10.5788974761963</v>
+        <v>10.5788984298706</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G208" t="n">
-        <v>10.9763174057007</v>
+        <v>10.9763164520264</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G210" t="n">
-        <v>10.9195413589478</v>
+        <v>10.9195423126221</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>11.4820003509521</v>
       </c>
       <c r="G212" t="n">
-        <v>10.8646602630615</v>
+        <v>10.8646612167358</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G217" t="n">
-        <v>10.4369621276855</v>
+        <v>10.4369630813599</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>10.8739995956421</v>
       </c>
       <c r="G218" t="n">
-        <v>10.2893495559692</v>
+        <v>10.2893505096436</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>11.2340002059937</v>
       </c>
       <c r="G222" t="n">
-        <v>10.629994392395</v>
+        <v>10.6299934387207</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>11.2128753662109</v>
+        <v>11.2128744125366</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>11.9340000152588</v>
       </c>
       <c r="G225" t="n">
-        <v>11.2923583984375</v>
+        <v>11.2923574447632</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G229" t="n">
-        <v>10.4558868408203</v>
+        <v>10.4558877944946</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G234" t="n">
-        <v>10.5126619338989</v>
+        <v>10.5126600265503</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G235" t="n">
-        <v>10.3234148025513</v>
+        <v>10.323413848877</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G236" t="n">
-        <v>10.2382535934448</v>
+        <v>10.2382526397705</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G238" t="n">
-        <v>10.2382535934448</v>
+        <v>10.2382526397705</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G242" t="n">
-        <v>10.1057806015015</v>
+        <v>10.1057815551758</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G247" t="n">
-        <v>9.90707206726074</v>
+        <v>9.90707111358643</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G252" t="n">
-        <v>9.81244850158691</v>
+        <v>9.8124475479126</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G253" t="n">
-        <v>9.87868499755859</v>
+        <v>9.87868404388428</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G255" t="n">
-        <v>10.2950267791748</v>
+        <v>10.2950277328491</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>10.8299999237061</v>
       </c>
       <c r="G259" t="n">
-        <v>10.2477149963379</v>
+        <v>10.2477159500122</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G260" t="n">
-        <v>10.2382535934448</v>
+        <v>10.2382526397705</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G262" t="n">
-        <v>10.2382535934448</v>
+        <v>10.2382526397705</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G268" t="n">
-        <v>10.0982227325439</v>
+        <v>10.0982236862183</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G275" t="n">
-        <v>10.3310346603394</v>
+        <v>10.3310356140137</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G283" t="n">
-        <v>10.6220502853394</v>
+        <v>10.6220512390137</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G285" t="n">
-        <v>10.5638484954834</v>
+        <v>10.5638475418091</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G287" t="n">
-        <v>10.2534313201904</v>
+        <v>10.2534303665161</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G288" t="n">
-        <v>10.3116340637207</v>
+        <v>10.311635017395</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G290" t="n">
-        <v>10.4377412796021</v>
+        <v>10.4377422332764</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G294" t="n">
-        <v>10.806360244751</v>
+        <v>10.8063611984253</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G297" t="n">
-        <v>10.951868057251</v>
+        <v>10.9518671035767</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G298" t="n">
-        <v>10.7578582763672</v>
+        <v>10.7578573226929</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G305" t="n">
-        <v>11.5823993682861</v>
+        <v>11.5824003219604</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G314" t="n">
-        <v>11.3398866653442</v>
+        <v>11.3398876190186</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G317" t="n">
-        <v>11.2525844573975</v>
+        <v>11.2525835037231</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G320" t="n">
-        <v>10.951868057251</v>
+        <v>10.9518671035767</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G322" t="n">
-        <v>10.9712696075439</v>
+        <v>10.9712686538696</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G324" t="n">
-        <v>10.7481575012207</v>
+        <v>10.7481565475464</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>10.7190551757812</v>
+        <v>10.7190561294556</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G328" t="n">
-        <v>10.7578582763672</v>
+        <v>10.7578573226929</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>10.8160600662231</v>
+        <v>10.8160610198975</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G334" t="n">
-        <v>11.1361770629883</v>
+        <v>11.136176109314</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G335" t="n">
-        <v>11.1361770629883</v>
+        <v>11.136176109314</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G341" t="n">
-        <v>11.4077911376953</v>
+        <v>11.4077920913696</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G345" t="n">
-        <v>10.9712696075439</v>
+        <v>10.9712686538696</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G346" t="n">
-        <v>10.9615688323975</v>
+        <v>10.9615678787231</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G347" t="n">
-        <v>11.0003700256348</v>
+        <v>11.0003709793091</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G348" t="n">
-        <v>11.0003700256348</v>
+        <v>11.0003709793091</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G357" t="n">
-        <v>11.0585737228394</v>
+        <v>11.058572769165</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G359" t="n">
-        <v>11.0003700256348</v>
+        <v>11.0003709793091</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>11.25</v>
       </c>
       <c r="G362" t="n">
-        <v>10.913064956665</v>
+        <v>10.9130659103394</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G364" t="n">
-        <v>11.1458778381348</v>
+        <v>11.1458768844604</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>11.0585737228394</v>
+        <v>11.058572769165</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G369" t="n">
-        <v>11.1458778381348</v>
+        <v>11.1458768844604</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G371" t="n">
-        <v>11.1361770629883</v>
+        <v>11.136176109314</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G373" t="n">
-        <v>11.0197706222534</v>
+        <v>11.0197715759277</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G377" t="n">
-        <v>11.0197706222534</v>
+        <v>11.0197715759277</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G383" t="n">
-        <v>11.1361770629883</v>
+        <v>11.136176109314</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G387" t="n">
-        <v>11.1749792098999</v>
+        <v>11.1749801635742</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G389" t="n">
-        <v>11.4465942382812</v>
+        <v>11.4465932846069</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G392" t="n">
-        <v>11.8540153503418</v>
+        <v>11.8540143966675</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G394" t="n">
-        <v>11.6988067626953</v>
+        <v>11.6988077163696</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G398" t="n">
-        <v>11.6309032440186</v>
+        <v>11.6309022903442</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G399" t="n">
-        <v>11.5823993682861</v>
+        <v>11.5824003219604</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G403" t="n">
-        <v>12.1935319900513</v>
+        <v>12.193531036377</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G405" t="n">
-        <v>12.1935319900513</v>
+        <v>12.193531036377</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G407" t="n">
-        <v>12.2226333618164</v>
+        <v>12.2226343154907</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G408" t="n">
-        <v>12.2517347335815</v>
+        <v>12.2517356872559</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G411" t="n">
-        <v>12.4651460647583</v>
+        <v>12.4651470184326</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G412" t="n">
-        <v>12.3875427246094</v>
+        <v>12.3875417709351</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G419" t="n">
-        <v>12.2517347335815</v>
+        <v>12.2517356872559</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G420" t="n">
-        <v>12.2226333618164</v>
+        <v>12.2226343154907</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G422" t="n">
-        <v>12.2129335403442</v>
+        <v>12.2129325866699</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G423" t="n">
-        <v>12.3875427246094</v>
+        <v>12.3875417709351</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G426" t="n">
-        <v>12.5427513122559</v>
+        <v>12.5427503585815</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G427" t="n">
-        <v>12.630054473877</v>
+        <v>12.6300554275513</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>13</v>
       </c>
       <c r="G430" t="n">
-        <v>12.610652923584</v>
+        <v>12.6106538772583</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G432" t="n">
-        <v>12.3972425460815</v>
+        <v>12.3972415924072</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G434" t="n">
-        <v>12.6882581710815</v>
+        <v>12.6882572174072</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G436" t="n">
-        <v>13.1538820266724</v>
+        <v>13.1538829803467</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G445" t="n">
-        <v>13.7844152450562</v>
+        <v>13.7844142913818</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G446" t="n">
-        <v>14.3373432159424</v>
+        <v>14.3373422622681</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G447" t="n">
-        <v>14.4537496566772</v>
+        <v>14.4537487030029</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G448" t="n">
-        <v>14.667160987854</v>
+        <v>14.6671600341797</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G450" t="n">
-        <v>14.8029670715332</v>
+        <v>14.8029680252075</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G457" t="n">
-        <v>16.0446338653564</v>
+        <v>16.0446319580078</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G459" t="n">
-        <v>15.9573268890381</v>
+        <v>15.9573278427124</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G463" t="n">
-        <v>16.0252304077148</v>
+        <v>16.0252323150635</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G464" t="n">
-        <v>15.6857128143311</v>
+        <v>15.6857137680054</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G471" t="n">
-        <v>15.870023727417</v>
+        <v>15.8700227737427</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G474" t="n">
-        <v>16.9273796081543</v>
+        <v>16.9273777008057</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G479" t="n">
-        <v>17.5870094299316</v>
+        <v>17.5870113372803</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G480" t="n">
-        <v>17.5870094299316</v>
+        <v>17.5870113372803</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G482" t="n">
-        <v>17.1601886749268</v>
+        <v>17.1601905822754</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G484" t="n">
-        <v>17.7519187927246</v>
+        <v>17.7519207000732</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G485" t="n">
-        <v>17.7422218322754</v>
+        <v>17.7422199249268</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G488" t="n">
-        <v>17.9071292877197</v>
+        <v>17.9071273803711</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G489" t="n">
-        <v>18.3727531433105</v>
+        <v>18.3727512359619</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>16.8303718566895</v>
+        <v>16.8303737640381</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G494" t="n">
-        <v>17.1601886749268</v>
+        <v>17.1601905822754</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G501" t="n">
-        <v>18.8480777740479</v>
+        <v>18.8480758666992</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>19.4699993133545</v>
       </c>
       <c r="G502" t="n">
-        <v>18.8868789672852</v>
+        <v>18.8868770599365</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G503" t="n">
-        <v>19.0226860046387</v>
+        <v>19.0226879119873</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G505" t="n">
-        <v>19.478609085083</v>
+        <v>19.4786109924316</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G506" t="n">
-        <v>19.45920753479</v>
+        <v>19.4592094421387</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G507" t="n">
-        <v>19.4398097991943</v>
+        <v>19.4398078918457</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G509" t="n">
-        <v>20.3128547668457</v>
+        <v>20.3128528594971</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G510" t="n">
-        <v>20.2352485656738</v>
+        <v>20.2352504730225</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G511" t="n">
-        <v>19.9248352050781</v>
+        <v>19.9248332977295</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>20</v>
       </c>
       <c r="G512" t="n">
-        <v>19.4010066986084</v>
+        <v>19.4010047912598</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>21.6321201324463</v>
+        <v>21.6321220397949</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G517" t="n">
-        <v>22.1171474456787</v>
+        <v>22.1171455383301</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G518" t="n">
-        <v>21.9619369506836</v>
+        <v>21.9619388580322</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -23174,6 +23174,32 @@
         <v>23.8400001525879</v>
       </c>
       <c r="H877" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B878" t="n">
+        <v>807112</v>
+      </c>
+      <c r="C878" t="n">
+        <v>24.1000003814697</v>
+      </c>
+      <c r="D878" t="n">
+        <v>23.6800003051758</v>
+      </c>
+      <c r="E878" t="n">
+        <v>23.8400001525879</v>
+      </c>
+      <c r="F878" t="n">
+        <v>24.0599994659424</v>
+      </c>
+      <c r="G878" t="n">
+        <v>24.0599994659424</v>
+      </c>
+      <c r="H878" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/LTMC.MI.xlsx
+++ b/data/LTMC.MI.xlsx
@@ -421,7 +421,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2" t="n">
-        <v>7.75912046432495</v>
+        <v>7.75911951065063</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G3" t="n">
-        <v>7.82535648345947</v>
+        <v>7.82535743713379</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>8.44600009918213</v>
       </c>
       <c r="G4" t="n">
-        <v>7.99189424514771</v>
+        <v>7.99189376831055</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G7" t="n">
-        <v>7.92944240570068</v>
+        <v>7.92944288253784</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>8.25</v>
       </c>
       <c r="G9" t="n">
-        <v>7.80643177032471</v>
+        <v>7.80643129348755</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G10" t="n">
-        <v>7.99567794799805</v>
+        <v>7.99567842483521</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>7.72300004959106</v>
       </c>
       <c r="G17" t="n">
-        <v>7.30776643753052</v>
+        <v>7.30776596069336</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G18" t="n">
-        <v>7.2670783996582</v>
+        <v>7.26707792282104</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>7.80100011825562</v>
       </c>
       <c r="G20" t="n">
-        <v>7.38157224655151</v>
+        <v>7.38157272338867</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>7.71199989318848</v>
       </c>
       <c r="G21" t="n">
-        <v>7.2973575592041</v>
+        <v>7.29735803604126</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G25" t="n">
-        <v>7.28600311279297</v>
+        <v>7.28600215911865</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>8.12600040435791</v>
       </c>
       <c r="G27" t="n">
-        <v>7.68909931182861</v>
+        <v>7.68909883499146</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G28" t="n">
-        <v>7.76858282089233</v>
+        <v>7.76858234405518</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>8.23200035095215</v>
       </c>
       <c r="G31" t="n">
-        <v>7.78939962387085</v>
+        <v>7.78940010070801</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>8.16199970245361</v>
       </c>
       <c r="G32" t="n">
-        <v>7.72316360473633</v>
+        <v>7.72316265106201</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>8.21399974822998</v>
       </c>
       <c r="G33" t="n">
-        <v>7.77236700057983</v>
+        <v>7.77236652374268</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>8.41300010681152</v>
       </c>
       <c r="G34" t="n">
-        <v>7.96066761016846</v>
+        <v>7.96066808700562</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G36" t="n">
-        <v>7.8111629486084</v>
+        <v>7.81116342544556</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G37" t="n">
-        <v>7.92944240570068</v>
+        <v>7.92944288253784</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>8.4379997253418</v>
       </c>
       <c r="G38" t="n">
-        <v>7.98432350158691</v>
+        <v>7.98432397842407</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>8.43299961090088</v>
       </c>
       <c r="G39" t="n">
-        <v>7.97959184646606</v>
+        <v>7.97959136962891</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>8.43599987030029</v>
       </c>
       <c r="G40" t="n">
-        <v>7.98243093490601</v>
+        <v>7.98243045806885</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G41" t="n">
-        <v>7.92944240570068</v>
+        <v>7.92944288253784</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>8.41300010681152</v>
       </c>
       <c r="G42" t="n">
-        <v>7.96066761016846</v>
+        <v>7.96066808700562</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>8.23223686218262</v>
+        <v>8.23223781585693</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>8.5620002746582</v>
       </c>
       <c r="G45" t="n">
-        <v>8.10165691375732</v>
+        <v>8.10165596008301</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>8.69499969482422</v>
       </c>
       <c r="G46" t="n">
-        <v>8.22750663757324</v>
+        <v>8.22750473022461</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G48" t="n">
-        <v>7.9436354637146</v>
+        <v>7.94363641738892</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>8.78800010681152</v>
       </c>
       <c r="G49" t="n">
-        <v>8.31550598144531</v>
+        <v>8.315505027771</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G50" t="n">
-        <v>8.49718284606934</v>
+        <v>8.49718189239502</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G52" t="n">
-        <v>8.7905158996582</v>
+        <v>8.79051494598389</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>9.4689998626709</v>
       </c>
       <c r="G53" t="n">
-        <v>8.9598913192749</v>
+        <v>8.95989036560059</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G54" t="n">
-        <v>8.97029972076416</v>
+        <v>8.97029876708984</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>9.38399982452393</v>
       </c>
       <c r="G57" t="n">
-        <v>8.87946033477783</v>
+        <v>8.87946128845215</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>9.27099990844727</v>
       </c>
       <c r="G59" t="n">
-        <v>8.772536277771</v>
+        <v>8.77253723144531</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>9.37600040435791</v>
       </c>
       <c r="G60" t="n">
-        <v>8.87189197540283</v>
+        <v>8.87189292907715</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G64" t="n">
-        <v>8.79997825622559</v>
+        <v>8.79997730255127</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G65" t="n">
-        <v>8.9419116973877</v>
+        <v>8.94191360473633</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>9.30300045013428</v>
       </c>
       <c r="G69" t="n">
-        <v>8.80281734466553</v>
+        <v>8.80281639099121</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G70" t="n">
-        <v>8.87567710876465</v>
+        <v>8.87567615509033</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>9.30300045013428</v>
       </c>
       <c r="G71" t="n">
-        <v>8.80281734466553</v>
+        <v>8.80281639099121</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>9.31900024414062</v>
       </c>
       <c r="G72" t="n">
-        <v>8.81795692443848</v>
+        <v>8.81795597076416</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G73" t="n">
-        <v>8.79997825622559</v>
+        <v>8.79997730255127</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>9.14700031280518</v>
       </c>
       <c r="G74" t="n">
-        <v>8.65520286560059</v>
+        <v>8.6552038192749</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>9.12600040435791</v>
       </c>
       <c r="G77" t="n">
-        <v>8.63533306121826</v>
+        <v>8.63533401489258</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>9.10799980163574</v>
       </c>
       <c r="G79" t="n">
-        <v>8.61830043792725</v>
+        <v>8.61829948425293</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G80" t="n">
-        <v>8.67696762084961</v>
+        <v>8.67696666717529</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G86" t="n">
-        <v>8.83782768249512</v>
+        <v>8.8378267288208</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>9</v>
       </c>
       <c r="G87" t="n">
-        <v>8.5161075592041</v>
+        <v>8.51610660552979</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>9.10799980163574</v>
       </c>
       <c r="G88" t="n">
-        <v>8.61830043792725</v>
+        <v>8.61829948425293</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G89" t="n">
-        <v>8.74320316314697</v>
+        <v>8.74320411682129</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>9.22700023651123</v>
       </c>
       <c r="G93" t="n">
-        <v>8.73090267181396</v>
+        <v>8.73090362548828</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>9.02299976348877</v>
       </c>
       <c r="G94" t="n">
-        <v>8.53786945343018</v>
+        <v>8.53787040710449</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>9</v>
       </c>
       <c r="G96" t="n">
-        <v>8.5161075592041</v>
+        <v>8.51610660552979</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>8.67696762084961</v>
+        <v>8.67696666717529</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>8.9069995880127</v>
       </c>
       <c r="G100" t="n">
-        <v>8.42810726165771</v>
+        <v>8.42810821533203</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>9.01900005340576</v>
       </c>
       <c r="G101" t="n">
-        <v>8.53408622741699</v>
+        <v>8.53408527374268</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>8.89700031280518</v>
       </c>
       <c r="G102" t="n">
-        <v>8.41864490509033</v>
+        <v>8.41864585876465</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>8.53899955749512</v>
       </c>
       <c r="G105" t="n">
-        <v>8.0798921585083</v>
+        <v>8.07989311218262</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G111" t="n">
-        <v>8.17546367645264</v>
+        <v>8.17546272277832</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>8.75500011444092</v>
       </c>
       <c r="G116" t="n">
-        <v>8.28427982330322</v>
+        <v>8.28428077697754</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G118" t="n">
-        <v>8.23223686218262</v>
+        <v>8.23223781585693</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>8.7209997177124</v>
       </c>
       <c r="G119" t="n">
-        <v>8.25210857391357</v>
+        <v>8.25210762023926</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>8.75</v>
       </c>
       <c r="G120" t="n">
-        <v>8.27954864501953</v>
+        <v>8.27954769134521</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>8.7810001373291</v>
       </c>
       <c r="G123" t="n">
-        <v>8.30888271331787</v>
+        <v>8.30888175964355</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>9</v>
       </c>
       <c r="G124" t="n">
-        <v>8.5161075592041</v>
+        <v>8.51610660552979</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G126" t="n">
-        <v>8.36470985412598</v>
+        <v>8.36470890045166</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>8.82100009918213</v>
       </c>
       <c r="G128" t="n">
-        <v>8.3467321395874</v>
+        <v>8.34673118591309</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>8.93599987030029</v>
       </c>
       <c r="G130" t="n">
-        <v>8.45554733276367</v>
+        <v>8.45554828643799</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>9.05300045013428</v>
       </c>
       <c r="G134" t="n">
-        <v>8.56625843048096</v>
+        <v>8.56625747680664</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G135" t="n">
-        <v>8.612624168396</v>
+        <v>8.61262321472168</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G137" t="n">
-        <v>8.612624168396</v>
+        <v>8.61262321472168</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>9</v>
       </c>
       <c r="G139" t="n">
-        <v>8.5161075592041</v>
+        <v>8.51610660552979</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G146" t="n">
-        <v>8.81890296936035</v>
+        <v>8.81890201568604</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>9.36699962615967</v>
       </c>
       <c r="G148" t="n">
-        <v>8.86337566375732</v>
+        <v>8.86337375640869</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G151" t="n">
-        <v>8.82836532592773</v>
+        <v>8.82836437225342</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>9.42599964141846</v>
       </c>
       <c r="G155" t="n">
-        <v>8.91920280456543</v>
+        <v>8.91920185089111</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G161" t="n">
-        <v>8.9419116973877</v>
+        <v>8.94191360473633</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>9.79300022125244</v>
       </c>
       <c r="G163" t="n">
-        <v>9.26647186279297</v>
+        <v>9.26646995544434</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>9.80599975585938</v>
       </c>
       <c r="G165" t="n">
-        <v>9.27877235412598</v>
+        <v>9.27877140045166</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>9.84700012207031</v>
       </c>
       <c r="G169" t="n">
-        <v>9.31756687164307</v>
+        <v>9.31756782531738</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>9.18793392181396</v>
+        <v>9.18793296813965</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>10.4580001831055</v>
       </c>
       <c r="G183" t="n">
-        <v>9.89571666717529</v>
+        <v>9.89571762084961</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>10.1619997024536</v>
       </c>
       <c r="G184" t="n">
-        <v>9.61563014984131</v>
+        <v>9.61563110351562</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G185" t="n">
-        <v>10.0395441055298</v>
+        <v>10.0395450592041</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>10.78600025177</v>
       </c>
       <c r="G186" t="n">
-        <v>10.2060813903809</v>
+        <v>10.2060823440552</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>10.6339998245239</v>
       </c>
       <c r="G187" t="n">
-        <v>10.0622529983521</v>
+        <v>10.0622539520264</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>11.0480003356934</v>
       </c>
       <c r="G197" t="n">
-        <v>10.4539947509766</v>
+        <v>10.4539957046509</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G198" t="n">
-        <v>10.4842748641968</v>
+        <v>10.4842739105225</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G201" t="n">
-        <v>10.5788984298706</v>
+        <v>10.5788974761963</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G202" t="n">
-        <v>10.5031986236572</v>
+        <v>10.5031995773315</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>11.3420000076294</v>
       </c>
       <c r="G205" t="n">
-        <v>10.7321882247925</v>
+        <v>10.7321872711182</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G207" t="n">
-        <v>10.966854095459</v>
+        <v>10.9668531417847</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>11.5579996109009</v>
       </c>
       <c r="G209" t="n">
-        <v>10.9365739822388</v>
+        <v>10.9365730285645</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>11.5019998550415</v>
       </c>
       <c r="G213" t="n">
-        <v>10.8835849761963</v>
+        <v>10.8835859298706</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G214" t="n">
-        <v>10.5031986236572</v>
+        <v>10.5031995773315</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>10.8739995956421</v>
       </c>
       <c r="G218" t="n">
-        <v>10.2893505096436</v>
+        <v>10.2893495559692</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>10.9619998931885</v>
       </c>
       <c r="G220" t="n">
-        <v>10.3726186752319</v>
+        <v>10.3726196289062</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>11.2340002059937</v>
       </c>
       <c r="G222" t="n">
-        <v>10.6299934387207</v>
+        <v>10.629994392395</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>11.2128744125366</v>
+        <v>11.2128753662109</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>11.9340000152588</v>
       </c>
       <c r="G225" t="n">
-        <v>11.2923574447632</v>
+        <v>11.2923583984375</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>11</v>
       </c>
       <c r="G228" t="n">
-        <v>10.4085760116577</v>
+        <v>10.4085750579834</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G230" t="n">
-        <v>10.3896512985229</v>
+        <v>10.3896503448486</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>11.0279998779297</v>
       </c>
       <c r="G232" t="n">
-        <v>10.4350700378418</v>
+        <v>10.4350690841675</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>10.5031986236572</v>
+        <v>10.5031995773315</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G234" t="n">
-        <v>10.5126600265503</v>
+        <v>10.5126609802246</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G236" t="n">
-        <v>10.2382526397705</v>
+        <v>10.2382535934448</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G238" t="n">
-        <v>10.2382526397705</v>
+        <v>10.2382535934448</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G240" t="n">
-        <v>10.0395441055298</v>
+        <v>10.0395450592041</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G241" t="n">
-        <v>10.0395441055298</v>
+        <v>10.0395450592041</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G242" t="n">
-        <v>10.1057815551758</v>
+        <v>10.1057806015015</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G244" t="n">
-        <v>10.0395441055298</v>
+        <v>10.0395450592041</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G247" t="n">
-        <v>9.90707111358643</v>
+        <v>9.90707206726074</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G254" t="n">
-        <v>9.99223232269287</v>
+        <v>9.99223327636719</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G256" t="n">
-        <v>10.3896512985229</v>
+        <v>10.3896503448486</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G260" t="n">
-        <v>10.2382526397705</v>
+        <v>10.2382535934448</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G262" t="n">
-        <v>10.2382526397705</v>
+        <v>10.2382535934448</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G266" t="n">
-        <v>10.143630027771</v>
+        <v>10.1436309814453</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G267" t="n">
-        <v>10.0206203460693</v>
+        <v>10.020619392395</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G268" t="n">
-        <v>10.0982236862183</v>
+        <v>10.0982227325439</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G275" t="n">
-        <v>10.3310356140137</v>
+        <v>10.3310346603394</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G283" t="n">
-        <v>10.6220512390137</v>
+        <v>10.6220502853394</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G285" t="n">
-        <v>10.5638475418091</v>
+        <v>10.5638484954834</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G287" t="n">
-        <v>10.2534303665161</v>
+        <v>10.2534313201904</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G288" t="n">
-        <v>10.311635017395</v>
+        <v>10.3116340637207</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G290" t="n">
-        <v>10.4377422332764</v>
+        <v>10.4377412796021</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G294" t="n">
-        <v>10.8063611984253</v>
+        <v>10.806360244751</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G297" t="n">
-        <v>10.9518671035767</v>
+        <v>10.951868057251</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G298" t="n">
-        <v>10.7578573226929</v>
+        <v>10.7578582763672</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G305" t="n">
-        <v>11.5824003219604</v>
+        <v>11.5823993682861</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G314" t="n">
-        <v>11.3398876190186</v>
+        <v>11.3398866653442</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G317" t="n">
-        <v>11.2525835037231</v>
+        <v>11.2525844573975</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G320" t="n">
-        <v>10.9518671035767</v>
+        <v>10.951868057251</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G322" t="n">
-        <v>10.9712686538696</v>
+        <v>10.9712696075439</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G324" t="n">
-        <v>10.7481565475464</v>
+        <v>10.7481575012207</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>10.7190561294556</v>
+        <v>10.7190551757812</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G328" t="n">
-        <v>10.7578573226929</v>
+        <v>10.7578582763672</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>10.8160610198975</v>
+        <v>10.8160600662231</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G334" t="n">
-        <v>11.136176109314</v>
+        <v>11.1361770629883</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G335" t="n">
-        <v>11.136176109314</v>
+        <v>11.1361770629883</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G341" t="n">
-        <v>11.4077920913696</v>
+        <v>11.4077911376953</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G345" t="n">
-        <v>10.9712686538696</v>
+        <v>10.9712696075439</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G346" t="n">
-        <v>10.9615678787231</v>
+        <v>10.9615688323975</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G347" t="n">
-        <v>11.0003709793091</v>
+        <v>11.0003700256348</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G348" t="n">
-        <v>11.0003709793091</v>
+        <v>11.0003700256348</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G357" t="n">
-        <v>11.058572769165</v>
+        <v>11.0585737228394</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G359" t="n">
-        <v>11.0003709793091</v>
+        <v>11.0003700256348</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>11.25</v>
       </c>
       <c r="G362" t="n">
-        <v>10.9130659103394</v>
+        <v>10.913064956665</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G364" t="n">
-        <v>11.1458768844604</v>
+        <v>11.1458778381348</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>11.058572769165</v>
+        <v>11.0585737228394</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G369" t="n">
-        <v>11.1458768844604</v>
+        <v>11.1458778381348</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G371" t="n">
-        <v>11.136176109314</v>
+        <v>11.1361770629883</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G373" t="n">
-        <v>11.0197715759277</v>
+        <v>11.0197706222534</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G377" t="n">
-        <v>11.0197715759277</v>
+        <v>11.0197706222534</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G383" t="n">
-        <v>11.136176109314</v>
+        <v>11.1361770629883</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G387" t="n">
-        <v>11.1749801635742</v>
+        <v>11.1749792098999</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G389" t="n">
-        <v>11.4465932846069</v>
+        <v>11.4465942382812</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G392" t="n">
-        <v>11.8540143966675</v>
+        <v>11.8540153503418</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G394" t="n">
-        <v>11.6988077163696</v>
+        <v>11.6988067626953</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G398" t="n">
-        <v>11.6309022903442</v>
+        <v>11.6309032440186</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G399" t="n">
-        <v>11.5824003219604</v>
+        <v>11.5823993682861</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G403" t="n">
-        <v>12.193531036377</v>
+        <v>12.1935319900513</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G405" t="n">
-        <v>12.193531036377</v>
+        <v>12.1935319900513</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G407" t="n">
-        <v>12.2226343154907</v>
+        <v>12.2226333618164</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G408" t="n">
-        <v>12.2517356872559</v>
+        <v>12.2517347335815</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G411" t="n">
-        <v>12.4651470184326</v>
+        <v>12.4651460647583</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G412" t="n">
-        <v>12.3875417709351</v>
+        <v>12.3875427246094</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G419" t="n">
-        <v>12.2517356872559</v>
+        <v>12.2517347335815</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G420" t="n">
-        <v>12.2226343154907</v>
+        <v>12.2226333618164</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G422" t="n">
-        <v>12.2129325866699</v>
+        <v>12.2129335403442</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G423" t="n">
-        <v>12.3875417709351</v>
+        <v>12.3875427246094</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G426" t="n">
-        <v>12.5427503585815</v>
+        <v>12.5427513122559</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G427" t="n">
-        <v>12.6300554275513</v>
+        <v>12.630054473877</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>13</v>
       </c>
       <c r="G430" t="n">
-        <v>12.6106538772583</v>
+        <v>12.610652923584</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G432" t="n">
-        <v>12.3972415924072</v>
+        <v>12.3972425460815</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G434" t="n">
-        <v>12.6882572174072</v>
+        <v>12.6882581710815</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G436" t="n">
-        <v>13.1538829803467</v>
+        <v>13.1538820266724</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G445" t="n">
-        <v>13.7844142913818</v>
+        <v>13.7844152450562</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G446" t="n">
-        <v>14.3373422622681</v>
+        <v>14.3373432159424</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G447" t="n">
-        <v>14.4537487030029</v>
+        <v>14.4537496566772</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G448" t="n">
-        <v>14.6671600341797</v>
+        <v>14.667160987854</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G450" t="n">
-        <v>14.8029680252075</v>
+        <v>14.8029670715332</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G457" t="n">
-        <v>16.0446319580078</v>
+        <v>16.0446338653564</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G459" t="n">
-        <v>15.9573278427124</v>
+        <v>15.9573268890381</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G463" t="n">
-        <v>16.0252323150635</v>
+        <v>16.0252304077148</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G464" t="n">
-        <v>15.6857137680054</v>
+        <v>15.6857128143311</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G471" t="n">
-        <v>15.8700227737427</v>
+        <v>15.870023727417</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G474" t="n">
-        <v>16.9273777008057</v>
+        <v>16.9273796081543</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G479" t="n">
-        <v>17.5870113372803</v>
+        <v>17.5870094299316</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G480" t="n">
-        <v>17.5870113372803</v>
+        <v>17.5870094299316</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G482" t="n">
-        <v>17.1601905822754</v>
+        <v>17.1601886749268</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G484" t="n">
-        <v>17.7519207000732</v>
+        <v>17.7519187927246</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G485" t="n">
-        <v>17.7422199249268</v>
+        <v>17.7422218322754</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G488" t="n">
-        <v>17.9071273803711</v>
+        <v>17.9071292877197</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G489" t="n">
-        <v>18.3727512359619</v>
+        <v>18.3727531433105</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>16.8303737640381</v>
+        <v>16.8303718566895</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G494" t="n">
-        <v>17.1601905822754</v>
+        <v>17.1601886749268</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G501" t="n">
-        <v>18.8480758666992</v>
+        <v>18.8480777740479</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>19.4699993133545</v>
       </c>
       <c r="G502" t="n">
-        <v>18.8868770599365</v>
+        <v>18.8868789672852</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G503" t="n">
-        <v>19.0226879119873</v>
+        <v>19.0226860046387</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G505" t="n">
-        <v>19.4786109924316</v>
+        <v>19.478609085083</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G506" t="n">
-        <v>19.4592094421387</v>
+        <v>19.45920753479</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G507" t="n">
-        <v>19.4398078918457</v>
+        <v>19.4398097991943</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G509" t="n">
-        <v>20.3128528594971</v>
+        <v>20.3128547668457</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G510" t="n">
-        <v>20.2352504730225</v>
+        <v>20.2352485656738</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G511" t="n">
-        <v>19.9248332977295</v>
+        <v>19.9248352050781</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>20</v>
       </c>
       <c r="G512" t="n">
-        <v>19.4010047912598</v>
+        <v>19.4010066986084</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>21.6321220397949</v>
+        <v>21.6321201324463</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G517" t="n">
-        <v>22.1171455383301</v>
+        <v>22.1171474456787</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G518" t="n">
-        <v>21.9619388580322</v>
+        <v>21.9619369506836</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -23200,6 +23200,32 @@
         <v>24.0599994659424</v>
       </c>
       <c r="H878" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B879" t="n">
+        <v>940536</v>
+      </c>
+      <c r="C879" t="n">
+        <v>24.3600006103516</v>
+      </c>
+      <c r="D879" t="n">
+        <v>24.0100002288818</v>
+      </c>
+      <c r="E879" t="n">
+        <v>24.2000007629395</v>
+      </c>
+      <c r="F879" t="n">
+        <v>24.1100006103516</v>
+      </c>
+      <c r="G879" t="n">
+        <v>24.1100006103516</v>
+      </c>
+      <c r="H879" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/LTMC.MI.xlsx
+++ b/data/LTMC.MI.xlsx
@@ -427,7 +427,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2" t="n">
-        <v>7.75911951065063</v>
+        <v>7.75912046432495</v>
       </c>
       <c r="H2" t="n">
         <v>13006120</v>
@@ -456,7 +456,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G3" t="n">
-        <v>7.82535743713379</v>
+        <v>7.82535648345947</v>
       </c>
       <c r="H3" t="n">
         <v>2759922</v>
@@ -485,7 +485,7 @@
         <v>8.44600009918213</v>
       </c>
       <c r="G4" t="n">
-        <v>7.99189376831055</v>
+        <v>7.99189424514771</v>
       </c>
       <c r="H4" t="n">
         <v>1476712</v>
@@ -572,7 +572,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G7" t="n">
-        <v>7.92944288253784</v>
+        <v>7.92944240570068</v>
       </c>
       <c r="H7" t="n">
         <v>640304</v>
@@ -630,7 +630,7 @@
         <v>8.25</v>
       </c>
       <c r="G9" t="n">
-        <v>7.80643129348755</v>
+        <v>7.80643177032471</v>
       </c>
       <c r="H9" t="n">
         <v>1073912</v>
@@ -659,7 +659,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G10" t="n">
-        <v>7.99567842483521</v>
+        <v>7.99567794799805</v>
       </c>
       <c r="H10" t="n">
         <v>1947465</v>
@@ -862,7 +862,7 @@
         <v>7.72300004959106</v>
       </c>
       <c r="G17" t="n">
-        <v>7.30776596069336</v>
+        <v>7.30776643753052</v>
       </c>
       <c r="H17" t="n">
         <v>588439</v>
@@ -891,7 +891,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G18" t="n">
-        <v>7.26707792282104</v>
+        <v>7.2670783996582</v>
       </c>
       <c r="H18" t="n">
         <v>228832</v>
@@ -949,7 +949,7 @@
         <v>7.80100011825562</v>
       </c>
       <c r="G20" t="n">
-        <v>7.38157272338867</v>
+        <v>7.38157224655151</v>
       </c>
       <c r="H20" t="n">
         <v>40924</v>
@@ -978,7 +978,7 @@
         <v>7.71199989318848</v>
       </c>
       <c r="G21" t="n">
-        <v>7.29735803604126</v>
+        <v>7.2973575592041</v>
       </c>
       <c r="H21" t="n">
         <v>118298</v>
@@ -1094,7 +1094,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G25" t="n">
-        <v>7.28600215911865</v>
+        <v>7.28600311279297</v>
       </c>
       <c r="H25" t="n">
         <v>218758</v>
@@ -1152,7 +1152,7 @@
         <v>8.12600040435791</v>
       </c>
       <c r="G27" t="n">
-        <v>7.68909883499146</v>
+        <v>7.68909931182861</v>
       </c>
       <c r="H27" t="n">
         <v>1170934</v>
@@ -1181,7 +1181,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G28" t="n">
-        <v>7.76858234405518</v>
+        <v>7.76858282089233</v>
       </c>
       <c r="H28" t="n">
         <v>1704311</v>
@@ -1268,7 +1268,7 @@
         <v>8.23200035095215</v>
       </c>
       <c r="G31" t="n">
-        <v>7.78940010070801</v>
+        <v>7.78939962387085</v>
       </c>
       <c r="H31" t="n">
         <v>749433</v>
@@ -1297,7 +1297,7 @@
         <v>8.16199970245361</v>
       </c>
       <c r="G32" t="n">
-        <v>7.72316265106201</v>
+        <v>7.72316360473633</v>
       </c>
       <c r="H32" t="n">
         <v>440552</v>
@@ -1326,7 +1326,7 @@
         <v>8.21399974822998</v>
       </c>
       <c r="G33" t="n">
-        <v>7.77236652374268</v>
+        <v>7.77236700057983</v>
       </c>
       <c r="H33" t="n">
         <v>327710</v>
@@ -1355,7 +1355,7 @@
         <v>8.41300010681152</v>
       </c>
       <c r="G34" t="n">
-        <v>7.96066808700562</v>
+        <v>7.96066761016846</v>
       </c>
       <c r="H34" t="n">
         <v>540974</v>
@@ -1413,7 +1413,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G36" t="n">
-        <v>7.81116342544556</v>
+        <v>7.8111629486084</v>
       </c>
       <c r="H36" t="n">
         <v>219714</v>
@@ -1442,7 +1442,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G37" t="n">
-        <v>7.92944288253784</v>
+        <v>7.92944240570068</v>
       </c>
       <c r="H37" t="n">
         <v>223839</v>
@@ -1471,7 +1471,7 @@
         <v>8.4379997253418</v>
       </c>
       <c r="G38" t="n">
-        <v>7.98432397842407</v>
+        <v>7.98432350158691</v>
       </c>
       <c r="H38" t="n">
         <v>178091</v>
@@ -1500,7 +1500,7 @@
         <v>8.43299961090088</v>
       </c>
       <c r="G39" t="n">
-        <v>7.97959136962891</v>
+        <v>7.97959184646606</v>
       </c>
       <c r="H39" t="n">
         <v>99001</v>
@@ -1529,7 +1529,7 @@
         <v>8.43599987030029</v>
       </c>
       <c r="G40" t="n">
-        <v>7.98243045806885</v>
+        <v>7.98243093490601</v>
       </c>
       <c r="H40" t="n">
         <v>155784</v>
@@ -1558,7 +1558,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G41" t="n">
-        <v>7.92944288253784</v>
+        <v>7.92944240570068</v>
       </c>
       <c r="H41" t="n">
         <v>133019</v>
@@ -1587,7 +1587,7 @@
         <v>8.41300010681152</v>
       </c>
       <c r="G42" t="n">
-        <v>7.96066808700562</v>
+        <v>7.96066761016846</v>
       </c>
       <c r="H42" t="n">
         <v>122155</v>
@@ -1616,7 +1616,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>8.23223781585693</v>
+        <v>8.23223686218262</v>
       </c>
       <c r="H43" t="n">
         <v>362592</v>
@@ -1674,7 +1674,7 @@
         <v>8.5620002746582</v>
       </c>
       <c r="G45" t="n">
-        <v>8.10165596008301</v>
+        <v>8.10165691375732</v>
       </c>
       <c r="H45" t="n">
         <v>252798</v>
@@ -1703,7 +1703,7 @@
         <v>8.69499969482422</v>
       </c>
       <c r="G46" t="n">
-        <v>8.22750473022461</v>
+        <v>8.22750663757324</v>
       </c>
       <c r="H46" t="n">
         <v>188291</v>
@@ -1761,7 +1761,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G48" t="n">
-        <v>7.94363641738892</v>
+        <v>7.9436354637146</v>
       </c>
       <c r="H48" t="n">
         <v>297588</v>
@@ -1790,7 +1790,7 @@
         <v>8.78800010681152</v>
       </c>
       <c r="G49" t="n">
-        <v>8.315505027771</v>
+        <v>8.31550598144531</v>
       </c>
       <c r="H49" t="n">
         <v>417701</v>
@@ -1819,7 +1819,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G50" t="n">
-        <v>8.49718189239502</v>
+        <v>8.49718284606934</v>
       </c>
       <c r="H50" t="n">
         <v>475388</v>
@@ -1877,7 +1877,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G52" t="n">
-        <v>8.79051494598389</v>
+        <v>8.7905158996582</v>
       </c>
       <c r="H52" t="n">
         <v>1027347</v>
@@ -1906,7 +1906,7 @@
         <v>9.4689998626709</v>
       </c>
       <c r="G53" t="n">
-        <v>8.95989036560059</v>
+        <v>8.9598913192749</v>
       </c>
       <c r="H53" t="n">
         <v>1003139</v>
@@ -1935,7 +1935,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G54" t="n">
-        <v>8.97029876708984</v>
+        <v>8.97029972076416</v>
       </c>
       <c r="H54" t="n">
         <v>321248</v>
@@ -2022,7 +2022,7 @@
         <v>9.38399982452393</v>
       </c>
       <c r="G57" t="n">
-        <v>8.87946128845215</v>
+        <v>8.87946033477783</v>
       </c>
       <c r="H57" t="n">
         <v>292101</v>
@@ -2080,7 +2080,7 @@
         <v>9.27099990844727</v>
       </c>
       <c r="G59" t="n">
-        <v>8.77253723144531</v>
+        <v>8.772536277771</v>
       </c>
       <c r="H59" t="n">
         <v>287274</v>
@@ -2109,7 +2109,7 @@
         <v>9.37600040435791</v>
       </c>
       <c r="G60" t="n">
-        <v>8.87189292907715</v>
+        <v>8.87189197540283</v>
       </c>
       <c r="H60" t="n">
         <v>240981</v>
@@ -2225,7 +2225,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G64" t="n">
-        <v>8.79997730255127</v>
+        <v>8.79997825622559</v>
       </c>
       <c r="H64" t="n">
         <v>396592</v>
@@ -2254,7 +2254,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G65" t="n">
-        <v>8.94191360473633</v>
+        <v>8.9419116973877</v>
       </c>
       <c r="H65" t="n">
         <v>900757</v>
@@ -2370,7 +2370,7 @@
         <v>9.30300045013428</v>
       </c>
       <c r="G69" t="n">
-        <v>8.80281639099121</v>
+        <v>8.80281734466553</v>
       </c>
       <c r="H69" t="n">
         <v>181453</v>
@@ -2399,7 +2399,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G70" t="n">
-        <v>8.87567615509033</v>
+        <v>8.87567710876465</v>
       </c>
       <c r="H70" t="n">
         <v>257403</v>
@@ -2428,7 +2428,7 @@
         <v>9.30300045013428</v>
       </c>
       <c r="G71" t="n">
-        <v>8.80281639099121</v>
+        <v>8.80281734466553</v>
       </c>
       <c r="H71" t="n">
         <v>228312</v>
@@ -2457,7 +2457,7 @@
         <v>9.31900024414062</v>
       </c>
       <c r="G72" t="n">
-        <v>8.81795597076416</v>
+        <v>8.81795692443848</v>
       </c>
       <c r="H72" t="n">
         <v>303822</v>
@@ -2486,7 +2486,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G73" t="n">
-        <v>8.79997730255127</v>
+        <v>8.79997825622559</v>
       </c>
       <c r="H73" t="n">
         <v>161362</v>
@@ -2515,7 +2515,7 @@
         <v>9.14700031280518</v>
       </c>
       <c r="G74" t="n">
-        <v>8.6552038192749</v>
+        <v>8.65520286560059</v>
       </c>
       <c r="H74" t="n">
         <v>250420</v>
@@ -2602,7 +2602,7 @@
         <v>9.12600040435791</v>
       </c>
       <c r="G77" t="n">
-        <v>8.63533401489258</v>
+        <v>8.63533306121826</v>
       </c>
       <c r="H77" t="n">
         <v>248031</v>
@@ -2660,7 +2660,7 @@
         <v>9.10799980163574</v>
       </c>
       <c r="G79" t="n">
-        <v>8.61829948425293</v>
+        <v>8.61830043792725</v>
       </c>
       <c r="H79" t="n">
         <v>127272</v>
@@ -2689,7 +2689,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G80" t="n">
-        <v>8.67696666717529</v>
+        <v>8.67696762084961</v>
       </c>
       <c r="H80" t="n">
         <v>180085</v>
@@ -2863,7 +2863,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G86" t="n">
-        <v>8.8378267288208</v>
+        <v>8.83782768249512</v>
       </c>
       <c r="H86" t="n">
         <v>322079</v>
@@ -2892,7 +2892,7 @@
         <v>9</v>
       </c>
       <c r="G87" t="n">
-        <v>8.51610660552979</v>
+        <v>8.5161075592041</v>
       </c>
       <c r="H87" t="n">
         <v>2756951</v>
@@ -2921,7 +2921,7 @@
         <v>9.10799980163574</v>
       </c>
       <c r="G88" t="n">
-        <v>8.61829948425293</v>
+        <v>8.61830043792725</v>
       </c>
       <c r="H88" t="n">
         <v>496089</v>
@@ -2950,7 +2950,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G89" t="n">
-        <v>8.74320411682129</v>
+        <v>8.74320316314697</v>
       </c>
       <c r="H89" t="n">
         <v>146265</v>
@@ -3066,7 +3066,7 @@
         <v>9.22700023651123</v>
       </c>
       <c r="G93" t="n">
-        <v>8.73090362548828</v>
+        <v>8.73090267181396</v>
       </c>
       <c r="H93" t="n">
         <v>184727</v>
@@ -3095,7 +3095,7 @@
         <v>9.02299976348877</v>
       </c>
       <c r="G94" t="n">
-        <v>8.53787040710449</v>
+        <v>8.53786945343018</v>
       </c>
       <c r="H94" t="n">
         <v>577462</v>
@@ -3153,7 +3153,7 @@
         <v>9</v>
       </c>
       <c r="G96" t="n">
-        <v>8.51610660552979</v>
+        <v>8.5161075592041</v>
       </c>
       <c r="H96" t="n">
         <v>322675</v>
@@ -3182,7 +3182,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>8.67696666717529</v>
+        <v>8.67696762084961</v>
       </c>
       <c r="H97" t="n">
         <v>420414</v>
@@ -3269,7 +3269,7 @@
         <v>8.9069995880127</v>
       </c>
       <c r="G100" t="n">
-        <v>8.42810821533203</v>
+        <v>8.42810726165771</v>
       </c>
       <c r="H100" t="n">
         <v>428743</v>
@@ -3298,7 +3298,7 @@
         <v>9.01900005340576</v>
       </c>
       <c r="G101" t="n">
-        <v>8.53408527374268</v>
+        <v>8.53408622741699</v>
       </c>
       <c r="H101" t="n">
         <v>120168</v>
@@ -3327,7 +3327,7 @@
         <v>8.89700031280518</v>
       </c>
       <c r="G102" t="n">
-        <v>8.41864585876465</v>
+        <v>8.41864490509033</v>
       </c>
       <c r="H102" t="n">
         <v>170277</v>
@@ -3414,7 +3414,7 @@
         <v>8.53899955749512</v>
       </c>
       <c r="G105" t="n">
-        <v>8.07989311218262</v>
+        <v>8.0798921585083</v>
       </c>
       <c r="H105" t="n">
         <v>153907</v>
@@ -3588,7 +3588,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G111" t="n">
-        <v>8.17546272277832</v>
+        <v>8.17546367645264</v>
       </c>
       <c r="H111" t="n">
         <v>213577</v>
@@ -3733,7 +3733,7 @@
         <v>8.75500011444092</v>
       </c>
       <c r="G116" t="n">
-        <v>8.28428077697754</v>
+        <v>8.28427982330322</v>
       </c>
       <c r="H116" t="n">
         <v>68870</v>
@@ -3791,7 +3791,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G118" t="n">
-        <v>8.23223781585693</v>
+        <v>8.23223686218262</v>
       </c>
       <c r="H118" t="n">
         <v>188950</v>
@@ -3820,7 +3820,7 @@
         <v>8.7209997177124</v>
       </c>
       <c r="G119" t="n">
-        <v>8.25210762023926</v>
+        <v>8.25210857391357</v>
       </c>
       <c r="H119" t="n">
         <v>127697</v>
@@ -3849,7 +3849,7 @@
         <v>8.75</v>
       </c>
       <c r="G120" t="n">
-        <v>8.27954769134521</v>
+        <v>8.27954864501953</v>
       </c>
       <c r="H120" t="n">
         <v>97384</v>
@@ -3936,7 +3936,7 @@
         <v>8.7810001373291</v>
       </c>
       <c r="G123" t="n">
-        <v>8.30888175964355</v>
+        <v>8.30888271331787</v>
       </c>
       <c r="H123" t="n">
         <v>162637</v>
@@ -3965,7 +3965,7 @@
         <v>9</v>
       </c>
       <c r="G124" t="n">
-        <v>8.51610660552979</v>
+        <v>8.5161075592041</v>
       </c>
       <c r="H124" t="n">
         <v>178371</v>
@@ -4023,7 +4023,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G126" t="n">
-        <v>8.36470890045166</v>
+        <v>8.36470985412598</v>
       </c>
       <c r="H126" t="n">
         <v>152716</v>
@@ -4081,7 +4081,7 @@
         <v>8.82100009918213</v>
       </c>
       <c r="G128" t="n">
-        <v>8.34673118591309</v>
+        <v>8.3467321395874</v>
       </c>
       <c r="H128" t="n">
         <v>174329</v>
@@ -4139,7 +4139,7 @@
         <v>8.93599987030029</v>
       </c>
       <c r="G130" t="n">
-        <v>8.45554828643799</v>
+        <v>8.45554733276367</v>
       </c>
       <c r="H130" t="n">
         <v>394314</v>
@@ -4255,7 +4255,7 @@
         <v>9.05300045013428</v>
       </c>
       <c r="G134" t="n">
-        <v>8.56625747680664</v>
+        <v>8.56625843048096</v>
       </c>
       <c r="H134" t="n">
         <v>123966</v>
@@ -4284,7 +4284,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G135" t="n">
-        <v>8.61262321472168</v>
+        <v>8.612624168396</v>
       </c>
       <c r="H135" t="n">
         <v>75451</v>
@@ -4342,7 +4342,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G137" t="n">
-        <v>8.61262321472168</v>
+        <v>8.612624168396</v>
       </c>
       <c r="H137" t="n">
         <v>197102</v>
@@ -4400,7 +4400,7 @@
         <v>9</v>
       </c>
       <c r="G139" t="n">
-        <v>8.51610660552979</v>
+        <v>8.5161075592041</v>
       </c>
       <c r="H139" t="n">
         <v>111082</v>
@@ -4603,7 +4603,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G146" t="n">
-        <v>8.81890201568604</v>
+        <v>8.81890296936035</v>
       </c>
       <c r="H146" t="n">
         <v>95465</v>
@@ -4661,7 +4661,7 @@
         <v>9.36699962615967</v>
       </c>
       <c r="G148" t="n">
-        <v>8.86337375640869</v>
+        <v>8.86337566375732</v>
       </c>
       <c r="H148" t="n">
         <v>76421</v>
@@ -4748,7 +4748,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G151" t="n">
-        <v>8.82836437225342</v>
+        <v>8.82836532592773</v>
       </c>
       <c r="H151" t="n">
         <v>103859</v>
@@ -4864,7 +4864,7 @@
         <v>9.42599964141846</v>
       </c>
       <c r="G155" t="n">
-        <v>8.91920185089111</v>
+        <v>8.91920280456543</v>
       </c>
       <c r="H155" t="n">
         <v>113950</v>
@@ -5038,7 +5038,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G161" t="n">
-        <v>8.94191360473633</v>
+        <v>8.9419116973877</v>
       </c>
       <c r="H161" t="n">
         <v>242695</v>
@@ -5096,7 +5096,7 @@
         <v>9.79300022125244</v>
       </c>
       <c r="G163" t="n">
-        <v>9.26646995544434</v>
+        <v>9.26647186279297</v>
       </c>
       <c r="H163" t="n">
         <v>2495031</v>
@@ -5154,7 +5154,7 @@
         <v>9.80599975585938</v>
       </c>
       <c r="G165" t="n">
-        <v>9.27877140045166</v>
+        <v>9.27877235412598</v>
       </c>
       <c r="H165" t="n">
         <v>183228</v>
@@ -5270,7 +5270,7 @@
         <v>9.84700012207031</v>
       </c>
       <c r="G169" t="n">
-        <v>9.31756782531738</v>
+        <v>9.31756687164307</v>
       </c>
       <c r="H169" t="n">
         <v>94635</v>
@@ -5531,7 +5531,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>9.18793296813965</v>
+        <v>9.18793392181396</v>
       </c>
       <c r="H178" t="n">
         <v>132214</v>
@@ -5676,7 +5676,7 @@
         <v>10.4580001831055</v>
       </c>
       <c r="G183" t="n">
-        <v>9.89571762084961</v>
+        <v>9.89571666717529</v>
       </c>
       <c r="H183" t="n">
         <v>362012</v>
@@ -5705,7 +5705,7 @@
         <v>10.1619997024536</v>
       </c>
       <c r="G184" t="n">
-        <v>9.61563110351562</v>
+        <v>9.61563014984131</v>
       </c>
       <c r="H184" t="n">
         <v>2039385</v>
@@ -5734,7 +5734,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G185" t="n">
-        <v>10.0395450592041</v>
+        <v>10.0395441055298</v>
       </c>
       <c r="H185" t="n">
         <v>748210</v>
@@ -5763,7 +5763,7 @@
         <v>10.78600025177</v>
       </c>
       <c r="G186" t="n">
-        <v>10.2060823440552</v>
+        <v>10.2060813903809</v>
       </c>
       <c r="H186" t="n">
         <v>469378</v>
@@ -5792,7 +5792,7 @@
         <v>10.6339998245239</v>
       </c>
       <c r="G187" t="n">
-        <v>10.0622539520264</v>
+        <v>10.0622529983521</v>
       </c>
       <c r="H187" t="n">
         <v>279044</v>
@@ -6082,7 +6082,7 @@
         <v>11.0480003356934</v>
       </c>
       <c r="G197" t="n">
-        <v>10.4539957046509</v>
+        <v>10.4539947509766</v>
       </c>
       <c r="H197" t="n">
         <v>281143</v>
@@ -6111,7 +6111,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G198" t="n">
-        <v>10.4842739105225</v>
+        <v>10.4842748641968</v>
       </c>
       <c r="H198" t="n">
         <v>255451</v>
@@ -6198,7 +6198,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G201" t="n">
-        <v>10.5788974761963</v>
+        <v>10.5788984298706</v>
       </c>
       <c r="H201" t="n">
         <v>211395</v>
@@ -6227,7 +6227,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G202" t="n">
-        <v>10.5031995773315</v>
+        <v>10.5031986236572</v>
       </c>
       <c r="H202" t="n">
         <v>244760</v>
@@ -6314,7 +6314,7 @@
         <v>11.3420000076294</v>
       </c>
       <c r="G205" t="n">
-        <v>10.7321872711182</v>
+        <v>10.7321882247925</v>
       </c>
       <c r="H205" t="n">
         <v>152325</v>
@@ -6372,7 +6372,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G207" t="n">
-        <v>10.9668531417847</v>
+        <v>10.966854095459</v>
       </c>
       <c r="H207" t="n">
         <v>191397</v>
@@ -6430,7 +6430,7 @@
         <v>11.5579996109009</v>
       </c>
       <c r="G209" t="n">
-        <v>10.9365730285645</v>
+        <v>10.9365739822388</v>
       </c>
       <c r="H209" t="n">
         <v>170731</v>
@@ -6546,7 +6546,7 @@
         <v>11.5019998550415</v>
       </c>
       <c r="G213" t="n">
-        <v>10.8835859298706</v>
+        <v>10.8835849761963</v>
       </c>
       <c r="H213" t="n">
         <v>216641</v>
@@ -6575,7 +6575,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G214" t="n">
-        <v>10.5031995773315</v>
+        <v>10.5031986236572</v>
       </c>
       <c r="H214" t="n">
         <v>940630</v>
@@ -6691,7 +6691,7 @@
         <v>10.8739995956421</v>
       </c>
       <c r="G218" t="n">
-        <v>10.2893495559692</v>
+        <v>10.2893505096436</v>
       </c>
       <c r="H218" t="n">
         <v>223312</v>
@@ -6749,7 +6749,7 @@
         <v>10.9619998931885</v>
       </c>
       <c r="G220" t="n">
-        <v>10.3726196289062</v>
+        <v>10.3726186752319</v>
       </c>
       <c r="H220" t="n">
         <v>156811</v>
@@ -6807,7 +6807,7 @@
         <v>11.2340002059937</v>
       </c>
       <c r="G222" t="n">
-        <v>10.629994392395</v>
+        <v>10.6299934387207</v>
       </c>
       <c r="H222" t="n">
         <v>159090</v>
@@ -6865,7 +6865,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>11.2128753662109</v>
+        <v>11.2128744125366</v>
       </c>
       <c r="H224" t="n">
         <v>273187</v>
@@ -6894,7 +6894,7 @@
         <v>11.9340000152588</v>
       </c>
       <c r="G225" t="n">
-        <v>11.2923583984375</v>
+        <v>11.2923574447632</v>
       </c>
       <c r="H225" t="n">
         <v>1392941</v>
@@ -6981,7 +6981,7 @@
         <v>11</v>
       </c>
       <c r="G228" t="n">
-        <v>10.4085750579834</v>
+        <v>10.4085760116577</v>
       </c>
       <c r="H228" t="n">
         <v>808095</v>
@@ -7039,7 +7039,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G230" t="n">
-        <v>10.3896503448486</v>
+        <v>10.3896512985229</v>
       </c>
       <c r="H230" t="n">
         <v>475068</v>
@@ -7097,7 +7097,7 @@
         <v>11.0279998779297</v>
       </c>
       <c r="G232" t="n">
-        <v>10.4350690841675</v>
+        <v>10.4350700378418</v>
       </c>
       <c r="H232" t="n">
         <v>329462</v>
@@ -7126,7 +7126,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>10.5031995773315</v>
+        <v>10.5031986236572</v>
       </c>
       <c r="H233" t="n">
         <v>228150</v>
@@ -7155,7 +7155,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G234" t="n">
-        <v>10.5126609802246</v>
+        <v>10.5126600265503</v>
       </c>
       <c r="H234" t="n">
         <v>148165</v>
@@ -7213,7 +7213,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G236" t="n">
-        <v>10.2382535934448</v>
+        <v>10.2382526397705</v>
       </c>
       <c r="H236" t="n">
         <v>356369</v>
@@ -7271,7 +7271,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G238" t="n">
-        <v>10.2382535934448</v>
+        <v>10.2382526397705</v>
       </c>
       <c r="H238" t="n">
         <v>235729</v>
@@ -7329,7 +7329,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G240" t="n">
-        <v>10.0395450592041</v>
+        <v>10.0395441055298</v>
       </c>
       <c r="H240" t="n">
         <v>634447</v>
@@ -7358,7 +7358,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G241" t="n">
-        <v>10.0395450592041</v>
+        <v>10.0395441055298</v>
       </c>
       <c r="H241" t="n">
         <v>254072</v>
@@ -7387,7 +7387,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G242" t="n">
-        <v>10.1057806015015</v>
+        <v>10.1057815551758</v>
       </c>
       <c r="H242" t="n">
         <v>332984</v>
@@ -7445,7 +7445,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G244" t="n">
-        <v>10.0395450592041</v>
+        <v>10.0395441055298</v>
       </c>
       <c r="H244" t="n">
         <v>132610</v>
@@ -7532,7 +7532,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G247" t="n">
-        <v>9.90707206726074</v>
+        <v>9.90707111358643</v>
       </c>
       <c r="H247" t="n">
         <v>223084</v>
@@ -7735,7 +7735,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G254" t="n">
-        <v>9.99223327636719</v>
+        <v>9.99223232269287</v>
       </c>
       <c r="H254" t="n">
         <v>244328</v>
@@ -7793,7 +7793,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G256" t="n">
-        <v>10.3896503448486</v>
+        <v>10.3896512985229</v>
       </c>
       <c r="H256" t="n">
         <v>552393</v>
@@ -7909,7 +7909,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G260" t="n">
-        <v>10.2382535934448</v>
+        <v>10.2382526397705</v>
       </c>
       <c r="H260" t="n">
         <v>290152</v>
@@ -7967,7 +7967,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G262" t="n">
-        <v>10.2382535934448</v>
+        <v>10.2382526397705</v>
       </c>
       <c r="H262" t="n">
         <v>242006</v>
@@ -8083,7 +8083,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G266" t="n">
-        <v>10.1436309814453</v>
+        <v>10.143630027771</v>
       </c>
       <c r="H266" t="n">
         <v>192613</v>
@@ -8112,7 +8112,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G267" t="n">
-        <v>10.020619392395</v>
+        <v>10.0206203460693</v>
       </c>
       <c r="H267" t="n">
         <v>171371</v>
@@ -8141,7 +8141,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G268" t="n">
-        <v>10.0982227325439</v>
+        <v>10.0982236862183</v>
       </c>
       <c r="H268" t="n">
         <v>162147</v>
@@ -8344,7 +8344,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G275" t="n">
-        <v>10.3310346603394</v>
+        <v>10.3310356140137</v>
       </c>
       <c r="H275" t="n">
         <v>417991</v>
@@ -8576,7 +8576,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G283" t="n">
-        <v>10.6220502853394</v>
+        <v>10.6220512390137</v>
       </c>
       <c r="H283" t="n">
         <v>129742</v>
@@ -8634,7 +8634,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G285" t="n">
-        <v>10.5638484954834</v>
+        <v>10.5638475418091</v>
       </c>
       <c r="H285" t="n">
         <v>180726</v>
@@ -8692,7 +8692,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G287" t="n">
-        <v>10.2534313201904</v>
+        <v>10.2534303665161</v>
       </c>
       <c r="H287" t="n">
         <v>235286</v>
@@ -8721,7 +8721,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G288" t="n">
-        <v>10.3116340637207</v>
+        <v>10.311635017395</v>
       </c>
       <c r="H288" t="n">
         <v>127440</v>
@@ -8779,7 +8779,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G290" t="n">
-        <v>10.4377412796021</v>
+        <v>10.4377422332764</v>
       </c>
       <c r="H290" t="n">
         <v>97733</v>
@@ -8895,7 +8895,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G294" t="n">
-        <v>10.806360244751</v>
+        <v>10.8063611984253</v>
       </c>
       <c r="H294" t="n">
         <v>209159</v>
@@ -8982,7 +8982,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G297" t="n">
-        <v>10.951868057251</v>
+        <v>10.9518671035767</v>
       </c>
       <c r="H297" t="n">
         <v>175726</v>
@@ -9011,7 +9011,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G298" t="n">
-        <v>10.7578582763672</v>
+        <v>10.7578573226929</v>
       </c>
       <c r="H298" t="n">
         <v>301876</v>
@@ -9214,7 +9214,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G305" t="n">
-        <v>11.5823993682861</v>
+        <v>11.5824003219604</v>
       </c>
       <c r="H305" t="n">
         <v>274687</v>
@@ -9475,7 +9475,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G314" t="n">
-        <v>11.3398866653442</v>
+        <v>11.3398876190186</v>
       </c>
       <c r="H314" t="n">
         <v>110179</v>
@@ -9562,7 +9562,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G317" t="n">
-        <v>11.2525844573975</v>
+        <v>11.2525835037231</v>
       </c>
       <c r="H317" t="n">
         <v>381622</v>
@@ -9649,7 +9649,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G320" t="n">
-        <v>10.951868057251</v>
+        <v>10.9518671035767</v>
       </c>
       <c r="H320" t="n">
         <v>279934</v>
@@ -9707,7 +9707,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G322" t="n">
-        <v>10.9712696075439</v>
+        <v>10.9712686538696</v>
       </c>
       <c r="H322" t="n">
         <v>185383</v>
@@ -9765,7 +9765,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G324" t="n">
-        <v>10.7481575012207</v>
+        <v>10.7481565475464</v>
       </c>
       <c r="H324" t="n">
         <v>184196</v>
@@ -9852,7 +9852,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>10.7190551757812</v>
+        <v>10.7190561294556</v>
       </c>
       <c r="H327" t="n">
         <v>80274</v>
@@ -9881,7 +9881,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G328" t="n">
-        <v>10.7578582763672</v>
+        <v>10.7578573226929</v>
       </c>
       <c r="H328" t="n">
         <v>81593</v>
@@ -9910,7 +9910,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>10.8160600662231</v>
+        <v>10.8160610198975</v>
       </c>
       <c r="H329" t="n">
         <v>255497</v>
@@ -10055,7 +10055,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G334" t="n">
-        <v>11.1361770629883</v>
+        <v>11.136176109314</v>
       </c>
       <c r="H334" t="n">
         <v>92993</v>
@@ -10084,7 +10084,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G335" t="n">
-        <v>11.1361770629883</v>
+        <v>11.136176109314</v>
       </c>
       <c r="H335" t="n">
         <v>109603</v>
@@ -10258,7 +10258,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G341" t="n">
-        <v>11.4077911376953</v>
+        <v>11.4077920913696</v>
       </c>
       <c r="H341" t="n">
         <v>275168</v>
@@ -10374,7 +10374,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G345" t="n">
-        <v>10.9712696075439</v>
+        <v>10.9712686538696</v>
       </c>
       <c r="H345" t="n">
         <v>250890</v>
@@ -10403,7 +10403,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G346" t="n">
-        <v>10.9615688323975</v>
+        <v>10.9615678787231</v>
       </c>
       <c r="H346" t="n">
         <v>157159</v>
@@ -10432,7 +10432,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G347" t="n">
-        <v>11.0003700256348</v>
+        <v>11.0003709793091</v>
       </c>
       <c r="H347" t="n">
         <v>187467</v>
@@ -10461,7 +10461,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G348" t="n">
-        <v>11.0003700256348</v>
+        <v>11.0003709793091</v>
       </c>
       <c r="H348" t="n">
         <v>109481</v>
@@ -10722,7 +10722,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G357" t="n">
-        <v>11.0585737228394</v>
+        <v>11.058572769165</v>
       </c>
       <c r="H357" t="n">
         <v>184343</v>
@@ -10780,7 +10780,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G359" t="n">
-        <v>11.0003700256348</v>
+        <v>11.0003709793091</v>
       </c>
       <c r="H359" t="n">
         <v>186510</v>
@@ -10867,7 +10867,7 @@
         <v>11.25</v>
       </c>
       <c r="G362" t="n">
-        <v>10.913064956665</v>
+        <v>10.9130659103394</v>
       </c>
       <c r="H362" t="n">
         <v>440278</v>
@@ -10925,7 +10925,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G364" t="n">
-        <v>11.1458778381348</v>
+        <v>11.1458768844604</v>
       </c>
       <c r="H364" t="n">
         <v>188007</v>
@@ -11012,7 +11012,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>11.0585737228394</v>
+        <v>11.058572769165</v>
       </c>
       <c r="H367" t="n">
         <v>195723</v>
@@ -11070,7 +11070,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G369" t="n">
-        <v>11.1458778381348</v>
+        <v>11.1458768844604</v>
       </c>
       <c r="H369" t="n">
         <v>107932</v>
@@ -11128,7 +11128,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G371" t="n">
-        <v>11.1361770629883</v>
+        <v>11.136176109314</v>
       </c>
       <c r="H371" t="n">
         <v>118399</v>
@@ -11186,7 +11186,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G373" t="n">
-        <v>11.0197706222534</v>
+        <v>11.0197715759277</v>
       </c>
       <c r="H373" t="n">
         <v>147161</v>
@@ -11302,7 +11302,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G377" t="n">
-        <v>11.0197706222534</v>
+        <v>11.0197715759277</v>
       </c>
       <c r="H377" t="n">
         <v>130368</v>
@@ -11476,7 +11476,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G383" t="n">
-        <v>11.1361770629883</v>
+        <v>11.136176109314</v>
       </c>
       <c r="H383" t="n">
         <v>194313</v>
@@ -11592,7 +11592,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G387" t="n">
-        <v>11.1749792098999</v>
+        <v>11.1749801635742</v>
       </c>
       <c r="H387" t="n">
         <v>197901</v>
@@ -11650,7 +11650,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G389" t="n">
-        <v>11.4465942382812</v>
+        <v>11.4465932846069</v>
       </c>
       <c r="H389" t="n">
         <v>259214</v>
@@ -11737,7 +11737,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G392" t="n">
-        <v>11.8540153503418</v>
+        <v>11.8540143966675</v>
       </c>
       <c r="H392" t="n">
         <v>194096</v>
@@ -11795,7 +11795,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G394" t="n">
-        <v>11.6988067626953</v>
+        <v>11.6988077163696</v>
       </c>
       <c r="H394" t="n">
         <v>171327</v>
@@ -11911,7 +11911,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G398" t="n">
-        <v>11.6309032440186</v>
+        <v>11.6309022903442</v>
       </c>
       <c r="H398" t="n">
         <v>192088</v>
@@ -11940,7 +11940,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G399" t="n">
-        <v>11.5823993682861</v>
+        <v>11.5824003219604</v>
       </c>
       <c r="H399" t="n">
         <v>137161</v>
@@ -12056,7 +12056,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G403" t="n">
-        <v>12.1935319900513</v>
+        <v>12.193531036377</v>
       </c>
       <c r="H403" t="n">
         <v>108069</v>
@@ -12114,7 +12114,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G405" t="n">
-        <v>12.1935319900513</v>
+        <v>12.193531036377</v>
       </c>
       <c r="H405" t="n">
         <v>135114</v>
@@ -12172,7 +12172,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G407" t="n">
-        <v>12.2226333618164</v>
+        <v>12.2226343154907</v>
       </c>
       <c r="H407" t="n">
         <v>185001</v>
@@ -12201,7 +12201,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G408" t="n">
-        <v>12.2517347335815</v>
+        <v>12.2517356872559</v>
       </c>
       <c r="H408" t="n">
         <v>172512</v>
@@ -12288,7 +12288,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G411" t="n">
-        <v>12.4651460647583</v>
+        <v>12.4651470184326</v>
       </c>
       <c r="H411" t="n">
         <v>133030</v>
@@ -12317,7 +12317,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G412" t="n">
-        <v>12.3875427246094</v>
+        <v>12.3875417709351</v>
       </c>
       <c r="H412" t="n">
         <v>148541</v>
@@ -12520,7 +12520,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G419" t="n">
-        <v>12.2517347335815</v>
+        <v>12.2517356872559</v>
       </c>
       <c r="H419" t="n">
         <v>165954</v>
@@ -12549,7 +12549,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G420" t="n">
-        <v>12.2226333618164</v>
+        <v>12.2226343154907</v>
       </c>
       <c r="H420" t="n">
         <v>258706</v>
@@ -12607,7 +12607,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G422" t="n">
-        <v>12.2129335403442</v>
+        <v>12.2129325866699</v>
       </c>
       <c r="H422" t="n">
         <v>137376</v>
@@ -12636,7 +12636,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G423" t="n">
-        <v>12.3875427246094</v>
+        <v>12.3875417709351</v>
       </c>
       <c r="H423" t="n">
         <v>99466</v>
@@ -12723,7 +12723,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G426" t="n">
-        <v>12.5427513122559</v>
+        <v>12.5427503585815</v>
       </c>
       <c r="H426" t="n">
         <v>197307</v>
@@ -12752,7 +12752,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G427" t="n">
-        <v>12.630054473877</v>
+        <v>12.6300554275513</v>
       </c>
       <c r="H427" t="n">
         <v>148262</v>
@@ -12839,7 +12839,7 @@
         <v>13</v>
       </c>
       <c r="G430" t="n">
-        <v>12.610652923584</v>
+        <v>12.6106538772583</v>
       </c>
       <c r="H430" t="n">
         <v>1807764</v>
@@ -12897,7 +12897,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G432" t="n">
-        <v>12.3972425460815</v>
+        <v>12.3972415924072</v>
       </c>
       <c r="H432" t="n">
         <v>1234024</v>
@@ -12955,7 +12955,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G434" t="n">
-        <v>12.6882581710815</v>
+        <v>12.6882572174072</v>
       </c>
       <c r="H434" t="n">
         <v>465320</v>
@@ -13013,7 +13013,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G436" t="n">
-        <v>13.1538820266724</v>
+        <v>13.1538829803467</v>
       </c>
       <c r="H436" t="n">
         <v>425963</v>
@@ -13274,7 +13274,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G445" t="n">
-        <v>13.7844152450562</v>
+        <v>13.7844142913818</v>
       </c>
       <c r="H445" t="n">
         <v>236771</v>
@@ -13303,7 +13303,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G446" t="n">
-        <v>14.3373432159424</v>
+        <v>14.3373422622681</v>
       </c>
       <c r="H446" t="n">
         <v>473165</v>
@@ -13332,7 +13332,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G447" t="n">
-        <v>14.4537496566772</v>
+        <v>14.4537487030029</v>
       </c>
       <c r="H447" t="n">
         <v>380386</v>
@@ -13361,7 +13361,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G448" t="n">
-        <v>14.667160987854</v>
+        <v>14.6671600341797</v>
       </c>
       <c r="H448" t="n">
         <v>267462</v>
@@ -13419,7 +13419,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G450" t="n">
-        <v>14.8029670715332</v>
+        <v>14.8029680252075</v>
       </c>
       <c r="H450" t="n">
         <v>391347</v>
@@ -13622,7 +13622,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G457" t="n">
-        <v>16.0446338653564</v>
+        <v>16.0446319580078</v>
       </c>
       <c r="H457" t="n">
         <v>378598</v>
@@ -13680,7 +13680,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G459" t="n">
-        <v>15.9573268890381</v>
+        <v>15.9573278427124</v>
       </c>
       <c r="H459" t="n">
         <v>261224</v>
@@ -13796,7 +13796,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G463" t="n">
-        <v>16.0252304077148</v>
+        <v>16.0252323150635</v>
       </c>
       <c r="H463" t="n">
         <v>392686</v>
@@ -13825,7 +13825,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G464" t="n">
-        <v>15.6857128143311</v>
+        <v>15.6857137680054</v>
       </c>
       <c r="H464" t="n">
         <v>532461</v>
@@ -14028,7 +14028,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G471" t="n">
-        <v>15.870023727417</v>
+        <v>15.8700227737427</v>
       </c>
       <c r="H471" t="n">
         <v>880362</v>
@@ -14115,7 +14115,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G474" t="n">
-        <v>16.9273796081543</v>
+        <v>16.9273777008057</v>
       </c>
       <c r="H474" t="n">
         <v>620043</v>
@@ -14260,7 +14260,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G479" t="n">
-        <v>17.5870094299316</v>
+        <v>17.5870113372803</v>
       </c>
       <c r="H479" t="n">
         <v>473621</v>
@@ -14289,7 +14289,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G480" t="n">
-        <v>17.5870094299316</v>
+        <v>17.5870113372803</v>
       </c>
       <c r="H480" t="n">
         <v>417252</v>
@@ -14347,7 +14347,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G482" t="n">
-        <v>17.1601886749268</v>
+        <v>17.1601905822754</v>
       </c>
       <c r="H482" t="n">
         <v>353508</v>
@@ -14405,7 +14405,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G484" t="n">
-        <v>17.7519187927246</v>
+        <v>17.7519207000732</v>
       </c>
       <c r="H484" t="n">
         <v>342388</v>
@@ -14434,7 +14434,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G485" t="n">
-        <v>17.7422218322754</v>
+        <v>17.7422199249268</v>
       </c>
       <c r="H485" t="n">
         <v>271126</v>
@@ -14521,7 +14521,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G488" t="n">
-        <v>17.9071292877197</v>
+        <v>17.9071273803711</v>
       </c>
       <c r="H488" t="n">
         <v>372109</v>
@@ -14550,7 +14550,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G489" t="n">
-        <v>18.3727531433105</v>
+        <v>18.3727512359619</v>
       </c>
       <c r="H489" t="n">
         <v>455016</v>
@@ -14608,7 +14608,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>16.8303718566895</v>
+        <v>16.8303737640381</v>
       </c>
       <c r="H491" t="n">
         <v>1164243</v>
@@ -14695,7 +14695,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G494" t="n">
-        <v>17.1601886749268</v>
+        <v>17.1601905822754</v>
       </c>
       <c r="H494" t="n">
         <v>564420</v>
@@ -14898,7 +14898,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G501" t="n">
-        <v>18.8480777740479</v>
+        <v>18.8480758666992</v>
       </c>
       <c r="H501" t="n">
         <v>377971</v>
@@ -14927,7 +14927,7 @@
         <v>19.4699993133545</v>
       </c>
       <c r="G502" t="n">
-        <v>18.8868789672852</v>
+        <v>18.8868770599365</v>
       </c>
       <c r="H502" t="n">
         <v>436832</v>
@@ -14956,7 +14956,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G503" t="n">
-        <v>19.0226860046387</v>
+        <v>19.0226879119873</v>
       </c>
       <c r="H503" t="n">
         <v>218294</v>
@@ -15014,7 +15014,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G505" t="n">
-        <v>19.478609085083</v>
+        <v>19.4786109924316</v>
       </c>
       <c r="H505" t="n">
         <v>375456</v>
@@ -15043,7 +15043,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G506" t="n">
-        <v>19.45920753479</v>
+        <v>19.4592094421387</v>
       </c>
       <c r="H506" t="n">
         <v>430857</v>
@@ -15072,7 +15072,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G507" t="n">
-        <v>19.4398097991943</v>
+        <v>19.4398078918457</v>
       </c>
       <c r="H507" t="n">
         <v>573705</v>
@@ -15130,7 +15130,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G509" t="n">
-        <v>20.3128547668457</v>
+        <v>20.3128528594971</v>
       </c>
       <c r="H509" t="n">
         <v>845381</v>
@@ -15159,7 +15159,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G510" t="n">
-        <v>20.2352485656738</v>
+        <v>20.2352504730225</v>
       </c>
       <c r="H510" t="n">
         <v>628106</v>
@@ -15188,7 +15188,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G511" t="n">
-        <v>19.9248352050781</v>
+        <v>19.9248332977295</v>
       </c>
       <c r="H511" t="n">
         <v>774008</v>
@@ -15217,7 +15217,7 @@
         <v>20</v>
       </c>
       <c r="G512" t="n">
-        <v>19.4010066986084</v>
+        <v>19.4010047912598</v>
       </c>
       <c r="H512" t="n">
         <v>769373</v>
@@ -15304,7 +15304,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>21.6321201324463</v>
+        <v>21.6321220397949</v>
       </c>
       <c r="H515" t="n">
         <v>2197577</v>
@@ -15362,7 +15362,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G517" t="n">
-        <v>22.1171474456787</v>
+        <v>22.1171455383301</v>
       </c>
       <c r="H517" t="n">
         <v>555528</v>
@@ -15391,7 +15391,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G518" t="n">
-        <v>21.9619369506836</v>
+        <v>21.9619388580322</v>
       </c>
       <c r="H518" t="n">
         <v>611058</v>
@@ -25866,6 +25866,64 @@
         <v>940799</v>
       </c>
       <c r="I879" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="s">
+        <v>9</v>
+      </c>
+      <c r="B880" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C880" t="n">
+        <v>24.1100006103516</v>
+      </c>
+      <c r="D880" t="n">
+        <v>24.1100006103516</v>
+      </c>
+      <c r="E880" t="n">
+        <v>23.6399993896484</v>
+      </c>
+      <c r="F880" t="n">
+        <v>23.9699993133545</v>
+      </c>
+      <c r="G880" t="n">
+        <v>23.9699993133545</v>
+      </c>
+      <c r="H880" t="n">
+        <v>667192</v>
+      </c>
+      <c r="I880" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="s">
+        <v>9</v>
+      </c>
+      <c r="B881" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C881" t="n">
+        <v>23.9099998474121</v>
+      </c>
+      <c r="D881" t="n">
+        <v>24.2099990844727</v>
+      </c>
+      <c r="E881" t="n">
+        <v>23.7600002288818</v>
+      </c>
+      <c r="F881" t="n">
+        <v>24.2000007629395</v>
+      </c>
+      <c r="G881" t="n">
+        <v>24.2000007629395</v>
+      </c>
+      <c r="H881" t="n">
+        <v>634512</v>
+      </c>
+      <c r="I881" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LTMC.MI.xlsx
+++ b/data/LTMC.MI.xlsx
@@ -427,7 +427,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2" t="n">
-        <v>7.75912046432495</v>
+        <v>7.75911998748779</v>
       </c>
       <c r="H2" t="n">
         <v>13006120</v>
@@ -543,7 +543,7 @@
         <v>8.59099960327148</v>
       </c>
       <c r="G6" t="n">
-        <v>8.12909698486328</v>
+        <v>8.1290979385376</v>
       </c>
       <c r="H6" t="n">
         <v>974676</v>
@@ -630,7 +630,7 @@
         <v>8.25</v>
       </c>
       <c r="G9" t="n">
-        <v>7.80643177032471</v>
+        <v>7.80643224716187</v>
       </c>
       <c r="H9" t="n">
         <v>1073912</v>
@@ -659,7 +659,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G10" t="n">
-        <v>7.99567794799805</v>
+        <v>7.99567890167236</v>
       </c>
       <c r="H10" t="n">
         <v>1947465</v>
@@ -833,7 +833,7 @@
         <v>7.86899995803833</v>
       </c>
       <c r="G16" t="n">
-        <v>7.44591665267944</v>
+        <v>7.44591617584229</v>
       </c>
       <c r="H16" t="n">
         <v>479599</v>
@@ -949,7 +949,7 @@
         <v>7.80100011825562</v>
       </c>
       <c r="G20" t="n">
-        <v>7.38157224655151</v>
+        <v>7.38157272338867</v>
       </c>
       <c r="H20" t="n">
         <v>40924</v>
@@ -1007,7 +1007,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G22" t="n">
-        <v>7.03525066375732</v>
+        <v>7.03525114059448</v>
       </c>
       <c r="H22" t="n">
         <v>597512</v>
@@ -1094,7 +1094,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G25" t="n">
-        <v>7.28600311279297</v>
+        <v>7.28600263595581</v>
       </c>
       <c r="H25" t="n">
         <v>218758</v>
@@ -1210,7 +1210,7 @@
         <v>8.52200031280518</v>
       </c>
       <c r="G29" t="n">
-        <v>8.06380748748779</v>
+        <v>8.06380844116211</v>
       </c>
       <c r="H29" t="n">
         <v>1531238</v>
@@ -1268,7 +1268,7 @@
         <v>8.23200035095215</v>
       </c>
       <c r="G31" t="n">
-        <v>7.78939962387085</v>
+        <v>7.78940010070801</v>
       </c>
       <c r="H31" t="n">
         <v>749433</v>
@@ -1297,7 +1297,7 @@
         <v>8.16199970245361</v>
       </c>
       <c r="G32" t="n">
-        <v>7.72316360473633</v>
+        <v>7.72316312789917</v>
       </c>
       <c r="H32" t="n">
         <v>440552</v>
@@ -1413,7 +1413,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G36" t="n">
-        <v>7.8111629486084</v>
+        <v>7.81116247177124</v>
       </c>
       <c r="H36" t="n">
         <v>219714</v>
@@ -1471,7 +1471,7 @@
         <v>8.4379997253418</v>
       </c>
       <c r="G38" t="n">
-        <v>7.98432350158691</v>
+        <v>7.98432397842407</v>
       </c>
       <c r="H38" t="n">
         <v>178091</v>
@@ -1703,7 +1703,7 @@
         <v>8.69499969482422</v>
       </c>
       <c r="G46" t="n">
-        <v>8.22750663757324</v>
+        <v>8.22750568389893</v>
       </c>
       <c r="H46" t="n">
         <v>188291</v>
@@ -1732,7 +1732,7 @@
         <v>8.58300018310547</v>
       </c>
       <c r="G47" t="n">
-        <v>8.12152862548828</v>
+        <v>8.12152767181396</v>
       </c>
       <c r="H47" t="n">
         <v>162361</v>
@@ -1761,7 +1761,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G48" t="n">
-        <v>7.9436354637146</v>
+        <v>7.94363641738892</v>
       </c>
       <c r="H48" t="n">
         <v>297588</v>
@@ -1819,7 +1819,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G50" t="n">
-        <v>8.49718284606934</v>
+        <v>8.49718189239502</v>
       </c>
       <c r="H50" t="n">
         <v>475388</v>
@@ -1877,7 +1877,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G52" t="n">
-        <v>8.7905158996582</v>
+        <v>8.79051494598389</v>
       </c>
       <c r="H52" t="n">
         <v>1027347</v>
@@ -1906,7 +1906,7 @@
         <v>9.4689998626709</v>
       </c>
       <c r="G53" t="n">
-        <v>8.9598913192749</v>
+        <v>8.95989036560059</v>
       </c>
       <c r="H53" t="n">
         <v>1003139</v>
@@ -2080,7 +2080,7 @@
         <v>9.27099990844727</v>
       </c>
       <c r="G59" t="n">
-        <v>8.772536277771</v>
+        <v>8.77253723144531</v>
       </c>
       <c r="H59" t="n">
         <v>287274</v>
@@ -2167,7 +2167,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G62" t="n">
-        <v>8.65804195404053</v>
+        <v>8.65804290771484</v>
       </c>
       <c r="H62" t="n">
         <v>407302</v>
@@ -2196,7 +2196,7 @@
         <v>9.17800045013428</v>
       </c>
       <c r="G63" t="n">
-        <v>8.68453788757324</v>
+        <v>8.68453693389893</v>
       </c>
       <c r="H63" t="n">
         <v>254936</v>
@@ -2254,7 +2254,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G65" t="n">
-        <v>8.9419116973877</v>
+        <v>8.94191265106201</v>
       </c>
       <c r="H65" t="n">
         <v>900757</v>
@@ -2312,7 +2312,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G67" t="n">
-        <v>8.82363319396973</v>
+        <v>8.82363224029541</v>
       </c>
       <c r="H67" t="n">
         <v>266872</v>
@@ -2399,7 +2399,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G70" t="n">
-        <v>8.87567710876465</v>
+        <v>8.87567615509033</v>
       </c>
       <c r="H70" t="n">
         <v>257403</v>
@@ -2457,7 +2457,7 @@
         <v>9.31900024414062</v>
       </c>
       <c r="G72" t="n">
-        <v>8.81795692443848</v>
+        <v>8.81795597076416</v>
       </c>
       <c r="H72" t="n">
         <v>303822</v>
@@ -2515,7 +2515,7 @@
         <v>9.14700031280518</v>
       </c>
       <c r="G74" t="n">
-        <v>8.65520286560059</v>
+        <v>8.6552038192749</v>
       </c>
       <c r="H74" t="n">
         <v>250420</v>
@@ -2689,7 +2689,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G80" t="n">
-        <v>8.67696762084961</v>
+        <v>8.67696666717529</v>
       </c>
       <c r="H80" t="n">
         <v>180085</v>
@@ -2805,7 +2805,7 @@
         <v>9.39200019836426</v>
       </c>
       <c r="G84" t="n">
-        <v>8.88703155517578</v>
+        <v>8.88703060150146</v>
       </c>
       <c r="H84" t="n">
         <v>248541</v>
@@ -2979,7 +2979,7 @@
         <v>9.17899990081787</v>
       </c>
       <c r="G90" t="n">
-        <v>8.6854829788208</v>
+        <v>8.68548393249512</v>
       </c>
       <c r="H90" t="n">
         <v>216140</v>
@@ -3124,7 +3124,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G95" t="n">
-        <v>8.53503322601318</v>
+        <v>8.53503227233887</v>
       </c>
       <c r="H95" t="n">
         <v>212825</v>
@@ -3182,7 +3182,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>8.67696762084961</v>
+        <v>8.67696666717529</v>
       </c>
       <c r="H97" t="n">
         <v>420414</v>
@@ -3298,7 +3298,7 @@
         <v>9.01900005340576</v>
       </c>
       <c r="G101" t="n">
-        <v>8.53408622741699</v>
+        <v>8.53408527374268</v>
       </c>
       <c r="H101" t="n">
         <v>120168</v>
@@ -3327,7 +3327,7 @@
         <v>8.89700031280518</v>
       </c>
       <c r="G102" t="n">
-        <v>8.41864490509033</v>
+        <v>8.41864585876465</v>
       </c>
       <c r="H102" t="n">
         <v>170277</v>
@@ -3530,7 +3530,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G109" t="n">
-        <v>8.27008628845215</v>
+        <v>8.27008724212646</v>
       </c>
       <c r="H109" t="n">
         <v>186396</v>
@@ -3559,7 +3559,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G110" t="n">
-        <v>8.37417221069336</v>
+        <v>8.37417316436768</v>
       </c>
       <c r="H110" t="n">
         <v>209809</v>
@@ -3762,7 +3762,7 @@
         <v>8.85400009155273</v>
       </c>
       <c r="G117" t="n">
-        <v>8.37795734405518</v>
+        <v>8.37795829772949</v>
       </c>
       <c r="H117" t="n">
         <v>105095</v>
@@ -3820,7 +3820,7 @@
         <v>8.7209997177124</v>
       </c>
       <c r="G119" t="n">
-        <v>8.25210857391357</v>
+        <v>8.25210762023926</v>
       </c>
       <c r="H119" t="n">
         <v>127697</v>
@@ -3849,7 +3849,7 @@
         <v>8.75</v>
       </c>
       <c r="G120" t="n">
-        <v>8.27954864501953</v>
+        <v>8.27954959869385</v>
       </c>
       <c r="H120" t="n">
         <v>97384</v>
@@ -4052,7 +4052,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G127" t="n">
-        <v>8.37417221069336</v>
+        <v>8.37417316436768</v>
       </c>
       <c r="H127" t="n">
         <v>102561</v>
@@ -4081,7 +4081,7 @@
         <v>8.82100009918213</v>
       </c>
       <c r="G128" t="n">
-        <v>8.3467321395874</v>
+        <v>8.34673118591309</v>
       </c>
       <c r="H128" t="n">
         <v>174329</v>
@@ -4139,7 +4139,7 @@
         <v>8.93599987030029</v>
       </c>
       <c r="G130" t="n">
-        <v>8.45554733276367</v>
+        <v>8.45554828643799</v>
       </c>
       <c r="H130" t="n">
         <v>394314</v>
@@ -4168,7 +4168,7 @@
         <v>9.03800010681152</v>
       </c>
       <c r="G131" t="n">
-        <v>8.55206394195557</v>
+        <v>8.55206489562988</v>
       </c>
       <c r="H131" t="n">
         <v>165794</v>
@@ -4226,7 +4226,7 @@
         <v>9.22200012207031</v>
       </c>
       <c r="G133" t="n">
-        <v>8.72617053985596</v>
+        <v>8.72617149353027</v>
       </c>
       <c r="H133" t="n">
         <v>178676</v>
@@ -4284,7 +4284,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G135" t="n">
-        <v>8.612624168396</v>
+        <v>8.61262321472168</v>
       </c>
       <c r="H135" t="n">
         <v>75451</v>
@@ -4313,7 +4313,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G136" t="n">
-        <v>8.53503322601318</v>
+        <v>8.53503227233887</v>
       </c>
       <c r="H136" t="n">
         <v>172542</v>
@@ -4342,7 +4342,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G137" t="n">
-        <v>8.612624168396</v>
+        <v>8.61262321472168</v>
       </c>
       <c r="H137" t="n">
         <v>197102</v>
@@ -4603,7 +4603,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G146" t="n">
-        <v>8.81890296936035</v>
+        <v>8.81890201568604</v>
       </c>
       <c r="H146" t="n">
         <v>95465</v>
@@ -4719,7 +4719,7 @@
         <v>9.45199966430664</v>
       </c>
       <c r="G150" t="n">
-        <v>8.94380474090576</v>
+        <v>8.94380569458008</v>
       </c>
       <c r="H150" t="n">
         <v>141690</v>
@@ -4835,7 +4835,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G154" t="n">
-        <v>8.96083736419678</v>
+        <v>8.96083641052246</v>
       </c>
       <c r="H154" t="n">
         <v>127739</v>
@@ -4922,7 +4922,7 @@
         <v>9.60900020599365</v>
       </c>
       <c r="G157" t="n">
-        <v>9.09236335754395</v>
+        <v>9.09236431121826</v>
       </c>
       <c r="H157" t="n">
         <v>302816</v>
@@ -5038,7 +5038,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G161" t="n">
-        <v>8.9419116973877</v>
+        <v>8.94191265106201</v>
       </c>
       <c r="H161" t="n">
         <v>242695</v>
@@ -5154,7 +5154,7 @@
         <v>9.80599975585938</v>
       </c>
       <c r="G165" t="n">
-        <v>9.27877235412598</v>
+        <v>9.27877140045166</v>
       </c>
       <c r="H165" t="n">
         <v>183228</v>
@@ -5212,7 +5212,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G167" t="n">
-        <v>9.32040691375732</v>
+        <v>9.32040786743164</v>
       </c>
       <c r="H167" t="n">
         <v>175516</v>
@@ -5270,7 +5270,7 @@
         <v>9.84700012207031</v>
       </c>
       <c r="G169" t="n">
-        <v>9.31756687164307</v>
+        <v>9.31756782531738</v>
       </c>
       <c r="H169" t="n">
         <v>94635</v>
@@ -5299,7 +5299,7 @@
         <v>9.7819995880127</v>
       </c>
       <c r="G170" t="n">
-        <v>9.25606250762939</v>
+        <v>9.25606155395508</v>
       </c>
       <c r="H170" t="n">
         <v>59025</v>
@@ -5415,7 +5415,7 @@
         <v>9.6230001449585</v>
       </c>
       <c r="G174" t="n">
-        <v>9.10561180114746</v>
+        <v>9.10561084747314</v>
       </c>
       <c r="H174" t="n">
         <v>254745</v>
@@ -5676,7 +5676,7 @@
         <v>10.4580001831055</v>
       </c>
       <c r="G183" t="n">
-        <v>9.89571666717529</v>
+        <v>9.89571762084961</v>
       </c>
       <c r="H183" t="n">
         <v>362012</v>
@@ -5705,7 +5705,7 @@
         <v>10.1619997024536</v>
       </c>
       <c r="G184" t="n">
-        <v>9.61563014984131</v>
+        <v>9.61563110351562</v>
       </c>
       <c r="H184" t="n">
         <v>2039385</v>
@@ -5792,7 +5792,7 @@
         <v>10.6339998245239</v>
       </c>
       <c r="G187" t="n">
-        <v>10.0622529983521</v>
+        <v>10.0622539520264</v>
       </c>
       <c r="H187" t="n">
         <v>279044</v>
@@ -5937,7 +5937,7 @@
         <v>10.7720003128052</v>
       </c>
       <c r="G192" t="n">
-        <v>10.192834854126</v>
+        <v>10.1928339004517</v>
       </c>
       <c r="H192" t="n">
         <v>183949</v>
@@ -5966,7 +5966,7 @@
         <v>10.7440004348755</v>
       </c>
       <c r="G193" t="n">
-        <v>10.1663398742676</v>
+        <v>10.1663408279419</v>
       </c>
       <c r="H193" t="n">
         <v>138082</v>
@@ -6082,7 +6082,7 @@
         <v>11.0480003356934</v>
       </c>
       <c r="G197" t="n">
-        <v>10.4539947509766</v>
+        <v>10.4539957046509</v>
       </c>
       <c r="H197" t="n">
         <v>281143</v>
@@ -6111,7 +6111,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G198" t="n">
-        <v>10.4842748641968</v>
+        <v>10.4842739105225</v>
       </c>
       <c r="H198" t="n">
         <v>255451</v>
@@ -6198,7 +6198,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G201" t="n">
-        <v>10.5788984298706</v>
+        <v>10.5788974761963</v>
       </c>
       <c r="H201" t="n">
         <v>211395</v>
@@ -6285,7 +6285,7 @@
         <v>11.2040004730225</v>
       </c>
       <c r="G204" t="n">
-        <v>10.6016082763672</v>
+        <v>10.6016073226929</v>
       </c>
       <c r="H204" t="n">
         <v>94315</v>
@@ -6430,7 +6430,7 @@
         <v>11.5579996109009</v>
       </c>
       <c r="G209" t="n">
-        <v>10.9365739822388</v>
+        <v>10.9365749359131</v>
       </c>
       <c r="H209" t="n">
         <v>170731</v>
@@ -6604,7 +6604,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G215" t="n">
-        <v>10.7870693206787</v>
+        <v>10.7870683670044</v>
       </c>
       <c r="H215" t="n">
         <v>622398</v>
@@ -6662,7 +6662,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G217" t="n">
-        <v>10.4369630813599</v>
+        <v>10.4369621276855</v>
       </c>
       <c r="H217" t="n">
         <v>269996</v>
@@ -6691,7 +6691,7 @@
         <v>10.8739995956421</v>
       </c>
       <c r="G218" t="n">
-        <v>10.2893505096436</v>
+        <v>10.2893495559692</v>
       </c>
       <c r="H218" t="n">
         <v>223312</v>
@@ -6720,7 +6720,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G219" t="n">
-        <v>10.266640663147</v>
+        <v>10.2666416168213</v>
       </c>
       <c r="H219" t="n">
         <v>238286</v>
@@ -6749,7 +6749,7 @@
         <v>10.9619998931885</v>
       </c>
       <c r="G220" t="n">
-        <v>10.3726186752319</v>
+        <v>10.3726196289062</v>
       </c>
       <c r="H220" t="n">
         <v>156811</v>
@@ -6807,7 +6807,7 @@
         <v>11.2340002059937</v>
       </c>
       <c r="G222" t="n">
-        <v>10.6299934387207</v>
+        <v>10.629994392395</v>
       </c>
       <c r="H222" t="n">
         <v>159090</v>
@@ -6865,7 +6865,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>11.2128744125366</v>
+        <v>11.2128753662109</v>
       </c>
       <c r="H224" t="n">
         <v>273187</v>
@@ -6894,7 +6894,7 @@
         <v>11.9340000152588</v>
       </c>
       <c r="G225" t="n">
-        <v>11.2923574447632</v>
+        <v>11.2923583984375</v>
       </c>
       <c r="H225" t="n">
         <v>1392941</v>
@@ -7039,7 +7039,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G230" t="n">
-        <v>10.3896512985229</v>
+        <v>10.3896503448486</v>
       </c>
       <c r="H230" t="n">
         <v>475068</v>
@@ -7068,7 +7068,7 @@
         <v>10.96399974823</v>
       </c>
       <c r="G231" t="n">
-        <v>10.3745107650757</v>
+        <v>10.37451171875</v>
       </c>
       <c r="H231" t="n">
         <v>204899</v>
@@ -7155,7 +7155,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G234" t="n">
-        <v>10.5126600265503</v>
+        <v>10.5126609802246</v>
       </c>
       <c r="H234" t="n">
         <v>148165</v>
@@ -7213,7 +7213,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G236" t="n">
-        <v>10.2382526397705</v>
+        <v>10.2382535934448</v>
       </c>
       <c r="H236" t="n">
         <v>356369</v>
@@ -7242,7 +7242,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>10.266640663147</v>
+        <v>10.2666416168213</v>
       </c>
       <c r="H237" t="n">
         <v>250841</v>
@@ -7271,7 +7271,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G238" t="n">
-        <v>10.2382526397705</v>
+        <v>10.2382535934448</v>
       </c>
       <c r="H238" t="n">
         <v>235729</v>
@@ -7387,7 +7387,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G242" t="n">
-        <v>10.1057815551758</v>
+        <v>10.1057806015015</v>
       </c>
       <c r="H242" t="n">
         <v>332984</v>
@@ -7648,7 +7648,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G251" t="n">
-        <v>9.89760875701904</v>
+        <v>9.89760971069336</v>
       </c>
       <c r="H251" t="n">
         <v>221470</v>
@@ -7706,7 +7706,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G253" t="n">
-        <v>9.87868404388428</v>
+        <v>9.87868499755859</v>
       </c>
       <c r="H253" t="n">
         <v>178647</v>
@@ -7735,7 +7735,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G254" t="n">
-        <v>9.99223232269287</v>
+        <v>9.99223327636719</v>
       </c>
       <c r="H254" t="n">
         <v>244328</v>
@@ -7764,7 +7764,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G255" t="n">
-        <v>10.2950277328491</v>
+        <v>10.2950267791748</v>
       </c>
       <c r="H255" t="n">
         <v>668230</v>
@@ -7793,7 +7793,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G256" t="n">
-        <v>10.3896512985229</v>
+        <v>10.3896503448486</v>
       </c>
       <c r="H256" t="n">
         <v>552393</v>
@@ -7822,7 +7822,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G257" t="n">
-        <v>10.266640663147</v>
+        <v>10.2666416168213</v>
       </c>
       <c r="H257" t="n">
         <v>500317</v>
@@ -7851,7 +7851,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G258" t="n">
-        <v>10.266640663147</v>
+        <v>10.2666416168213</v>
       </c>
       <c r="H258" t="n">
         <v>138687</v>
@@ -7909,7 +7909,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G260" t="n">
-        <v>10.2382526397705</v>
+        <v>10.2382535934448</v>
       </c>
       <c r="H260" t="n">
         <v>290152</v>
@@ -7938,7 +7938,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G261" t="n">
-        <v>10.1814794540405</v>
+        <v>10.1814804077148</v>
       </c>
       <c r="H261" t="n">
         <v>113192</v>
@@ -7967,7 +7967,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G262" t="n">
-        <v>10.2382526397705</v>
+        <v>10.2382535934448</v>
       </c>
       <c r="H262" t="n">
         <v>242006</v>
@@ -7996,7 +7996,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G263" t="n">
-        <v>10.1814794540405</v>
+        <v>10.1814804077148</v>
       </c>
       <c r="H263" t="n">
         <v>175964</v>
@@ -25924,6 +25924,35 @@
         <v>634512</v>
       </c>
       <c r="I881" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="s">
+        <v>9</v>
+      </c>
+      <c r="B882" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C882" t="n">
+        <v>24.0499992370605</v>
+      </c>
+      <c r="D882" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="E882" t="n">
+        <v>24.0400009155273</v>
+      </c>
+      <c r="F882" t="n">
+        <v>24.6900005340576</v>
+      </c>
+      <c r="G882" t="n">
+        <v>24.6900005340576</v>
+      </c>
+      <c r="H882" t="n">
+        <v>1014372</v>
+      </c>
+      <c r="I882" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LTMC.MI.xlsx
+++ b/data/LTMC.MI.xlsx
@@ -427,7 +427,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2" t="n">
-        <v>7.75911998748779</v>
+        <v>7.75911951065063</v>
       </c>
       <c r="H2" t="n">
         <v>13006120</v>
@@ -456,7 +456,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G3" t="n">
-        <v>7.82535648345947</v>
+        <v>7.82535743713379</v>
       </c>
       <c r="H3" t="n">
         <v>2759922</v>
@@ -514,7 +514,7 @@
         <v>8.48400020599365</v>
       </c>
       <c r="G5" t="n">
-        <v>8.02785110473633</v>
+        <v>8.02785015106201</v>
       </c>
       <c r="H5" t="n">
         <v>738523</v>
@@ -601,7 +601,7 @@
         <v>7.98600006103516</v>
       </c>
       <c r="G8" t="n">
-        <v>7.5566258430481</v>
+        <v>7.55662631988525</v>
       </c>
       <c r="H8" t="n">
         <v>1283605</v>
@@ -775,7 +775,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G14" t="n">
-        <v>7.52256107330322</v>
+        <v>7.52256155014038</v>
       </c>
       <c r="H14" t="n">
         <v>981832</v>
@@ -804,7 +804,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G15" t="n">
-        <v>7.24815320968628</v>
+        <v>7.24815368652344</v>
       </c>
       <c r="H15" t="n">
         <v>941850</v>
@@ -891,7 +891,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G18" t="n">
-        <v>7.2670783996582</v>
+        <v>7.26707792282104</v>
       </c>
       <c r="H18" t="n">
         <v>228832</v>
@@ -949,7 +949,7 @@
         <v>7.80100011825562</v>
       </c>
       <c r="G20" t="n">
-        <v>7.38157272338867</v>
+        <v>7.38157320022583</v>
       </c>
       <c r="H20" t="n">
         <v>40924</v>
@@ -1007,7 +1007,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G22" t="n">
-        <v>7.03525114059448</v>
+        <v>7.03525066375732</v>
       </c>
       <c r="H22" t="n">
         <v>597512</v>
@@ -1152,7 +1152,7 @@
         <v>8.12600040435791</v>
       </c>
       <c r="G27" t="n">
-        <v>7.68909931182861</v>
+        <v>7.68909883499146</v>
       </c>
       <c r="H27" t="n">
         <v>1170934</v>
@@ -1210,7 +1210,7 @@
         <v>8.52200031280518</v>
       </c>
       <c r="G29" t="n">
-        <v>8.06380844116211</v>
+        <v>8.06380748748779</v>
       </c>
       <c r="H29" t="n">
         <v>1531238</v>
@@ -1239,7 +1239,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G30" t="n">
-        <v>7.93890476226807</v>
+        <v>7.93890380859375</v>
       </c>
       <c r="H30" t="n">
         <v>748680</v>
@@ -1268,7 +1268,7 @@
         <v>8.23200035095215</v>
       </c>
       <c r="G31" t="n">
-        <v>7.78940010070801</v>
+        <v>7.78939962387085</v>
       </c>
       <c r="H31" t="n">
         <v>749433</v>
@@ -1297,7 +1297,7 @@
         <v>8.16199970245361</v>
       </c>
       <c r="G32" t="n">
-        <v>7.72316312789917</v>
+        <v>7.72316265106201</v>
       </c>
       <c r="H32" t="n">
         <v>440552</v>
@@ -1326,7 +1326,7 @@
         <v>8.21399974822998</v>
       </c>
       <c r="G33" t="n">
-        <v>7.77236700057983</v>
+        <v>7.77236747741699</v>
       </c>
       <c r="H33" t="n">
         <v>327710</v>
@@ -1384,7 +1384,7 @@
         <v>8.24600028991699</v>
       </c>
       <c r="G35" t="n">
-        <v>7.80264663696289</v>
+        <v>7.80264759063721</v>
       </c>
       <c r="H35" t="n">
         <v>379647</v>
@@ -1645,7 +1645,7 @@
         <v>8.71599960327148</v>
       </c>
       <c r="G44" t="n">
-        <v>8.24737644195557</v>
+        <v>8.24737548828125</v>
       </c>
       <c r="H44" t="n">
         <v>146543</v>
@@ -1703,7 +1703,7 @@
         <v>8.69499969482422</v>
       </c>
       <c r="G46" t="n">
-        <v>8.22750568389893</v>
+        <v>8.22750473022461</v>
       </c>
       <c r="H46" t="n">
         <v>188291</v>
@@ -2022,7 +2022,7 @@
         <v>9.38399982452393</v>
       </c>
       <c r="G57" t="n">
-        <v>8.87946033477783</v>
+        <v>8.87946128845215</v>
       </c>
       <c r="H57" t="n">
         <v>292101</v>
@@ -2051,7 +2051,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G58" t="n">
-        <v>8.8472900390625</v>
+        <v>8.84728908538818</v>
       </c>
       <c r="H58" t="n">
         <v>404952</v>
@@ -2080,7 +2080,7 @@
         <v>9.27099990844727</v>
       </c>
       <c r="G59" t="n">
-        <v>8.77253723144531</v>
+        <v>8.772536277771</v>
       </c>
       <c r="H59" t="n">
         <v>287274</v>
@@ -2167,7 +2167,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G62" t="n">
-        <v>8.65804290771484</v>
+        <v>8.65804195404053</v>
       </c>
       <c r="H62" t="n">
         <v>407302</v>
@@ -2225,7 +2225,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G64" t="n">
-        <v>8.79997825622559</v>
+        <v>8.79997730255127</v>
       </c>
       <c r="H64" t="n">
         <v>396592</v>
@@ -2312,7 +2312,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G67" t="n">
-        <v>8.82363224029541</v>
+        <v>8.82363319396973</v>
       </c>
       <c r="H67" t="n">
         <v>266872</v>
@@ -2341,7 +2341,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G68" t="n">
-        <v>8.8472900390625</v>
+        <v>8.84728908538818</v>
       </c>
       <c r="H68" t="n">
         <v>269589</v>
@@ -2370,7 +2370,7 @@
         <v>9.30300045013428</v>
       </c>
       <c r="G69" t="n">
-        <v>8.80281734466553</v>
+        <v>8.80281639099121</v>
       </c>
       <c r="H69" t="n">
         <v>181453</v>
@@ -2399,7 +2399,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G70" t="n">
-        <v>8.87567615509033</v>
+        <v>8.87567710876465</v>
       </c>
       <c r="H70" t="n">
         <v>257403</v>
@@ -2428,7 +2428,7 @@
         <v>9.30300045013428</v>
       </c>
       <c r="G71" t="n">
-        <v>8.80281734466553</v>
+        <v>8.80281639099121</v>
       </c>
       <c r="H71" t="n">
         <v>228312</v>
@@ -2486,7 +2486,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G73" t="n">
-        <v>8.79997825622559</v>
+        <v>8.79997730255127</v>
       </c>
       <c r="H73" t="n">
         <v>161362</v>
@@ -2573,7 +2573,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G76" t="n">
-        <v>8.75455856323242</v>
+        <v>8.75455760955811</v>
       </c>
       <c r="H76" t="n">
         <v>344778</v>
@@ -2631,7 +2631,7 @@
         <v>9.08300018310547</v>
       </c>
       <c r="G78" t="n">
-        <v>8.59464550018311</v>
+        <v>8.59464454650879</v>
       </c>
       <c r="H78" t="n">
         <v>262830</v>
@@ -2805,7 +2805,7 @@
         <v>9.39200019836426</v>
       </c>
       <c r="G84" t="n">
-        <v>8.88703060150146</v>
+        <v>8.88703155517578</v>
       </c>
       <c r="H84" t="n">
         <v>248541</v>
@@ -2979,7 +2979,7 @@
         <v>9.17899990081787</v>
       </c>
       <c r="G90" t="n">
-        <v>8.68548393249512</v>
+        <v>8.6854829788208</v>
       </c>
       <c r="H90" t="n">
         <v>216140</v>
@@ -3008,7 +3008,7 @@
         <v>9.08100032806396</v>
       </c>
       <c r="G91" t="n">
-        <v>8.59275245666504</v>
+        <v>8.59275341033936</v>
       </c>
       <c r="H91" t="n">
         <v>211156</v>
@@ -3037,7 +3037,7 @@
         <v>9.17099952697754</v>
       </c>
       <c r="G92" t="n">
-        <v>8.67791271209717</v>
+        <v>8.67791175842285</v>
       </c>
       <c r="H92" t="n">
         <v>204917</v>
@@ -3095,7 +3095,7 @@
         <v>9.02299976348877</v>
       </c>
       <c r="G94" t="n">
-        <v>8.53786945343018</v>
+        <v>8.53787040710449</v>
       </c>
       <c r="H94" t="n">
         <v>577462</v>
@@ -3211,7 +3211,7 @@
         <v>9.08100032806396</v>
       </c>
       <c r="G98" t="n">
-        <v>8.59275245666504</v>
+        <v>8.59275341033936</v>
       </c>
       <c r="H98" t="n">
         <v>901629</v>
@@ -3298,7 +3298,7 @@
         <v>9.01900005340576</v>
       </c>
       <c r="G101" t="n">
-        <v>8.53408527374268</v>
+        <v>8.53408622741699</v>
       </c>
       <c r="H101" t="n">
         <v>120168</v>
@@ -3356,7 +3356,7 @@
         <v>8.78400039672852</v>
       </c>
       <c r="G103" t="n">
-        <v>8.3117208480835</v>
+        <v>8.31172180175781</v>
       </c>
       <c r="H103" t="n">
         <v>125113</v>
@@ -3472,7 +3472,7 @@
         <v>8.78400039672852</v>
       </c>
       <c r="G107" t="n">
-        <v>8.3117208480835</v>
+        <v>8.31172180175781</v>
       </c>
       <c r="H107" t="n">
         <v>245795</v>
@@ -3501,7 +3501,7 @@
         <v>8.80700016021729</v>
       </c>
       <c r="G108" t="n">
-        <v>8.3334846496582</v>
+        <v>8.33348369598389</v>
       </c>
       <c r="H108" t="n">
         <v>188343</v>
@@ -3704,7 +3704,7 @@
         <v>8.80099964141846</v>
       </c>
       <c r="G115" t="n">
-        <v>8.32780647277832</v>
+        <v>8.327805519104</v>
       </c>
       <c r="H115" t="n">
         <v>109286</v>
@@ -3762,7 +3762,7 @@
         <v>8.85400009155273</v>
       </c>
       <c r="G117" t="n">
-        <v>8.37795829772949</v>
+        <v>8.37795734405518</v>
       </c>
       <c r="H117" t="n">
         <v>105095</v>
@@ -3849,7 +3849,7 @@
         <v>8.75</v>
       </c>
       <c r="G120" t="n">
-        <v>8.27954959869385</v>
+        <v>8.27954864501953</v>
       </c>
       <c r="H120" t="n">
         <v>97384</v>
@@ -4110,7 +4110,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G129" t="n">
-        <v>8.44987201690674</v>
+        <v>8.44987106323242</v>
       </c>
       <c r="H129" t="n">
         <v>141108</v>
@@ -4255,7 +4255,7 @@
         <v>9.05300045013428</v>
       </c>
       <c r="G134" t="n">
-        <v>8.56625843048096</v>
+        <v>8.56625747680664</v>
       </c>
       <c r="H134" t="n">
         <v>123966</v>
@@ -4429,7 +4429,7 @@
         <v>9.08300018310547</v>
       </c>
       <c r="G140" t="n">
-        <v>8.59464550018311</v>
+        <v>8.59464454650879</v>
       </c>
       <c r="H140" t="n">
         <v>217994</v>
@@ -4487,7 +4487,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G142" t="n">
-        <v>8.6296558380127</v>
+        <v>8.62965488433838</v>
       </c>
       <c r="H142" t="n">
         <v>176941</v>
@@ -4603,7 +4603,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G146" t="n">
-        <v>8.81890201568604</v>
+        <v>8.81890106201172</v>
       </c>
       <c r="H146" t="n">
         <v>95465</v>
@@ -4661,7 +4661,7 @@
         <v>9.36699962615967</v>
       </c>
       <c r="G148" t="n">
-        <v>8.86337566375732</v>
+        <v>8.86337471008301</v>
       </c>
       <c r="H148" t="n">
         <v>76421</v>
@@ -4690,7 +4690,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G149" t="n">
-        <v>8.8472900390625</v>
+        <v>8.84728908538818</v>
       </c>
       <c r="H149" t="n">
         <v>91350</v>
@@ -4719,7 +4719,7 @@
         <v>9.45199966430664</v>
       </c>
       <c r="G150" t="n">
-        <v>8.94380569458008</v>
+        <v>8.94380474090576</v>
       </c>
       <c r="H150" t="n">
         <v>141690</v>
@@ -4835,7 +4835,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G154" t="n">
-        <v>8.96083641052246</v>
+        <v>8.96083736419678</v>
       </c>
       <c r="H154" t="n">
         <v>127739</v>
@@ -4864,7 +4864,7 @@
         <v>9.42599964141846</v>
       </c>
       <c r="G155" t="n">
-        <v>8.91920280456543</v>
+        <v>8.91920185089111</v>
       </c>
       <c r="H155" t="n">
         <v>113950</v>
@@ -4893,7 +4893,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G156" t="n">
-        <v>9.00815010070801</v>
+        <v>9.00814914703369</v>
       </c>
       <c r="H156" t="n">
         <v>146799</v>
@@ -5009,7 +5009,7 @@
         <v>9.58500003814697</v>
       </c>
       <c r="G160" t="n">
-        <v>9.06965446472168</v>
+        <v>9.06965351104736</v>
       </c>
       <c r="H160" t="n">
         <v>66904</v>
@@ -5096,7 +5096,7 @@
         <v>9.79300022125244</v>
       </c>
       <c r="G163" t="n">
-        <v>9.26647186279297</v>
+        <v>9.26647090911865</v>
       </c>
       <c r="H163" t="n">
         <v>2495031</v>
@@ -5125,7 +5125,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G164" t="n">
-        <v>9.27309417724609</v>
+        <v>9.27309513092041</v>
       </c>
       <c r="H164" t="n">
         <v>159322</v>
@@ -5241,7 +5241,7 @@
         <v>9.8149995803833</v>
       </c>
       <c r="G168" t="n">
-        <v>9.28728771209717</v>
+        <v>9.28728866577148</v>
       </c>
       <c r="H168" t="n">
         <v>125832</v>
@@ -5270,7 +5270,7 @@
         <v>9.84700012207031</v>
       </c>
       <c r="G169" t="n">
-        <v>9.31756782531738</v>
+        <v>9.3175687789917</v>
       </c>
       <c r="H169" t="n">
         <v>94635</v>
@@ -5299,7 +5299,7 @@
         <v>9.7819995880127</v>
       </c>
       <c r="G170" t="n">
-        <v>9.25606155395508</v>
+        <v>9.25606250762939</v>
       </c>
       <c r="H170" t="n">
         <v>59025</v>
@@ -5473,7 +5473,7 @@
         <v>9.66800022125244</v>
       </c>
       <c r="G176" t="n">
-        <v>9.14819145202637</v>
+        <v>9.14819240570068</v>
       </c>
       <c r="H176" t="n">
         <v>121337</v>
@@ -5676,7 +5676,7 @@
         <v>10.4580001831055</v>
       </c>
       <c r="G183" t="n">
-        <v>9.89571762084961</v>
+        <v>9.89571666717529</v>
       </c>
       <c r="H183" t="n">
         <v>362012</v>
@@ -5850,7 +5850,7 @@
         <v>10.7840003967285</v>
       </c>
       <c r="G189" t="n">
-        <v>10.2041893005371</v>
+        <v>10.2041902542114</v>
       </c>
       <c r="H189" t="n">
         <v>162445</v>
@@ -5908,7 +5908,7 @@
         <v>10.6820001602173</v>
       </c>
       <c r="G191" t="n">
-        <v>10.1076726913452</v>
+        <v>10.1076736450195</v>
       </c>
       <c r="H191" t="n">
         <v>152759</v>
@@ -5937,7 +5937,7 @@
         <v>10.7720003128052</v>
       </c>
       <c r="G192" t="n">
-        <v>10.1928339004517</v>
+        <v>10.192834854126</v>
       </c>
       <c r="H192" t="n">
         <v>183949</v>
@@ -5966,7 +5966,7 @@
         <v>10.7440004348755</v>
       </c>
       <c r="G193" t="n">
-        <v>10.1663408279419</v>
+        <v>10.1663398742676</v>
       </c>
       <c r="H193" t="n">
         <v>138082</v>
@@ -6111,7 +6111,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G198" t="n">
-        <v>10.4842739105225</v>
+        <v>10.4842748641968</v>
       </c>
       <c r="H198" t="n">
         <v>255451</v>
@@ -6285,7 +6285,7 @@
         <v>11.2040004730225</v>
       </c>
       <c r="G204" t="n">
-        <v>10.6016073226929</v>
+        <v>10.6016082763672</v>
       </c>
       <c r="H204" t="n">
         <v>94315</v>
@@ -6401,7 +6401,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G208" t="n">
-        <v>10.9763164520264</v>
+        <v>10.9763174057007</v>
       </c>
       <c r="H208" t="n">
         <v>197138</v>
@@ -6430,7 +6430,7 @@
         <v>11.5579996109009</v>
       </c>
       <c r="G209" t="n">
-        <v>10.9365749359131</v>
+        <v>10.9365739822388</v>
       </c>
       <c r="H209" t="n">
         <v>170731</v>
@@ -6459,7 +6459,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G210" t="n">
-        <v>10.9195423126221</v>
+        <v>10.9195413589478</v>
       </c>
       <c r="H210" t="n">
         <v>166746</v>
@@ -6517,7 +6517,7 @@
         <v>11.4820003509521</v>
       </c>
       <c r="G212" t="n">
-        <v>10.8646612167358</v>
+        <v>10.8646602630615</v>
       </c>
       <c r="H212" t="n">
         <v>251501</v>
@@ -6604,7 +6604,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G215" t="n">
-        <v>10.7870683670044</v>
+        <v>10.7870693206787</v>
       </c>
       <c r="H215" t="n">
         <v>622398</v>
@@ -6720,7 +6720,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G219" t="n">
-        <v>10.2666416168213</v>
+        <v>10.266640663147</v>
       </c>
       <c r="H219" t="n">
         <v>238286</v>
@@ -6749,7 +6749,7 @@
         <v>10.9619998931885</v>
       </c>
       <c r="G220" t="n">
-        <v>10.3726196289062</v>
+        <v>10.3726186752319</v>
       </c>
       <c r="H220" t="n">
         <v>156811</v>
@@ -7010,7 +7010,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G229" t="n">
-        <v>10.4558877944946</v>
+        <v>10.4558868408203</v>
       </c>
       <c r="H229" t="n">
         <v>563146</v>
@@ -7039,7 +7039,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G230" t="n">
-        <v>10.3896503448486</v>
+        <v>10.3896512985229</v>
       </c>
       <c r="H230" t="n">
         <v>475068</v>
@@ -7068,7 +7068,7 @@
         <v>10.96399974823</v>
       </c>
       <c r="G231" t="n">
-        <v>10.37451171875</v>
+        <v>10.3745107650757</v>
       </c>
       <c r="H231" t="n">
         <v>204899</v>
@@ -7155,7 +7155,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G234" t="n">
-        <v>10.5126609802246</v>
+        <v>10.5126619338989</v>
       </c>
       <c r="H234" t="n">
         <v>148165</v>
@@ -7184,7 +7184,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G235" t="n">
-        <v>10.323413848877</v>
+        <v>10.3234148025513</v>
       </c>
       <c r="H235" t="n">
         <v>263197</v>
@@ -7242,7 +7242,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>10.2666416168213</v>
+        <v>10.266640663147</v>
       </c>
       <c r="H237" t="n">
         <v>250841</v>
@@ -7532,7 +7532,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G247" t="n">
-        <v>9.90707111358643</v>
+        <v>9.90707206726074</v>
       </c>
       <c r="H247" t="n">
         <v>223084</v>
@@ -7648,7 +7648,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G251" t="n">
-        <v>9.89760971069336</v>
+        <v>9.89760875701904</v>
       </c>
       <c r="H251" t="n">
         <v>221470</v>
@@ -7677,7 +7677,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G252" t="n">
-        <v>9.8124475479126</v>
+        <v>9.81244850158691</v>
       </c>
       <c r="H252" t="n">
         <v>215067</v>
@@ -7735,7 +7735,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G254" t="n">
-        <v>9.99223327636719</v>
+        <v>9.99223232269287</v>
       </c>
       <c r="H254" t="n">
         <v>244328</v>
@@ -7793,7 +7793,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G256" t="n">
-        <v>10.3896503448486</v>
+        <v>10.3896512985229</v>
       </c>
       <c r="H256" t="n">
         <v>552393</v>
@@ -7822,7 +7822,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G257" t="n">
-        <v>10.2666416168213</v>
+        <v>10.266640663147</v>
       </c>
       <c r="H257" t="n">
         <v>500317</v>
@@ -7851,7 +7851,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G258" t="n">
-        <v>10.2666416168213</v>
+        <v>10.266640663147</v>
       </c>
       <c r="H258" t="n">
         <v>138687</v>
@@ -7880,7 +7880,7 @@
         <v>10.8299999237061</v>
       </c>
       <c r="G259" t="n">
-        <v>10.2477159500122</v>
+        <v>10.2477149963379</v>
       </c>
       <c r="H259" t="n">
         <v>180911</v>
@@ -7938,7 +7938,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G261" t="n">
-        <v>10.1814804077148</v>
+        <v>10.1814794540405</v>
       </c>
       <c r="H261" t="n">
         <v>113192</v>
@@ -7996,7 +7996,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G263" t="n">
-        <v>10.1814804077148</v>
+        <v>10.1814794540405</v>
       </c>
       <c r="H263" t="n">
         <v>175964</v>
@@ -8141,7 +8141,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G268" t="n">
-        <v>10.0982236862183</v>
+        <v>10.0982227325439</v>
       </c>
       <c r="H268" t="n">
         <v>162147</v>
@@ -8344,7 +8344,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G275" t="n">
-        <v>10.3310356140137</v>
+        <v>10.3310346603394</v>
       </c>
       <c r="H275" t="n">
         <v>417991</v>
@@ -8576,7 +8576,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G283" t="n">
-        <v>10.6220512390137</v>
+        <v>10.6220502853394</v>
       </c>
       <c r="H283" t="n">
         <v>129742</v>
@@ -8634,7 +8634,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G285" t="n">
-        <v>10.5638475418091</v>
+        <v>10.5638484954834</v>
       </c>
       <c r="H285" t="n">
         <v>180726</v>
@@ -8692,7 +8692,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G287" t="n">
-        <v>10.2534303665161</v>
+        <v>10.2534313201904</v>
       </c>
       <c r="H287" t="n">
         <v>235286</v>
@@ -8721,7 +8721,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G288" t="n">
-        <v>10.311635017395</v>
+        <v>10.3116340637207</v>
       </c>
       <c r="H288" t="n">
         <v>127440</v>
@@ -8779,7 +8779,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G290" t="n">
-        <v>10.4377422332764</v>
+        <v>10.4377412796021</v>
       </c>
       <c r="H290" t="n">
         <v>97733</v>
@@ -8895,7 +8895,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G294" t="n">
-        <v>10.8063611984253</v>
+        <v>10.806360244751</v>
       </c>
       <c r="H294" t="n">
         <v>209159</v>
@@ -8982,7 +8982,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G297" t="n">
-        <v>10.9518671035767</v>
+        <v>10.951868057251</v>
       </c>
       <c r="H297" t="n">
         <v>175726</v>
@@ -9011,7 +9011,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G298" t="n">
-        <v>10.7578573226929</v>
+        <v>10.7578582763672</v>
       </c>
       <c r="H298" t="n">
         <v>301876</v>
@@ -9214,7 +9214,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G305" t="n">
-        <v>11.5824003219604</v>
+        <v>11.5823993682861</v>
       </c>
       <c r="H305" t="n">
         <v>274687</v>
@@ -9475,7 +9475,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G314" t="n">
-        <v>11.3398876190186</v>
+        <v>11.3398866653442</v>
       </c>
       <c r="H314" t="n">
         <v>110179</v>
@@ -9562,7 +9562,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G317" t="n">
-        <v>11.2525835037231</v>
+        <v>11.2525844573975</v>
       </c>
       <c r="H317" t="n">
         <v>381622</v>
@@ -9649,7 +9649,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G320" t="n">
-        <v>10.9518671035767</v>
+        <v>10.951868057251</v>
       </c>
       <c r="H320" t="n">
         <v>279934</v>
@@ -9707,7 +9707,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G322" t="n">
-        <v>10.9712686538696</v>
+        <v>10.9712696075439</v>
       </c>
       <c r="H322" t="n">
         <v>185383</v>
@@ -9765,7 +9765,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G324" t="n">
-        <v>10.7481565475464</v>
+        <v>10.7481575012207</v>
       </c>
       <c r="H324" t="n">
         <v>184196</v>
@@ -9852,7 +9852,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>10.7190561294556</v>
+        <v>10.7190551757812</v>
       </c>
       <c r="H327" t="n">
         <v>80274</v>
@@ -9881,7 +9881,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G328" t="n">
-        <v>10.7578573226929</v>
+        <v>10.7578582763672</v>
       </c>
       <c r="H328" t="n">
         <v>81593</v>
@@ -9910,7 +9910,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>10.8160610198975</v>
+        <v>10.8160600662231</v>
       </c>
       <c r="H329" t="n">
         <v>255497</v>
@@ -10055,7 +10055,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G334" t="n">
-        <v>11.136176109314</v>
+        <v>11.1361770629883</v>
       </c>
       <c r="H334" t="n">
         <v>92993</v>
@@ -10084,7 +10084,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G335" t="n">
-        <v>11.136176109314</v>
+        <v>11.1361770629883</v>
       </c>
       <c r="H335" t="n">
         <v>109603</v>
@@ -10258,7 +10258,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G341" t="n">
-        <v>11.4077920913696</v>
+        <v>11.4077911376953</v>
       </c>
       <c r="H341" t="n">
         <v>275168</v>
@@ -10374,7 +10374,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G345" t="n">
-        <v>10.9712686538696</v>
+        <v>10.9712696075439</v>
       </c>
       <c r="H345" t="n">
         <v>250890</v>
@@ -10403,7 +10403,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G346" t="n">
-        <v>10.9615678787231</v>
+        <v>10.9615688323975</v>
       </c>
       <c r="H346" t="n">
         <v>157159</v>
@@ -10432,7 +10432,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G347" t="n">
-        <v>11.0003709793091</v>
+        <v>11.0003700256348</v>
       </c>
       <c r="H347" t="n">
         <v>187467</v>
@@ -10461,7 +10461,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G348" t="n">
-        <v>11.0003709793091</v>
+        <v>11.0003700256348</v>
       </c>
       <c r="H348" t="n">
         <v>109481</v>
@@ -10722,7 +10722,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G357" t="n">
-        <v>11.058572769165</v>
+        <v>11.0585737228394</v>
       </c>
       <c r="H357" t="n">
         <v>184343</v>
@@ -10780,7 +10780,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G359" t="n">
-        <v>11.0003709793091</v>
+        <v>11.0003700256348</v>
       </c>
       <c r="H359" t="n">
         <v>186510</v>
@@ -10867,7 +10867,7 @@
         <v>11.25</v>
       </c>
       <c r="G362" t="n">
-        <v>10.9130659103394</v>
+        <v>10.913064956665</v>
       </c>
       <c r="H362" t="n">
         <v>440278</v>
@@ -10925,7 +10925,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G364" t="n">
-        <v>11.1458768844604</v>
+        <v>11.1458778381348</v>
       </c>
       <c r="H364" t="n">
         <v>188007</v>
@@ -11012,7 +11012,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>11.058572769165</v>
+        <v>11.0585737228394</v>
       </c>
       <c r="H367" t="n">
         <v>195723</v>
@@ -11070,7 +11070,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G369" t="n">
-        <v>11.1458768844604</v>
+        <v>11.1458778381348</v>
       </c>
       <c r="H369" t="n">
         <v>107932</v>
@@ -11128,7 +11128,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G371" t="n">
-        <v>11.136176109314</v>
+        <v>11.1361770629883</v>
       </c>
       <c r="H371" t="n">
         <v>118399</v>
@@ -11186,7 +11186,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G373" t="n">
-        <v>11.0197715759277</v>
+        <v>11.0197706222534</v>
       </c>
       <c r="H373" t="n">
         <v>147161</v>
@@ -11302,7 +11302,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G377" t="n">
-        <v>11.0197715759277</v>
+        <v>11.0197706222534</v>
       </c>
       <c r="H377" t="n">
         <v>130368</v>
@@ -11476,7 +11476,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G383" t="n">
-        <v>11.136176109314</v>
+        <v>11.1361770629883</v>
       </c>
       <c r="H383" t="n">
         <v>194313</v>
@@ -11592,7 +11592,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G387" t="n">
-        <v>11.1749801635742</v>
+        <v>11.1749792098999</v>
       </c>
       <c r="H387" t="n">
         <v>197901</v>
@@ -11650,7 +11650,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G389" t="n">
-        <v>11.4465932846069</v>
+        <v>11.4465942382812</v>
       </c>
       <c r="H389" t="n">
         <v>259214</v>
@@ -11737,7 +11737,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G392" t="n">
-        <v>11.8540143966675</v>
+        <v>11.8540153503418</v>
       </c>
       <c r="H392" t="n">
         <v>194096</v>
@@ -11795,7 +11795,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G394" t="n">
-        <v>11.6988077163696</v>
+        <v>11.6988067626953</v>
       </c>
       <c r="H394" t="n">
         <v>171327</v>
@@ -11911,7 +11911,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G398" t="n">
-        <v>11.6309022903442</v>
+        <v>11.6309032440186</v>
       </c>
       <c r="H398" t="n">
         <v>192088</v>
@@ -11940,7 +11940,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G399" t="n">
-        <v>11.5824003219604</v>
+        <v>11.5823993682861</v>
       </c>
       <c r="H399" t="n">
         <v>137161</v>
@@ -12056,7 +12056,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G403" t="n">
-        <v>12.193531036377</v>
+        <v>12.1935319900513</v>
       </c>
       <c r="H403" t="n">
         <v>108069</v>
@@ -12114,7 +12114,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G405" t="n">
-        <v>12.193531036377</v>
+        <v>12.1935319900513</v>
       </c>
       <c r="H405" t="n">
         <v>135114</v>
@@ -12172,7 +12172,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G407" t="n">
-        <v>12.2226343154907</v>
+        <v>12.2226333618164</v>
       </c>
       <c r="H407" t="n">
         <v>185001</v>
@@ -12201,7 +12201,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G408" t="n">
-        <v>12.2517356872559</v>
+        <v>12.2517347335815</v>
       </c>
       <c r="H408" t="n">
         <v>172512</v>
@@ -12288,7 +12288,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G411" t="n">
-        <v>12.4651470184326</v>
+        <v>12.4651460647583</v>
       </c>
       <c r="H411" t="n">
         <v>133030</v>
@@ -12317,7 +12317,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G412" t="n">
-        <v>12.3875417709351</v>
+        <v>12.3875427246094</v>
       </c>
       <c r="H412" t="n">
         <v>148541</v>
@@ -12520,7 +12520,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G419" t="n">
-        <v>12.2517356872559</v>
+        <v>12.2517347335815</v>
       </c>
       <c r="H419" t="n">
         <v>165954</v>
@@ -12549,7 +12549,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G420" t="n">
-        <v>12.2226343154907</v>
+        <v>12.2226333618164</v>
       </c>
       <c r="H420" t="n">
         <v>258706</v>
@@ -12607,7 +12607,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G422" t="n">
-        <v>12.2129325866699</v>
+        <v>12.2129335403442</v>
       </c>
       <c r="H422" t="n">
         <v>137376</v>
@@ -12636,7 +12636,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G423" t="n">
-        <v>12.3875417709351</v>
+        <v>12.3875427246094</v>
       </c>
       <c r="H423" t="n">
         <v>99466</v>
@@ -12723,7 +12723,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G426" t="n">
-        <v>12.5427503585815</v>
+        <v>12.5427513122559</v>
       </c>
       <c r="H426" t="n">
         <v>197307</v>
@@ -12752,7 +12752,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G427" t="n">
-        <v>12.6300554275513</v>
+        <v>12.630054473877</v>
       </c>
       <c r="H427" t="n">
         <v>148262</v>
@@ -12839,7 +12839,7 @@
         <v>13</v>
       </c>
       <c r="G430" t="n">
-        <v>12.6106538772583</v>
+        <v>12.610652923584</v>
       </c>
       <c r="H430" t="n">
         <v>1807764</v>
@@ -12897,7 +12897,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G432" t="n">
-        <v>12.3972415924072</v>
+        <v>12.3972425460815</v>
       </c>
       <c r="H432" t="n">
         <v>1234024</v>
@@ -12955,7 +12955,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G434" t="n">
-        <v>12.6882572174072</v>
+        <v>12.6882581710815</v>
       </c>
       <c r="H434" t="n">
         <v>465320</v>
@@ -13013,7 +13013,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G436" t="n">
-        <v>13.1538829803467</v>
+        <v>13.1538820266724</v>
       </c>
       <c r="H436" t="n">
         <v>425963</v>
@@ -13274,7 +13274,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G445" t="n">
-        <v>13.7844142913818</v>
+        <v>13.7844152450562</v>
       </c>
       <c r="H445" t="n">
         <v>236771</v>
@@ -13303,7 +13303,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G446" t="n">
-        <v>14.3373422622681</v>
+        <v>14.3373432159424</v>
       </c>
       <c r="H446" t="n">
         <v>473165</v>
@@ -13332,7 +13332,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G447" t="n">
-        <v>14.4537487030029</v>
+        <v>14.4537496566772</v>
       </c>
       <c r="H447" t="n">
         <v>380386</v>
@@ -13361,7 +13361,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G448" t="n">
-        <v>14.6671600341797</v>
+        <v>14.667160987854</v>
       </c>
       <c r="H448" t="n">
         <v>267462</v>
@@ -13419,7 +13419,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G450" t="n">
-        <v>14.8029680252075</v>
+        <v>14.8029670715332</v>
       </c>
       <c r="H450" t="n">
         <v>391347</v>
@@ -13622,7 +13622,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G457" t="n">
-        <v>16.0446319580078</v>
+        <v>16.0446338653564</v>
       </c>
       <c r="H457" t="n">
         <v>378598</v>
@@ -13680,7 +13680,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G459" t="n">
-        <v>15.9573278427124</v>
+        <v>15.9573268890381</v>
       </c>
       <c r="H459" t="n">
         <v>261224</v>
@@ -13796,7 +13796,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G463" t="n">
-        <v>16.0252323150635</v>
+        <v>16.0252304077148</v>
       </c>
       <c r="H463" t="n">
         <v>392686</v>
@@ -13825,7 +13825,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G464" t="n">
-        <v>15.6857137680054</v>
+        <v>15.6857128143311</v>
       </c>
       <c r="H464" t="n">
         <v>532461</v>
@@ -14028,7 +14028,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G471" t="n">
-        <v>15.8700227737427</v>
+        <v>15.870023727417</v>
       </c>
       <c r="H471" t="n">
         <v>880362</v>
@@ -14115,7 +14115,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G474" t="n">
-        <v>16.9273777008057</v>
+        <v>16.9273796081543</v>
       </c>
       <c r="H474" t="n">
         <v>620043</v>
@@ -14260,7 +14260,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G479" t="n">
-        <v>17.5870113372803</v>
+        <v>17.5870094299316</v>
       </c>
       <c r="H479" t="n">
         <v>473621</v>
@@ -14289,7 +14289,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G480" t="n">
-        <v>17.5870113372803</v>
+        <v>17.5870094299316</v>
       </c>
       <c r="H480" t="n">
         <v>417252</v>
@@ -14347,7 +14347,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G482" t="n">
-        <v>17.1601905822754</v>
+        <v>17.1601886749268</v>
       </c>
       <c r="H482" t="n">
         <v>353508</v>
@@ -14405,7 +14405,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G484" t="n">
-        <v>17.7519207000732</v>
+        <v>17.7519187927246</v>
       </c>
       <c r="H484" t="n">
         <v>342388</v>
@@ -14434,7 +14434,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G485" t="n">
-        <v>17.7422199249268</v>
+        <v>17.7422218322754</v>
       </c>
       <c r="H485" t="n">
         <v>271126</v>
@@ -14521,7 +14521,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G488" t="n">
-        <v>17.9071273803711</v>
+        <v>17.9071292877197</v>
       </c>
       <c r="H488" t="n">
         <v>372109</v>
@@ -14550,7 +14550,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G489" t="n">
-        <v>18.3727512359619</v>
+        <v>18.3727531433105</v>
       </c>
       <c r="H489" t="n">
         <v>455016</v>
@@ -14608,7 +14608,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>16.8303737640381</v>
+        <v>16.8303718566895</v>
       </c>
       <c r="H491" t="n">
         <v>1164243</v>
@@ -14695,7 +14695,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G494" t="n">
-        <v>17.1601905822754</v>
+        <v>17.1601886749268</v>
       </c>
       <c r="H494" t="n">
         <v>564420</v>
@@ -14898,7 +14898,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G501" t="n">
-        <v>18.8480758666992</v>
+        <v>18.8480777740479</v>
       </c>
       <c r="H501" t="n">
         <v>377971</v>
@@ -14927,7 +14927,7 @@
         <v>19.4699993133545</v>
       </c>
       <c r="G502" t="n">
-        <v>18.8868770599365</v>
+        <v>18.8868789672852</v>
       </c>
       <c r="H502" t="n">
         <v>436832</v>
@@ -14956,7 +14956,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G503" t="n">
-        <v>19.0226879119873</v>
+        <v>19.0226860046387</v>
       </c>
       <c r="H503" t="n">
         <v>218294</v>
@@ -15014,7 +15014,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G505" t="n">
-        <v>19.4786109924316</v>
+        <v>19.478609085083</v>
       </c>
       <c r="H505" t="n">
         <v>375456</v>
@@ -15043,7 +15043,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G506" t="n">
-        <v>19.4592094421387</v>
+        <v>19.45920753479</v>
       </c>
       <c r="H506" t="n">
         <v>430857</v>
@@ -15072,7 +15072,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G507" t="n">
-        <v>19.4398078918457</v>
+        <v>19.4398097991943</v>
       </c>
       <c r="H507" t="n">
         <v>573705</v>
@@ -15130,7 +15130,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G509" t="n">
-        <v>20.3128528594971</v>
+        <v>20.3128547668457</v>
       </c>
       <c r="H509" t="n">
         <v>845381</v>
@@ -15159,7 +15159,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G510" t="n">
-        <v>20.2352504730225</v>
+        <v>20.2352485656738</v>
       </c>
       <c r="H510" t="n">
         <v>628106</v>
@@ -15188,7 +15188,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G511" t="n">
-        <v>19.9248332977295</v>
+        <v>19.9248352050781</v>
       </c>
       <c r="H511" t="n">
         <v>774008</v>
@@ -15217,7 +15217,7 @@
         <v>20</v>
       </c>
       <c r="G512" t="n">
-        <v>19.4010047912598</v>
+        <v>19.4010066986084</v>
       </c>
       <c r="H512" t="n">
         <v>769373</v>
@@ -15304,7 +15304,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>21.6321220397949</v>
+        <v>21.6321201324463</v>
       </c>
       <c r="H515" t="n">
         <v>2197577</v>
@@ -15362,7 +15362,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G517" t="n">
-        <v>22.1171455383301</v>
+        <v>22.1171474456787</v>
       </c>
       <c r="H517" t="n">
         <v>555528</v>
@@ -15391,7 +15391,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G518" t="n">
-        <v>21.9619388580322</v>
+        <v>21.9619369506836</v>
       </c>
       <c r="H518" t="n">
         <v>611058</v>
@@ -25953,6 +25953,35 @@
         <v>1014372</v>
       </c>
       <c r="I882" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="s">
+        <v>9</v>
+      </c>
+      <c r="B883" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C883" t="n">
+        <v>24.3600006103516</v>
+      </c>
+      <c r="D883" t="n">
+        <v>24.9400005340576</v>
+      </c>
+      <c r="E883" t="n">
+        <v>24.2600002288818</v>
+      </c>
+      <c r="F883" t="n">
+        <v>24.8299999237061</v>
+      </c>
+      <c r="G883" t="n">
+        <v>24.8299999237061</v>
+      </c>
+      <c r="H883" t="n">
+        <v>872309</v>
+      </c>
+      <c r="I883" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LTMC.MI.xlsx
+++ b/data/LTMC.MI.xlsx
@@ -427,7 +427,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2" t="n">
-        <v>7.75911951065063</v>
+        <v>7.75912046432495</v>
       </c>
       <c r="H2" t="n">
         <v>13006120</v>
@@ -456,7 +456,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G3" t="n">
-        <v>7.82535743713379</v>
+        <v>7.82535648345947</v>
       </c>
       <c r="H3" t="n">
         <v>2759922</v>
@@ -514,7 +514,7 @@
         <v>8.48400020599365</v>
       </c>
       <c r="G5" t="n">
-        <v>8.02785015106201</v>
+        <v>8.02785110473633</v>
       </c>
       <c r="H5" t="n">
         <v>738523</v>
@@ -543,7 +543,7 @@
         <v>8.59099960327148</v>
       </c>
       <c r="G6" t="n">
-        <v>8.1290979385376</v>
+        <v>8.12909698486328</v>
       </c>
       <c r="H6" t="n">
         <v>974676</v>
@@ -601,7 +601,7 @@
         <v>7.98600006103516</v>
       </c>
       <c r="G8" t="n">
-        <v>7.55662631988525</v>
+        <v>7.5566258430481</v>
       </c>
       <c r="H8" t="n">
         <v>1283605</v>
@@ -630,7 +630,7 @@
         <v>8.25</v>
       </c>
       <c r="G9" t="n">
-        <v>7.80643224716187</v>
+        <v>7.80643177032471</v>
       </c>
       <c r="H9" t="n">
         <v>1073912</v>
@@ -659,7 +659,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G10" t="n">
-        <v>7.99567890167236</v>
+        <v>7.99567794799805</v>
       </c>
       <c r="H10" t="n">
         <v>1947465</v>
@@ -775,7 +775,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G14" t="n">
-        <v>7.52256155014038</v>
+        <v>7.52256107330322</v>
       </c>
       <c r="H14" t="n">
         <v>981832</v>
@@ -804,7 +804,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G15" t="n">
-        <v>7.24815368652344</v>
+        <v>7.24815320968628</v>
       </c>
       <c r="H15" t="n">
         <v>941850</v>
@@ -833,7 +833,7 @@
         <v>7.86899995803833</v>
       </c>
       <c r="G16" t="n">
-        <v>7.44591617584229</v>
+        <v>7.44591665267944</v>
       </c>
       <c r="H16" t="n">
         <v>479599</v>
@@ -891,7 +891,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G18" t="n">
-        <v>7.26707792282104</v>
+        <v>7.2670783996582</v>
       </c>
       <c r="H18" t="n">
         <v>228832</v>
@@ -949,7 +949,7 @@
         <v>7.80100011825562</v>
       </c>
       <c r="G20" t="n">
-        <v>7.38157320022583</v>
+        <v>7.38157224655151</v>
       </c>
       <c r="H20" t="n">
         <v>40924</v>
@@ -1094,7 +1094,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G25" t="n">
-        <v>7.28600263595581</v>
+        <v>7.28600311279297</v>
       </c>
       <c r="H25" t="n">
         <v>218758</v>
@@ -1152,7 +1152,7 @@
         <v>8.12600040435791</v>
       </c>
       <c r="G27" t="n">
-        <v>7.68909883499146</v>
+        <v>7.68909931182861</v>
       </c>
       <c r="H27" t="n">
         <v>1170934</v>
@@ -1239,7 +1239,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G30" t="n">
-        <v>7.93890380859375</v>
+        <v>7.93890476226807</v>
       </c>
       <c r="H30" t="n">
         <v>748680</v>
@@ -1297,7 +1297,7 @@
         <v>8.16199970245361</v>
       </c>
       <c r="G32" t="n">
-        <v>7.72316265106201</v>
+        <v>7.72316360473633</v>
       </c>
       <c r="H32" t="n">
         <v>440552</v>
@@ -1326,7 +1326,7 @@
         <v>8.21399974822998</v>
       </c>
       <c r="G33" t="n">
-        <v>7.77236747741699</v>
+        <v>7.77236700057983</v>
       </c>
       <c r="H33" t="n">
         <v>327710</v>
@@ -1384,7 +1384,7 @@
         <v>8.24600028991699</v>
       </c>
       <c r="G35" t="n">
-        <v>7.80264759063721</v>
+        <v>7.80264663696289</v>
       </c>
       <c r="H35" t="n">
         <v>379647</v>
@@ -1413,7 +1413,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G36" t="n">
-        <v>7.81116247177124</v>
+        <v>7.8111629486084</v>
       </c>
       <c r="H36" t="n">
         <v>219714</v>
@@ -1471,7 +1471,7 @@
         <v>8.4379997253418</v>
       </c>
       <c r="G38" t="n">
-        <v>7.98432397842407</v>
+        <v>7.98432350158691</v>
       </c>
       <c r="H38" t="n">
         <v>178091</v>
@@ -1645,7 +1645,7 @@
         <v>8.71599960327148</v>
       </c>
       <c r="G44" t="n">
-        <v>8.24737548828125</v>
+        <v>8.24737644195557</v>
       </c>
       <c r="H44" t="n">
         <v>146543</v>
@@ -1703,7 +1703,7 @@
         <v>8.69499969482422</v>
       </c>
       <c r="G46" t="n">
-        <v>8.22750473022461</v>
+        <v>8.22750663757324</v>
       </c>
       <c r="H46" t="n">
         <v>188291</v>
@@ -1732,7 +1732,7 @@
         <v>8.58300018310547</v>
       </c>
       <c r="G47" t="n">
-        <v>8.12152767181396</v>
+        <v>8.12152862548828</v>
       </c>
       <c r="H47" t="n">
         <v>162361</v>
@@ -1761,7 +1761,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G48" t="n">
-        <v>7.94363641738892</v>
+        <v>7.9436354637146</v>
       </c>
       <c r="H48" t="n">
         <v>297588</v>
@@ -1819,7 +1819,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G50" t="n">
-        <v>8.49718189239502</v>
+        <v>8.49718284606934</v>
       </c>
       <c r="H50" t="n">
         <v>475388</v>
@@ -1877,7 +1877,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G52" t="n">
-        <v>8.79051494598389</v>
+        <v>8.7905158996582</v>
       </c>
       <c r="H52" t="n">
         <v>1027347</v>
@@ -1906,7 +1906,7 @@
         <v>9.4689998626709</v>
       </c>
       <c r="G53" t="n">
-        <v>8.95989036560059</v>
+        <v>8.9598913192749</v>
       </c>
       <c r="H53" t="n">
         <v>1003139</v>
@@ -2022,7 +2022,7 @@
         <v>9.38399982452393</v>
       </c>
       <c r="G57" t="n">
-        <v>8.87946128845215</v>
+        <v>8.87946033477783</v>
       </c>
       <c r="H57" t="n">
         <v>292101</v>
@@ -2051,7 +2051,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G58" t="n">
-        <v>8.84728908538818</v>
+        <v>8.8472900390625</v>
       </c>
       <c r="H58" t="n">
         <v>404952</v>
@@ -2196,7 +2196,7 @@
         <v>9.17800045013428</v>
       </c>
       <c r="G63" t="n">
-        <v>8.68453693389893</v>
+        <v>8.68453788757324</v>
       </c>
       <c r="H63" t="n">
         <v>254936</v>
@@ -2225,7 +2225,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G64" t="n">
-        <v>8.79997730255127</v>
+        <v>8.79997825622559</v>
       </c>
       <c r="H64" t="n">
         <v>396592</v>
@@ -2254,7 +2254,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G65" t="n">
-        <v>8.94191265106201</v>
+        <v>8.9419116973877</v>
       </c>
       <c r="H65" t="n">
         <v>900757</v>
@@ -2341,7 +2341,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G68" t="n">
-        <v>8.84728908538818</v>
+        <v>8.8472900390625</v>
       </c>
       <c r="H68" t="n">
         <v>269589</v>
@@ -2370,7 +2370,7 @@
         <v>9.30300045013428</v>
       </c>
       <c r="G69" t="n">
-        <v>8.80281639099121</v>
+        <v>8.80281734466553</v>
       </c>
       <c r="H69" t="n">
         <v>181453</v>
@@ -2428,7 +2428,7 @@
         <v>9.30300045013428</v>
       </c>
       <c r="G71" t="n">
-        <v>8.80281639099121</v>
+        <v>8.80281734466553</v>
       </c>
       <c r="H71" t="n">
         <v>228312</v>
@@ -2457,7 +2457,7 @@
         <v>9.31900024414062</v>
       </c>
       <c r="G72" t="n">
-        <v>8.81795597076416</v>
+        <v>8.81795692443848</v>
       </c>
       <c r="H72" t="n">
         <v>303822</v>
@@ -2486,7 +2486,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G73" t="n">
-        <v>8.79997730255127</v>
+        <v>8.79997825622559</v>
       </c>
       <c r="H73" t="n">
         <v>161362</v>
@@ -2515,7 +2515,7 @@
         <v>9.14700031280518</v>
       </c>
       <c r="G74" t="n">
-        <v>8.6552038192749</v>
+        <v>8.65520286560059</v>
       </c>
       <c r="H74" t="n">
         <v>250420</v>
@@ -2573,7 +2573,7 @@
         <v>9.2519998550415</v>
       </c>
       <c r="G76" t="n">
-        <v>8.75455760955811</v>
+        <v>8.75455856323242</v>
       </c>
       <c r="H76" t="n">
         <v>344778</v>
@@ -2631,7 +2631,7 @@
         <v>9.08300018310547</v>
       </c>
       <c r="G78" t="n">
-        <v>8.59464454650879</v>
+        <v>8.59464550018311</v>
       </c>
       <c r="H78" t="n">
         <v>262830</v>
@@ -2689,7 +2689,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G80" t="n">
-        <v>8.67696666717529</v>
+        <v>8.67696762084961</v>
       </c>
       <c r="H80" t="n">
         <v>180085</v>
@@ -3008,7 +3008,7 @@
         <v>9.08100032806396</v>
       </c>
       <c r="G91" t="n">
-        <v>8.59275341033936</v>
+        <v>8.59275245666504</v>
       </c>
       <c r="H91" t="n">
         <v>211156</v>
@@ -3037,7 +3037,7 @@
         <v>9.17099952697754</v>
       </c>
       <c r="G92" t="n">
-        <v>8.67791175842285</v>
+        <v>8.67791271209717</v>
       </c>
       <c r="H92" t="n">
         <v>204917</v>
@@ -3095,7 +3095,7 @@
         <v>9.02299976348877</v>
       </c>
       <c r="G94" t="n">
-        <v>8.53787040710449</v>
+        <v>8.53786945343018</v>
       </c>
       <c r="H94" t="n">
         <v>577462</v>
@@ -3124,7 +3124,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G95" t="n">
-        <v>8.53503227233887</v>
+        <v>8.53503322601318</v>
       </c>
       <c r="H95" t="n">
         <v>212825</v>
@@ -3182,7 +3182,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>8.67696666717529</v>
+        <v>8.67696762084961</v>
       </c>
       <c r="H97" t="n">
         <v>420414</v>
@@ -3211,7 +3211,7 @@
         <v>9.08100032806396</v>
       </c>
       <c r="G98" t="n">
-        <v>8.59275341033936</v>
+        <v>8.59275245666504</v>
       </c>
       <c r="H98" t="n">
         <v>901629</v>
@@ -3327,7 +3327,7 @@
         <v>8.89700031280518</v>
       </c>
       <c r="G102" t="n">
-        <v>8.41864585876465</v>
+        <v>8.41864490509033</v>
       </c>
       <c r="H102" t="n">
         <v>170277</v>
@@ -3356,7 +3356,7 @@
         <v>8.78400039672852</v>
       </c>
       <c r="G103" t="n">
-        <v>8.31172180175781</v>
+        <v>8.3117208480835</v>
       </c>
       <c r="H103" t="n">
         <v>125113</v>
@@ -3472,7 +3472,7 @@
         <v>8.78400039672852</v>
       </c>
       <c r="G107" t="n">
-        <v>8.31172180175781</v>
+        <v>8.3117208480835</v>
       </c>
       <c r="H107" t="n">
         <v>245795</v>
@@ -3501,7 +3501,7 @@
         <v>8.80700016021729</v>
       </c>
       <c r="G108" t="n">
-        <v>8.33348369598389</v>
+        <v>8.3334846496582</v>
       </c>
       <c r="H108" t="n">
         <v>188343</v>
@@ -3530,7 +3530,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G109" t="n">
-        <v>8.27008724212646</v>
+        <v>8.27008628845215</v>
       </c>
       <c r="H109" t="n">
         <v>186396</v>
@@ -3559,7 +3559,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G110" t="n">
-        <v>8.37417316436768</v>
+        <v>8.37417221069336</v>
       </c>
       <c r="H110" t="n">
         <v>209809</v>
@@ -3704,7 +3704,7 @@
         <v>8.80099964141846</v>
       </c>
       <c r="G115" t="n">
-        <v>8.327805519104</v>
+        <v>8.32780647277832</v>
       </c>
       <c r="H115" t="n">
         <v>109286</v>
@@ -3820,7 +3820,7 @@
         <v>8.7209997177124</v>
       </c>
       <c r="G119" t="n">
-        <v>8.25210762023926</v>
+        <v>8.25210857391357</v>
       </c>
       <c r="H119" t="n">
         <v>127697</v>
@@ -4052,7 +4052,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G127" t="n">
-        <v>8.37417316436768</v>
+        <v>8.37417221069336</v>
       </c>
       <c r="H127" t="n">
         <v>102561</v>
@@ -4081,7 +4081,7 @@
         <v>8.82100009918213</v>
       </c>
       <c r="G128" t="n">
-        <v>8.34673118591309</v>
+        <v>8.3467321395874</v>
       </c>
       <c r="H128" t="n">
         <v>174329</v>
@@ -4110,7 +4110,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G129" t="n">
-        <v>8.44987106323242</v>
+        <v>8.44987201690674</v>
       </c>
       <c r="H129" t="n">
         <v>141108</v>
@@ -4139,7 +4139,7 @@
         <v>8.93599987030029</v>
       </c>
       <c r="G130" t="n">
-        <v>8.45554828643799</v>
+        <v>8.45554733276367</v>
       </c>
       <c r="H130" t="n">
         <v>394314</v>
@@ -4168,7 +4168,7 @@
         <v>9.03800010681152</v>
       </c>
       <c r="G131" t="n">
-        <v>8.55206489562988</v>
+        <v>8.55206394195557</v>
       </c>
       <c r="H131" t="n">
         <v>165794</v>
@@ -4226,7 +4226,7 @@
         <v>9.22200012207031</v>
       </c>
       <c r="G133" t="n">
-        <v>8.72617149353027</v>
+        <v>8.72617053985596</v>
       </c>
       <c r="H133" t="n">
         <v>178676</v>
@@ -4255,7 +4255,7 @@
         <v>9.05300045013428</v>
       </c>
       <c r="G134" t="n">
-        <v>8.56625747680664</v>
+        <v>8.56625843048096</v>
       </c>
       <c r="H134" t="n">
         <v>123966</v>
@@ -4284,7 +4284,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G135" t="n">
-        <v>8.61262321472168</v>
+        <v>8.612624168396</v>
       </c>
       <c r="H135" t="n">
         <v>75451</v>
@@ -4313,7 +4313,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G136" t="n">
-        <v>8.53503227233887</v>
+        <v>8.53503322601318</v>
       </c>
       <c r="H136" t="n">
         <v>172542</v>
@@ -4342,7 +4342,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G137" t="n">
-        <v>8.61262321472168</v>
+        <v>8.612624168396</v>
       </c>
       <c r="H137" t="n">
         <v>197102</v>
@@ -4429,7 +4429,7 @@
         <v>9.08300018310547</v>
       </c>
       <c r="G140" t="n">
-        <v>8.59464454650879</v>
+        <v>8.59464550018311</v>
       </c>
       <c r="H140" t="n">
         <v>217994</v>
@@ -4487,7 +4487,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G142" t="n">
-        <v>8.62965488433838</v>
+        <v>8.6296558380127</v>
       </c>
       <c r="H142" t="n">
         <v>176941</v>
@@ -4603,7 +4603,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G146" t="n">
-        <v>8.81890106201172</v>
+        <v>8.81890296936035</v>
       </c>
       <c r="H146" t="n">
         <v>95465</v>
@@ -4661,7 +4661,7 @@
         <v>9.36699962615967</v>
       </c>
       <c r="G148" t="n">
-        <v>8.86337471008301</v>
+        <v>8.86337566375732</v>
       </c>
       <c r="H148" t="n">
         <v>76421</v>
@@ -4690,7 +4690,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G149" t="n">
-        <v>8.84728908538818</v>
+        <v>8.8472900390625</v>
       </c>
       <c r="H149" t="n">
         <v>91350</v>
@@ -4864,7 +4864,7 @@
         <v>9.42599964141846</v>
       </c>
       <c r="G155" t="n">
-        <v>8.91920185089111</v>
+        <v>8.91920280456543</v>
       </c>
       <c r="H155" t="n">
         <v>113950</v>
@@ -4893,7 +4893,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G156" t="n">
-        <v>9.00814914703369</v>
+        <v>9.00815010070801</v>
       </c>
       <c r="H156" t="n">
         <v>146799</v>
@@ -4922,7 +4922,7 @@
         <v>9.60900020599365</v>
       </c>
       <c r="G157" t="n">
-        <v>9.09236431121826</v>
+        <v>9.09236335754395</v>
       </c>
       <c r="H157" t="n">
         <v>302816</v>
@@ -5009,7 +5009,7 @@
         <v>9.58500003814697</v>
       </c>
       <c r="G160" t="n">
-        <v>9.06965351104736</v>
+        <v>9.06965446472168</v>
       </c>
       <c r="H160" t="n">
         <v>66904</v>
@@ -5038,7 +5038,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G161" t="n">
-        <v>8.94191265106201</v>
+        <v>8.9419116973877</v>
       </c>
       <c r="H161" t="n">
         <v>242695</v>
@@ -5096,7 +5096,7 @@
         <v>9.79300022125244</v>
       </c>
       <c r="G163" t="n">
-        <v>9.26647090911865</v>
+        <v>9.26647186279297</v>
       </c>
       <c r="H163" t="n">
         <v>2495031</v>
@@ -5125,7 +5125,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G164" t="n">
-        <v>9.27309513092041</v>
+        <v>9.27309417724609</v>
       </c>
       <c r="H164" t="n">
         <v>159322</v>
@@ -5154,7 +5154,7 @@
         <v>9.80599975585938</v>
       </c>
       <c r="G165" t="n">
-        <v>9.27877140045166</v>
+        <v>9.27877235412598</v>
       </c>
       <c r="H165" t="n">
         <v>183228</v>
@@ -5212,7 +5212,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G167" t="n">
-        <v>9.32040786743164</v>
+        <v>9.32040691375732</v>
       </c>
       <c r="H167" t="n">
         <v>175516</v>
@@ -5241,7 +5241,7 @@
         <v>9.8149995803833</v>
       </c>
       <c r="G168" t="n">
-        <v>9.28728866577148</v>
+        <v>9.28728771209717</v>
       </c>
       <c r="H168" t="n">
         <v>125832</v>
@@ -5270,7 +5270,7 @@
         <v>9.84700012207031</v>
       </c>
       <c r="G169" t="n">
-        <v>9.3175687789917</v>
+        <v>9.31756687164307</v>
       </c>
       <c r="H169" t="n">
         <v>94635</v>
@@ -5415,7 +5415,7 @@
         <v>9.6230001449585</v>
       </c>
       <c r="G174" t="n">
-        <v>9.10561084747314</v>
+        <v>9.10561180114746</v>
       </c>
       <c r="H174" t="n">
         <v>254745</v>
@@ -5473,7 +5473,7 @@
         <v>9.66800022125244</v>
       </c>
       <c r="G176" t="n">
-        <v>9.14819240570068</v>
+        <v>9.14819145202637</v>
       </c>
       <c r="H176" t="n">
         <v>121337</v>
@@ -5705,7 +5705,7 @@
         <v>10.1619997024536</v>
       </c>
       <c r="G184" t="n">
-        <v>9.61563110351562</v>
+        <v>9.61563014984131</v>
       </c>
       <c r="H184" t="n">
         <v>2039385</v>
@@ -5792,7 +5792,7 @@
         <v>10.6339998245239</v>
       </c>
       <c r="G187" t="n">
-        <v>10.0622539520264</v>
+        <v>10.0622529983521</v>
       </c>
       <c r="H187" t="n">
         <v>279044</v>
@@ -5850,7 +5850,7 @@
         <v>10.7840003967285</v>
       </c>
       <c r="G189" t="n">
-        <v>10.2041902542114</v>
+        <v>10.2041893005371</v>
       </c>
       <c r="H189" t="n">
         <v>162445</v>
@@ -5908,7 +5908,7 @@
         <v>10.6820001602173</v>
       </c>
       <c r="G191" t="n">
-        <v>10.1076736450195</v>
+        <v>10.1076726913452</v>
       </c>
       <c r="H191" t="n">
         <v>152759</v>
@@ -6082,7 +6082,7 @@
         <v>11.0480003356934</v>
       </c>
       <c r="G197" t="n">
-        <v>10.4539957046509</v>
+        <v>10.4539947509766</v>
       </c>
       <c r="H197" t="n">
         <v>281143</v>
@@ -6198,7 +6198,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G201" t="n">
-        <v>10.5788974761963</v>
+        <v>10.5788984298706</v>
       </c>
       <c r="H201" t="n">
         <v>211395</v>
@@ -6401,7 +6401,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G208" t="n">
-        <v>10.9763174057007</v>
+        <v>10.9763164520264</v>
       </c>
       <c r="H208" t="n">
         <v>197138</v>
@@ -6459,7 +6459,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G210" t="n">
-        <v>10.9195413589478</v>
+        <v>10.9195423126221</v>
       </c>
       <c r="H210" t="n">
         <v>166746</v>
@@ -6517,7 +6517,7 @@
         <v>11.4820003509521</v>
       </c>
       <c r="G212" t="n">
-        <v>10.8646602630615</v>
+        <v>10.8646612167358</v>
       </c>
       <c r="H212" t="n">
         <v>251501</v>
@@ -6662,7 +6662,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G217" t="n">
-        <v>10.4369621276855</v>
+        <v>10.4369630813599</v>
       </c>
       <c r="H217" t="n">
         <v>269996</v>
@@ -6691,7 +6691,7 @@
         <v>10.8739995956421</v>
       </c>
       <c r="G218" t="n">
-        <v>10.2893495559692</v>
+        <v>10.2893505096436</v>
       </c>
       <c r="H218" t="n">
         <v>223312</v>
@@ -6807,7 +6807,7 @@
         <v>11.2340002059937</v>
       </c>
       <c r="G222" t="n">
-        <v>10.629994392395</v>
+        <v>10.6299934387207</v>
       </c>
       <c r="H222" t="n">
         <v>159090</v>
@@ -6865,7 +6865,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>11.2128753662109</v>
+        <v>11.2128744125366</v>
       </c>
       <c r="H224" t="n">
         <v>273187</v>
@@ -6894,7 +6894,7 @@
         <v>11.9340000152588</v>
       </c>
       <c r="G225" t="n">
-        <v>11.2923583984375</v>
+        <v>11.2923574447632</v>
       </c>
       <c r="H225" t="n">
         <v>1392941</v>
@@ -7010,7 +7010,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G229" t="n">
-        <v>10.4558868408203</v>
+        <v>10.4558877944946</v>
       </c>
       <c r="H229" t="n">
         <v>563146</v>
@@ -7155,7 +7155,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G234" t="n">
-        <v>10.5126619338989</v>
+        <v>10.5126600265503</v>
       </c>
       <c r="H234" t="n">
         <v>148165</v>
@@ -7184,7 +7184,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G235" t="n">
-        <v>10.3234148025513</v>
+        <v>10.323413848877</v>
       </c>
       <c r="H235" t="n">
         <v>263197</v>
@@ -7213,7 +7213,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G236" t="n">
-        <v>10.2382535934448</v>
+        <v>10.2382526397705</v>
       </c>
       <c r="H236" t="n">
         <v>356369</v>
@@ -7271,7 +7271,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G238" t="n">
-        <v>10.2382535934448</v>
+        <v>10.2382526397705</v>
       </c>
       <c r="H238" t="n">
         <v>235729</v>
@@ -7387,7 +7387,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G242" t="n">
-        <v>10.1057806015015</v>
+        <v>10.1057815551758</v>
       </c>
       <c r="H242" t="n">
         <v>332984</v>
@@ -7532,7 +7532,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G247" t="n">
-        <v>9.90707206726074</v>
+        <v>9.90707111358643</v>
       </c>
       <c r="H247" t="n">
         <v>223084</v>
@@ -7677,7 +7677,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G252" t="n">
-        <v>9.81244850158691</v>
+        <v>9.8124475479126</v>
       </c>
       <c r="H252" t="n">
         <v>215067</v>
@@ -7706,7 +7706,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G253" t="n">
-        <v>9.87868499755859</v>
+        <v>9.87868404388428</v>
       </c>
       <c r="H253" t="n">
         <v>178647</v>
@@ -7764,7 +7764,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G255" t="n">
-        <v>10.2950267791748</v>
+        <v>10.2950277328491</v>
       </c>
       <c r="H255" t="n">
         <v>668230</v>
@@ -7880,7 +7880,7 @@
         <v>10.8299999237061</v>
       </c>
       <c r="G259" t="n">
-        <v>10.2477149963379</v>
+        <v>10.2477159500122</v>
       </c>
       <c r="H259" t="n">
         <v>180911</v>
@@ -7909,7 +7909,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G260" t="n">
-        <v>10.2382535934448</v>
+        <v>10.2382526397705</v>
       </c>
       <c r="H260" t="n">
         <v>290152</v>
@@ -7967,7 +7967,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G262" t="n">
-        <v>10.2382535934448</v>
+        <v>10.2382526397705</v>
       </c>
       <c r="H262" t="n">
         <v>242006</v>
@@ -8141,7 +8141,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G268" t="n">
-        <v>10.0982227325439</v>
+        <v>10.0982236862183</v>
       </c>
       <c r="H268" t="n">
         <v>162147</v>
@@ -8344,7 +8344,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G275" t="n">
-        <v>10.3310346603394</v>
+        <v>10.3310356140137</v>
       </c>
       <c r="H275" t="n">
         <v>417991</v>
@@ -8576,7 +8576,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G283" t="n">
-        <v>10.6220502853394</v>
+        <v>10.6220512390137</v>
       </c>
       <c r="H283" t="n">
         <v>129742</v>
@@ -8634,7 +8634,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G285" t="n">
-        <v>10.5638484954834</v>
+        <v>10.5638475418091</v>
       </c>
       <c r="H285" t="n">
         <v>180726</v>
@@ -8692,7 +8692,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G287" t="n">
-        <v>10.2534313201904</v>
+        <v>10.2534303665161</v>
       </c>
       <c r="H287" t="n">
         <v>235286</v>
@@ -8721,7 +8721,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G288" t="n">
-        <v>10.3116340637207</v>
+        <v>10.311635017395</v>
       </c>
       <c r="H288" t="n">
         <v>127440</v>
@@ -8779,7 +8779,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G290" t="n">
-        <v>10.4377412796021</v>
+        <v>10.4377422332764</v>
       </c>
       <c r="H290" t="n">
         <v>97733</v>
@@ -8895,7 +8895,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G294" t="n">
-        <v>10.806360244751</v>
+        <v>10.8063611984253</v>
       </c>
       <c r="H294" t="n">
         <v>209159</v>
@@ -8982,7 +8982,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G297" t="n">
-        <v>10.951868057251</v>
+        <v>10.9518671035767</v>
       </c>
       <c r="H297" t="n">
         <v>175726</v>
@@ -9011,7 +9011,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G298" t="n">
-        <v>10.7578582763672</v>
+        <v>10.7578573226929</v>
       </c>
       <c r="H298" t="n">
         <v>301876</v>
@@ -9214,7 +9214,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G305" t="n">
-        <v>11.5823993682861</v>
+        <v>11.5824003219604</v>
       </c>
       <c r="H305" t="n">
         <v>274687</v>
@@ -9475,7 +9475,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G314" t="n">
-        <v>11.3398866653442</v>
+        <v>11.3398876190186</v>
       </c>
       <c r="H314" t="n">
         <v>110179</v>
@@ -9562,7 +9562,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G317" t="n">
-        <v>11.2525844573975</v>
+        <v>11.2525835037231</v>
       </c>
       <c r="H317" t="n">
         <v>381622</v>
@@ -9649,7 +9649,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G320" t="n">
-        <v>10.951868057251</v>
+        <v>10.9518671035767</v>
       </c>
       <c r="H320" t="n">
         <v>279934</v>
@@ -9707,7 +9707,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G322" t="n">
-        <v>10.9712696075439</v>
+        <v>10.9712686538696</v>
       </c>
       <c r="H322" t="n">
         <v>185383</v>
@@ -9765,7 +9765,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G324" t="n">
-        <v>10.7481575012207</v>
+        <v>10.7481565475464</v>
       </c>
       <c r="H324" t="n">
         <v>184196</v>
@@ -9852,7 +9852,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>10.7190551757812</v>
+        <v>10.7190561294556</v>
       </c>
       <c r="H327" t="n">
         <v>80274</v>
@@ -9881,7 +9881,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G328" t="n">
-        <v>10.7578582763672</v>
+        <v>10.7578573226929</v>
       </c>
       <c r="H328" t="n">
         <v>81593</v>
@@ -9910,7 +9910,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>10.8160600662231</v>
+        <v>10.8160610198975</v>
       </c>
       <c r="H329" t="n">
         <v>255497</v>
@@ -10055,7 +10055,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G334" t="n">
-        <v>11.1361770629883</v>
+        <v>11.136176109314</v>
       </c>
       <c r="H334" t="n">
         <v>92993</v>
@@ -10084,7 +10084,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G335" t="n">
-        <v>11.1361770629883</v>
+        <v>11.136176109314</v>
       </c>
       <c r="H335" t="n">
         <v>109603</v>
@@ -10258,7 +10258,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G341" t="n">
-        <v>11.4077911376953</v>
+        <v>11.4077920913696</v>
       </c>
       <c r="H341" t="n">
         <v>275168</v>
@@ -10374,7 +10374,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G345" t="n">
-        <v>10.9712696075439</v>
+        <v>10.9712686538696</v>
       </c>
       <c r="H345" t="n">
         <v>250890</v>
@@ -10403,7 +10403,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G346" t="n">
-        <v>10.9615688323975</v>
+        <v>10.9615678787231</v>
       </c>
       <c r="H346" t="n">
         <v>157159</v>
@@ -10432,7 +10432,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G347" t="n">
-        <v>11.0003700256348</v>
+        <v>11.0003709793091</v>
       </c>
       <c r="H347" t="n">
         <v>187467</v>
@@ -10461,7 +10461,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G348" t="n">
-        <v>11.0003700256348</v>
+        <v>11.0003709793091</v>
       </c>
       <c r="H348" t="n">
         <v>109481</v>
@@ -10722,7 +10722,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G357" t="n">
-        <v>11.0585737228394</v>
+        <v>11.058572769165</v>
       </c>
       <c r="H357" t="n">
         <v>184343</v>
@@ -10780,7 +10780,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G359" t="n">
-        <v>11.0003700256348</v>
+        <v>11.0003709793091</v>
       </c>
       <c r="H359" t="n">
         <v>186510</v>
@@ -10867,7 +10867,7 @@
         <v>11.25</v>
       </c>
       <c r="G362" t="n">
-        <v>10.913064956665</v>
+        <v>10.9130659103394</v>
       </c>
       <c r="H362" t="n">
         <v>440278</v>
@@ -10925,7 +10925,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G364" t="n">
-        <v>11.1458778381348</v>
+        <v>11.1458768844604</v>
       </c>
       <c r="H364" t="n">
         <v>188007</v>
@@ -11012,7 +11012,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>11.0585737228394</v>
+        <v>11.058572769165</v>
       </c>
       <c r="H367" t="n">
         <v>195723</v>
@@ -11070,7 +11070,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G369" t="n">
-        <v>11.1458778381348</v>
+        <v>11.1458768844604</v>
       </c>
       <c r="H369" t="n">
         <v>107932</v>
@@ -11128,7 +11128,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G371" t="n">
-        <v>11.1361770629883</v>
+        <v>11.136176109314</v>
       </c>
       <c r="H371" t="n">
         <v>118399</v>
@@ -11186,7 +11186,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G373" t="n">
-        <v>11.0197706222534</v>
+        <v>11.0197715759277</v>
       </c>
       <c r="H373" t="n">
         <v>147161</v>
@@ -11302,7 +11302,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G377" t="n">
-        <v>11.0197706222534</v>
+        <v>11.0197715759277</v>
       </c>
       <c r="H377" t="n">
         <v>130368</v>
@@ -11476,7 +11476,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G383" t="n">
-        <v>11.1361770629883</v>
+        <v>11.136176109314</v>
       </c>
       <c r="H383" t="n">
         <v>194313</v>
@@ -11592,7 +11592,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G387" t="n">
-        <v>11.1749792098999</v>
+        <v>11.1749801635742</v>
       </c>
       <c r="H387" t="n">
         <v>197901</v>
@@ -11650,7 +11650,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G389" t="n">
-        <v>11.4465942382812</v>
+        <v>11.4465932846069</v>
       </c>
       <c r="H389" t="n">
         <v>259214</v>
@@ -11737,7 +11737,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G392" t="n">
-        <v>11.8540153503418</v>
+        <v>11.8540143966675</v>
       </c>
       <c r="H392" t="n">
         <v>194096</v>
@@ -11795,7 +11795,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G394" t="n">
-        <v>11.6988067626953</v>
+        <v>11.6988077163696</v>
       </c>
       <c r="H394" t="n">
         <v>171327</v>
@@ -11911,7 +11911,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G398" t="n">
-        <v>11.6309032440186</v>
+        <v>11.6309022903442</v>
       </c>
       <c r="H398" t="n">
         <v>192088</v>
@@ -11940,7 +11940,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G399" t="n">
-        <v>11.5823993682861</v>
+        <v>11.5824003219604</v>
       </c>
       <c r="H399" t="n">
         <v>137161</v>
@@ -12056,7 +12056,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G403" t="n">
-        <v>12.1935319900513</v>
+        <v>12.193531036377</v>
       </c>
       <c r="H403" t="n">
         <v>108069</v>
@@ -12114,7 +12114,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G405" t="n">
-        <v>12.1935319900513</v>
+        <v>12.193531036377</v>
       </c>
       <c r="H405" t="n">
         <v>135114</v>
@@ -12172,7 +12172,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G407" t="n">
-        <v>12.2226333618164</v>
+        <v>12.2226343154907</v>
       </c>
       <c r="H407" t="n">
         <v>185001</v>
@@ -12201,7 +12201,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G408" t="n">
-        <v>12.2517347335815</v>
+        <v>12.2517356872559</v>
       </c>
       <c r="H408" t="n">
         <v>172512</v>
@@ -12288,7 +12288,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G411" t="n">
-        <v>12.4651460647583</v>
+        <v>12.4651470184326</v>
       </c>
       <c r="H411" t="n">
         <v>133030</v>
@@ -12317,7 +12317,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G412" t="n">
-        <v>12.3875427246094</v>
+        <v>12.3875417709351</v>
       </c>
       <c r="H412" t="n">
         <v>148541</v>
@@ -12520,7 +12520,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G419" t="n">
-        <v>12.2517347335815</v>
+        <v>12.2517356872559</v>
       </c>
       <c r="H419" t="n">
         <v>165954</v>
@@ -12549,7 +12549,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G420" t="n">
-        <v>12.2226333618164</v>
+        <v>12.2226343154907</v>
       </c>
       <c r="H420" t="n">
         <v>258706</v>
@@ -12607,7 +12607,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G422" t="n">
-        <v>12.2129335403442</v>
+        <v>12.2129325866699</v>
       </c>
       <c r="H422" t="n">
         <v>137376</v>
@@ -12636,7 +12636,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G423" t="n">
-        <v>12.3875427246094</v>
+        <v>12.3875417709351</v>
       </c>
       <c r="H423" t="n">
         <v>99466</v>
@@ -12723,7 +12723,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G426" t="n">
-        <v>12.5427513122559</v>
+        <v>12.5427503585815</v>
       </c>
       <c r="H426" t="n">
         <v>197307</v>
@@ -12752,7 +12752,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G427" t="n">
-        <v>12.630054473877</v>
+        <v>12.6300554275513</v>
       </c>
       <c r="H427" t="n">
         <v>148262</v>
@@ -12839,7 +12839,7 @@
         <v>13</v>
       </c>
       <c r="G430" t="n">
-        <v>12.610652923584</v>
+        <v>12.6106538772583</v>
       </c>
       <c r="H430" t="n">
         <v>1807764</v>
@@ -12897,7 +12897,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G432" t="n">
-        <v>12.3972425460815</v>
+        <v>12.3972415924072</v>
       </c>
       <c r="H432" t="n">
         <v>1234024</v>
@@ -12955,7 +12955,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G434" t="n">
-        <v>12.6882581710815</v>
+        <v>12.6882572174072</v>
       </c>
       <c r="H434" t="n">
         <v>465320</v>
@@ -13013,7 +13013,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G436" t="n">
-        <v>13.1538820266724</v>
+        <v>13.1538829803467</v>
       </c>
       <c r="H436" t="n">
         <v>425963</v>
@@ -13274,7 +13274,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G445" t="n">
-        <v>13.7844152450562</v>
+        <v>13.7844142913818</v>
       </c>
       <c r="H445" t="n">
         <v>236771</v>
@@ -13303,7 +13303,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G446" t="n">
-        <v>14.3373432159424</v>
+        <v>14.3373422622681</v>
       </c>
       <c r="H446" t="n">
         <v>473165</v>
@@ -13332,7 +13332,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G447" t="n">
-        <v>14.4537496566772</v>
+        <v>14.4537487030029</v>
       </c>
       <c r="H447" t="n">
         <v>380386</v>
@@ -13361,7 +13361,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G448" t="n">
-        <v>14.667160987854</v>
+        <v>14.6671600341797</v>
       </c>
       <c r="H448" t="n">
         <v>267462</v>
@@ -13419,7 +13419,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G450" t="n">
-        <v>14.8029670715332</v>
+        <v>14.8029680252075</v>
       </c>
       <c r="H450" t="n">
         <v>391347</v>
@@ -13622,7 +13622,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G457" t="n">
-        <v>16.0446338653564</v>
+        <v>16.0446319580078</v>
       </c>
       <c r="H457" t="n">
         <v>378598</v>
@@ -13680,7 +13680,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G459" t="n">
-        <v>15.9573268890381</v>
+        <v>15.9573278427124</v>
       </c>
       <c r="H459" t="n">
         <v>261224</v>
@@ -13796,7 +13796,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G463" t="n">
-        <v>16.0252304077148</v>
+        <v>16.0252323150635</v>
       </c>
       <c r="H463" t="n">
         <v>392686</v>
@@ -13825,7 +13825,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G464" t="n">
-        <v>15.6857128143311</v>
+        <v>15.6857137680054</v>
       </c>
       <c r="H464" t="n">
         <v>532461</v>
@@ -14028,7 +14028,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G471" t="n">
-        <v>15.870023727417</v>
+        <v>15.8700227737427</v>
       </c>
       <c r="H471" t="n">
         <v>880362</v>
@@ -14115,7 +14115,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G474" t="n">
-        <v>16.9273796081543</v>
+        <v>16.9273777008057</v>
       </c>
       <c r="H474" t="n">
         <v>620043</v>
@@ -14260,7 +14260,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G479" t="n">
-        <v>17.5870094299316</v>
+        <v>17.5870113372803</v>
       </c>
       <c r="H479" t="n">
         <v>473621</v>
@@ -14289,7 +14289,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G480" t="n">
-        <v>17.5870094299316</v>
+        <v>17.5870113372803</v>
       </c>
       <c r="H480" t="n">
         <v>417252</v>
@@ -14347,7 +14347,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G482" t="n">
-        <v>17.1601886749268</v>
+        <v>17.1601905822754</v>
       </c>
       <c r="H482" t="n">
         <v>353508</v>
@@ -14405,7 +14405,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G484" t="n">
-        <v>17.7519187927246</v>
+        <v>17.7519207000732</v>
       </c>
       <c r="H484" t="n">
         <v>342388</v>
@@ -14434,7 +14434,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G485" t="n">
-        <v>17.7422218322754</v>
+        <v>17.7422199249268</v>
       </c>
       <c r="H485" t="n">
         <v>271126</v>
@@ -14521,7 +14521,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G488" t="n">
-        <v>17.9071292877197</v>
+        <v>17.9071273803711</v>
       </c>
       <c r="H488" t="n">
         <v>372109</v>
@@ -14550,7 +14550,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G489" t="n">
-        <v>18.3727531433105</v>
+        <v>18.3727512359619</v>
       </c>
       <c r="H489" t="n">
         <v>455016</v>
@@ -14608,7 +14608,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>16.8303718566895</v>
+        <v>16.8303737640381</v>
       </c>
       <c r="H491" t="n">
         <v>1164243</v>
@@ -14695,7 +14695,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G494" t="n">
-        <v>17.1601886749268</v>
+        <v>17.1601905822754</v>
       </c>
       <c r="H494" t="n">
         <v>564420</v>
@@ -14898,7 +14898,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G501" t="n">
-        <v>18.8480777740479</v>
+        <v>18.8480758666992</v>
       </c>
       <c r="H501" t="n">
         <v>377971</v>
@@ -14927,7 +14927,7 @@
         <v>19.4699993133545</v>
       </c>
       <c r="G502" t="n">
-        <v>18.8868789672852</v>
+        <v>18.8868770599365</v>
       </c>
       <c r="H502" t="n">
         <v>436832</v>
@@ -14956,7 +14956,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G503" t="n">
-        <v>19.0226860046387</v>
+        <v>19.0226879119873</v>
       </c>
       <c r="H503" t="n">
         <v>218294</v>
@@ -15014,7 +15014,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G505" t="n">
-        <v>19.478609085083</v>
+        <v>19.4786109924316</v>
       </c>
       <c r="H505" t="n">
         <v>375456</v>
@@ -15043,7 +15043,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G506" t="n">
-        <v>19.45920753479</v>
+        <v>19.4592094421387</v>
       </c>
       <c r="H506" t="n">
         <v>430857</v>
@@ -15072,7 +15072,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G507" t="n">
-        <v>19.4398097991943</v>
+        <v>19.4398078918457</v>
       </c>
       <c r="H507" t="n">
         <v>573705</v>
@@ -15130,7 +15130,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G509" t="n">
-        <v>20.3128547668457</v>
+        <v>20.3128528594971</v>
       </c>
       <c r="H509" t="n">
         <v>845381</v>
@@ -15159,7 +15159,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G510" t="n">
-        <v>20.2352485656738</v>
+        <v>20.2352504730225</v>
       </c>
       <c r="H510" t="n">
         <v>628106</v>
@@ -15188,7 +15188,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G511" t="n">
-        <v>19.9248352050781</v>
+        <v>19.9248332977295</v>
       </c>
       <c r="H511" t="n">
         <v>774008</v>
@@ -15217,7 +15217,7 @@
         <v>20</v>
       </c>
       <c r="G512" t="n">
-        <v>19.4010066986084</v>
+        <v>19.4010047912598</v>
       </c>
       <c r="H512" t="n">
         <v>769373</v>
@@ -15304,7 +15304,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>21.6321201324463</v>
+        <v>21.6321220397949</v>
       </c>
       <c r="H515" t="n">
         <v>2197577</v>
@@ -15362,7 +15362,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G517" t="n">
-        <v>22.1171474456787</v>
+        <v>22.1171455383301</v>
       </c>
       <c r="H517" t="n">
         <v>555528</v>
@@ -15391,7 +15391,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G518" t="n">
-        <v>21.9619369506836</v>
+        <v>21.9619388580322</v>
       </c>
       <c r="H518" t="n">
         <v>611058</v>
@@ -25982,6 +25982,35 @@
         <v>872309</v>
       </c>
       <c r="I883" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="s">
+        <v>9</v>
+      </c>
+      <c r="B884" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C884" t="n">
+        <v>24.7700004577637</v>
+      </c>
+      <c r="D884" t="n">
+        <v>25.2900009155273</v>
+      </c>
+      <c r="E884" t="n">
+        <v>24.7199993133545</v>
+      </c>
+      <c r="F884" t="n">
+        <v>25.1399993896484</v>
+      </c>
+      <c r="G884" t="n">
+        <v>25.1399993896484</v>
+      </c>
+      <c r="H884" t="n">
+        <v>965672</v>
+      </c>
+      <c r="I884" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LTMC.MI.xlsx
+++ b/data/LTMC.MI.xlsx
@@ -427,7 +427,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2" t="n">
-        <v>7.75912046432495</v>
+        <v>7.75911951065063</v>
       </c>
       <c r="H2" t="n">
         <v>13006120</v>
@@ -456,7 +456,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G3" t="n">
-        <v>7.82535648345947</v>
+        <v>7.82535743713379</v>
       </c>
       <c r="H3" t="n">
         <v>2759922</v>
@@ -485,7 +485,7 @@
         <v>8.44600009918213</v>
       </c>
       <c r="G4" t="n">
-        <v>7.99189424514771</v>
+        <v>7.99189376831055</v>
       </c>
       <c r="H4" t="n">
         <v>1476712</v>
@@ -572,7 +572,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G7" t="n">
-        <v>7.92944240570068</v>
+        <v>7.92944288253784</v>
       </c>
       <c r="H7" t="n">
         <v>640304</v>
@@ -630,7 +630,7 @@
         <v>8.25</v>
       </c>
       <c r="G9" t="n">
-        <v>7.80643177032471</v>
+        <v>7.80643129348755</v>
       </c>
       <c r="H9" t="n">
         <v>1073912</v>
@@ -659,7 +659,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G10" t="n">
-        <v>7.99567794799805</v>
+        <v>7.99567842483521</v>
       </c>
       <c r="H10" t="n">
         <v>1947465</v>
@@ -862,7 +862,7 @@
         <v>7.72300004959106</v>
       </c>
       <c r="G17" t="n">
-        <v>7.30776643753052</v>
+        <v>7.30776596069336</v>
       </c>
       <c r="H17" t="n">
         <v>588439</v>
@@ -891,7 +891,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G18" t="n">
-        <v>7.2670783996582</v>
+        <v>7.26707792282104</v>
       </c>
       <c r="H18" t="n">
         <v>228832</v>
@@ -949,7 +949,7 @@
         <v>7.80100011825562</v>
       </c>
       <c r="G20" t="n">
-        <v>7.38157224655151</v>
+        <v>7.38157272338867</v>
       </c>
       <c r="H20" t="n">
         <v>40924</v>
@@ -978,7 +978,7 @@
         <v>7.71199989318848</v>
       </c>
       <c r="G21" t="n">
-        <v>7.2973575592041</v>
+        <v>7.29735803604126</v>
       </c>
       <c r="H21" t="n">
         <v>118298</v>
@@ -1094,7 +1094,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G25" t="n">
-        <v>7.28600311279297</v>
+        <v>7.28600215911865</v>
       </c>
       <c r="H25" t="n">
         <v>218758</v>
@@ -1152,7 +1152,7 @@
         <v>8.12600040435791</v>
       </c>
       <c r="G27" t="n">
-        <v>7.68909931182861</v>
+        <v>7.68909883499146</v>
       </c>
       <c r="H27" t="n">
         <v>1170934</v>
@@ -1181,7 +1181,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G28" t="n">
-        <v>7.76858282089233</v>
+        <v>7.76858234405518</v>
       </c>
       <c r="H28" t="n">
         <v>1704311</v>
@@ -1268,7 +1268,7 @@
         <v>8.23200035095215</v>
       </c>
       <c r="G31" t="n">
-        <v>7.78939962387085</v>
+        <v>7.78940010070801</v>
       </c>
       <c r="H31" t="n">
         <v>749433</v>
@@ -1297,7 +1297,7 @@
         <v>8.16199970245361</v>
       </c>
       <c r="G32" t="n">
-        <v>7.72316360473633</v>
+        <v>7.72316265106201</v>
       </c>
       <c r="H32" t="n">
         <v>440552</v>
@@ -1326,7 +1326,7 @@
         <v>8.21399974822998</v>
       </c>
       <c r="G33" t="n">
-        <v>7.77236700057983</v>
+        <v>7.77236652374268</v>
       </c>
       <c r="H33" t="n">
         <v>327710</v>
@@ -1355,7 +1355,7 @@
         <v>8.41300010681152</v>
       </c>
       <c r="G34" t="n">
-        <v>7.96066761016846</v>
+        <v>7.96066808700562</v>
       </c>
       <c r="H34" t="n">
         <v>540974</v>
@@ -1413,7 +1413,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G36" t="n">
-        <v>7.8111629486084</v>
+        <v>7.81116342544556</v>
       </c>
       <c r="H36" t="n">
         <v>219714</v>
@@ -1442,7 +1442,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G37" t="n">
-        <v>7.92944240570068</v>
+        <v>7.92944288253784</v>
       </c>
       <c r="H37" t="n">
         <v>223839</v>
@@ -1471,7 +1471,7 @@
         <v>8.4379997253418</v>
       </c>
       <c r="G38" t="n">
-        <v>7.98432350158691</v>
+        <v>7.98432397842407</v>
       </c>
       <c r="H38" t="n">
         <v>178091</v>
@@ -1500,7 +1500,7 @@
         <v>8.43299961090088</v>
       </c>
       <c r="G39" t="n">
-        <v>7.97959184646606</v>
+        <v>7.97959136962891</v>
       </c>
       <c r="H39" t="n">
         <v>99001</v>
@@ -1529,7 +1529,7 @@
         <v>8.43599987030029</v>
       </c>
       <c r="G40" t="n">
-        <v>7.98243093490601</v>
+        <v>7.98243045806885</v>
       </c>
       <c r="H40" t="n">
         <v>155784</v>
@@ -1558,7 +1558,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G41" t="n">
-        <v>7.92944240570068</v>
+        <v>7.92944288253784</v>
       </c>
       <c r="H41" t="n">
         <v>133019</v>
@@ -1587,7 +1587,7 @@
         <v>8.41300010681152</v>
       </c>
       <c r="G42" t="n">
-        <v>7.96066761016846</v>
+        <v>7.96066808700562</v>
       </c>
       <c r="H42" t="n">
         <v>122155</v>
@@ -1616,7 +1616,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>8.23223686218262</v>
+        <v>8.23223781585693</v>
       </c>
       <c r="H43" t="n">
         <v>362592</v>
@@ -1674,7 +1674,7 @@
         <v>8.5620002746582</v>
       </c>
       <c r="G45" t="n">
-        <v>8.10165691375732</v>
+        <v>8.10165596008301</v>
       </c>
       <c r="H45" t="n">
         <v>252798</v>
@@ -1703,7 +1703,7 @@
         <v>8.69499969482422</v>
       </c>
       <c r="G46" t="n">
-        <v>8.22750663757324</v>
+        <v>8.22750473022461</v>
       </c>
       <c r="H46" t="n">
         <v>188291</v>
@@ -1761,7 +1761,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G48" t="n">
-        <v>7.9436354637146</v>
+        <v>7.94363641738892</v>
       </c>
       <c r="H48" t="n">
         <v>297588</v>
@@ -1790,7 +1790,7 @@
         <v>8.78800010681152</v>
       </c>
       <c r="G49" t="n">
-        <v>8.31550598144531</v>
+        <v>8.315505027771</v>
       </c>
       <c r="H49" t="n">
         <v>417701</v>
@@ -1819,7 +1819,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G50" t="n">
-        <v>8.49718284606934</v>
+        <v>8.49718189239502</v>
       </c>
       <c r="H50" t="n">
         <v>475388</v>
@@ -1877,7 +1877,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G52" t="n">
-        <v>8.7905158996582</v>
+        <v>8.79051494598389</v>
       </c>
       <c r="H52" t="n">
         <v>1027347</v>
@@ -1906,7 +1906,7 @@
         <v>9.4689998626709</v>
       </c>
       <c r="G53" t="n">
-        <v>8.9598913192749</v>
+        <v>8.95989036560059</v>
       </c>
       <c r="H53" t="n">
         <v>1003139</v>
@@ -1935,7 +1935,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G54" t="n">
-        <v>8.97029972076416</v>
+        <v>8.97029876708984</v>
       </c>
       <c r="H54" t="n">
         <v>321248</v>
@@ -2022,7 +2022,7 @@
         <v>9.38399982452393</v>
       </c>
       <c r="G57" t="n">
-        <v>8.87946033477783</v>
+        <v>8.87946128845215</v>
       </c>
       <c r="H57" t="n">
         <v>292101</v>
@@ -2080,7 +2080,7 @@
         <v>9.27099990844727</v>
       </c>
       <c r="G59" t="n">
-        <v>8.772536277771</v>
+        <v>8.77253723144531</v>
       </c>
       <c r="H59" t="n">
         <v>287274</v>
@@ -2109,7 +2109,7 @@
         <v>9.37600040435791</v>
       </c>
       <c r="G60" t="n">
-        <v>8.87189197540283</v>
+        <v>8.87189292907715</v>
       </c>
       <c r="H60" t="n">
         <v>240981</v>
@@ -2225,7 +2225,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G64" t="n">
-        <v>8.79997825622559</v>
+        <v>8.79997730255127</v>
       </c>
       <c r="H64" t="n">
         <v>396592</v>
@@ -2254,7 +2254,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G65" t="n">
-        <v>8.9419116973877</v>
+        <v>8.94191360473633</v>
       </c>
       <c r="H65" t="n">
         <v>900757</v>
@@ -2370,7 +2370,7 @@
         <v>9.30300045013428</v>
       </c>
       <c r="G69" t="n">
-        <v>8.80281734466553</v>
+        <v>8.80281639099121</v>
       </c>
       <c r="H69" t="n">
         <v>181453</v>
@@ -2399,7 +2399,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G70" t="n">
-        <v>8.87567710876465</v>
+        <v>8.87567615509033</v>
       </c>
       <c r="H70" t="n">
         <v>257403</v>
@@ -2428,7 +2428,7 @@
         <v>9.30300045013428</v>
       </c>
       <c r="G71" t="n">
-        <v>8.80281734466553</v>
+        <v>8.80281639099121</v>
       </c>
       <c r="H71" t="n">
         <v>228312</v>
@@ -2457,7 +2457,7 @@
         <v>9.31900024414062</v>
       </c>
       <c r="G72" t="n">
-        <v>8.81795692443848</v>
+        <v>8.81795597076416</v>
       </c>
       <c r="H72" t="n">
         <v>303822</v>
@@ -2486,7 +2486,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G73" t="n">
-        <v>8.79997825622559</v>
+        <v>8.79997730255127</v>
       </c>
       <c r="H73" t="n">
         <v>161362</v>
@@ -2515,7 +2515,7 @@
         <v>9.14700031280518</v>
       </c>
       <c r="G74" t="n">
-        <v>8.65520286560059</v>
+        <v>8.6552038192749</v>
       </c>
       <c r="H74" t="n">
         <v>250420</v>
@@ -2602,7 +2602,7 @@
         <v>9.12600040435791</v>
       </c>
       <c r="G77" t="n">
-        <v>8.63533306121826</v>
+        <v>8.63533401489258</v>
       </c>
       <c r="H77" t="n">
         <v>248031</v>
@@ -2660,7 +2660,7 @@
         <v>9.10799980163574</v>
       </c>
       <c r="G79" t="n">
-        <v>8.61830043792725</v>
+        <v>8.61829948425293</v>
       </c>
       <c r="H79" t="n">
         <v>127272</v>
@@ -2689,7 +2689,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G80" t="n">
-        <v>8.67696762084961</v>
+        <v>8.67696666717529</v>
       </c>
       <c r="H80" t="n">
         <v>180085</v>
@@ -2863,7 +2863,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G86" t="n">
-        <v>8.83782768249512</v>
+        <v>8.8378267288208</v>
       </c>
       <c r="H86" t="n">
         <v>322079</v>
@@ -2892,7 +2892,7 @@
         <v>9</v>
       </c>
       <c r="G87" t="n">
-        <v>8.5161075592041</v>
+        <v>8.51610660552979</v>
       </c>
       <c r="H87" t="n">
         <v>2756951</v>
@@ -2921,7 +2921,7 @@
         <v>9.10799980163574</v>
       </c>
       <c r="G88" t="n">
-        <v>8.61830043792725</v>
+        <v>8.61829948425293</v>
       </c>
       <c r="H88" t="n">
         <v>496089</v>
@@ -2950,7 +2950,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G89" t="n">
-        <v>8.74320316314697</v>
+        <v>8.74320411682129</v>
       </c>
       <c r="H89" t="n">
         <v>146265</v>
@@ -3066,7 +3066,7 @@
         <v>9.22700023651123</v>
       </c>
       <c r="G93" t="n">
-        <v>8.73090267181396</v>
+        <v>8.73090362548828</v>
       </c>
       <c r="H93" t="n">
         <v>184727</v>
@@ -3095,7 +3095,7 @@
         <v>9.02299976348877</v>
       </c>
       <c r="G94" t="n">
-        <v>8.53786945343018</v>
+        <v>8.53787040710449</v>
       </c>
       <c r="H94" t="n">
         <v>577462</v>
@@ -3153,7 +3153,7 @@
         <v>9</v>
       </c>
       <c r="G96" t="n">
-        <v>8.5161075592041</v>
+        <v>8.51610660552979</v>
       </c>
       <c r="H96" t="n">
         <v>322675</v>
@@ -3182,7 +3182,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>8.67696762084961</v>
+        <v>8.67696666717529</v>
       </c>
       <c r="H97" t="n">
         <v>420414</v>
@@ -3269,7 +3269,7 @@
         <v>8.9069995880127</v>
       </c>
       <c r="G100" t="n">
-        <v>8.42810726165771</v>
+        <v>8.42810821533203</v>
       </c>
       <c r="H100" t="n">
         <v>428743</v>
@@ -3298,7 +3298,7 @@
         <v>9.01900005340576</v>
       </c>
       <c r="G101" t="n">
-        <v>8.53408622741699</v>
+        <v>8.53408527374268</v>
       </c>
       <c r="H101" t="n">
         <v>120168</v>
@@ -3327,7 +3327,7 @@
         <v>8.89700031280518</v>
       </c>
       <c r="G102" t="n">
-        <v>8.41864490509033</v>
+        <v>8.41864585876465</v>
       </c>
       <c r="H102" t="n">
         <v>170277</v>
@@ -3414,7 +3414,7 @@
         <v>8.53899955749512</v>
       </c>
       <c r="G105" t="n">
-        <v>8.0798921585083</v>
+        <v>8.07989311218262</v>
       </c>
       <c r="H105" t="n">
         <v>153907</v>
@@ -3588,7 +3588,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G111" t="n">
-        <v>8.17546367645264</v>
+        <v>8.17546272277832</v>
       </c>
       <c r="H111" t="n">
         <v>213577</v>
@@ -3733,7 +3733,7 @@
         <v>8.75500011444092</v>
       </c>
       <c r="G116" t="n">
-        <v>8.28427982330322</v>
+        <v>8.28428077697754</v>
       </c>
       <c r="H116" t="n">
         <v>68870</v>
@@ -3791,7 +3791,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G118" t="n">
-        <v>8.23223686218262</v>
+        <v>8.23223781585693</v>
       </c>
       <c r="H118" t="n">
         <v>188950</v>
@@ -3820,7 +3820,7 @@
         <v>8.7209997177124</v>
       </c>
       <c r="G119" t="n">
-        <v>8.25210857391357</v>
+        <v>8.25210762023926</v>
       </c>
       <c r="H119" t="n">
         <v>127697</v>
@@ -3849,7 +3849,7 @@
         <v>8.75</v>
       </c>
       <c r="G120" t="n">
-        <v>8.27954864501953</v>
+        <v>8.27954769134521</v>
       </c>
       <c r="H120" t="n">
         <v>97384</v>
@@ -3936,7 +3936,7 @@
         <v>8.7810001373291</v>
       </c>
       <c r="G123" t="n">
-        <v>8.30888271331787</v>
+        <v>8.30888175964355</v>
       </c>
       <c r="H123" t="n">
         <v>162637</v>
@@ -3965,7 +3965,7 @@
         <v>9</v>
       </c>
       <c r="G124" t="n">
-        <v>8.5161075592041</v>
+        <v>8.51610660552979</v>
       </c>
       <c r="H124" t="n">
         <v>178371</v>
@@ -4023,7 +4023,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G126" t="n">
-        <v>8.36470985412598</v>
+        <v>8.36470890045166</v>
       </c>
       <c r="H126" t="n">
         <v>152716</v>
@@ -4081,7 +4081,7 @@
         <v>8.82100009918213</v>
       </c>
       <c r="G128" t="n">
-        <v>8.3467321395874</v>
+        <v>8.34673118591309</v>
       </c>
       <c r="H128" t="n">
         <v>174329</v>
@@ -4139,7 +4139,7 @@
         <v>8.93599987030029</v>
       </c>
       <c r="G130" t="n">
-        <v>8.45554733276367</v>
+        <v>8.45554828643799</v>
       </c>
       <c r="H130" t="n">
         <v>394314</v>
@@ -4255,7 +4255,7 @@
         <v>9.05300045013428</v>
       </c>
       <c r="G134" t="n">
-        <v>8.56625843048096</v>
+        <v>8.56625747680664</v>
       </c>
       <c r="H134" t="n">
         <v>123966</v>
@@ -4284,7 +4284,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G135" t="n">
-        <v>8.612624168396</v>
+        <v>8.61262321472168</v>
       </c>
       <c r="H135" t="n">
         <v>75451</v>
@@ -4342,7 +4342,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G137" t="n">
-        <v>8.612624168396</v>
+        <v>8.61262321472168</v>
       </c>
       <c r="H137" t="n">
         <v>197102</v>
@@ -4400,7 +4400,7 @@
         <v>9</v>
       </c>
       <c r="G139" t="n">
-        <v>8.5161075592041</v>
+        <v>8.51610660552979</v>
       </c>
       <c r="H139" t="n">
         <v>111082</v>
@@ -4603,7 +4603,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G146" t="n">
-        <v>8.81890296936035</v>
+        <v>8.81890201568604</v>
       </c>
       <c r="H146" t="n">
         <v>95465</v>
@@ -4661,7 +4661,7 @@
         <v>9.36699962615967</v>
       </c>
       <c r="G148" t="n">
-        <v>8.86337566375732</v>
+        <v>8.86337375640869</v>
       </c>
       <c r="H148" t="n">
         <v>76421</v>
@@ -4748,7 +4748,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G151" t="n">
-        <v>8.82836532592773</v>
+        <v>8.82836437225342</v>
       </c>
       <c r="H151" t="n">
         <v>103859</v>
@@ -4864,7 +4864,7 @@
         <v>9.42599964141846</v>
       </c>
       <c r="G155" t="n">
-        <v>8.91920280456543</v>
+        <v>8.91920185089111</v>
       </c>
       <c r="H155" t="n">
         <v>113950</v>
@@ -5038,7 +5038,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G161" t="n">
-        <v>8.9419116973877</v>
+        <v>8.94191360473633</v>
       </c>
       <c r="H161" t="n">
         <v>242695</v>
@@ -5096,7 +5096,7 @@
         <v>9.79300022125244</v>
       </c>
       <c r="G163" t="n">
-        <v>9.26647186279297</v>
+        <v>9.26646995544434</v>
       </c>
       <c r="H163" t="n">
         <v>2495031</v>
@@ -5154,7 +5154,7 @@
         <v>9.80599975585938</v>
       </c>
       <c r="G165" t="n">
-        <v>9.27877235412598</v>
+        <v>9.27877140045166</v>
       </c>
       <c r="H165" t="n">
         <v>183228</v>
@@ -5270,7 +5270,7 @@
         <v>9.84700012207031</v>
       </c>
       <c r="G169" t="n">
-        <v>9.31756687164307</v>
+        <v>9.31756782531738</v>
       </c>
       <c r="H169" t="n">
         <v>94635</v>
@@ -5531,7 +5531,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>9.18793392181396</v>
+        <v>9.18793296813965</v>
       </c>
       <c r="H178" t="n">
         <v>132214</v>
@@ -5676,7 +5676,7 @@
         <v>10.4580001831055</v>
       </c>
       <c r="G183" t="n">
-        <v>9.89571666717529</v>
+        <v>9.89571762084961</v>
       </c>
       <c r="H183" t="n">
         <v>362012</v>
@@ -5705,7 +5705,7 @@
         <v>10.1619997024536</v>
       </c>
       <c r="G184" t="n">
-        <v>9.61563014984131</v>
+        <v>9.61563110351562</v>
       </c>
       <c r="H184" t="n">
         <v>2039385</v>
@@ -5734,7 +5734,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G185" t="n">
-        <v>10.0395441055298</v>
+        <v>10.0395450592041</v>
       </c>
       <c r="H185" t="n">
         <v>748210</v>
@@ -5763,7 +5763,7 @@
         <v>10.78600025177</v>
       </c>
       <c r="G186" t="n">
-        <v>10.2060813903809</v>
+        <v>10.2060823440552</v>
       </c>
       <c r="H186" t="n">
         <v>469378</v>
@@ -5792,7 +5792,7 @@
         <v>10.6339998245239</v>
       </c>
       <c r="G187" t="n">
-        <v>10.0622529983521</v>
+        <v>10.0622539520264</v>
       </c>
       <c r="H187" t="n">
         <v>279044</v>
@@ -6082,7 +6082,7 @@
         <v>11.0480003356934</v>
       </c>
       <c r="G197" t="n">
-        <v>10.4539947509766</v>
+        <v>10.4539957046509</v>
       </c>
       <c r="H197" t="n">
         <v>281143</v>
@@ -6111,7 +6111,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G198" t="n">
-        <v>10.4842748641968</v>
+        <v>10.4842739105225</v>
       </c>
       <c r="H198" t="n">
         <v>255451</v>
@@ -6198,7 +6198,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G201" t="n">
-        <v>10.5788984298706</v>
+        <v>10.5788974761963</v>
       </c>
       <c r="H201" t="n">
         <v>211395</v>
@@ -6227,7 +6227,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G202" t="n">
-        <v>10.5031986236572</v>
+        <v>10.5031995773315</v>
       </c>
       <c r="H202" t="n">
         <v>244760</v>
@@ -6314,7 +6314,7 @@
         <v>11.3420000076294</v>
       </c>
       <c r="G205" t="n">
-        <v>10.7321882247925</v>
+        <v>10.7321872711182</v>
       </c>
       <c r="H205" t="n">
         <v>152325</v>
@@ -6372,7 +6372,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G207" t="n">
-        <v>10.966854095459</v>
+        <v>10.9668531417847</v>
       </c>
       <c r="H207" t="n">
         <v>191397</v>
@@ -6430,7 +6430,7 @@
         <v>11.5579996109009</v>
       </c>
       <c r="G209" t="n">
-        <v>10.9365739822388</v>
+        <v>10.9365730285645</v>
       </c>
       <c r="H209" t="n">
         <v>170731</v>
@@ -6546,7 +6546,7 @@
         <v>11.5019998550415</v>
       </c>
       <c r="G213" t="n">
-        <v>10.8835849761963</v>
+        <v>10.8835859298706</v>
       </c>
       <c r="H213" t="n">
         <v>216641</v>
@@ -6575,7 +6575,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G214" t="n">
-        <v>10.5031986236572</v>
+        <v>10.5031995773315</v>
       </c>
       <c r="H214" t="n">
         <v>940630</v>
@@ -6691,7 +6691,7 @@
         <v>10.8739995956421</v>
       </c>
       <c r="G218" t="n">
-        <v>10.2893505096436</v>
+        <v>10.2893495559692</v>
       </c>
       <c r="H218" t="n">
         <v>223312</v>
@@ -6749,7 +6749,7 @@
         <v>10.9619998931885</v>
       </c>
       <c r="G220" t="n">
-        <v>10.3726186752319</v>
+        <v>10.3726196289062</v>
       </c>
       <c r="H220" t="n">
         <v>156811</v>
@@ -6807,7 +6807,7 @@
         <v>11.2340002059937</v>
       </c>
       <c r="G222" t="n">
-        <v>10.6299934387207</v>
+        <v>10.629994392395</v>
       </c>
       <c r="H222" t="n">
         <v>159090</v>
@@ -6865,7 +6865,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>11.2128744125366</v>
+        <v>11.2128753662109</v>
       </c>
       <c r="H224" t="n">
         <v>273187</v>
@@ -6894,7 +6894,7 @@
         <v>11.9340000152588</v>
       </c>
       <c r="G225" t="n">
-        <v>11.2923574447632</v>
+        <v>11.2923583984375</v>
       </c>
       <c r="H225" t="n">
         <v>1392941</v>
@@ -6981,7 +6981,7 @@
         <v>11</v>
       </c>
       <c r="G228" t="n">
-        <v>10.4085760116577</v>
+        <v>10.4085750579834</v>
       </c>
       <c r="H228" t="n">
         <v>808095</v>
@@ -7039,7 +7039,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G230" t="n">
-        <v>10.3896512985229</v>
+        <v>10.3896503448486</v>
       </c>
       <c r="H230" t="n">
         <v>475068</v>
@@ -7097,7 +7097,7 @@
         <v>11.0279998779297</v>
       </c>
       <c r="G232" t="n">
-        <v>10.4350700378418</v>
+        <v>10.4350690841675</v>
       </c>
       <c r="H232" t="n">
         <v>329462</v>
@@ -7126,7 +7126,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>10.5031986236572</v>
+        <v>10.5031995773315</v>
       </c>
       <c r="H233" t="n">
         <v>228150</v>
@@ -7155,7 +7155,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G234" t="n">
-        <v>10.5126600265503</v>
+        <v>10.5126609802246</v>
       </c>
       <c r="H234" t="n">
         <v>148165</v>
@@ -7213,7 +7213,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G236" t="n">
-        <v>10.2382526397705</v>
+        <v>10.2382535934448</v>
       </c>
       <c r="H236" t="n">
         <v>356369</v>
@@ -7271,7 +7271,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G238" t="n">
-        <v>10.2382526397705</v>
+        <v>10.2382535934448</v>
       </c>
       <c r="H238" t="n">
         <v>235729</v>
@@ -7329,7 +7329,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G240" t="n">
-        <v>10.0395441055298</v>
+        <v>10.0395450592041</v>
       </c>
       <c r="H240" t="n">
         <v>634447</v>
@@ -7358,7 +7358,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G241" t="n">
-        <v>10.0395441055298</v>
+        <v>10.0395450592041</v>
       </c>
       <c r="H241" t="n">
         <v>254072</v>
@@ -7387,7 +7387,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G242" t="n">
-        <v>10.1057815551758</v>
+        <v>10.1057806015015</v>
       </c>
       <c r="H242" t="n">
         <v>332984</v>
@@ -7445,7 +7445,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G244" t="n">
-        <v>10.0395441055298</v>
+        <v>10.0395450592041</v>
       </c>
       <c r="H244" t="n">
         <v>132610</v>
@@ -7532,7 +7532,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G247" t="n">
-        <v>9.90707111358643</v>
+        <v>9.90707206726074</v>
       </c>
       <c r="H247" t="n">
         <v>223084</v>
@@ -7735,7 +7735,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G254" t="n">
-        <v>9.99223232269287</v>
+        <v>9.99223327636719</v>
       </c>
       <c r="H254" t="n">
         <v>244328</v>
@@ -7793,7 +7793,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G256" t="n">
-        <v>10.3896512985229</v>
+        <v>10.3896503448486</v>
       </c>
       <c r="H256" t="n">
         <v>552393</v>
@@ -7909,7 +7909,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G260" t="n">
-        <v>10.2382526397705</v>
+        <v>10.2382535934448</v>
       </c>
       <c r="H260" t="n">
         <v>290152</v>
@@ -7967,7 +7967,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G262" t="n">
-        <v>10.2382526397705</v>
+        <v>10.2382535934448</v>
       </c>
       <c r="H262" t="n">
         <v>242006</v>
@@ -8083,7 +8083,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G266" t="n">
-        <v>10.143630027771</v>
+        <v>10.1436309814453</v>
       </c>
       <c r="H266" t="n">
         <v>192613</v>
@@ -8112,7 +8112,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G267" t="n">
-        <v>10.0206203460693</v>
+        <v>10.020619392395</v>
       </c>
       <c r="H267" t="n">
         <v>171371</v>
@@ -8141,7 +8141,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G268" t="n">
-        <v>10.0982236862183</v>
+        <v>10.0982227325439</v>
       </c>
       <c r="H268" t="n">
         <v>162147</v>
@@ -8344,7 +8344,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G275" t="n">
-        <v>10.3310356140137</v>
+        <v>10.3310346603394</v>
       </c>
       <c r="H275" t="n">
         <v>417991</v>
@@ -8576,7 +8576,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G283" t="n">
-        <v>10.6220512390137</v>
+        <v>10.6220502853394</v>
       </c>
       <c r="H283" t="n">
         <v>129742</v>
@@ -8634,7 +8634,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G285" t="n">
-        <v>10.5638475418091</v>
+        <v>10.5638484954834</v>
       </c>
       <c r="H285" t="n">
         <v>180726</v>
@@ -8692,7 +8692,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G287" t="n">
-        <v>10.2534303665161</v>
+        <v>10.2534313201904</v>
       </c>
       <c r="H287" t="n">
         <v>235286</v>
@@ -8721,7 +8721,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G288" t="n">
-        <v>10.311635017395</v>
+        <v>10.3116340637207</v>
       </c>
       <c r="H288" t="n">
         <v>127440</v>
@@ -8779,7 +8779,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G290" t="n">
-        <v>10.4377422332764</v>
+        <v>10.4377412796021</v>
       </c>
       <c r="H290" t="n">
         <v>97733</v>
@@ -8895,7 +8895,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G294" t="n">
-        <v>10.8063611984253</v>
+        <v>10.806360244751</v>
       </c>
       <c r="H294" t="n">
         <v>209159</v>
@@ -8982,7 +8982,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G297" t="n">
-        <v>10.9518671035767</v>
+        <v>10.951868057251</v>
       </c>
       <c r="H297" t="n">
         <v>175726</v>
@@ -9011,7 +9011,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G298" t="n">
-        <v>10.7578573226929</v>
+        <v>10.7578582763672</v>
       </c>
       <c r="H298" t="n">
         <v>301876</v>
@@ -9214,7 +9214,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G305" t="n">
-        <v>11.5824003219604</v>
+        <v>11.5823993682861</v>
       </c>
       <c r="H305" t="n">
         <v>274687</v>
@@ -9475,7 +9475,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G314" t="n">
-        <v>11.3398876190186</v>
+        <v>11.3398866653442</v>
       </c>
       <c r="H314" t="n">
         <v>110179</v>
@@ -9562,7 +9562,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G317" t="n">
-        <v>11.2525835037231</v>
+        <v>11.2525844573975</v>
       </c>
       <c r="H317" t="n">
         <v>381622</v>
@@ -9649,7 +9649,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G320" t="n">
-        <v>10.9518671035767</v>
+        <v>10.951868057251</v>
       </c>
       <c r="H320" t="n">
         <v>279934</v>
@@ -9707,7 +9707,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G322" t="n">
-        <v>10.9712686538696</v>
+        <v>10.9712696075439</v>
       </c>
       <c r="H322" t="n">
         <v>185383</v>
@@ -9765,7 +9765,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G324" t="n">
-        <v>10.7481565475464</v>
+        <v>10.7481575012207</v>
       </c>
       <c r="H324" t="n">
         <v>184196</v>
@@ -9852,7 +9852,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>10.7190561294556</v>
+        <v>10.7190551757812</v>
       </c>
       <c r="H327" t="n">
         <v>80274</v>
@@ -9881,7 +9881,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G328" t="n">
-        <v>10.7578573226929</v>
+        <v>10.7578582763672</v>
       </c>
       <c r="H328" t="n">
         <v>81593</v>
@@ -9910,7 +9910,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>10.8160610198975</v>
+        <v>10.8160600662231</v>
       </c>
       <c r="H329" t="n">
         <v>255497</v>
@@ -10055,7 +10055,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G334" t="n">
-        <v>11.136176109314</v>
+        <v>11.1361770629883</v>
       </c>
       <c r="H334" t="n">
         <v>92993</v>
@@ -10084,7 +10084,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G335" t="n">
-        <v>11.136176109314</v>
+        <v>11.1361770629883</v>
       </c>
       <c r="H335" t="n">
         <v>109603</v>
@@ -10258,7 +10258,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G341" t="n">
-        <v>11.4077920913696</v>
+        <v>11.4077911376953</v>
       </c>
       <c r="H341" t="n">
         <v>275168</v>
@@ -10374,7 +10374,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G345" t="n">
-        <v>10.9712686538696</v>
+        <v>10.9712696075439</v>
       </c>
       <c r="H345" t="n">
         <v>250890</v>
@@ -10403,7 +10403,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G346" t="n">
-        <v>10.9615678787231</v>
+        <v>10.9615688323975</v>
       </c>
       <c r="H346" t="n">
         <v>157159</v>
@@ -10432,7 +10432,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G347" t="n">
-        <v>11.0003709793091</v>
+        <v>11.0003700256348</v>
       </c>
       <c r="H347" t="n">
         <v>187467</v>
@@ -10461,7 +10461,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G348" t="n">
-        <v>11.0003709793091</v>
+        <v>11.0003700256348</v>
       </c>
       <c r="H348" t="n">
         <v>109481</v>
@@ -10722,7 +10722,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G357" t="n">
-        <v>11.058572769165</v>
+        <v>11.0585737228394</v>
       </c>
       <c r="H357" t="n">
         <v>184343</v>
@@ -10780,7 +10780,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G359" t="n">
-        <v>11.0003709793091</v>
+        <v>11.0003700256348</v>
       </c>
       <c r="H359" t="n">
         <v>186510</v>
@@ -10867,7 +10867,7 @@
         <v>11.25</v>
       </c>
       <c r="G362" t="n">
-        <v>10.9130659103394</v>
+        <v>10.913064956665</v>
       </c>
       <c r="H362" t="n">
         <v>440278</v>
@@ -10925,7 +10925,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G364" t="n">
-        <v>11.1458768844604</v>
+        <v>11.1458778381348</v>
       </c>
       <c r="H364" t="n">
         <v>188007</v>
@@ -11012,7 +11012,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>11.058572769165</v>
+        <v>11.0585737228394</v>
       </c>
       <c r="H367" t="n">
         <v>195723</v>
@@ -11070,7 +11070,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G369" t="n">
-        <v>11.1458768844604</v>
+        <v>11.1458778381348</v>
       </c>
       <c r="H369" t="n">
         <v>107932</v>
@@ -11128,7 +11128,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G371" t="n">
-        <v>11.136176109314</v>
+        <v>11.1361770629883</v>
       </c>
       <c r="H371" t="n">
         <v>118399</v>
@@ -11186,7 +11186,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G373" t="n">
-        <v>11.0197715759277</v>
+        <v>11.0197706222534</v>
       </c>
       <c r="H373" t="n">
         <v>147161</v>
@@ -11302,7 +11302,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G377" t="n">
-        <v>11.0197715759277</v>
+        <v>11.0197706222534</v>
       </c>
       <c r="H377" t="n">
         <v>130368</v>
@@ -11476,7 +11476,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G383" t="n">
-        <v>11.136176109314</v>
+        <v>11.1361770629883</v>
       </c>
       <c r="H383" t="n">
         <v>194313</v>
@@ -11592,7 +11592,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G387" t="n">
-        <v>11.1749801635742</v>
+        <v>11.1749792098999</v>
       </c>
       <c r="H387" t="n">
         <v>197901</v>
@@ -11650,7 +11650,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G389" t="n">
-        <v>11.4465932846069</v>
+        <v>11.4465942382812</v>
       </c>
       <c r="H389" t="n">
         <v>259214</v>
@@ -11737,7 +11737,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G392" t="n">
-        <v>11.8540143966675</v>
+        <v>11.8540153503418</v>
       </c>
       <c r="H392" t="n">
         <v>194096</v>
@@ -11795,7 +11795,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G394" t="n">
-        <v>11.6988077163696</v>
+        <v>11.6988067626953</v>
       </c>
       <c r="H394" t="n">
         <v>171327</v>
@@ -11911,7 +11911,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G398" t="n">
-        <v>11.6309022903442</v>
+        <v>11.6309032440186</v>
       </c>
       <c r="H398" t="n">
         <v>192088</v>
@@ -11940,7 +11940,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G399" t="n">
-        <v>11.5824003219604</v>
+        <v>11.5823993682861</v>
       </c>
       <c r="H399" t="n">
         <v>137161</v>
@@ -12056,7 +12056,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G403" t="n">
-        <v>12.193531036377</v>
+        <v>12.1935319900513</v>
       </c>
       <c r="H403" t="n">
         <v>108069</v>
@@ -12114,7 +12114,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G405" t="n">
-        <v>12.193531036377</v>
+        <v>12.1935319900513</v>
       </c>
       <c r="H405" t="n">
         <v>135114</v>
@@ -12172,7 +12172,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G407" t="n">
-        <v>12.2226343154907</v>
+        <v>12.2226333618164</v>
       </c>
       <c r="H407" t="n">
         <v>185001</v>
@@ -12201,7 +12201,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G408" t="n">
-        <v>12.2517356872559</v>
+        <v>12.2517347335815</v>
       </c>
       <c r="H408" t="n">
         <v>172512</v>
@@ -12288,7 +12288,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G411" t="n">
-        <v>12.4651470184326</v>
+        <v>12.4651460647583</v>
       </c>
       <c r="H411" t="n">
         <v>133030</v>
@@ -12317,7 +12317,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G412" t="n">
-        <v>12.3875417709351</v>
+        <v>12.3875427246094</v>
       </c>
       <c r="H412" t="n">
         <v>148541</v>
@@ -12520,7 +12520,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G419" t="n">
-        <v>12.2517356872559</v>
+        <v>12.2517347335815</v>
       </c>
       <c r="H419" t="n">
         <v>165954</v>
@@ -12549,7 +12549,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G420" t="n">
-        <v>12.2226343154907</v>
+        <v>12.2226333618164</v>
       </c>
       <c r="H420" t="n">
         <v>258706</v>
@@ -12607,7 +12607,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G422" t="n">
-        <v>12.2129325866699</v>
+        <v>12.2129335403442</v>
       </c>
       <c r="H422" t="n">
         <v>137376</v>
@@ -12636,7 +12636,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G423" t="n">
-        <v>12.3875417709351</v>
+        <v>12.3875427246094</v>
       </c>
       <c r="H423" t="n">
         <v>99466</v>
@@ -12723,7 +12723,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G426" t="n">
-        <v>12.5427503585815</v>
+        <v>12.5427513122559</v>
       </c>
       <c r="H426" t="n">
         <v>197307</v>
@@ -12752,7 +12752,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G427" t="n">
-        <v>12.6300554275513</v>
+        <v>12.630054473877</v>
       </c>
       <c r="H427" t="n">
         <v>148262</v>
@@ -12839,7 +12839,7 @@
         <v>13</v>
       </c>
       <c r="G430" t="n">
-        <v>12.6106538772583</v>
+        <v>12.610652923584</v>
       </c>
       <c r="H430" t="n">
         <v>1807764</v>
@@ -12897,7 +12897,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G432" t="n">
-        <v>12.3972415924072</v>
+        <v>12.3972425460815</v>
       </c>
       <c r="H432" t="n">
         <v>1234024</v>
@@ -12955,7 +12955,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G434" t="n">
-        <v>12.6882572174072</v>
+        <v>12.6882581710815</v>
       </c>
       <c r="H434" t="n">
         <v>465320</v>
@@ -13013,7 +13013,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G436" t="n">
-        <v>13.1538829803467</v>
+        <v>13.1538820266724</v>
       </c>
       <c r="H436" t="n">
         <v>425963</v>
@@ -13274,7 +13274,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G445" t="n">
-        <v>13.7844142913818</v>
+        <v>13.7844152450562</v>
       </c>
       <c r="H445" t="n">
         <v>236771</v>
@@ -13303,7 +13303,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G446" t="n">
-        <v>14.3373422622681</v>
+        <v>14.3373432159424</v>
       </c>
       <c r="H446" t="n">
         <v>473165</v>
@@ -13332,7 +13332,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G447" t="n">
-        <v>14.4537487030029</v>
+        <v>14.4537496566772</v>
       </c>
       <c r="H447" t="n">
         <v>380386</v>
@@ -13361,7 +13361,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G448" t="n">
-        <v>14.6671600341797</v>
+        <v>14.667160987854</v>
       </c>
       <c r="H448" t="n">
         <v>267462</v>
@@ -13419,7 +13419,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G450" t="n">
-        <v>14.8029680252075</v>
+        <v>14.8029670715332</v>
       </c>
       <c r="H450" t="n">
         <v>391347</v>
@@ -13622,7 +13622,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G457" t="n">
-        <v>16.0446319580078</v>
+        <v>16.0446338653564</v>
       </c>
       <c r="H457" t="n">
         <v>378598</v>
@@ -13680,7 +13680,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G459" t="n">
-        <v>15.9573278427124</v>
+        <v>15.9573268890381</v>
       </c>
       <c r="H459" t="n">
         <v>261224</v>
@@ -13796,7 +13796,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G463" t="n">
-        <v>16.0252323150635</v>
+        <v>16.0252304077148</v>
       </c>
       <c r="H463" t="n">
         <v>392686</v>
@@ -13825,7 +13825,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G464" t="n">
-        <v>15.6857137680054</v>
+        <v>15.6857128143311</v>
       </c>
       <c r="H464" t="n">
         <v>532461</v>
@@ -14028,7 +14028,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G471" t="n">
-        <v>15.8700227737427</v>
+        <v>15.870023727417</v>
       </c>
       <c r="H471" t="n">
         <v>880362</v>
@@ -14115,7 +14115,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G474" t="n">
-        <v>16.9273777008057</v>
+        <v>16.9273796081543</v>
       </c>
       <c r="H474" t="n">
         <v>620043</v>
@@ -14260,7 +14260,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G479" t="n">
-        <v>17.5870113372803</v>
+        <v>17.5870094299316</v>
       </c>
       <c r="H479" t="n">
         <v>473621</v>
@@ -14289,7 +14289,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G480" t="n">
-        <v>17.5870113372803</v>
+        <v>17.5870094299316</v>
       </c>
       <c r="H480" t="n">
         <v>417252</v>
@@ -14347,7 +14347,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G482" t="n">
-        <v>17.1601905822754</v>
+        <v>17.1601886749268</v>
       </c>
       <c r="H482" t="n">
         <v>353508</v>
@@ -14405,7 +14405,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G484" t="n">
-        <v>17.7519207000732</v>
+        <v>17.7519187927246</v>
       </c>
       <c r="H484" t="n">
         <v>342388</v>
@@ -14434,7 +14434,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G485" t="n">
-        <v>17.7422199249268</v>
+        <v>17.7422218322754</v>
       </c>
       <c r="H485" t="n">
         <v>271126</v>
@@ -14521,7 +14521,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G488" t="n">
-        <v>17.9071273803711</v>
+        <v>17.9071292877197</v>
       </c>
       <c r="H488" t="n">
         <v>372109</v>
@@ -14550,7 +14550,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G489" t="n">
-        <v>18.3727512359619</v>
+        <v>18.3727531433105</v>
       </c>
       <c r="H489" t="n">
         <v>455016</v>
@@ -14608,7 +14608,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>16.8303737640381</v>
+        <v>16.8303718566895</v>
       </c>
       <c r="H491" t="n">
         <v>1164243</v>
@@ -14695,7 +14695,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G494" t="n">
-        <v>17.1601905822754</v>
+        <v>17.1601886749268</v>
       </c>
       <c r="H494" t="n">
         <v>564420</v>
@@ -14898,7 +14898,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G501" t="n">
-        <v>18.8480758666992</v>
+        <v>18.8480777740479</v>
       </c>
       <c r="H501" t="n">
         <v>377971</v>
@@ -14927,7 +14927,7 @@
         <v>19.4699993133545</v>
       </c>
       <c r="G502" t="n">
-        <v>18.8868770599365</v>
+        <v>18.8868789672852</v>
       </c>
       <c r="H502" t="n">
         <v>436832</v>
@@ -14956,7 +14956,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G503" t="n">
-        <v>19.0226879119873</v>
+        <v>19.0226860046387</v>
       </c>
       <c r="H503" t="n">
         <v>218294</v>
@@ -15014,7 +15014,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G505" t="n">
-        <v>19.4786109924316</v>
+        <v>19.478609085083</v>
       </c>
       <c r="H505" t="n">
         <v>375456</v>
@@ -15043,7 +15043,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G506" t="n">
-        <v>19.4592094421387</v>
+        <v>19.45920753479</v>
       </c>
       <c r="H506" t="n">
         <v>430857</v>
@@ -15072,7 +15072,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G507" t="n">
-        <v>19.4398078918457</v>
+        <v>19.4398097991943</v>
       </c>
       <c r="H507" t="n">
         <v>573705</v>
@@ -15130,7 +15130,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G509" t="n">
-        <v>20.3128528594971</v>
+        <v>20.3128547668457</v>
       </c>
       <c r="H509" t="n">
         <v>845381</v>
@@ -15159,7 +15159,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G510" t="n">
-        <v>20.2352504730225</v>
+        <v>20.2352485656738</v>
       </c>
       <c r="H510" t="n">
         <v>628106</v>
@@ -15188,7 +15188,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G511" t="n">
-        <v>19.9248332977295</v>
+        <v>19.9248352050781</v>
       </c>
       <c r="H511" t="n">
         <v>774008</v>
@@ -15217,7 +15217,7 @@
         <v>20</v>
       </c>
       <c r="G512" t="n">
-        <v>19.4010047912598</v>
+        <v>19.4010066986084</v>
       </c>
       <c r="H512" t="n">
         <v>769373</v>
@@ -15304,7 +15304,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>21.6321220397949</v>
+        <v>21.6321201324463</v>
       </c>
       <c r="H515" t="n">
         <v>2197577</v>
@@ -15362,7 +15362,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G517" t="n">
-        <v>22.1171455383301</v>
+        <v>22.1171474456787</v>
       </c>
       <c r="H517" t="n">
         <v>555528</v>
@@ -15391,7 +15391,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G518" t="n">
-        <v>21.9619388580322</v>
+        <v>21.9619369506836</v>
       </c>
       <c r="H518" t="n">
         <v>611058</v>
@@ -26011,6 +26011,35 @@
         <v>965672</v>
       </c>
       <c r="I884" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="s">
+        <v>9</v>
+      </c>
+      <c r="B885" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C885" t="n">
+        <v>25.2399997711182</v>
+      </c>
+      <c r="D885" t="n">
+        <v>25.2399997711182</v>
+      </c>
+      <c r="E885" t="n">
+        <v>24.7000007629395</v>
+      </c>
+      <c r="F885" t="n">
+        <v>25</v>
+      </c>
+      <c r="G885" t="n">
+        <v>25</v>
+      </c>
+      <c r="H885" t="n">
+        <v>811568</v>
+      </c>
+      <c r="I885" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LTMC.MI.xlsx
+++ b/data/LTMC.MI.xlsx
@@ -26043,6 +26043,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="886">
+      <c r="A886" t="s">
+        <v>9</v>
+      </c>
+      <c r="B886" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C886" t="n">
+        <v>24.9200000762939</v>
+      </c>
+      <c r="D886" t="n">
+        <v>25.1299991607666</v>
+      </c>
+      <c r="E886" t="n">
+        <v>24.5499992370605</v>
+      </c>
+      <c r="F886" t="n">
+        <v>24.6700000762939</v>
+      </c>
+      <c r="G886" t="n">
+        <v>24.6700000762939</v>
+      </c>
+      <c r="H886" t="n">
+        <v>725015</v>
+      </c>
+      <c r="I886" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LTMC.MI.xlsx
+++ b/data/LTMC.MI.xlsx
@@ -427,7 +427,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2" t="n">
-        <v>7.75911951065063</v>
+        <v>7.75911998748779</v>
       </c>
       <c r="H2" t="n">
         <v>13006120</v>
@@ -456,7 +456,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G3" t="n">
-        <v>7.82535743713379</v>
+        <v>7.82535648345947</v>
       </c>
       <c r="H3" t="n">
         <v>2759922</v>
@@ -485,7 +485,7 @@
         <v>8.44600009918213</v>
       </c>
       <c r="G4" t="n">
-        <v>7.99189376831055</v>
+        <v>7.99189424514771</v>
       </c>
       <c r="H4" t="n">
         <v>1476712</v>
@@ -543,7 +543,7 @@
         <v>8.59099960327148</v>
       </c>
       <c r="G6" t="n">
-        <v>8.12909698486328</v>
+        <v>8.1290979385376</v>
       </c>
       <c r="H6" t="n">
         <v>974676</v>
@@ -572,7 +572,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G7" t="n">
-        <v>7.92944288253784</v>
+        <v>7.92944240570068</v>
       </c>
       <c r="H7" t="n">
         <v>640304</v>
@@ -630,7 +630,7 @@
         <v>8.25</v>
       </c>
       <c r="G9" t="n">
-        <v>7.80643129348755</v>
+        <v>7.80643224716187</v>
       </c>
       <c r="H9" t="n">
         <v>1073912</v>
@@ -659,7 +659,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G10" t="n">
-        <v>7.99567842483521</v>
+        <v>7.99567890167236</v>
       </c>
       <c r="H10" t="n">
         <v>1947465</v>
@@ -833,7 +833,7 @@
         <v>7.86899995803833</v>
       </c>
       <c r="G16" t="n">
-        <v>7.44591665267944</v>
+        <v>7.44591617584229</v>
       </c>
       <c r="H16" t="n">
         <v>479599</v>
@@ -862,7 +862,7 @@
         <v>7.72300004959106</v>
       </c>
       <c r="G17" t="n">
-        <v>7.30776596069336</v>
+        <v>7.30776643753052</v>
       </c>
       <c r="H17" t="n">
         <v>588439</v>
@@ -891,7 +891,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G18" t="n">
-        <v>7.26707792282104</v>
+        <v>7.2670783996582</v>
       </c>
       <c r="H18" t="n">
         <v>228832</v>
@@ -978,7 +978,7 @@
         <v>7.71199989318848</v>
       </c>
       <c r="G21" t="n">
-        <v>7.29735803604126</v>
+        <v>7.2973575592041</v>
       </c>
       <c r="H21" t="n">
         <v>118298</v>
@@ -1007,7 +1007,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G22" t="n">
-        <v>7.03525066375732</v>
+        <v>7.03525114059448</v>
       </c>
       <c r="H22" t="n">
         <v>597512</v>
@@ -1094,7 +1094,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G25" t="n">
-        <v>7.28600215911865</v>
+        <v>7.28600263595581</v>
       </c>
       <c r="H25" t="n">
         <v>218758</v>
@@ -1152,7 +1152,7 @@
         <v>8.12600040435791</v>
       </c>
       <c r="G27" t="n">
-        <v>7.68909883499146</v>
+        <v>7.68909931182861</v>
       </c>
       <c r="H27" t="n">
         <v>1170934</v>
@@ -1181,7 +1181,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G28" t="n">
-        <v>7.76858234405518</v>
+        <v>7.76858282089233</v>
       </c>
       <c r="H28" t="n">
         <v>1704311</v>
@@ -1210,7 +1210,7 @@
         <v>8.52200031280518</v>
       </c>
       <c r="G29" t="n">
-        <v>8.06380748748779</v>
+        <v>8.06380844116211</v>
       </c>
       <c r="H29" t="n">
         <v>1531238</v>
@@ -1297,7 +1297,7 @@
         <v>8.16199970245361</v>
       </c>
       <c r="G32" t="n">
-        <v>7.72316265106201</v>
+        <v>7.72316312789917</v>
       </c>
       <c r="H32" t="n">
         <v>440552</v>
@@ -1326,7 +1326,7 @@
         <v>8.21399974822998</v>
       </c>
       <c r="G33" t="n">
-        <v>7.77236652374268</v>
+        <v>7.77236700057983</v>
       </c>
       <c r="H33" t="n">
         <v>327710</v>
@@ -1355,7 +1355,7 @@
         <v>8.41300010681152</v>
       </c>
       <c r="G34" t="n">
-        <v>7.96066808700562</v>
+        <v>7.96066761016846</v>
       </c>
       <c r="H34" t="n">
         <v>540974</v>
@@ -1413,7 +1413,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G36" t="n">
-        <v>7.81116342544556</v>
+        <v>7.81116247177124</v>
       </c>
       <c r="H36" t="n">
         <v>219714</v>
@@ -1442,7 +1442,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G37" t="n">
-        <v>7.92944288253784</v>
+        <v>7.92944240570068</v>
       </c>
       <c r="H37" t="n">
         <v>223839</v>
@@ -1500,7 +1500,7 @@
         <v>8.43299961090088</v>
       </c>
       <c r="G39" t="n">
-        <v>7.97959136962891</v>
+        <v>7.97959184646606</v>
       </c>
       <c r="H39" t="n">
         <v>99001</v>
@@ -1529,7 +1529,7 @@
         <v>8.43599987030029</v>
       </c>
       <c r="G40" t="n">
-        <v>7.98243045806885</v>
+        <v>7.98243093490601</v>
       </c>
       <c r="H40" t="n">
         <v>155784</v>
@@ -1558,7 +1558,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G41" t="n">
-        <v>7.92944288253784</v>
+        <v>7.92944240570068</v>
       </c>
       <c r="H41" t="n">
         <v>133019</v>
@@ -1587,7 +1587,7 @@
         <v>8.41300010681152</v>
       </c>
       <c r="G42" t="n">
-        <v>7.96066808700562</v>
+        <v>7.96066761016846</v>
       </c>
       <c r="H42" t="n">
         <v>122155</v>
@@ -1616,7 +1616,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G43" t="n">
-        <v>8.23223781585693</v>
+        <v>8.23223686218262</v>
       </c>
       <c r="H43" t="n">
         <v>362592</v>
@@ -1674,7 +1674,7 @@
         <v>8.5620002746582</v>
       </c>
       <c r="G45" t="n">
-        <v>8.10165596008301</v>
+        <v>8.10165691375732</v>
       </c>
       <c r="H45" t="n">
         <v>252798</v>
@@ -1703,7 +1703,7 @@
         <v>8.69499969482422</v>
       </c>
       <c r="G46" t="n">
-        <v>8.22750473022461</v>
+        <v>8.22750568389893</v>
       </c>
       <c r="H46" t="n">
         <v>188291</v>
@@ -1732,7 +1732,7 @@
         <v>8.58300018310547</v>
       </c>
       <c r="G47" t="n">
-        <v>8.12152862548828</v>
+        <v>8.12152767181396</v>
       </c>
       <c r="H47" t="n">
         <v>162361</v>
@@ -1790,7 +1790,7 @@
         <v>8.78800010681152</v>
       </c>
       <c r="G49" t="n">
-        <v>8.315505027771</v>
+        <v>8.31550598144531</v>
       </c>
       <c r="H49" t="n">
         <v>417701</v>
@@ -1935,7 +1935,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G54" t="n">
-        <v>8.97029876708984</v>
+        <v>8.97029972076416</v>
       </c>
       <c r="H54" t="n">
         <v>321248</v>
@@ -2022,7 +2022,7 @@
         <v>9.38399982452393</v>
       </c>
       <c r="G57" t="n">
-        <v>8.87946128845215</v>
+        <v>8.87946033477783</v>
       </c>
       <c r="H57" t="n">
         <v>292101</v>
@@ -2109,7 +2109,7 @@
         <v>9.37600040435791</v>
       </c>
       <c r="G60" t="n">
-        <v>8.87189292907715</v>
+        <v>8.87189197540283</v>
       </c>
       <c r="H60" t="n">
         <v>240981</v>
@@ -2167,7 +2167,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G62" t="n">
-        <v>8.65804195404053</v>
+        <v>8.65804290771484</v>
       </c>
       <c r="H62" t="n">
         <v>407302</v>
@@ -2196,7 +2196,7 @@
         <v>9.17800045013428</v>
       </c>
       <c r="G63" t="n">
-        <v>8.68453788757324</v>
+        <v>8.68453693389893</v>
       </c>
       <c r="H63" t="n">
         <v>254936</v>
@@ -2225,7 +2225,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G64" t="n">
-        <v>8.79997730255127</v>
+        <v>8.79997825622559</v>
       </c>
       <c r="H64" t="n">
         <v>396592</v>
@@ -2254,7 +2254,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G65" t="n">
-        <v>8.94191360473633</v>
+        <v>8.94191265106201</v>
       </c>
       <c r="H65" t="n">
         <v>900757</v>
@@ -2312,7 +2312,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G67" t="n">
-        <v>8.82363319396973</v>
+        <v>8.82363224029541</v>
       </c>
       <c r="H67" t="n">
         <v>266872</v>
@@ -2370,7 +2370,7 @@
         <v>9.30300045013428</v>
       </c>
       <c r="G69" t="n">
-        <v>8.80281639099121</v>
+        <v>8.80281734466553</v>
       </c>
       <c r="H69" t="n">
         <v>181453</v>
@@ -2428,7 +2428,7 @@
         <v>9.30300045013428</v>
       </c>
       <c r="G71" t="n">
-        <v>8.80281639099121</v>
+        <v>8.80281734466553</v>
       </c>
       <c r="H71" t="n">
         <v>228312</v>
@@ -2486,7 +2486,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G73" t="n">
-        <v>8.79997730255127</v>
+        <v>8.79997825622559</v>
       </c>
       <c r="H73" t="n">
         <v>161362</v>
@@ -2602,7 +2602,7 @@
         <v>9.12600040435791</v>
       </c>
       <c r="G77" t="n">
-        <v>8.63533401489258</v>
+        <v>8.63533306121826</v>
       </c>
       <c r="H77" t="n">
         <v>248031</v>
@@ -2660,7 +2660,7 @@
         <v>9.10799980163574</v>
       </c>
       <c r="G79" t="n">
-        <v>8.61829948425293</v>
+        <v>8.61830043792725</v>
       </c>
       <c r="H79" t="n">
         <v>127272</v>
@@ -2805,7 +2805,7 @@
         <v>9.39200019836426</v>
       </c>
       <c r="G84" t="n">
-        <v>8.88703155517578</v>
+        <v>8.88703060150146</v>
       </c>
       <c r="H84" t="n">
         <v>248541</v>
@@ -2863,7 +2863,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G86" t="n">
-        <v>8.8378267288208</v>
+        <v>8.83782768249512</v>
       </c>
       <c r="H86" t="n">
         <v>322079</v>
@@ -2892,7 +2892,7 @@
         <v>9</v>
       </c>
       <c r="G87" t="n">
-        <v>8.51610660552979</v>
+        <v>8.5161075592041</v>
       </c>
       <c r="H87" t="n">
         <v>2756951</v>
@@ -2921,7 +2921,7 @@
         <v>9.10799980163574</v>
       </c>
       <c r="G88" t="n">
-        <v>8.61829948425293</v>
+        <v>8.61830043792725</v>
       </c>
       <c r="H88" t="n">
         <v>496089</v>
@@ -2950,7 +2950,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G89" t="n">
-        <v>8.74320411682129</v>
+        <v>8.74320316314697</v>
       </c>
       <c r="H89" t="n">
         <v>146265</v>
@@ -2979,7 +2979,7 @@
         <v>9.17899990081787</v>
       </c>
       <c r="G90" t="n">
-        <v>8.6854829788208</v>
+        <v>8.68548393249512</v>
       </c>
       <c r="H90" t="n">
         <v>216140</v>
@@ -3066,7 +3066,7 @@
         <v>9.22700023651123</v>
       </c>
       <c r="G93" t="n">
-        <v>8.73090362548828</v>
+        <v>8.73090267181396</v>
       </c>
       <c r="H93" t="n">
         <v>184727</v>
@@ -3095,7 +3095,7 @@
         <v>9.02299976348877</v>
       </c>
       <c r="G94" t="n">
-        <v>8.53787040710449</v>
+        <v>8.53786945343018</v>
       </c>
       <c r="H94" t="n">
         <v>577462</v>
@@ -3124,7 +3124,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G95" t="n">
-        <v>8.53503322601318</v>
+        <v>8.53503227233887</v>
       </c>
       <c r="H95" t="n">
         <v>212825</v>
@@ -3153,7 +3153,7 @@
         <v>9</v>
       </c>
       <c r="G96" t="n">
-        <v>8.51610660552979</v>
+        <v>8.5161075592041</v>
       </c>
       <c r="H96" t="n">
         <v>322675</v>
@@ -3269,7 +3269,7 @@
         <v>8.9069995880127</v>
       </c>
       <c r="G100" t="n">
-        <v>8.42810821533203</v>
+        <v>8.42810726165771</v>
       </c>
       <c r="H100" t="n">
         <v>428743</v>
@@ -3414,7 +3414,7 @@
         <v>8.53899955749512</v>
       </c>
       <c r="G105" t="n">
-        <v>8.07989311218262</v>
+        <v>8.0798921585083</v>
       </c>
       <c r="H105" t="n">
         <v>153907</v>
@@ -3530,7 +3530,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G109" t="n">
-        <v>8.27008628845215</v>
+        <v>8.27008724212646</v>
       </c>
       <c r="H109" t="n">
         <v>186396</v>
@@ -3559,7 +3559,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G110" t="n">
-        <v>8.37417221069336</v>
+        <v>8.37417316436768</v>
       </c>
       <c r="H110" t="n">
         <v>209809</v>
@@ -3588,7 +3588,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G111" t="n">
-        <v>8.17546272277832</v>
+        <v>8.17546367645264</v>
       </c>
       <c r="H111" t="n">
         <v>213577</v>
@@ -3733,7 +3733,7 @@
         <v>8.75500011444092</v>
       </c>
       <c r="G116" t="n">
-        <v>8.28428077697754</v>
+        <v>8.28427982330322</v>
       </c>
       <c r="H116" t="n">
         <v>68870</v>
@@ -3762,7 +3762,7 @@
         <v>8.85400009155273</v>
       </c>
       <c r="G117" t="n">
-        <v>8.37795734405518</v>
+        <v>8.37795829772949</v>
       </c>
       <c r="H117" t="n">
         <v>105095</v>
@@ -3791,7 +3791,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G118" t="n">
-        <v>8.23223781585693</v>
+        <v>8.23223686218262</v>
       </c>
       <c r="H118" t="n">
         <v>188950</v>
@@ -3849,7 +3849,7 @@
         <v>8.75</v>
       </c>
       <c r="G120" t="n">
-        <v>8.27954769134521</v>
+        <v>8.27954959869385</v>
       </c>
       <c r="H120" t="n">
         <v>97384</v>
@@ -3936,7 +3936,7 @@
         <v>8.7810001373291</v>
       </c>
       <c r="G123" t="n">
-        <v>8.30888175964355</v>
+        <v>8.30888271331787</v>
       </c>
       <c r="H123" t="n">
         <v>162637</v>
@@ -3965,7 +3965,7 @@
         <v>9</v>
       </c>
       <c r="G124" t="n">
-        <v>8.51610660552979</v>
+        <v>8.5161075592041</v>
       </c>
       <c r="H124" t="n">
         <v>178371</v>
@@ -4023,7 +4023,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G126" t="n">
-        <v>8.36470890045166</v>
+        <v>8.36470985412598</v>
       </c>
       <c r="H126" t="n">
         <v>152716</v>
@@ -4052,7 +4052,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G127" t="n">
-        <v>8.37417221069336</v>
+        <v>8.37417316436768</v>
       </c>
       <c r="H127" t="n">
         <v>102561</v>
@@ -4168,7 +4168,7 @@
         <v>9.03800010681152</v>
       </c>
       <c r="G131" t="n">
-        <v>8.55206394195557</v>
+        <v>8.55206489562988</v>
       </c>
       <c r="H131" t="n">
         <v>165794</v>
@@ -4226,7 +4226,7 @@
         <v>9.22200012207031</v>
       </c>
       <c r="G133" t="n">
-        <v>8.72617053985596</v>
+        <v>8.72617149353027</v>
       </c>
       <c r="H133" t="n">
         <v>178676</v>
@@ -4255,7 +4255,7 @@
         <v>9.05300045013428</v>
       </c>
       <c r="G134" t="n">
-        <v>8.56625747680664</v>
+        <v>8.56625843048096</v>
       </c>
       <c r="H134" t="n">
         <v>123966</v>
@@ -4313,7 +4313,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G136" t="n">
-        <v>8.53503322601318</v>
+        <v>8.53503227233887</v>
       </c>
       <c r="H136" t="n">
         <v>172542</v>
@@ -4400,7 +4400,7 @@
         <v>9</v>
       </c>
       <c r="G139" t="n">
-        <v>8.51610660552979</v>
+        <v>8.5161075592041</v>
       </c>
       <c r="H139" t="n">
         <v>111082</v>
@@ -4661,7 +4661,7 @@
         <v>9.36699962615967</v>
       </c>
       <c r="G148" t="n">
-        <v>8.86337375640869</v>
+        <v>8.86337566375732</v>
       </c>
       <c r="H148" t="n">
         <v>76421</v>
@@ -4719,7 +4719,7 @@
         <v>9.45199966430664</v>
       </c>
       <c r="G150" t="n">
-        <v>8.94380474090576</v>
+        <v>8.94380569458008</v>
       </c>
       <c r="H150" t="n">
         <v>141690</v>
@@ -4748,7 +4748,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G151" t="n">
-        <v>8.82836437225342</v>
+        <v>8.82836532592773</v>
       </c>
       <c r="H151" t="n">
         <v>103859</v>
@@ -4835,7 +4835,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G154" t="n">
-        <v>8.96083736419678</v>
+        <v>8.96083641052246</v>
       </c>
       <c r="H154" t="n">
         <v>127739</v>
@@ -4864,7 +4864,7 @@
         <v>9.42599964141846</v>
       </c>
       <c r="G155" t="n">
-        <v>8.91920185089111</v>
+        <v>8.91920280456543</v>
       </c>
       <c r="H155" t="n">
         <v>113950</v>
@@ -4922,7 +4922,7 @@
         <v>9.60900020599365</v>
       </c>
       <c r="G157" t="n">
-        <v>9.09236335754395</v>
+        <v>9.09236431121826</v>
       </c>
       <c r="H157" t="n">
         <v>302816</v>
@@ -5038,7 +5038,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G161" t="n">
-        <v>8.94191360473633</v>
+        <v>8.94191265106201</v>
       </c>
       <c r="H161" t="n">
         <v>242695</v>
@@ -5096,7 +5096,7 @@
         <v>9.79300022125244</v>
       </c>
       <c r="G163" t="n">
-        <v>9.26646995544434</v>
+        <v>9.26647186279297</v>
       </c>
       <c r="H163" t="n">
         <v>2495031</v>
@@ -5212,7 +5212,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G167" t="n">
-        <v>9.32040691375732</v>
+        <v>9.32040786743164</v>
       </c>
       <c r="H167" t="n">
         <v>175516</v>
@@ -5299,7 +5299,7 @@
         <v>9.7819995880127</v>
       </c>
       <c r="G170" t="n">
-        <v>9.25606250762939</v>
+        <v>9.25606155395508</v>
       </c>
       <c r="H170" t="n">
         <v>59025</v>
@@ -5415,7 +5415,7 @@
         <v>9.6230001449585</v>
       </c>
       <c r="G174" t="n">
-        <v>9.10561180114746</v>
+        <v>9.10561084747314</v>
       </c>
       <c r="H174" t="n">
         <v>254745</v>
@@ -5531,7 +5531,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>9.18793296813965</v>
+        <v>9.18793392181396</v>
       </c>
       <c r="H178" t="n">
         <v>132214</v>
@@ -5734,7 +5734,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G185" t="n">
-        <v>10.0395450592041</v>
+        <v>10.0395441055298</v>
       </c>
       <c r="H185" t="n">
         <v>748210</v>
@@ -5763,7 +5763,7 @@
         <v>10.78600025177</v>
       </c>
       <c r="G186" t="n">
-        <v>10.2060823440552</v>
+        <v>10.2060813903809</v>
       </c>
       <c r="H186" t="n">
         <v>469378</v>
@@ -5937,7 +5937,7 @@
         <v>10.7720003128052</v>
       </c>
       <c r="G192" t="n">
-        <v>10.192834854126</v>
+        <v>10.1928339004517</v>
       </c>
       <c r="H192" t="n">
         <v>183949</v>
@@ -5966,7 +5966,7 @@
         <v>10.7440004348755</v>
       </c>
       <c r="G193" t="n">
-        <v>10.1663398742676</v>
+        <v>10.1663408279419</v>
       </c>
       <c r="H193" t="n">
         <v>138082</v>
@@ -6227,7 +6227,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G202" t="n">
-        <v>10.5031995773315</v>
+        <v>10.5031986236572</v>
       </c>
       <c r="H202" t="n">
         <v>244760</v>
@@ -6285,7 +6285,7 @@
         <v>11.2040004730225</v>
       </c>
       <c r="G204" t="n">
-        <v>10.6016082763672</v>
+        <v>10.6016073226929</v>
       </c>
       <c r="H204" t="n">
         <v>94315</v>
@@ -6314,7 +6314,7 @@
         <v>11.3420000076294</v>
       </c>
       <c r="G205" t="n">
-        <v>10.7321872711182</v>
+        <v>10.7321882247925</v>
       </c>
       <c r="H205" t="n">
         <v>152325</v>
@@ -6372,7 +6372,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G207" t="n">
-        <v>10.9668531417847</v>
+        <v>10.966854095459</v>
       </c>
       <c r="H207" t="n">
         <v>191397</v>
@@ -6430,7 +6430,7 @@
         <v>11.5579996109009</v>
       </c>
       <c r="G209" t="n">
-        <v>10.9365730285645</v>
+        <v>10.9365749359131</v>
       </c>
       <c r="H209" t="n">
         <v>170731</v>
@@ -6546,7 +6546,7 @@
         <v>11.5019998550415</v>
       </c>
       <c r="G213" t="n">
-        <v>10.8835859298706</v>
+        <v>10.8835849761963</v>
       </c>
       <c r="H213" t="n">
         <v>216641</v>
@@ -6575,7 +6575,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G214" t="n">
-        <v>10.5031995773315</v>
+        <v>10.5031986236572</v>
       </c>
       <c r="H214" t="n">
         <v>940630</v>
@@ -6604,7 +6604,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G215" t="n">
-        <v>10.7870693206787</v>
+        <v>10.7870683670044</v>
       </c>
       <c r="H215" t="n">
         <v>622398</v>
@@ -6662,7 +6662,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G217" t="n">
-        <v>10.4369630813599</v>
+        <v>10.4369621276855</v>
       </c>
       <c r="H217" t="n">
         <v>269996</v>
@@ -6720,7 +6720,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G219" t="n">
-        <v>10.266640663147</v>
+        <v>10.2666416168213</v>
       </c>
       <c r="H219" t="n">
         <v>238286</v>
@@ -6981,7 +6981,7 @@
         <v>11</v>
       </c>
       <c r="G228" t="n">
-        <v>10.4085750579834</v>
+        <v>10.4085760116577</v>
       </c>
       <c r="H228" t="n">
         <v>808095</v>
@@ -7068,7 +7068,7 @@
         <v>10.96399974823</v>
       </c>
       <c r="G231" t="n">
-        <v>10.3745107650757</v>
+        <v>10.37451171875</v>
       </c>
       <c r="H231" t="n">
         <v>204899</v>
@@ -7097,7 +7097,7 @@
         <v>11.0279998779297</v>
       </c>
       <c r="G232" t="n">
-        <v>10.4350690841675</v>
+        <v>10.4350700378418</v>
       </c>
       <c r="H232" t="n">
         <v>329462</v>
@@ -7126,7 +7126,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>10.5031995773315</v>
+        <v>10.5031986236572</v>
       </c>
       <c r="H233" t="n">
         <v>228150</v>
@@ -7242,7 +7242,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>10.266640663147</v>
+        <v>10.2666416168213</v>
       </c>
       <c r="H237" t="n">
         <v>250841</v>
@@ -7329,7 +7329,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G240" t="n">
-        <v>10.0395450592041</v>
+        <v>10.0395441055298</v>
       </c>
       <c r="H240" t="n">
         <v>634447</v>
@@ -7358,7 +7358,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G241" t="n">
-        <v>10.0395450592041</v>
+        <v>10.0395441055298</v>
       </c>
       <c r="H241" t="n">
         <v>254072</v>
@@ -7445,7 +7445,7 @@
         <v>10.6099996566772</v>
       </c>
       <c r="G244" t="n">
-        <v>10.0395450592041</v>
+        <v>10.0395441055298</v>
       </c>
       <c r="H244" t="n">
         <v>132610</v>
@@ -7532,7 +7532,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G247" t="n">
-        <v>9.90707206726074</v>
+        <v>9.90707111358643</v>
       </c>
       <c r="H247" t="n">
         <v>223084</v>
@@ -7648,7 +7648,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G251" t="n">
-        <v>9.89760875701904</v>
+        <v>9.89760971069336</v>
       </c>
       <c r="H251" t="n">
         <v>221470</v>
@@ -7706,7 +7706,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G253" t="n">
-        <v>9.87868404388428</v>
+        <v>9.87868499755859</v>
       </c>
       <c r="H253" t="n">
         <v>178647</v>
@@ -7764,7 +7764,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G255" t="n">
-        <v>10.2950277328491</v>
+        <v>10.2950267791748</v>
       </c>
       <c r="H255" t="n">
         <v>668230</v>
@@ -7822,7 +7822,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G257" t="n">
-        <v>10.266640663147</v>
+        <v>10.2666416168213</v>
       </c>
       <c r="H257" t="n">
         <v>500317</v>
@@ -7851,7 +7851,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G258" t="n">
-        <v>10.266640663147</v>
+        <v>10.2666416168213</v>
       </c>
       <c r="H258" t="n">
         <v>138687</v>
@@ -7938,7 +7938,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G261" t="n">
-        <v>10.1814794540405</v>
+        <v>10.1814804077148</v>
       </c>
       <c r="H261" t="n">
         <v>113192</v>
@@ -7996,7 +7996,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G263" t="n">
-        <v>10.1814794540405</v>
+        <v>10.1814804077148</v>
       </c>
       <c r="H263" t="n">
         <v>175964</v>
@@ -8083,7 +8083,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G266" t="n">
-        <v>10.1436309814453</v>
+        <v>10.143630027771</v>
       </c>
       <c r="H266" t="n">
         <v>192613</v>
@@ -8112,7 +8112,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G267" t="n">
-        <v>10.020619392395</v>
+        <v>10.0206203460693</v>
       </c>
       <c r="H267" t="n">
         <v>171371</v>
@@ -8141,7 +8141,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G268" t="n">
-        <v>10.0982227325439</v>
+        <v>10.0982236862183</v>
       </c>
       <c r="H268" t="n">
         <v>162147</v>
@@ -8344,7 +8344,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G275" t="n">
-        <v>10.3310346603394</v>
+        <v>10.3310356140137</v>
       </c>
       <c r="H275" t="n">
         <v>417991</v>
@@ -8576,7 +8576,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G283" t="n">
-        <v>10.6220502853394</v>
+        <v>10.6220512390137</v>
       </c>
       <c r="H283" t="n">
         <v>129742</v>
@@ -8634,7 +8634,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G285" t="n">
-        <v>10.5638484954834</v>
+        <v>10.5638475418091</v>
       </c>
       <c r="H285" t="n">
         <v>180726</v>
@@ -8692,7 +8692,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G287" t="n">
-        <v>10.2534313201904</v>
+        <v>10.2534303665161</v>
       </c>
       <c r="H287" t="n">
         <v>235286</v>
@@ -8721,7 +8721,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G288" t="n">
-        <v>10.3116340637207</v>
+        <v>10.311635017395</v>
       </c>
       <c r="H288" t="n">
         <v>127440</v>
@@ -8779,7 +8779,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G290" t="n">
-        <v>10.4377412796021</v>
+        <v>10.4377422332764</v>
       </c>
       <c r="H290" t="n">
         <v>97733</v>
@@ -8895,7 +8895,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G294" t="n">
-        <v>10.806360244751</v>
+        <v>10.8063611984253</v>
       </c>
       <c r="H294" t="n">
         <v>209159</v>
@@ -8982,7 +8982,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G297" t="n">
-        <v>10.951868057251</v>
+        <v>10.9518671035767</v>
       </c>
       <c r="H297" t="n">
         <v>175726</v>
@@ -9011,7 +9011,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G298" t="n">
-        <v>10.7578582763672</v>
+        <v>10.7578573226929</v>
       </c>
       <c r="H298" t="n">
         <v>301876</v>
@@ -9214,7 +9214,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G305" t="n">
-        <v>11.5823993682861</v>
+        <v>11.5824003219604</v>
       </c>
       <c r="H305" t="n">
         <v>274687</v>
@@ -9475,7 +9475,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G314" t="n">
-        <v>11.3398866653442</v>
+        <v>11.3398876190186</v>
       </c>
       <c r="H314" t="n">
         <v>110179</v>
@@ -9562,7 +9562,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G317" t="n">
-        <v>11.2525844573975</v>
+        <v>11.2525835037231</v>
       </c>
       <c r="H317" t="n">
         <v>381622</v>
@@ -9649,7 +9649,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G320" t="n">
-        <v>10.951868057251</v>
+        <v>10.9518671035767</v>
       </c>
       <c r="H320" t="n">
         <v>279934</v>
@@ -9707,7 +9707,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G322" t="n">
-        <v>10.9712696075439</v>
+        <v>10.9712686538696</v>
       </c>
       <c r="H322" t="n">
         <v>185383</v>
@@ -9765,7 +9765,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G324" t="n">
-        <v>10.7481575012207</v>
+        <v>10.7481565475464</v>
       </c>
       <c r="H324" t="n">
         <v>184196</v>
@@ -9852,7 +9852,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>10.7190551757812</v>
+        <v>10.7190561294556</v>
       </c>
       <c r="H327" t="n">
         <v>80274</v>
@@ -9881,7 +9881,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G328" t="n">
-        <v>10.7578582763672</v>
+        <v>10.7578573226929</v>
       </c>
       <c r="H328" t="n">
         <v>81593</v>
@@ -9910,7 +9910,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>10.8160600662231</v>
+        <v>10.8160610198975</v>
       </c>
       <c r="H329" t="n">
         <v>255497</v>
@@ -10055,7 +10055,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G334" t="n">
-        <v>11.1361770629883</v>
+        <v>11.136176109314</v>
       </c>
       <c r="H334" t="n">
         <v>92993</v>
@@ -10084,7 +10084,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G335" t="n">
-        <v>11.1361770629883</v>
+        <v>11.136176109314</v>
       </c>
       <c r="H335" t="n">
         <v>109603</v>
@@ -10258,7 +10258,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G341" t="n">
-        <v>11.4077911376953</v>
+        <v>11.4077920913696</v>
       </c>
       <c r="H341" t="n">
         <v>275168</v>
@@ -10374,7 +10374,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G345" t="n">
-        <v>10.9712696075439</v>
+        <v>10.9712686538696</v>
       </c>
       <c r="H345" t="n">
         <v>250890</v>
@@ -10403,7 +10403,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G346" t="n">
-        <v>10.9615688323975</v>
+        <v>10.9615678787231</v>
       </c>
       <c r="H346" t="n">
         <v>157159</v>
@@ -10432,7 +10432,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G347" t="n">
-        <v>11.0003700256348</v>
+        <v>11.0003709793091</v>
       </c>
       <c r="H347" t="n">
         <v>187467</v>
@@ -10461,7 +10461,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G348" t="n">
-        <v>11.0003700256348</v>
+        <v>11.0003709793091</v>
       </c>
       <c r="H348" t="n">
         <v>109481</v>
@@ -10722,7 +10722,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G357" t="n">
-        <v>11.0585737228394</v>
+        <v>11.058572769165</v>
       </c>
       <c r="H357" t="n">
         <v>184343</v>
@@ -10780,7 +10780,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G359" t="n">
-        <v>11.0003700256348</v>
+        <v>11.0003709793091</v>
       </c>
       <c r="H359" t="n">
         <v>186510</v>
@@ -10867,7 +10867,7 @@
         <v>11.25</v>
       </c>
       <c r="G362" t="n">
-        <v>10.913064956665</v>
+        <v>10.9130659103394</v>
       </c>
       <c r="H362" t="n">
         <v>440278</v>
@@ -10925,7 +10925,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G364" t="n">
-        <v>11.1458778381348</v>
+        <v>11.1458768844604</v>
       </c>
       <c r="H364" t="n">
         <v>188007</v>
@@ -11012,7 +11012,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>11.0585737228394</v>
+        <v>11.058572769165</v>
       </c>
       <c r="H367" t="n">
         <v>195723</v>
@@ -11070,7 +11070,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G369" t="n">
-        <v>11.1458778381348</v>
+        <v>11.1458768844604</v>
       </c>
       <c r="H369" t="n">
         <v>107932</v>
@@ -11128,7 +11128,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G371" t="n">
-        <v>11.1361770629883</v>
+        <v>11.136176109314</v>
       </c>
       <c r="H371" t="n">
         <v>118399</v>
@@ -11186,7 +11186,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G373" t="n">
-        <v>11.0197706222534</v>
+        <v>11.0197715759277</v>
       </c>
       <c r="H373" t="n">
         <v>147161</v>
@@ -11302,7 +11302,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G377" t="n">
-        <v>11.0197706222534</v>
+        <v>11.0197715759277</v>
       </c>
       <c r="H377" t="n">
         <v>130368</v>
@@ -11476,7 +11476,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G383" t="n">
-        <v>11.1361770629883</v>
+        <v>11.136176109314</v>
       </c>
       <c r="H383" t="n">
         <v>194313</v>
@@ -11592,7 +11592,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G387" t="n">
-        <v>11.1749792098999</v>
+        <v>11.1749801635742</v>
       </c>
       <c r="H387" t="n">
         <v>197901</v>
@@ -11650,7 +11650,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G389" t="n">
-        <v>11.4465942382812</v>
+        <v>11.4465932846069</v>
       </c>
       <c r="H389" t="n">
         <v>259214</v>
@@ -11737,7 +11737,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G392" t="n">
-        <v>11.8540153503418</v>
+        <v>11.8540143966675</v>
       </c>
       <c r="H392" t="n">
         <v>194096</v>
@@ -11795,7 +11795,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G394" t="n">
-        <v>11.6988067626953</v>
+        <v>11.6988077163696</v>
       </c>
       <c r="H394" t="n">
         <v>171327</v>
@@ -11911,7 +11911,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G398" t="n">
-        <v>11.6309032440186</v>
+        <v>11.6309022903442</v>
       </c>
       <c r="H398" t="n">
         <v>192088</v>
@@ -11940,7 +11940,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G399" t="n">
-        <v>11.5823993682861</v>
+        <v>11.5824003219604</v>
       </c>
       <c r="H399" t="n">
         <v>137161</v>
@@ -12056,7 +12056,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G403" t="n">
-        <v>12.1935319900513</v>
+        <v>12.193531036377</v>
       </c>
       <c r="H403" t="n">
         <v>108069</v>
@@ -12114,7 +12114,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G405" t="n">
-        <v>12.1935319900513</v>
+        <v>12.193531036377</v>
       </c>
       <c r="H405" t="n">
         <v>135114</v>
@@ -12172,7 +12172,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G407" t="n">
-        <v>12.2226333618164</v>
+        <v>12.2226343154907</v>
       </c>
       <c r="H407" t="n">
         <v>185001</v>
@@ -12201,7 +12201,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G408" t="n">
-        <v>12.2517347335815</v>
+        <v>12.2517356872559</v>
       </c>
       <c r="H408" t="n">
         <v>172512</v>
@@ -12288,7 +12288,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G411" t="n">
-        <v>12.4651460647583</v>
+        <v>12.4651470184326</v>
       </c>
       <c r="H411" t="n">
         <v>133030</v>
@@ -12317,7 +12317,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G412" t="n">
-        <v>12.3875427246094</v>
+        <v>12.3875417709351</v>
       </c>
       <c r="H412" t="n">
         <v>148541</v>
@@ -12520,7 +12520,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G419" t="n">
-        <v>12.2517347335815</v>
+        <v>12.2517356872559</v>
       </c>
       <c r="H419" t="n">
         <v>165954</v>
@@ -12549,7 +12549,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G420" t="n">
-        <v>12.2226333618164</v>
+        <v>12.2226343154907</v>
       </c>
       <c r="H420" t="n">
         <v>258706</v>
@@ -12607,7 +12607,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G422" t="n">
-        <v>12.2129335403442</v>
+        <v>12.2129325866699</v>
       </c>
       <c r="H422" t="n">
         <v>137376</v>
@@ -12636,7 +12636,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G423" t="n">
-        <v>12.3875427246094</v>
+        <v>12.3875417709351</v>
       </c>
       <c r="H423" t="n">
         <v>99466</v>
@@ -12723,7 +12723,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G426" t="n">
-        <v>12.5427513122559</v>
+        <v>12.5427503585815</v>
       </c>
       <c r="H426" t="n">
         <v>197307</v>
@@ -12752,7 +12752,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G427" t="n">
-        <v>12.630054473877</v>
+        <v>12.6300554275513</v>
       </c>
       <c r="H427" t="n">
         <v>148262</v>
@@ -12839,7 +12839,7 @@
         <v>13</v>
       </c>
       <c r="G430" t="n">
-        <v>12.610652923584</v>
+        <v>12.6106538772583</v>
       </c>
       <c r="H430" t="n">
         <v>1807764</v>
@@ -12897,7 +12897,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G432" t="n">
-        <v>12.3972425460815</v>
+        <v>12.3972415924072</v>
       </c>
       <c r="H432" t="n">
         <v>1234024</v>
@@ -12955,7 +12955,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G434" t="n">
-        <v>12.6882581710815</v>
+        <v>12.6882572174072</v>
       </c>
       <c r="H434" t="n">
         <v>465320</v>
@@ -13013,7 +13013,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G436" t="n">
-        <v>13.1538820266724</v>
+        <v>13.1538829803467</v>
       </c>
       <c r="H436" t="n">
         <v>425963</v>
@@ -13274,7 +13274,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G445" t="n">
-        <v>13.7844152450562</v>
+        <v>13.7844142913818</v>
       </c>
       <c r="H445" t="n">
         <v>236771</v>
@@ -13303,7 +13303,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G446" t="n">
-        <v>14.3373432159424</v>
+        <v>14.3373422622681</v>
       </c>
       <c r="H446" t="n">
         <v>473165</v>
@@ -13332,7 +13332,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G447" t="n">
-        <v>14.4537496566772</v>
+        <v>14.4537487030029</v>
       </c>
       <c r="H447" t="n">
         <v>380386</v>
@@ -13361,7 +13361,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G448" t="n">
-        <v>14.667160987854</v>
+        <v>14.6671600341797</v>
       </c>
       <c r="H448" t="n">
         <v>267462</v>
@@ -13419,7 +13419,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G450" t="n">
-        <v>14.8029670715332</v>
+        <v>14.8029680252075</v>
       </c>
       <c r="H450" t="n">
         <v>391347</v>
@@ -13622,7 +13622,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G457" t="n">
-        <v>16.0446338653564</v>
+        <v>16.0446319580078</v>
       </c>
       <c r="H457" t="n">
         <v>378598</v>
@@ -13680,7 +13680,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G459" t="n">
-        <v>15.9573268890381</v>
+        <v>15.9573278427124</v>
       </c>
       <c r="H459" t="n">
         <v>261224</v>
@@ -13796,7 +13796,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G463" t="n">
-        <v>16.0252304077148</v>
+        <v>16.0252323150635</v>
       </c>
       <c r="H463" t="n">
         <v>392686</v>
@@ -13825,7 +13825,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G464" t="n">
-        <v>15.6857128143311</v>
+        <v>15.6857137680054</v>
       </c>
       <c r="H464" t="n">
         <v>532461</v>
@@ -14028,7 +14028,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G471" t="n">
-        <v>15.870023727417</v>
+        <v>15.8700227737427</v>
       </c>
       <c r="H471" t="n">
         <v>880362</v>
@@ -14115,7 +14115,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G474" t="n">
-        <v>16.9273796081543</v>
+        <v>16.9273777008057</v>
       </c>
       <c r="H474" t="n">
         <v>620043</v>
@@ -14260,7 +14260,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G479" t="n">
-        <v>17.5870094299316</v>
+        <v>17.5870113372803</v>
       </c>
       <c r="H479" t="n">
         <v>473621</v>
@@ -14289,7 +14289,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G480" t="n">
-        <v>17.5870094299316</v>
+        <v>17.5870113372803</v>
       </c>
       <c r="H480" t="n">
         <v>417252</v>
@@ -14347,7 +14347,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G482" t="n">
-        <v>17.1601886749268</v>
+        <v>17.1601905822754</v>
       </c>
       <c r="H482" t="n">
         <v>353508</v>
@@ -14405,7 +14405,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G484" t="n">
-        <v>17.7519187927246</v>
+        <v>17.7519207000732</v>
       </c>
       <c r="H484" t="n">
         <v>342388</v>
@@ -14434,7 +14434,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G485" t="n">
-        <v>17.7422218322754</v>
+        <v>17.7422199249268</v>
       </c>
       <c r="H485" t="n">
         <v>271126</v>
@@ -14521,7 +14521,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G488" t="n">
-        <v>17.9071292877197</v>
+        <v>17.9071273803711</v>
       </c>
       <c r="H488" t="n">
         <v>372109</v>
@@ -14550,7 +14550,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G489" t="n">
-        <v>18.3727531433105</v>
+        <v>18.3727512359619</v>
       </c>
       <c r="H489" t="n">
         <v>455016</v>
@@ -14608,7 +14608,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>16.8303718566895</v>
+        <v>16.8303737640381</v>
       </c>
       <c r="H491" t="n">
         <v>1164243</v>
@@ -14695,7 +14695,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G494" t="n">
-        <v>17.1601886749268</v>
+        <v>17.1601905822754</v>
       </c>
       <c r="H494" t="n">
         <v>564420</v>
@@ -14898,7 +14898,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G501" t="n">
-        <v>18.8480777740479</v>
+        <v>18.8480758666992</v>
       </c>
       <c r="H501" t="n">
         <v>377971</v>
@@ -14927,7 +14927,7 @@
         <v>19.4699993133545</v>
       </c>
       <c r="G502" t="n">
-        <v>18.8868789672852</v>
+        <v>18.8868770599365</v>
       </c>
       <c r="H502" t="n">
         <v>436832</v>
@@ -14956,7 +14956,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G503" t="n">
-        <v>19.0226860046387</v>
+        <v>19.0226879119873</v>
       </c>
       <c r="H503" t="n">
         <v>218294</v>
@@ -15014,7 +15014,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G505" t="n">
-        <v>19.478609085083</v>
+        <v>19.4786109924316</v>
       </c>
       <c r="H505" t="n">
         <v>375456</v>
@@ -15043,7 +15043,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G506" t="n">
-        <v>19.45920753479</v>
+        <v>19.4592094421387</v>
       </c>
       <c r="H506" t="n">
         <v>430857</v>
@@ -15072,7 +15072,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G507" t="n">
-        <v>19.4398097991943</v>
+        <v>19.4398078918457</v>
       </c>
       <c r="H507" t="n">
         <v>573705</v>
@@ -15130,7 +15130,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G509" t="n">
-        <v>20.3128547668457</v>
+        <v>20.3128528594971</v>
       </c>
       <c r="H509" t="n">
         <v>845381</v>
@@ -15159,7 +15159,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G510" t="n">
-        <v>20.2352485656738</v>
+        <v>20.2352504730225</v>
       </c>
       <c r="H510" t="n">
         <v>628106</v>
@@ -15188,7 +15188,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G511" t="n">
-        <v>19.9248352050781</v>
+        <v>19.9248332977295</v>
       </c>
       <c r="H511" t="n">
         <v>774008</v>
@@ -15217,7 +15217,7 @@
         <v>20</v>
       </c>
       <c r="G512" t="n">
-        <v>19.4010066986084</v>
+        <v>19.4010047912598</v>
       </c>
       <c r="H512" t="n">
         <v>769373</v>
@@ -15304,7 +15304,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>21.6321201324463</v>
+        <v>21.6321220397949</v>
       </c>
       <c r="H515" t="n">
         <v>2197577</v>
@@ -15362,7 +15362,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G517" t="n">
-        <v>22.1171474456787</v>
+        <v>22.1171455383301</v>
       </c>
       <c r="H517" t="n">
         <v>555528</v>
@@ -15391,7 +15391,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G518" t="n">
-        <v>21.9619369506836</v>
+        <v>21.9619388580322</v>
       </c>
       <c r="H518" t="n">
         <v>611058</v>
@@ -26069,6 +26069,35 @@
         <v>725015</v>
       </c>
       <c r="I886" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="s">
+        <v>9</v>
+      </c>
+      <c r="B887" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C887" t="n">
+        <v>24.6900005340576</v>
+      </c>
+      <c r="D887" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E887" t="n">
+        <v>24.6000003814697</v>
+      </c>
+      <c r="F887" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G887" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="H887" t="n">
+        <v>780061</v>
+      </c>
+      <c r="I887" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LTMC.MI.xlsx
+++ b/data/LTMC.MI.xlsx
@@ -427,7 +427,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2" t="n">
-        <v>7.75911998748779</v>
+        <v>7.75911951065063</v>
       </c>
       <c r="H2" t="n">
         <v>13006120</v>
@@ -456,7 +456,7 @@
         <v>8.27000045776367</v>
       </c>
       <c r="G3" t="n">
-        <v>7.82535648345947</v>
+        <v>7.82535696029663</v>
       </c>
       <c r="H3" t="n">
         <v>2759922</v>
@@ -485,7 +485,7 @@
         <v>8.44600009918213</v>
       </c>
       <c r="G4" t="n">
-        <v>7.99189424514771</v>
+        <v>7.99189376831055</v>
       </c>
       <c r="H4" t="n">
         <v>1476712</v>
@@ -572,7 +572,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G7" t="n">
-        <v>7.92944240570068</v>
+        <v>7.92944288253784</v>
       </c>
       <c r="H7" t="n">
         <v>640304</v>
@@ -630,7 +630,7 @@
         <v>8.25</v>
       </c>
       <c r="G9" t="n">
-        <v>7.80643224716187</v>
+        <v>7.80643177032471</v>
       </c>
       <c r="H9" t="n">
         <v>1073912</v>
@@ -659,7 +659,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G10" t="n">
-        <v>7.99567890167236</v>
+        <v>7.99567842483521</v>
       </c>
       <c r="H10" t="n">
         <v>1947465</v>
@@ -775,7 +775,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G14" t="n">
-        <v>7.52256107330322</v>
+        <v>7.52256155014038</v>
       </c>
       <c r="H14" t="n">
         <v>981832</v>
@@ -833,7 +833,7 @@
         <v>7.86899995803833</v>
       </c>
       <c r="G16" t="n">
-        <v>7.44591617584229</v>
+        <v>7.44591665267944</v>
       </c>
       <c r="H16" t="n">
         <v>479599</v>
@@ -891,7 +891,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G18" t="n">
-        <v>7.2670783996582</v>
+        <v>7.26707792282104</v>
       </c>
       <c r="H18" t="n">
         <v>228832</v>
@@ -1007,7 +1007,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G22" t="n">
-        <v>7.03525114059448</v>
+        <v>7.03525066375732</v>
       </c>
       <c r="H22" t="n">
         <v>597512</v>
@@ -1123,7 +1123,7 @@
         <v>7.86800003051758</v>
       </c>
       <c r="G26" t="n">
-        <v>7.44497013092041</v>
+        <v>7.44497060775757</v>
       </c>
       <c r="H26" t="n">
         <v>235788</v>
@@ -1152,7 +1152,7 @@
         <v>8.12600040435791</v>
       </c>
       <c r="G27" t="n">
-        <v>7.68909931182861</v>
+        <v>7.68909883499146</v>
       </c>
       <c r="H27" t="n">
         <v>1170934</v>
@@ -1210,7 +1210,7 @@
         <v>8.52200031280518</v>
       </c>
       <c r="G29" t="n">
-        <v>8.06380844116211</v>
+        <v>8.06380748748779</v>
       </c>
       <c r="H29" t="n">
         <v>1531238</v>
@@ -1297,7 +1297,7 @@
         <v>8.16199970245361</v>
       </c>
       <c r="G32" t="n">
-        <v>7.72316312789917</v>
+        <v>7.72316265106201</v>
       </c>
       <c r="H32" t="n">
         <v>440552</v>
@@ -1326,7 +1326,7 @@
         <v>8.21399974822998</v>
       </c>
       <c r="G33" t="n">
-        <v>7.77236700057983</v>
+        <v>7.77236747741699</v>
       </c>
       <c r="H33" t="n">
         <v>327710</v>
@@ -1355,7 +1355,7 @@
         <v>8.41300010681152</v>
       </c>
       <c r="G34" t="n">
-        <v>7.96066761016846</v>
+        <v>7.9606671333313</v>
       </c>
       <c r="H34" t="n">
         <v>540974</v>
@@ -1384,7 +1384,7 @@
         <v>8.24600028991699</v>
       </c>
       <c r="G35" t="n">
-        <v>7.80264663696289</v>
+        <v>7.80264759063721</v>
       </c>
       <c r="H35" t="n">
         <v>379647</v>
@@ -1413,7 +1413,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G36" t="n">
-        <v>7.81116247177124</v>
+        <v>7.8111629486084</v>
       </c>
       <c r="H36" t="n">
         <v>219714</v>
@@ -1442,7 +1442,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G37" t="n">
-        <v>7.92944240570068</v>
+        <v>7.92944288253784</v>
       </c>
       <c r="H37" t="n">
         <v>223839</v>
@@ -1500,7 +1500,7 @@
         <v>8.43299961090088</v>
       </c>
       <c r="G39" t="n">
-        <v>7.97959184646606</v>
+        <v>7.97959136962891</v>
       </c>
       <c r="H39" t="n">
         <v>99001</v>
@@ -1529,7 +1529,7 @@
         <v>8.43599987030029</v>
       </c>
       <c r="G40" t="n">
-        <v>7.98243093490601</v>
+        <v>7.98243045806885</v>
       </c>
       <c r="H40" t="n">
         <v>155784</v>
@@ -1558,7 +1558,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G41" t="n">
-        <v>7.92944240570068</v>
+        <v>7.92944288253784</v>
       </c>
       <c r="H41" t="n">
         <v>133019</v>
@@ -1587,7 +1587,7 @@
         <v>8.41300010681152</v>
       </c>
       <c r="G42" t="n">
-        <v>7.96066761016846</v>
+        <v>7.9606671333313</v>
       </c>
       <c r="H42" t="n">
         <v>122155</v>
@@ -1645,7 +1645,7 @@
         <v>8.71599960327148</v>
       </c>
       <c r="G44" t="n">
-        <v>8.24737644195557</v>
+        <v>8.24737548828125</v>
       </c>
       <c r="H44" t="n">
         <v>146543</v>
@@ -1732,7 +1732,7 @@
         <v>8.58300018310547</v>
       </c>
       <c r="G47" t="n">
-        <v>8.12152767181396</v>
+        <v>8.12152862548828</v>
       </c>
       <c r="H47" t="n">
         <v>162361</v>
@@ -1819,7 +1819,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G50" t="n">
-        <v>8.49718189239502</v>
+        <v>8.49718284606934</v>
       </c>
       <c r="H50" t="n">
         <v>475388</v>
@@ -1935,7 +1935,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G54" t="n">
-        <v>8.97029972076416</v>
+        <v>8.97029876708984</v>
       </c>
       <c r="H54" t="n">
         <v>321248</v>
@@ -2022,7 +2022,7 @@
         <v>9.38399982452393</v>
       </c>
       <c r="G57" t="n">
-        <v>8.87946033477783</v>
+        <v>8.87946128845215</v>
       </c>
       <c r="H57" t="n">
         <v>292101</v>
@@ -2167,7 +2167,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G62" t="n">
-        <v>8.65804290771484</v>
+        <v>8.65804195404053</v>
       </c>
       <c r="H62" t="n">
         <v>407302</v>
@@ -2196,7 +2196,7 @@
         <v>9.17800045013428</v>
       </c>
       <c r="G63" t="n">
-        <v>8.68453693389893</v>
+        <v>8.68453788757324</v>
       </c>
       <c r="H63" t="n">
         <v>254936</v>
@@ -2225,7 +2225,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G64" t="n">
-        <v>8.79997825622559</v>
+        <v>8.79997730255127</v>
       </c>
       <c r="H64" t="n">
         <v>396592</v>
@@ -2254,7 +2254,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G65" t="n">
-        <v>8.94191265106201</v>
+        <v>8.94191360473633</v>
       </c>
       <c r="H65" t="n">
         <v>900757</v>
@@ -2312,7 +2312,7 @@
         <v>9.32499980926514</v>
       </c>
       <c r="G67" t="n">
-        <v>8.82363224029541</v>
+        <v>8.82363319396973</v>
       </c>
       <c r="H67" t="n">
         <v>266872</v>
@@ -2370,7 +2370,7 @@
         <v>9.30300045013428</v>
       </c>
       <c r="G69" t="n">
-        <v>8.80281734466553</v>
+        <v>8.80281639099121</v>
       </c>
       <c r="H69" t="n">
         <v>181453</v>
@@ -2428,7 +2428,7 @@
         <v>9.30300045013428</v>
       </c>
       <c r="G71" t="n">
-        <v>8.80281734466553</v>
+        <v>8.80281639099121</v>
       </c>
       <c r="H71" t="n">
         <v>228312</v>
@@ -2486,7 +2486,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G73" t="n">
-        <v>8.79997825622559</v>
+        <v>8.79997730255127</v>
       </c>
       <c r="H73" t="n">
         <v>161362</v>
@@ -2602,7 +2602,7 @@
         <v>9.12600040435791</v>
       </c>
       <c r="G77" t="n">
-        <v>8.63533306121826</v>
+        <v>8.63533401489258</v>
       </c>
       <c r="H77" t="n">
         <v>248031</v>
@@ -2660,7 +2660,7 @@
         <v>9.10799980163574</v>
       </c>
       <c r="G79" t="n">
-        <v>8.61830043792725</v>
+        <v>8.61829948425293</v>
       </c>
       <c r="H79" t="n">
         <v>127272</v>
@@ -2805,7 +2805,7 @@
         <v>9.39200019836426</v>
       </c>
       <c r="G84" t="n">
-        <v>8.88703060150146</v>
+        <v>8.88703155517578</v>
       </c>
       <c r="H84" t="n">
         <v>248541</v>
@@ -2892,7 +2892,7 @@
         <v>9</v>
       </c>
       <c r="G87" t="n">
-        <v>8.5161075592041</v>
+        <v>8.51610660552979</v>
       </c>
       <c r="H87" t="n">
         <v>2756951</v>
@@ -2921,7 +2921,7 @@
         <v>9.10799980163574</v>
       </c>
       <c r="G88" t="n">
-        <v>8.61830043792725</v>
+        <v>8.61829948425293</v>
       </c>
       <c r="H88" t="n">
         <v>496089</v>
@@ -2979,7 +2979,7 @@
         <v>9.17899990081787</v>
       </c>
       <c r="G90" t="n">
-        <v>8.68548393249512</v>
+        <v>8.68548202514648</v>
       </c>
       <c r="H90" t="n">
         <v>216140</v>
@@ -3095,7 +3095,7 @@
         <v>9.02299976348877</v>
       </c>
       <c r="G94" t="n">
-        <v>8.53786945343018</v>
+        <v>8.53787040710449</v>
       </c>
       <c r="H94" t="n">
         <v>577462</v>
@@ -3153,7 +3153,7 @@
         <v>9</v>
       </c>
       <c r="G96" t="n">
-        <v>8.5161075592041</v>
+        <v>8.51610660552979</v>
       </c>
       <c r="H96" t="n">
         <v>322675</v>
@@ -3298,7 +3298,7 @@
         <v>9.01900005340576</v>
       </c>
       <c r="G101" t="n">
-        <v>8.53408527374268</v>
+        <v>8.53408622741699</v>
       </c>
       <c r="H101" t="n">
         <v>120168</v>
@@ -3414,7 +3414,7 @@
         <v>8.53899955749512</v>
       </c>
       <c r="G105" t="n">
-        <v>8.0798921585083</v>
+        <v>8.07989311218262</v>
       </c>
       <c r="H105" t="n">
         <v>153907</v>
@@ -3588,7 +3588,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G111" t="n">
-        <v>8.17546367645264</v>
+        <v>8.17546272277832</v>
       </c>
       <c r="H111" t="n">
         <v>213577</v>
@@ -3762,7 +3762,7 @@
         <v>8.85400009155273</v>
       </c>
       <c r="G117" t="n">
-        <v>8.37795829772949</v>
+        <v>8.37795734405518</v>
       </c>
       <c r="H117" t="n">
         <v>105095</v>
@@ -3849,7 +3849,7 @@
         <v>8.75</v>
       </c>
       <c r="G120" t="n">
-        <v>8.27954959869385</v>
+        <v>8.27954864501953</v>
       </c>
       <c r="H120" t="n">
         <v>97384</v>
@@ -3936,7 +3936,7 @@
         <v>8.7810001373291</v>
       </c>
       <c r="G123" t="n">
-        <v>8.30888271331787</v>
+        <v>8.30888175964355</v>
       </c>
       <c r="H123" t="n">
         <v>162637</v>
@@ -3965,7 +3965,7 @@
         <v>9</v>
       </c>
       <c r="G124" t="n">
-        <v>8.5161075592041</v>
+        <v>8.51610660552979</v>
       </c>
       <c r="H124" t="n">
         <v>178371</v>
@@ -4110,7 +4110,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G129" t="n">
-        <v>8.44987201690674</v>
+        <v>8.44987106323242</v>
       </c>
       <c r="H129" t="n">
         <v>141108</v>
@@ -4226,7 +4226,7 @@
         <v>9.22200012207031</v>
       </c>
       <c r="G133" t="n">
-        <v>8.72617149353027</v>
+        <v>8.72617053985596</v>
       </c>
       <c r="H133" t="n">
         <v>178676</v>
@@ -4255,7 +4255,7 @@
         <v>9.05300045013428</v>
       </c>
       <c r="G134" t="n">
-        <v>8.56625843048096</v>
+        <v>8.56625747680664</v>
       </c>
       <c r="H134" t="n">
         <v>123966</v>
@@ -4400,7 +4400,7 @@
         <v>9</v>
       </c>
       <c r="G139" t="n">
-        <v>8.5161075592041</v>
+        <v>8.51610660552979</v>
       </c>
       <c r="H139" t="n">
         <v>111082</v>
@@ -4487,7 +4487,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G142" t="n">
-        <v>8.6296558380127</v>
+        <v>8.62965488433838</v>
       </c>
       <c r="H142" t="n">
         <v>176941</v>
@@ -4661,7 +4661,7 @@
         <v>9.36699962615967</v>
       </c>
       <c r="G148" t="n">
-        <v>8.86337566375732</v>
+        <v>8.86337375640869</v>
       </c>
       <c r="H148" t="n">
         <v>76421</v>
@@ -4719,7 +4719,7 @@
         <v>9.45199966430664</v>
       </c>
       <c r="G150" t="n">
-        <v>8.94380569458008</v>
+        <v>8.94380474090576</v>
       </c>
       <c r="H150" t="n">
         <v>141690</v>
@@ -4748,7 +4748,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G151" t="n">
-        <v>8.82836532592773</v>
+        <v>8.82836437225342</v>
       </c>
       <c r="H151" t="n">
         <v>103859</v>
@@ -4835,7 +4835,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G154" t="n">
-        <v>8.96083641052246</v>
+        <v>8.96083736419678</v>
       </c>
       <c r="H154" t="n">
         <v>127739</v>
@@ -4864,7 +4864,7 @@
         <v>9.42599964141846</v>
       </c>
       <c r="G155" t="n">
-        <v>8.91920280456543</v>
+        <v>8.91920185089111</v>
       </c>
       <c r="H155" t="n">
         <v>113950</v>
@@ -4893,7 +4893,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G156" t="n">
-        <v>9.00815010070801</v>
+        <v>9.00814914703369</v>
       </c>
       <c r="H156" t="n">
         <v>146799</v>
@@ -5038,7 +5038,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G161" t="n">
-        <v>8.94191265106201</v>
+        <v>8.94191360473633</v>
       </c>
       <c r="H161" t="n">
         <v>242695</v>
@@ -5067,7 +5067,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G162" t="n">
-        <v>9.1122350692749</v>
+        <v>9.11223411560059</v>
       </c>
       <c r="H162" t="n">
         <v>177419</v>
@@ -5096,7 +5096,7 @@
         <v>9.79300022125244</v>
       </c>
       <c r="G163" t="n">
-        <v>9.26647186279297</v>
+        <v>9.26647090911865</v>
       </c>
       <c r="H163" t="n">
         <v>2495031</v>
@@ -5125,7 +5125,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G164" t="n">
-        <v>9.27309417724609</v>
+        <v>9.27309513092041</v>
       </c>
       <c r="H164" t="n">
         <v>159322</v>
@@ -5212,7 +5212,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G167" t="n">
-        <v>9.32040786743164</v>
+        <v>9.32040691375732</v>
       </c>
       <c r="H167" t="n">
         <v>175516</v>
@@ -5386,7 +5386,7 @@
         <v>9.57100009918213</v>
       </c>
       <c r="G173" t="n">
-        <v>9.05640697479248</v>
+        <v>9.05640602111816</v>
       </c>
       <c r="H173" t="n">
         <v>138205</v>
@@ -5415,7 +5415,7 @@
         <v>9.6230001449585</v>
       </c>
       <c r="G174" t="n">
-        <v>9.10561084747314</v>
+        <v>9.10561180114746</v>
       </c>
       <c r="H174" t="n">
         <v>254745</v>
@@ -5531,7 +5531,7 @@
         <v>9.71000003814697</v>
       </c>
       <c r="G178" t="n">
-        <v>9.18793392181396</v>
+        <v>9.18793296813965</v>
       </c>
       <c r="H178" t="n">
         <v>132214</v>
@@ -5560,7 +5560,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>9.1122350692749</v>
+        <v>9.11223411560059</v>
       </c>
       <c r="H179" t="n">
         <v>138026</v>
@@ -5676,7 +5676,7 @@
         <v>10.4580001831055</v>
       </c>
       <c r="G183" t="n">
-        <v>9.89571762084961</v>
+        <v>9.89571666717529</v>
       </c>
       <c r="H183" t="n">
         <v>362012</v>
@@ -5763,7 +5763,7 @@
         <v>10.78600025177</v>
       </c>
       <c r="G186" t="n">
-        <v>10.2060813903809</v>
+        <v>10.2060823440552</v>
       </c>
       <c r="H186" t="n">
         <v>469378</v>
@@ -5908,7 +5908,7 @@
         <v>10.6820001602173</v>
       </c>
       <c r="G191" t="n">
-        <v>10.1076726913452</v>
+        <v>10.1076736450195</v>
       </c>
       <c r="H191" t="n">
         <v>152759</v>
@@ -5937,7 +5937,7 @@
         <v>10.7720003128052</v>
       </c>
       <c r="G192" t="n">
-        <v>10.1928339004517</v>
+        <v>10.192834854126</v>
       </c>
       <c r="H192" t="n">
         <v>183949</v>
@@ -5966,7 +5966,7 @@
         <v>10.7440004348755</v>
       </c>
       <c r="G193" t="n">
-        <v>10.1663408279419</v>
+        <v>10.1663398742676</v>
       </c>
       <c r="H193" t="n">
         <v>138082</v>
@@ -5995,7 +5995,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G194" t="n">
-        <v>10.1909418106079</v>
+        <v>10.1909427642822</v>
       </c>
       <c r="H194" t="n">
         <v>199527</v>
@@ -6227,7 +6227,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G202" t="n">
-        <v>10.5031986236572</v>
+        <v>10.5031995773315</v>
       </c>
       <c r="H202" t="n">
         <v>244760</v>
@@ -6285,7 +6285,7 @@
         <v>11.2040004730225</v>
       </c>
       <c r="G204" t="n">
-        <v>10.6016073226929</v>
+        <v>10.6016082763672</v>
       </c>
       <c r="H204" t="n">
         <v>94315</v>
@@ -6314,7 +6314,7 @@
         <v>11.3420000076294</v>
       </c>
       <c r="G205" t="n">
-        <v>10.7321882247925</v>
+        <v>10.7321872711182</v>
       </c>
       <c r="H205" t="n">
         <v>152325</v>
@@ -6401,7 +6401,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G208" t="n">
-        <v>10.9763164520264</v>
+        <v>10.9763174057007</v>
       </c>
       <c r="H208" t="n">
         <v>197138</v>
@@ -6430,7 +6430,7 @@
         <v>11.5579996109009</v>
       </c>
       <c r="G209" t="n">
-        <v>10.9365749359131</v>
+        <v>10.9365739822388</v>
       </c>
       <c r="H209" t="n">
         <v>170731</v>
@@ -6459,7 +6459,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G210" t="n">
-        <v>10.9195423126221</v>
+        <v>10.9195413589478</v>
       </c>
       <c r="H210" t="n">
         <v>166746</v>
@@ -6517,7 +6517,7 @@
         <v>11.4820003509521</v>
       </c>
       <c r="G212" t="n">
-        <v>10.8646612167358</v>
+        <v>10.8646602630615</v>
       </c>
       <c r="H212" t="n">
         <v>251501</v>
@@ -6546,7 +6546,7 @@
         <v>11.5019998550415</v>
       </c>
       <c r="G213" t="n">
-        <v>10.8835849761963</v>
+        <v>10.8835859298706</v>
       </c>
       <c r="H213" t="n">
         <v>216641</v>
@@ -6575,7 +6575,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G214" t="n">
-        <v>10.5031986236572</v>
+        <v>10.5031995773315</v>
       </c>
       <c r="H214" t="n">
         <v>940630</v>
@@ -6604,7 +6604,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G215" t="n">
-        <v>10.7870683670044</v>
+        <v>10.7870693206787</v>
       </c>
       <c r="H215" t="n">
         <v>622398</v>
@@ -6691,7 +6691,7 @@
         <v>10.8739995956421</v>
       </c>
       <c r="G218" t="n">
-        <v>10.2893495559692</v>
+        <v>10.2893505096436</v>
       </c>
       <c r="H218" t="n">
         <v>223312</v>
@@ -6720,7 +6720,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G219" t="n">
-        <v>10.2666416168213</v>
+        <v>10.266640663147</v>
       </c>
       <c r="H219" t="n">
         <v>238286</v>
@@ -6749,7 +6749,7 @@
         <v>10.9619998931885</v>
       </c>
       <c r="G220" t="n">
-        <v>10.3726196289062</v>
+        <v>10.3726186752319</v>
       </c>
       <c r="H220" t="n">
         <v>156811</v>
@@ -6894,7 +6894,7 @@
         <v>11.9340000152588</v>
       </c>
       <c r="G225" t="n">
-        <v>11.2923583984375</v>
+        <v>11.2923593521118</v>
       </c>
       <c r="H225" t="n">
         <v>1392941</v>
@@ -7010,7 +7010,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G229" t="n">
-        <v>10.4558877944946</v>
+        <v>10.4558868408203</v>
       </c>
       <c r="H229" t="n">
         <v>563146</v>
@@ -7039,7 +7039,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G230" t="n">
-        <v>10.3896503448486</v>
+        <v>10.3896512985229</v>
       </c>
       <c r="H230" t="n">
         <v>475068</v>
@@ -7068,7 +7068,7 @@
         <v>10.96399974823</v>
       </c>
       <c r="G231" t="n">
-        <v>10.37451171875</v>
+        <v>10.3745107650757</v>
       </c>
       <c r="H231" t="n">
         <v>204899</v>
@@ -7126,7 +7126,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>10.5031986236572</v>
+        <v>10.5031995773315</v>
       </c>
       <c r="H233" t="n">
         <v>228150</v>
@@ -7155,7 +7155,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G234" t="n">
-        <v>10.5126609802246</v>
+        <v>10.5126619338989</v>
       </c>
       <c r="H234" t="n">
         <v>148165</v>
@@ -7242,7 +7242,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>10.2666416168213</v>
+        <v>10.266640663147</v>
       </c>
       <c r="H237" t="n">
         <v>250841</v>
@@ -7532,7 +7532,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G247" t="n">
-        <v>9.90707111358643</v>
+        <v>9.90707206726074</v>
       </c>
       <c r="H247" t="n">
         <v>223084</v>
@@ -7648,7 +7648,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G251" t="n">
-        <v>9.89760971069336</v>
+        <v>9.89760875701904</v>
       </c>
       <c r="H251" t="n">
         <v>221470</v>
@@ -7706,7 +7706,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G253" t="n">
-        <v>9.87868499755859</v>
+        <v>9.87868404388428</v>
       </c>
       <c r="H253" t="n">
         <v>178647</v>
@@ -7735,7 +7735,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G254" t="n">
-        <v>9.99223327636719</v>
+        <v>9.99223232269287</v>
       </c>
       <c r="H254" t="n">
         <v>244328</v>
@@ -7764,7 +7764,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G255" t="n">
-        <v>10.2950267791748</v>
+        <v>10.2950277328491</v>
       </c>
       <c r="H255" t="n">
         <v>668230</v>
@@ -7793,7 +7793,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G256" t="n">
-        <v>10.3896503448486</v>
+        <v>10.3896512985229</v>
       </c>
       <c r="H256" t="n">
         <v>552393</v>
@@ -7822,7 +7822,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G257" t="n">
-        <v>10.2666416168213</v>
+        <v>10.266640663147</v>
       </c>
       <c r="H257" t="n">
         <v>500317</v>
@@ -7851,7 +7851,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G258" t="n">
-        <v>10.2666416168213</v>
+        <v>10.266640663147</v>
       </c>
       <c r="H258" t="n">
         <v>138687</v>
@@ -7880,7 +7880,7 @@
         <v>10.8299999237061</v>
       </c>
       <c r="G259" t="n">
-        <v>10.2477159500122</v>
+        <v>10.2477149963379</v>
       </c>
       <c r="H259" t="n">
         <v>180911</v>
@@ -7938,7 +7938,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G261" t="n">
-        <v>10.1814804077148</v>
+        <v>10.1814794540405</v>
       </c>
       <c r="H261" t="n">
         <v>113192</v>
@@ -7996,7 +7996,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G263" t="n">
-        <v>10.1814804077148</v>
+        <v>10.1814794540405</v>
       </c>
       <c r="H263" t="n">
         <v>175964</v>
@@ -8112,7 +8112,7 @@
         <v>10.5900001525879</v>
       </c>
       <c r="G267" t="n">
-        <v>10.0206203460693</v>
+        <v>10.020619392395</v>
       </c>
       <c r="H267" t="n">
         <v>171371</v>
@@ -8141,7 +8141,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G268" t="n">
-        <v>10.0982236862183</v>
+        <v>10.0982227325439</v>
       </c>
       <c r="H268" t="n">
         <v>162147</v>
@@ -8344,7 +8344,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G275" t="n">
-        <v>10.3310356140137</v>
+        <v>10.3310346603394</v>
       </c>
       <c r="H275" t="n">
         <v>417991</v>
@@ -8576,7 +8576,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G283" t="n">
-        <v>10.6220512390137</v>
+        <v>10.6220502853394</v>
       </c>
       <c r="H283" t="n">
         <v>129742</v>
@@ -8634,7 +8634,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G285" t="n">
-        <v>10.5638475418091</v>
+        <v>10.5638484954834</v>
       </c>
       <c r="H285" t="n">
         <v>180726</v>
@@ -8692,7 +8692,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G287" t="n">
-        <v>10.2534303665161</v>
+        <v>10.2534313201904</v>
       </c>
       <c r="H287" t="n">
         <v>235286</v>
@@ -8721,7 +8721,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G288" t="n">
-        <v>10.311635017395</v>
+        <v>10.3116340637207</v>
       </c>
       <c r="H288" t="n">
         <v>127440</v>
@@ -8779,7 +8779,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G290" t="n">
-        <v>10.4377422332764</v>
+        <v>10.4377412796021</v>
       </c>
       <c r="H290" t="n">
         <v>97733</v>
@@ -8895,7 +8895,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G294" t="n">
-        <v>10.8063611984253</v>
+        <v>10.806360244751</v>
       </c>
       <c r="H294" t="n">
         <v>209159</v>
@@ -8982,7 +8982,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G297" t="n">
-        <v>10.9518671035767</v>
+        <v>10.951868057251</v>
       </c>
       <c r="H297" t="n">
         <v>175726</v>
@@ -9011,7 +9011,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G298" t="n">
-        <v>10.7578573226929</v>
+        <v>10.7578582763672</v>
       </c>
       <c r="H298" t="n">
         <v>301876</v>
@@ -9214,7 +9214,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G305" t="n">
-        <v>11.5824003219604</v>
+        <v>11.5823993682861</v>
       </c>
       <c r="H305" t="n">
         <v>274687</v>
@@ -9475,7 +9475,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G314" t="n">
-        <v>11.3398876190186</v>
+        <v>11.3398866653442</v>
       </c>
       <c r="H314" t="n">
         <v>110179</v>
@@ -9562,7 +9562,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G317" t="n">
-        <v>11.2525835037231</v>
+        <v>11.2525844573975</v>
       </c>
       <c r="H317" t="n">
         <v>381622</v>
@@ -9649,7 +9649,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G320" t="n">
-        <v>10.9518671035767</v>
+        <v>10.951868057251</v>
       </c>
       <c r="H320" t="n">
         <v>279934</v>
@@ -9707,7 +9707,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G322" t="n">
-        <v>10.9712686538696</v>
+        <v>10.9712696075439</v>
       </c>
       <c r="H322" t="n">
         <v>185383</v>
@@ -9765,7 +9765,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G324" t="n">
-        <v>10.7481565475464</v>
+        <v>10.7481575012207</v>
       </c>
       <c r="H324" t="n">
         <v>184196</v>
@@ -9852,7 +9852,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>10.7190561294556</v>
+        <v>10.7190551757812</v>
       </c>
       <c r="H327" t="n">
         <v>80274</v>
@@ -9881,7 +9881,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G328" t="n">
-        <v>10.7578573226929</v>
+        <v>10.7578582763672</v>
       </c>
       <c r="H328" t="n">
         <v>81593</v>
@@ -9910,7 +9910,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>10.8160610198975</v>
+        <v>10.8160600662231</v>
       </c>
       <c r="H329" t="n">
         <v>255497</v>
@@ -10055,7 +10055,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G334" t="n">
-        <v>11.136176109314</v>
+        <v>11.1361770629883</v>
       </c>
       <c r="H334" t="n">
         <v>92993</v>
@@ -10084,7 +10084,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G335" t="n">
-        <v>11.136176109314</v>
+        <v>11.1361770629883</v>
       </c>
       <c r="H335" t="n">
         <v>109603</v>
@@ -10258,7 +10258,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G341" t="n">
-        <v>11.4077920913696</v>
+        <v>11.4077911376953</v>
       </c>
       <c r="H341" t="n">
         <v>275168</v>
@@ -10374,7 +10374,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G345" t="n">
-        <v>10.9712686538696</v>
+        <v>10.9712696075439</v>
       </c>
       <c r="H345" t="n">
         <v>250890</v>
@@ -10403,7 +10403,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G346" t="n">
-        <v>10.9615678787231</v>
+        <v>10.9615688323975</v>
       </c>
       <c r="H346" t="n">
         <v>157159</v>
@@ -10432,7 +10432,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G347" t="n">
-        <v>11.0003709793091</v>
+        <v>11.0003700256348</v>
       </c>
       <c r="H347" t="n">
         <v>187467</v>
@@ -10461,7 +10461,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G348" t="n">
-        <v>11.0003709793091</v>
+        <v>11.0003700256348</v>
       </c>
       <c r="H348" t="n">
         <v>109481</v>
@@ -10722,7 +10722,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G357" t="n">
-        <v>11.058572769165</v>
+        <v>11.0585737228394</v>
       </c>
       <c r="H357" t="n">
         <v>184343</v>
@@ -10780,7 +10780,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G359" t="n">
-        <v>11.0003709793091</v>
+        <v>11.0003700256348</v>
       </c>
       <c r="H359" t="n">
         <v>186510</v>
@@ -10867,7 +10867,7 @@
         <v>11.25</v>
       </c>
       <c r="G362" t="n">
-        <v>10.9130659103394</v>
+        <v>10.913064956665</v>
       </c>
       <c r="H362" t="n">
         <v>440278</v>
@@ -10925,7 +10925,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G364" t="n">
-        <v>11.1458768844604</v>
+        <v>11.1458778381348</v>
       </c>
       <c r="H364" t="n">
         <v>188007</v>
@@ -11012,7 +11012,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>11.058572769165</v>
+        <v>11.0585737228394</v>
       </c>
       <c r="H367" t="n">
         <v>195723</v>
@@ -11070,7 +11070,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G369" t="n">
-        <v>11.1458768844604</v>
+        <v>11.1458778381348</v>
       </c>
       <c r="H369" t="n">
         <v>107932</v>
@@ -11128,7 +11128,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G371" t="n">
-        <v>11.136176109314</v>
+        <v>11.1361770629883</v>
       </c>
       <c r="H371" t="n">
         <v>118399</v>
@@ -11186,7 +11186,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G373" t="n">
-        <v>11.0197715759277</v>
+        <v>11.0197706222534</v>
       </c>
       <c r="H373" t="n">
         <v>147161</v>
@@ -11302,7 +11302,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G377" t="n">
-        <v>11.0197715759277</v>
+        <v>11.0197706222534</v>
       </c>
       <c r="H377" t="n">
         <v>130368</v>
@@ -11476,7 +11476,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G383" t="n">
-        <v>11.136176109314</v>
+        <v>11.1361770629883</v>
       </c>
       <c r="H383" t="n">
         <v>194313</v>
@@ -11592,7 +11592,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G387" t="n">
-        <v>11.1749801635742</v>
+        <v>11.1749792098999</v>
       </c>
       <c r="H387" t="n">
         <v>197901</v>
@@ -11650,7 +11650,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G389" t="n">
-        <v>11.4465932846069</v>
+        <v>11.4465942382812</v>
       </c>
       <c r="H389" t="n">
         <v>259214</v>
@@ -11737,7 +11737,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G392" t="n">
-        <v>11.8540143966675</v>
+        <v>11.8540153503418</v>
       </c>
       <c r="H392" t="n">
         <v>194096</v>
@@ -11795,7 +11795,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G394" t="n">
-        <v>11.6988077163696</v>
+        <v>11.6988067626953</v>
       </c>
       <c r="H394" t="n">
         <v>171327</v>
@@ -11911,7 +11911,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G398" t="n">
-        <v>11.6309022903442</v>
+        <v>11.6309032440186</v>
       </c>
       <c r="H398" t="n">
         <v>192088</v>
@@ -11940,7 +11940,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G399" t="n">
-        <v>11.5824003219604</v>
+        <v>11.5823993682861</v>
       </c>
       <c r="H399" t="n">
         <v>137161</v>
@@ -12056,7 +12056,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G403" t="n">
-        <v>12.193531036377</v>
+        <v>12.1935319900513</v>
       </c>
       <c r="H403" t="n">
         <v>108069</v>
@@ -12114,7 +12114,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G405" t="n">
-        <v>12.193531036377</v>
+        <v>12.1935319900513</v>
       </c>
       <c r="H405" t="n">
         <v>135114</v>
@@ -12172,7 +12172,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G407" t="n">
-        <v>12.2226343154907</v>
+        <v>12.2226333618164</v>
       </c>
       <c r="H407" t="n">
         <v>185001</v>
@@ -12201,7 +12201,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G408" t="n">
-        <v>12.2517356872559</v>
+        <v>12.2517347335815</v>
       </c>
       <c r="H408" t="n">
         <v>172512</v>
@@ -12288,7 +12288,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G411" t="n">
-        <v>12.4651470184326</v>
+        <v>12.4651460647583</v>
       </c>
       <c r="H411" t="n">
         <v>133030</v>
@@ -12317,7 +12317,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G412" t="n">
-        <v>12.3875417709351</v>
+        <v>12.3875427246094</v>
       </c>
       <c r="H412" t="n">
         <v>148541</v>
@@ -12520,7 +12520,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G419" t="n">
-        <v>12.2517356872559</v>
+        <v>12.2517347335815</v>
       </c>
       <c r="H419" t="n">
         <v>165954</v>
@@ -12549,7 +12549,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G420" t="n">
-        <v>12.2226343154907</v>
+        <v>12.2226333618164</v>
       </c>
       <c r="H420" t="n">
         <v>258706</v>
@@ -12607,7 +12607,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G422" t="n">
-        <v>12.2129325866699</v>
+        <v>12.2129335403442</v>
       </c>
       <c r="H422" t="n">
         <v>137376</v>
@@ -12636,7 +12636,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G423" t="n">
-        <v>12.3875417709351</v>
+        <v>12.3875427246094</v>
       </c>
       <c r="H423" t="n">
         <v>99466</v>
@@ -12723,7 +12723,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G426" t="n">
-        <v>12.5427503585815</v>
+        <v>12.5427513122559</v>
       </c>
       <c r="H426" t="n">
         <v>197307</v>
@@ -12752,7 +12752,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G427" t="n">
-        <v>12.6300554275513</v>
+        <v>12.630054473877</v>
       </c>
       <c r="H427" t="n">
         <v>148262</v>
@@ -12839,7 +12839,7 @@
         <v>13</v>
       </c>
       <c r="G430" t="n">
-        <v>12.6106538772583</v>
+        <v>12.610652923584</v>
       </c>
       <c r="H430" t="n">
         <v>1807764</v>
@@ -12897,7 +12897,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G432" t="n">
-        <v>12.3972415924072</v>
+        <v>12.3972425460815</v>
       </c>
       <c r="H432" t="n">
         <v>1234024</v>
@@ -12955,7 +12955,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G434" t="n">
-        <v>12.6882572174072</v>
+        <v>12.6882581710815</v>
       </c>
       <c r="H434" t="n">
         <v>465320</v>
@@ -13013,7 +13013,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G436" t="n">
-        <v>13.1538829803467</v>
+        <v>13.1538820266724</v>
       </c>
       <c r="H436" t="n">
         <v>425963</v>
@@ -13274,7 +13274,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G445" t="n">
-        <v>13.7844142913818</v>
+        <v>13.7844152450562</v>
       </c>
       <c r="H445" t="n">
         <v>236771</v>
@@ -13303,7 +13303,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G446" t="n">
-        <v>14.3373422622681</v>
+        <v>14.3373432159424</v>
       </c>
       <c r="H446" t="n">
         <v>473165</v>
@@ -13332,7 +13332,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G447" t="n">
-        <v>14.4537487030029</v>
+        <v>14.4537496566772</v>
       </c>
       <c r="H447" t="n">
         <v>380386</v>
@@ -13361,7 +13361,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G448" t="n">
-        <v>14.6671600341797</v>
+        <v>14.667160987854</v>
       </c>
       <c r="H448" t="n">
         <v>267462</v>
@@ -13419,7 +13419,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G450" t="n">
-        <v>14.8029680252075</v>
+        <v>14.8029670715332</v>
       </c>
       <c r="H450" t="n">
         <v>391347</v>
@@ -13622,7 +13622,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G457" t="n">
-        <v>16.0446319580078</v>
+        <v>16.0446338653564</v>
       </c>
       <c r="H457" t="n">
         <v>378598</v>
@@ -13680,7 +13680,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G459" t="n">
-        <v>15.9573278427124</v>
+        <v>15.9573268890381</v>
       </c>
       <c r="H459" t="n">
         <v>261224</v>
@@ -13796,7 +13796,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G463" t="n">
-        <v>16.0252323150635</v>
+        <v>16.0252304077148</v>
       </c>
       <c r="H463" t="n">
         <v>392686</v>
@@ -13825,7 +13825,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G464" t="n">
-        <v>15.6857137680054</v>
+        <v>15.6857128143311</v>
       </c>
       <c r="H464" t="n">
         <v>532461</v>
@@ -14028,7 +14028,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G471" t="n">
-        <v>15.8700227737427</v>
+        <v>15.870023727417</v>
       </c>
       <c r="H471" t="n">
         <v>880362</v>
@@ -14115,7 +14115,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G474" t="n">
-        <v>16.9273777008057</v>
+        <v>16.9273796081543</v>
       </c>
       <c r="H474" t="n">
         <v>620043</v>
@@ -14260,7 +14260,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G479" t="n">
-        <v>17.5870113372803</v>
+        <v>17.5870094299316</v>
       </c>
       <c r="H479" t="n">
         <v>473621</v>
@@ -14289,7 +14289,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G480" t="n">
-        <v>17.5870113372803</v>
+        <v>17.5870094299316</v>
       </c>
       <c r="H480" t="n">
         <v>417252</v>
@@ -14347,7 +14347,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G482" t="n">
-        <v>17.1601905822754</v>
+        <v>17.1601886749268</v>
       </c>
       <c r="H482" t="n">
         <v>353508</v>
@@ -14405,7 +14405,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G484" t="n">
-        <v>17.7519207000732</v>
+        <v>17.7519187927246</v>
       </c>
       <c r="H484" t="n">
         <v>342388</v>
@@ -14434,7 +14434,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G485" t="n">
-        <v>17.7422199249268</v>
+        <v>17.7422218322754</v>
       </c>
       <c r="H485" t="n">
         <v>271126</v>
@@ -14521,7 +14521,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G488" t="n">
-        <v>17.9071273803711</v>
+        <v>17.9071292877197</v>
       </c>
       <c r="H488" t="n">
         <v>372109</v>
@@ -14550,7 +14550,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G489" t="n">
-        <v>18.3727512359619</v>
+        <v>18.3727531433105</v>
       </c>
       <c r="H489" t="n">
         <v>455016</v>
@@ -14608,7 +14608,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>16.8303737640381</v>
+        <v>16.8303718566895</v>
       </c>
       <c r="H491" t="n">
         <v>1164243</v>
@@ -14695,7 +14695,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G494" t="n">
-        <v>17.1601905822754</v>
+        <v>17.1601886749268</v>
       </c>
       <c r="H494" t="n">
         <v>564420</v>
@@ -14898,7 +14898,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G501" t="n">
-        <v>18.8480758666992</v>
+        <v>18.8480777740479</v>
       </c>
       <c r="H501" t="n">
         <v>377971</v>
@@ -14927,7 +14927,7 @@
         <v>19.4699993133545</v>
       </c>
       <c r="G502" t="n">
-        <v>18.8868770599365</v>
+        <v>18.8868789672852</v>
       </c>
       <c r="H502" t="n">
         <v>436832</v>
@@ -14956,7 +14956,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G503" t="n">
-        <v>19.0226879119873</v>
+        <v>19.0226860046387</v>
       </c>
       <c r="H503" t="n">
         <v>218294</v>
@@ -15014,7 +15014,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G505" t="n">
-        <v>19.4786109924316</v>
+        <v>19.478609085083</v>
       </c>
       <c r="H505" t="n">
         <v>375456</v>
@@ -15043,7 +15043,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G506" t="n">
-        <v>19.4592094421387</v>
+        <v>19.45920753479</v>
       </c>
       <c r="H506" t="n">
         <v>430857</v>
@@ -15072,7 +15072,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G507" t="n">
-        <v>19.4398078918457</v>
+        <v>19.4398097991943</v>
       </c>
       <c r="H507" t="n">
         <v>573705</v>
@@ -15130,7 +15130,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G509" t="n">
-        <v>20.3128528594971</v>
+        <v>20.3128547668457</v>
       </c>
       <c r="H509" t="n">
         <v>845381</v>
@@ -15159,7 +15159,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G510" t="n">
-        <v>20.2352504730225</v>
+        <v>20.2352485656738</v>
       </c>
       <c r="H510" t="n">
         <v>628106</v>
@@ -15188,7 +15188,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G511" t="n">
-        <v>19.9248332977295</v>
+        <v>19.9248352050781</v>
       </c>
       <c r="H511" t="n">
         <v>774008</v>
@@ -15217,7 +15217,7 @@
         <v>20</v>
       </c>
       <c r="G512" t="n">
-        <v>19.4010047912598</v>
+        <v>19.4010066986084</v>
       </c>
       <c r="H512" t="n">
         <v>769373</v>
@@ -15304,7 +15304,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>21.6321220397949</v>
+        <v>21.6321201324463</v>
       </c>
       <c r="H515" t="n">
         <v>2197577</v>
@@ -15362,7 +15362,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G517" t="n">
-        <v>22.1171455383301</v>
+        <v>22.1171474456787</v>
       </c>
       <c r="H517" t="n">
         <v>555528</v>
@@ -15391,7 +15391,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G518" t="n">
-        <v>21.9619388580322</v>
+        <v>21.9619369506836</v>
       </c>
       <c r="H518" t="n">
         <v>611058</v>
@@ -26098,6 +26098,35 @@
         <v>780061</v>
       </c>
       <c r="I887" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="s">
+        <v>9</v>
+      </c>
+      <c r="B888" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C888" t="n">
+        <v>25.4300003051758</v>
+      </c>
+      <c r="D888" t="n">
+        <v>25.6100006103516</v>
+      </c>
+      <c r="E888" t="n">
+        <v>25.2399997711182</v>
+      </c>
+      <c r="F888" t="n">
+        <v>25.5599994659424</v>
+      </c>
+      <c r="G888" t="n">
+        <v>25.5599994659424</v>
+      </c>
+      <c r="H888" t="n">
+        <v>570269</v>
+      </c>
+      <c r="I888" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LTMC.MI.xlsx
+++ b/data/LTMC.MI.xlsx
@@ -427,7 +427,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2" t="n">
-        <v>7.75911951065063</v>
+        <v>7.75911998748779</v>
       </c>
       <c r="H2" t="n">
         <v>13006120</v>
@@ -485,7 +485,7 @@
         <v>8.44600009918213</v>
       </c>
       <c r="G4" t="n">
-        <v>7.99189376831055</v>
+        <v>7.99189424514771</v>
       </c>
       <c r="H4" t="n">
         <v>1476712</v>
@@ -543,7 +543,7 @@
         <v>8.59099960327148</v>
       </c>
       <c r="G6" t="n">
-        <v>8.1290979385376</v>
+        <v>8.12909698486328</v>
       </c>
       <c r="H6" t="n">
         <v>974676</v>
@@ -572,7 +572,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G7" t="n">
-        <v>7.92944288253784</v>
+        <v>7.92944240570068</v>
       </c>
       <c r="H7" t="n">
         <v>640304</v>
@@ -601,7 +601,7 @@
         <v>7.98600006103516</v>
       </c>
       <c r="G8" t="n">
-        <v>7.5566258430481</v>
+        <v>7.55662631988525</v>
       </c>
       <c r="H8" t="n">
         <v>1283605</v>
@@ -630,7 +630,7 @@
         <v>8.25</v>
       </c>
       <c r="G9" t="n">
-        <v>7.80643177032471</v>
+        <v>7.80643129348755</v>
       </c>
       <c r="H9" t="n">
         <v>1073912</v>
@@ -659,7 +659,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G10" t="n">
-        <v>7.99567842483521</v>
+        <v>7.99567890167236</v>
       </c>
       <c r="H10" t="n">
         <v>1947465</v>
@@ -775,7 +775,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G14" t="n">
-        <v>7.52256155014038</v>
+        <v>7.52256107330322</v>
       </c>
       <c r="H14" t="n">
         <v>981832</v>
@@ -949,7 +949,7 @@
         <v>7.80100011825562</v>
       </c>
       <c r="G20" t="n">
-        <v>7.38157272338867</v>
+        <v>7.38157224655151</v>
       </c>
       <c r="H20" t="n">
         <v>40924</v>
@@ -978,7 +978,7 @@
         <v>7.71199989318848</v>
       </c>
       <c r="G21" t="n">
-        <v>7.2973575592041</v>
+        <v>7.29735803604126</v>
       </c>
       <c r="H21" t="n">
         <v>118298</v>
@@ -1036,7 +1036,7 @@
         <v>7.50699996948242</v>
       </c>
       <c r="G23" t="n">
-        <v>7.10337972640991</v>
+        <v>7.10338020324707</v>
       </c>
       <c r="H23" t="n">
         <v>387333</v>
@@ -1123,7 +1123,7 @@
         <v>7.86800003051758</v>
       </c>
       <c r="G26" t="n">
-        <v>7.44497060775757</v>
+        <v>7.44497013092041</v>
       </c>
       <c r="H26" t="n">
         <v>235788</v>
@@ -1181,7 +1181,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G28" t="n">
-        <v>7.76858282089233</v>
+        <v>7.76858234405518</v>
       </c>
       <c r="H28" t="n">
         <v>1704311</v>
@@ -1268,7 +1268,7 @@
         <v>8.23200035095215</v>
       </c>
       <c r="G31" t="n">
-        <v>7.78940010070801</v>
+        <v>7.78939962387085</v>
       </c>
       <c r="H31" t="n">
         <v>749433</v>
@@ -1297,7 +1297,7 @@
         <v>8.16199970245361</v>
       </c>
       <c r="G32" t="n">
-        <v>7.72316265106201</v>
+        <v>7.72316312789917</v>
       </c>
       <c r="H32" t="n">
         <v>440552</v>
@@ -1326,7 +1326,7 @@
         <v>8.21399974822998</v>
       </c>
       <c r="G33" t="n">
-        <v>7.77236747741699</v>
+        <v>7.77236652374268</v>
       </c>
       <c r="H33" t="n">
         <v>327710</v>
@@ -1355,7 +1355,7 @@
         <v>8.41300010681152</v>
       </c>
       <c r="G34" t="n">
-        <v>7.9606671333313</v>
+        <v>7.96066761016846</v>
       </c>
       <c r="H34" t="n">
         <v>540974</v>
@@ -1384,7 +1384,7 @@
         <v>8.24600028991699</v>
       </c>
       <c r="G35" t="n">
-        <v>7.80264759063721</v>
+        <v>7.80264663696289</v>
       </c>
       <c r="H35" t="n">
         <v>379647</v>
@@ -1413,7 +1413,7 @@
         <v>8.25500011444092</v>
       </c>
       <c r="G36" t="n">
-        <v>7.8111629486084</v>
+        <v>7.81116342544556</v>
       </c>
       <c r="H36" t="n">
         <v>219714</v>
@@ -1442,7 +1442,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G37" t="n">
-        <v>7.92944288253784</v>
+        <v>7.92944240570068</v>
       </c>
       <c r="H37" t="n">
         <v>223839</v>
@@ -1471,7 +1471,7 @@
         <v>8.4379997253418</v>
       </c>
       <c r="G38" t="n">
-        <v>7.98432397842407</v>
+        <v>7.98432350158691</v>
       </c>
       <c r="H38" t="n">
         <v>178091</v>
@@ -1500,7 +1500,7 @@
         <v>8.43299961090088</v>
       </c>
       <c r="G39" t="n">
-        <v>7.97959136962891</v>
+        <v>7.97959184646606</v>
       </c>
       <c r="H39" t="n">
         <v>99001</v>
@@ -1529,7 +1529,7 @@
         <v>8.43599987030029</v>
       </c>
       <c r="G40" t="n">
-        <v>7.98243045806885</v>
+        <v>7.98243093490601</v>
       </c>
       <c r="H40" t="n">
         <v>155784</v>
@@ -1558,7 +1558,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G41" t="n">
-        <v>7.92944288253784</v>
+        <v>7.92944240570068</v>
       </c>
       <c r="H41" t="n">
         <v>133019</v>
@@ -1587,7 +1587,7 @@
         <v>8.41300010681152</v>
       </c>
       <c r="G42" t="n">
-        <v>7.9606671333313</v>
+        <v>7.96066761016846</v>
       </c>
       <c r="H42" t="n">
         <v>122155</v>
@@ -1645,7 +1645,7 @@
         <v>8.71599960327148</v>
       </c>
       <c r="G44" t="n">
-        <v>8.24737548828125</v>
+        <v>8.24737644195557</v>
       </c>
       <c r="H44" t="n">
         <v>146543</v>
@@ -1790,7 +1790,7 @@
         <v>8.78800010681152</v>
       </c>
       <c r="G49" t="n">
-        <v>8.31550598144531</v>
+        <v>8.315505027771</v>
       </c>
       <c r="H49" t="n">
         <v>417701</v>
@@ -1819,7 +1819,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G50" t="n">
-        <v>8.49718284606934</v>
+        <v>8.49718189239502</v>
       </c>
       <c r="H50" t="n">
         <v>475388</v>
@@ -1877,7 +1877,7 @@
         <v>9.28999996185303</v>
       </c>
       <c r="G52" t="n">
-        <v>8.79051494598389</v>
+        <v>8.7905158996582</v>
       </c>
       <c r="H52" t="n">
         <v>1027347</v>
@@ -1906,7 +1906,7 @@
         <v>9.4689998626709</v>
       </c>
       <c r="G53" t="n">
-        <v>8.95989036560059</v>
+        <v>8.9598913192749</v>
       </c>
       <c r="H53" t="n">
         <v>1003139</v>
@@ -1993,7 +1993,7 @@
         <v>9.39500045776367</v>
       </c>
       <c r="G56" t="n">
-        <v>8.88987064361572</v>
+        <v>8.88987159729004</v>
       </c>
       <c r="H56" t="n">
         <v>278706</v>
@@ -2051,7 +2051,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G58" t="n">
-        <v>8.8472900390625</v>
+        <v>8.84728908538818</v>
       </c>
       <c r="H58" t="n">
         <v>404952</v>
@@ -2080,7 +2080,7 @@
         <v>9.27099990844727</v>
       </c>
       <c r="G59" t="n">
-        <v>8.77253723144531</v>
+        <v>8.772536277771</v>
       </c>
       <c r="H59" t="n">
         <v>287274</v>
@@ -2254,7 +2254,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G65" t="n">
-        <v>8.94191360473633</v>
+        <v>8.94191265106201</v>
       </c>
       <c r="H65" t="n">
         <v>900757</v>
@@ -2341,7 +2341,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G68" t="n">
-        <v>8.8472900390625</v>
+        <v>8.84728908538818</v>
       </c>
       <c r="H68" t="n">
         <v>269589</v>
@@ -2399,7 +2399,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G70" t="n">
-        <v>8.87567615509033</v>
+        <v>8.87567710876465</v>
       </c>
       <c r="H70" t="n">
         <v>257403</v>
@@ -2457,7 +2457,7 @@
         <v>9.31900024414062</v>
       </c>
       <c r="G72" t="n">
-        <v>8.81795597076416</v>
+        <v>8.81795692443848</v>
       </c>
       <c r="H72" t="n">
         <v>303822</v>
@@ -2602,7 +2602,7 @@
         <v>9.12600040435791</v>
       </c>
       <c r="G77" t="n">
-        <v>8.63533401489258</v>
+        <v>8.63533306121826</v>
       </c>
       <c r="H77" t="n">
         <v>248031</v>
@@ -2660,7 +2660,7 @@
         <v>9.10799980163574</v>
       </c>
       <c r="G79" t="n">
-        <v>8.61829948425293</v>
+        <v>8.61830043792725</v>
       </c>
       <c r="H79" t="n">
         <v>127272</v>
@@ -2689,7 +2689,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G80" t="n">
-        <v>8.67696666717529</v>
+        <v>8.67696762084961</v>
       </c>
       <c r="H80" t="n">
         <v>180085</v>
@@ -2776,7 +2776,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G83" t="n">
-        <v>8.91352558135986</v>
+        <v>8.91352653503418</v>
       </c>
       <c r="H83" t="n">
         <v>325430</v>
@@ -2834,7 +2834,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G85" t="n">
-        <v>8.91352558135986</v>
+        <v>8.91352653503418</v>
       </c>
       <c r="H85" t="n">
         <v>265573</v>
@@ -2863,7 +2863,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G86" t="n">
-        <v>8.83782768249512</v>
+        <v>8.8378267288208</v>
       </c>
       <c r="H86" t="n">
         <v>322079</v>
@@ -2921,7 +2921,7 @@
         <v>9.10799980163574</v>
       </c>
       <c r="G88" t="n">
-        <v>8.61829948425293</v>
+        <v>8.61830043792725</v>
       </c>
       <c r="H88" t="n">
         <v>496089</v>
@@ -2979,7 +2979,7 @@
         <v>9.17899990081787</v>
       </c>
       <c r="G90" t="n">
-        <v>8.68548202514648</v>
+        <v>8.6854829788208</v>
       </c>
       <c r="H90" t="n">
         <v>216140</v>
@@ -3095,7 +3095,7 @@
         <v>9.02299976348877</v>
       </c>
       <c r="G94" t="n">
-        <v>8.53787040710449</v>
+        <v>8.53786945343018</v>
       </c>
       <c r="H94" t="n">
         <v>577462</v>
@@ -3124,7 +3124,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G95" t="n">
-        <v>8.53503227233887</v>
+        <v>8.53503322601318</v>
       </c>
       <c r="H95" t="n">
         <v>212825</v>
@@ -3182,7 +3182,7 @@
         <v>9.17000007629395</v>
       </c>
       <c r="G97" t="n">
-        <v>8.67696666717529</v>
+        <v>8.67696762084961</v>
       </c>
       <c r="H97" t="n">
         <v>420414</v>
@@ -3269,7 +3269,7 @@
         <v>8.9069995880127</v>
       </c>
       <c r="G100" t="n">
-        <v>8.42810726165771</v>
+        <v>8.42810821533203</v>
       </c>
       <c r="H100" t="n">
         <v>428743</v>
@@ -3327,7 +3327,7 @@
         <v>8.89700031280518</v>
       </c>
       <c r="G102" t="n">
-        <v>8.41864585876465</v>
+        <v>8.41864490509033</v>
       </c>
       <c r="H102" t="n">
         <v>170277</v>
@@ -3414,7 +3414,7 @@
         <v>8.53899955749512</v>
       </c>
       <c r="G105" t="n">
-        <v>8.07989311218262</v>
+        <v>8.0798921585083</v>
       </c>
       <c r="H105" t="n">
         <v>153907</v>
@@ -3530,7 +3530,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G109" t="n">
-        <v>8.27008724212646</v>
+        <v>8.27008628845215</v>
       </c>
       <c r="H109" t="n">
         <v>186396</v>
@@ -3559,7 +3559,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G110" t="n">
-        <v>8.37417316436768</v>
+        <v>8.37417221069336</v>
       </c>
       <c r="H110" t="n">
         <v>209809</v>
@@ -3617,7 +3617,7 @@
         <v>8.56900024414062</v>
       </c>
       <c r="G112" t="n">
-        <v>8.10828018188477</v>
+        <v>8.10828113555908</v>
       </c>
       <c r="H112" t="n">
         <v>111567</v>
@@ -3675,7 +3675,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G114" t="n">
-        <v>8.13761425018311</v>
+        <v>8.13761329650879</v>
       </c>
       <c r="H114" t="n">
         <v>108045</v>
@@ -3733,7 +3733,7 @@
         <v>8.75500011444092</v>
       </c>
       <c r="G116" t="n">
-        <v>8.28427982330322</v>
+        <v>8.28428077697754</v>
       </c>
       <c r="H116" t="n">
         <v>68870</v>
@@ -3820,7 +3820,7 @@
         <v>8.7209997177124</v>
       </c>
       <c r="G119" t="n">
-        <v>8.25210762023926</v>
+        <v>8.25210857391357</v>
       </c>
       <c r="H119" t="n">
         <v>127697</v>
@@ -3849,7 +3849,7 @@
         <v>8.75</v>
       </c>
       <c r="G120" t="n">
-        <v>8.27954864501953</v>
+        <v>8.27954769134521</v>
       </c>
       <c r="H120" t="n">
         <v>97384</v>
@@ -3878,7 +3878,7 @@
         <v>8.82600021362305</v>
       </c>
       <c r="G121" t="n">
-        <v>8.35146331787109</v>
+        <v>8.35146236419678</v>
       </c>
       <c r="H121" t="n">
         <v>222699</v>
@@ -4052,7 +4052,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G127" t="n">
-        <v>8.37417316436768</v>
+        <v>8.37417221069336</v>
       </c>
       <c r="H127" t="n">
         <v>102561</v>
@@ -4081,7 +4081,7 @@
         <v>8.82100009918213</v>
       </c>
       <c r="G128" t="n">
-        <v>8.34673118591309</v>
+        <v>8.3467321395874</v>
       </c>
       <c r="H128" t="n">
         <v>174329</v>
@@ -4110,7 +4110,7 @@
         <v>8.93000030517578</v>
       </c>
       <c r="G129" t="n">
-        <v>8.44987106323242</v>
+        <v>8.44987201690674</v>
       </c>
       <c r="H129" t="n">
         <v>141108</v>
@@ -4168,7 +4168,7 @@
         <v>9.03800010681152</v>
       </c>
       <c r="G131" t="n">
-        <v>8.55206489562988</v>
+        <v>8.55206394195557</v>
       </c>
       <c r="H131" t="n">
         <v>165794</v>
@@ -4255,7 +4255,7 @@
         <v>9.05300045013428</v>
       </c>
       <c r="G134" t="n">
-        <v>8.56625747680664</v>
+        <v>8.56625843048096</v>
       </c>
       <c r="H134" t="n">
         <v>123966</v>
@@ -4284,7 +4284,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G135" t="n">
-        <v>8.61262321472168</v>
+        <v>8.612624168396</v>
       </c>
       <c r="H135" t="n">
         <v>75451</v>
@@ -4313,7 +4313,7 @@
         <v>9.02000045776367</v>
       </c>
       <c r="G136" t="n">
-        <v>8.53503227233887</v>
+        <v>8.53503322601318</v>
       </c>
       <c r="H136" t="n">
         <v>172542</v>
@@ -4342,7 +4342,7 @@
         <v>9.10200023651123</v>
       </c>
       <c r="G137" t="n">
-        <v>8.61262321472168</v>
+        <v>8.612624168396</v>
       </c>
       <c r="H137" t="n">
         <v>197102</v>
@@ -4371,7 +4371,7 @@
         <v>9.02799987792969</v>
       </c>
       <c r="G138" t="n">
-        <v>8.54260158538818</v>
+        <v>8.5426025390625</v>
       </c>
       <c r="H138" t="n">
         <v>270693</v>
@@ -4458,7 +4458,7 @@
         <v>9.07999992370605</v>
       </c>
       <c r="G141" t="n">
-        <v>8.59180545806885</v>
+        <v>8.59180641174316</v>
       </c>
       <c r="H141" t="n">
         <v>114910</v>
@@ -4487,7 +4487,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G142" t="n">
-        <v>8.62965488433838</v>
+        <v>8.6296558380127</v>
       </c>
       <c r="H142" t="n">
         <v>176941</v>
@@ -4545,7 +4545,7 @@
         <v>9.39299964904785</v>
       </c>
       <c r="G144" t="n">
-        <v>8.88797664642334</v>
+        <v>8.88797760009766</v>
       </c>
       <c r="H144" t="n">
         <v>219022</v>
@@ -4632,7 +4632,7 @@
         <v>9.26200008392334</v>
       </c>
       <c r="G147" t="n">
-        <v>8.7640209197998</v>
+        <v>8.76401996612549</v>
       </c>
       <c r="H147" t="n">
         <v>55579</v>
@@ -4661,7 +4661,7 @@
         <v>9.36699962615967</v>
       </c>
       <c r="G148" t="n">
-        <v>8.86337375640869</v>
+        <v>8.86337471008301</v>
       </c>
       <c r="H148" t="n">
         <v>76421</v>
@@ -4690,7 +4690,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G149" t="n">
-        <v>8.8472900390625</v>
+        <v>8.84728908538818</v>
       </c>
       <c r="H149" t="n">
         <v>91350</v>
@@ -4835,7 +4835,7 @@
         <v>9.47000026702881</v>
       </c>
       <c r="G154" t="n">
-        <v>8.96083736419678</v>
+        <v>8.96083831787109</v>
       </c>
       <c r="H154" t="n">
         <v>127739</v>
@@ -4893,7 +4893,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G156" t="n">
-        <v>9.00814914703369</v>
+        <v>9.00815010070801</v>
       </c>
       <c r="H156" t="n">
         <v>146799</v>
@@ -4922,7 +4922,7 @@
         <v>9.60900020599365</v>
       </c>
       <c r="G157" t="n">
-        <v>9.09236431121826</v>
+        <v>9.09236335754395</v>
       </c>
       <c r="H157" t="n">
         <v>302816</v>
@@ -4980,7 +4980,7 @@
         <v>9.51799964904785</v>
       </c>
       <c r="G159" t="n">
-        <v>9.00625705718994</v>
+        <v>9.00625610351562</v>
       </c>
       <c r="H159" t="n">
         <v>122948</v>
@@ -5009,7 +5009,7 @@
         <v>9.58500003814697</v>
       </c>
       <c r="G160" t="n">
-        <v>9.06965446472168</v>
+        <v>9.06965351104736</v>
       </c>
       <c r="H160" t="n">
         <v>66904</v>
@@ -5038,7 +5038,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G161" t="n">
-        <v>8.94191360473633</v>
+        <v>8.94191265106201</v>
       </c>
       <c r="H161" t="n">
         <v>242695</v>
@@ -5067,7 +5067,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G162" t="n">
-        <v>9.11223411560059</v>
+        <v>9.1122350692749</v>
       </c>
       <c r="H162" t="n">
         <v>177419</v>
@@ -5125,7 +5125,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G164" t="n">
-        <v>9.27309513092041</v>
+        <v>9.27309417724609</v>
       </c>
       <c r="H164" t="n">
         <v>159322</v>
@@ -5154,7 +5154,7 @@
         <v>9.80599975585938</v>
       </c>
       <c r="G165" t="n">
-        <v>9.27877140045166</v>
+        <v>9.27877235412598</v>
       </c>
       <c r="H165" t="n">
         <v>183228</v>
@@ -5270,7 +5270,7 @@
         <v>9.84700012207031</v>
       </c>
       <c r="G169" t="n">
-        <v>9.31756782531738</v>
+        <v>9.31756687164307</v>
       </c>
       <c r="H169" t="n">
         <v>94635</v>
@@ -5299,7 +5299,7 @@
         <v>9.7819995880127</v>
       </c>
       <c r="G170" t="n">
-        <v>9.25606155395508</v>
+        <v>9.25606250762939</v>
       </c>
       <c r="H170" t="n">
         <v>59025</v>
@@ -5328,7 +5328,7 @@
         <v>9.78999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>9.26363182067871</v>
+        <v>9.26363277435303</v>
       </c>
       <c r="H171" t="n">
         <v>112232</v>
@@ -5386,7 +5386,7 @@
         <v>9.57100009918213</v>
       </c>
       <c r="G173" t="n">
-        <v>9.05640602111816</v>
+        <v>9.05640697479248</v>
       </c>
       <c r="H173" t="n">
         <v>138205</v>
@@ -5415,7 +5415,7 @@
         <v>9.6230001449585</v>
       </c>
       <c r="G174" t="n">
-        <v>9.10561180114746</v>
+        <v>9.10561084747314</v>
       </c>
       <c r="H174" t="n">
         <v>254745</v>
@@ -5560,7 +5560,7 @@
         <v>9.63000011444092</v>
       </c>
       <c r="G179" t="n">
-        <v>9.11223411560059</v>
+        <v>9.1122350692749</v>
       </c>
       <c r="H179" t="n">
         <v>138026</v>
@@ -5908,7 +5908,7 @@
         <v>10.6820001602173</v>
       </c>
       <c r="G191" t="n">
-        <v>10.1076736450195</v>
+        <v>10.1076726913452</v>
       </c>
       <c r="H191" t="n">
         <v>152759</v>
@@ -5937,7 +5937,7 @@
         <v>10.7720003128052</v>
       </c>
       <c r="G192" t="n">
-        <v>10.192834854126</v>
+        <v>10.1928339004517</v>
       </c>
       <c r="H192" t="n">
         <v>183949</v>
@@ -5995,7 +5995,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G194" t="n">
-        <v>10.1909427642822</v>
+        <v>10.1909418106079</v>
       </c>
       <c r="H194" t="n">
         <v>199527</v>
@@ -6024,7 +6024,7 @@
         <v>10.7740001678467</v>
       </c>
       <c r="G195" t="n">
-        <v>10.1947269439697</v>
+        <v>10.1947259902954</v>
       </c>
       <c r="H195" t="n">
         <v>175955</v>
@@ -6111,7 +6111,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G198" t="n">
-        <v>10.4842739105225</v>
+        <v>10.4842748641968</v>
       </c>
       <c r="H198" t="n">
         <v>255451</v>
@@ -6140,7 +6140,7 @@
         <v>11.1260004043579</v>
       </c>
       <c r="G199" t="n">
-        <v>10.5278015136719</v>
+        <v>10.5278024673462</v>
       </c>
       <c r="H199" t="n">
         <v>264065</v>
@@ -6198,7 +6198,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G201" t="n">
-        <v>10.5788974761963</v>
+        <v>10.5788984298706</v>
       </c>
       <c r="H201" t="n">
         <v>211395</v>
@@ -6256,7 +6256,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G203" t="n">
-        <v>10.5978221893311</v>
+        <v>10.5978231430054</v>
       </c>
       <c r="H203" t="n">
         <v>128498</v>
@@ -6314,7 +6314,7 @@
         <v>11.3420000076294</v>
       </c>
       <c r="G205" t="n">
-        <v>10.7321872711182</v>
+        <v>10.7321882247925</v>
       </c>
       <c r="H205" t="n">
         <v>152325</v>
@@ -6401,7 +6401,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G208" t="n">
-        <v>10.9763174057007</v>
+        <v>10.9763164520264</v>
       </c>
       <c r="H208" t="n">
         <v>197138</v>
@@ -6430,7 +6430,7 @@
         <v>11.5579996109009</v>
       </c>
       <c r="G209" t="n">
-        <v>10.9365739822388</v>
+        <v>10.9365730285645</v>
       </c>
       <c r="H209" t="n">
         <v>170731</v>
@@ -6459,7 +6459,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G210" t="n">
-        <v>10.9195413589478</v>
+        <v>10.9195423126221</v>
       </c>
       <c r="H210" t="n">
         <v>166746</v>
@@ -6546,7 +6546,7 @@
         <v>11.5019998550415</v>
       </c>
       <c r="G213" t="n">
-        <v>10.8835859298706</v>
+        <v>10.8835849761963</v>
       </c>
       <c r="H213" t="n">
         <v>216641</v>
@@ -6662,7 +6662,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G217" t="n">
-        <v>10.4369621276855</v>
+        <v>10.4369630813599</v>
       </c>
       <c r="H217" t="n">
         <v>269996</v>
@@ -6691,7 +6691,7 @@
         <v>10.8739995956421</v>
       </c>
       <c r="G218" t="n">
-        <v>10.2893505096436</v>
+        <v>10.2893495559692</v>
       </c>
       <c r="H218" t="n">
         <v>223312</v>
@@ -6836,7 +6836,7 @@
         <v>11.6719999313354</v>
       </c>
       <c r="G223" t="n">
-        <v>11.0444450378418</v>
+        <v>11.0444440841675</v>
       </c>
       <c r="H223" t="n">
         <v>345428</v>
@@ -6894,7 +6894,7 @@
         <v>11.9340000152588</v>
       </c>
       <c r="G225" t="n">
-        <v>11.2923593521118</v>
+        <v>11.2923574447632</v>
       </c>
       <c r="H225" t="n">
         <v>1392941</v>
@@ -6981,7 +6981,7 @@
         <v>11</v>
       </c>
       <c r="G228" t="n">
-        <v>10.4085760116577</v>
+        <v>10.4085750579834</v>
       </c>
       <c r="H228" t="n">
         <v>808095</v>
@@ -7010,7 +7010,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G229" t="n">
-        <v>10.4558868408203</v>
+        <v>10.4558877944946</v>
       </c>
       <c r="H229" t="n">
         <v>563146</v>
@@ -7039,7 +7039,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G230" t="n">
-        <v>10.3896512985229</v>
+        <v>10.3896503448486</v>
       </c>
       <c r="H230" t="n">
         <v>475068</v>
@@ -7155,7 +7155,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G234" t="n">
-        <v>10.5126619338989</v>
+        <v>10.5126600265503</v>
       </c>
       <c r="H234" t="n">
         <v>148165</v>
@@ -7213,7 +7213,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G236" t="n">
-        <v>10.2382535934448</v>
+        <v>10.2382526397705</v>
       </c>
       <c r="H236" t="n">
         <v>356369</v>
@@ -7271,7 +7271,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G238" t="n">
-        <v>10.2382535934448</v>
+        <v>10.2382526397705</v>
       </c>
       <c r="H238" t="n">
         <v>235729</v>
@@ -7474,7 +7474,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G245" t="n">
-        <v>9.97330760955811</v>
+        <v>9.97330856323242</v>
       </c>
       <c r="H245" t="n">
         <v>173366</v>
@@ -7735,7 +7735,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G254" t="n">
-        <v>9.99223232269287</v>
+        <v>9.99223327636719</v>
       </c>
       <c r="H254" t="n">
         <v>244328</v>
@@ -7764,7 +7764,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G255" t="n">
-        <v>10.2950277328491</v>
+        <v>10.2950286865234</v>
       </c>
       <c r="H255" t="n">
         <v>668230</v>
@@ -7793,7 +7793,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G256" t="n">
-        <v>10.3896512985229</v>
+        <v>10.3896503448486</v>
       </c>
       <c r="H256" t="n">
         <v>552393</v>
@@ -7880,7 +7880,7 @@
         <v>10.8299999237061</v>
       </c>
       <c r="G259" t="n">
-        <v>10.2477149963379</v>
+        <v>10.2477159500122</v>
       </c>
       <c r="H259" t="n">
         <v>180911</v>
@@ -7909,7 +7909,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G260" t="n">
-        <v>10.2382535934448</v>
+        <v>10.2382526397705</v>
       </c>
       <c r="H260" t="n">
         <v>290152</v>
@@ -7967,7 +7967,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G262" t="n">
-        <v>10.2382535934448</v>
+        <v>10.2382526397705</v>
       </c>
       <c r="H262" t="n">
         <v>242006</v>
@@ -8141,7 +8141,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G268" t="n">
-        <v>10.0982227325439</v>
+        <v>10.0982236862183</v>
       </c>
       <c r="H268" t="n">
         <v>162147</v>
@@ -8344,7 +8344,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G275" t="n">
-        <v>10.3310346603394</v>
+        <v>10.3310356140137</v>
       </c>
       <c r="H275" t="n">
         <v>417991</v>
@@ -8576,7 +8576,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G283" t="n">
-        <v>10.6220502853394</v>
+        <v>10.6220512390137</v>
       </c>
       <c r="H283" t="n">
         <v>129742</v>
@@ -8634,7 +8634,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G285" t="n">
-        <v>10.5638484954834</v>
+        <v>10.5638475418091</v>
       </c>
       <c r="H285" t="n">
         <v>180726</v>
@@ -8692,7 +8692,7 @@
         <v>10.5699996948242</v>
       </c>
       <c r="G287" t="n">
-        <v>10.2534313201904</v>
+        <v>10.2534303665161</v>
       </c>
       <c r="H287" t="n">
         <v>235286</v>
@@ -8721,7 +8721,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G288" t="n">
-        <v>10.3116340637207</v>
+        <v>10.311635017395</v>
       </c>
       <c r="H288" t="n">
         <v>127440</v>
@@ -8779,7 +8779,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G290" t="n">
-        <v>10.4377412796021</v>
+        <v>10.4377422332764</v>
       </c>
       <c r="H290" t="n">
         <v>97733</v>
@@ -8895,7 +8895,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G294" t="n">
-        <v>10.806360244751</v>
+        <v>10.8063611984253</v>
       </c>
       <c r="H294" t="n">
         <v>209159</v>
@@ -8982,7 +8982,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G297" t="n">
-        <v>10.951868057251</v>
+        <v>10.9518671035767</v>
       </c>
       <c r="H297" t="n">
         <v>175726</v>
@@ -9011,7 +9011,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G298" t="n">
-        <v>10.7578582763672</v>
+        <v>10.7578573226929</v>
       </c>
       <c r="H298" t="n">
         <v>301876</v>
@@ -9214,7 +9214,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G305" t="n">
-        <v>11.5823993682861</v>
+        <v>11.5824003219604</v>
       </c>
       <c r="H305" t="n">
         <v>274687</v>
@@ -9475,7 +9475,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G314" t="n">
-        <v>11.3398866653442</v>
+        <v>11.3398876190186</v>
       </c>
       <c r="H314" t="n">
         <v>110179</v>
@@ -9562,7 +9562,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G317" t="n">
-        <v>11.2525844573975</v>
+        <v>11.2525835037231</v>
       </c>
       <c r="H317" t="n">
         <v>381622</v>
@@ -9649,7 +9649,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G320" t="n">
-        <v>10.951868057251</v>
+        <v>10.9518671035767</v>
       </c>
       <c r="H320" t="n">
         <v>279934</v>
@@ -9707,7 +9707,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G322" t="n">
-        <v>10.9712696075439</v>
+        <v>10.9712686538696</v>
       </c>
       <c r="H322" t="n">
         <v>185383</v>
@@ -9765,7 +9765,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G324" t="n">
-        <v>10.7481575012207</v>
+        <v>10.7481565475464</v>
       </c>
       <c r="H324" t="n">
         <v>184196</v>
@@ -9852,7 +9852,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G327" t="n">
-        <v>10.7190551757812</v>
+        <v>10.7190561294556</v>
       </c>
       <c r="H327" t="n">
         <v>80274</v>
@@ -9881,7 +9881,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G328" t="n">
-        <v>10.7578582763672</v>
+        <v>10.7578573226929</v>
       </c>
       <c r="H328" t="n">
         <v>81593</v>
@@ -9910,7 +9910,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G329" t="n">
-        <v>10.8160600662231</v>
+        <v>10.8160610198975</v>
       </c>
       <c r="H329" t="n">
         <v>255497</v>
@@ -10055,7 +10055,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G334" t="n">
-        <v>11.1361770629883</v>
+        <v>11.136176109314</v>
       </c>
       <c r="H334" t="n">
         <v>92993</v>
@@ -10084,7 +10084,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G335" t="n">
-        <v>11.1361770629883</v>
+        <v>11.136176109314</v>
       </c>
       <c r="H335" t="n">
         <v>109603</v>
@@ -10258,7 +10258,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G341" t="n">
-        <v>11.4077911376953</v>
+        <v>11.4077920913696</v>
       </c>
       <c r="H341" t="n">
         <v>275168</v>
@@ -10374,7 +10374,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G345" t="n">
-        <v>10.9712696075439</v>
+        <v>10.9712686538696</v>
       </c>
       <c r="H345" t="n">
         <v>250890</v>
@@ -10403,7 +10403,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G346" t="n">
-        <v>10.9615688323975</v>
+        <v>10.9615678787231</v>
       </c>
       <c r="H346" t="n">
         <v>157159</v>
@@ -10432,7 +10432,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G347" t="n">
-        <v>11.0003700256348</v>
+        <v>11.0003709793091</v>
       </c>
       <c r="H347" t="n">
         <v>187467</v>
@@ -10461,7 +10461,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G348" t="n">
-        <v>11.0003700256348</v>
+        <v>11.0003709793091</v>
       </c>
       <c r="H348" t="n">
         <v>109481</v>
@@ -10722,7 +10722,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G357" t="n">
-        <v>11.0585737228394</v>
+        <v>11.058572769165</v>
       </c>
       <c r="H357" t="n">
         <v>184343</v>
@@ -10780,7 +10780,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G359" t="n">
-        <v>11.0003700256348</v>
+        <v>11.0003709793091</v>
       </c>
       <c r="H359" t="n">
         <v>186510</v>
@@ -10867,7 +10867,7 @@
         <v>11.25</v>
       </c>
       <c r="G362" t="n">
-        <v>10.913064956665</v>
+        <v>10.9130659103394</v>
       </c>
       <c r="H362" t="n">
         <v>440278</v>
@@ -10925,7 +10925,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G364" t="n">
-        <v>11.1458778381348</v>
+        <v>11.1458768844604</v>
       </c>
       <c r="H364" t="n">
         <v>188007</v>
@@ -11012,7 +11012,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G367" t="n">
-        <v>11.0585737228394</v>
+        <v>11.058572769165</v>
       </c>
       <c r="H367" t="n">
         <v>195723</v>
@@ -11070,7 +11070,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G369" t="n">
-        <v>11.1458778381348</v>
+        <v>11.1458768844604</v>
       </c>
       <c r="H369" t="n">
         <v>107932</v>
@@ -11128,7 +11128,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G371" t="n">
-        <v>11.1361770629883</v>
+        <v>11.136176109314</v>
       </c>
       <c r="H371" t="n">
         <v>118399</v>
@@ -11186,7 +11186,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G373" t="n">
-        <v>11.0197706222534</v>
+        <v>11.0197715759277</v>
       </c>
       <c r="H373" t="n">
         <v>147161</v>
@@ -11302,7 +11302,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G377" t="n">
-        <v>11.0197706222534</v>
+        <v>11.0197715759277</v>
       </c>
       <c r="H377" t="n">
         <v>130368</v>
@@ -11476,7 +11476,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G383" t="n">
-        <v>11.1361770629883</v>
+        <v>11.136176109314</v>
       </c>
       <c r="H383" t="n">
         <v>194313</v>
@@ -11592,7 +11592,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G387" t="n">
-        <v>11.1749792098999</v>
+        <v>11.1749801635742</v>
       </c>
       <c r="H387" t="n">
         <v>197901</v>
@@ -11650,7 +11650,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G389" t="n">
-        <v>11.4465942382812</v>
+        <v>11.4465932846069</v>
       </c>
       <c r="H389" t="n">
         <v>259214</v>
@@ -11737,7 +11737,7 @@
         <v>12.2200002670288</v>
       </c>
       <c r="G392" t="n">
-        <v>11.8540153503418</v>
+        <v>11.8540143966675</v>
       </c>
       <c r="H392" t="n">
         <v>194096</v>
@@ -11795,7 +11795,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G394" t="n">
-        <v>11.6988067626953</v>
+        <v>11.6988077163696</v>
       </c>
       <c r="H394" t="n">
         <v>171327</v>
@@ -11911,7 +11911,7 @@
         <v>11.9899997711182</v>
       </c>
       <c r="G398" t="n">
-        <v>11.6309032440186</v>
+        <v>11.6309022903442</v>
       </c>
       <c r="H398" t="n">
         <v>192088</v>
@@ -11940,7 +11940,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G399" t="n">
-        <v>11.5823993682861</v>
+        <v>11.5824003219604</v>
       </c>
       <c r="H399" t="n">
         <v>137161</v>
@@ -12056,7 +12056,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G403" t="n">
-        <v>12.1935319900513</v>
+        <v>12.193531036377</v>
       </c>
       <c r="H403" t="n">
         <v>108069</v>
@@ -12114,7 +12114,7 @@
         <v>12.5699996948242</v>
       </c>
       <c r="G405" t="n">
-        <v>12.1935319900513</v>
+        <v>12.193531036377</v>
       </c>
       <c r="H405" t="n">
         <v>135114</v>
@@ -12172,7 +12172,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G407" t="n">
-        <v>12.2226333618164</v>
+        <v>12.2226343154907</v>
       </c>
       <c r="H407" t="n">
         <v>185001</v>
@@ -12201,7 +12201,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G408" t="n">
-        <v>12.2517347335815</v>
+        <v>12.2517356872559</v>
       </c>
       <c r="H408" t="n">
         <v>172512</v>
@@ -12288,7 +12288,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G411" t="n">
-        <v>12.4651460647583</v>
+        <v>12.4651470184326</v>
       </c>
       <c r="H411" t="n">
         <v>133030</v>
@@ -12317,7 +12317,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G412" t="n">
-        <v>12.3875427246094</v>
+        <v>12.3875417709351</v>
       </c>
       <c r="H412" t="n">
         <v>148541</v>
@@ -12520,7 +12520,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G419" t="n">
-        <v>12.2517347335815</v>
+        <v>12.2517356872559</v>
       </c>
       <c r="H419" t="n">
         <v>165954</v>
@@ -12549,7 +12549,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G420" t="n">
-        <v>12.2226333618164</v>
+        <v>12.2226343154907</v>
       </c>
       <c r="H420" t="n">
         <v>258706</v>
@@ -12607,7 +12607,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G422" t="n">
-        <v>12.2129335403442</v>
+        <v>12.2129325866699</v>
       </c>
       <c r="H422" t="n">
         <v>137376</v>
@@ -12636,7 +12636,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G423" t="n">
-        <v>12.3875427246094</v>
+        <v>12.3875417709351</v>
       </c>
       <c r="H423" t="n">
         <v>99466</v>
@@ -12723,7 +12723,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G426" t="n">
-        <v>12.5427513122559</v>
+        <v>12.5427503585815</v>
       </c>
       <c r="H426" t="n">
         <v>197307</v>
@@ -12752,7 +12752,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G427" t="n">
-        <v>12.630054473877</v>
+        <v>12.6300554275513</v>
       </c>
       <c r="H427" t="n">
         <v>148262</v>
@@ -12839,7 +12839,7 @@
         <v>13</v>
       </c>
       <c r="G430" t="n">
-        <v>12.610652923584</v>
+        <v>12.6106538772583</v>
       </c>
       <c r="H430" t="n">
         <v>1807764</v>
@@ -12897,7 +12897,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G432" t="n">
-        <v>12.3972425460815</v>
+        <v>12.3972415924072</v>
       </c>
       <c r="H432" t="n">
         <v>1234024</v>
@@ -12955,7 +12955,7 @@
         <v>13.0799999237061</v>
       </c>
       <c r="G434" t="n">
-        <v>12.6882581710815</v>
+        <v>12.6882572174072</v>
       </c>
       <c r="H434" t="n">
         <v>465320</v>
@@ -13013,7 +13013,7 @@
         <v>13.5600004196167</v>
       </c>
       <c r="G436" t="n">
-        <v>13.1538820266724</v>
+        <v>13.1538829803467</v>
       </c>
       <c r="H436" t="n">
         <v>425963</v>
@@ -13274,7 +13274,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G445" t="n">
-        <v>13.7844152450562</v>
+        <v>13.7844142913818</v>
       </c>
       <c r="H445" t="n">
         <v>236771</v>
@@ -13303,7 +13303,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G446" t="n">
-        <v>14.3373432159424</v>
+        <v>14.3373422622681</v>
       </c>
       <c r="H446" t="n">
         <v>473165</v>
@@ -13332,7 +13332,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G447" t="n">
-        <v>14.4537496566772</v>
+        <v>14.4537487030029</v>
       </c>
       <c r="H447" t="n">
         <v>380386</v>
@@ -13361,7 +13361,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G448" t="n">
-        <v>14.667160987854</v>
+        <v>14.6671600341797</v>
       </c>
       <c r="H448" t="n">
         <v>267462</v>
@@ -13419,7 +13419,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G450" t="n">
-        <v>14.8029670715332</v>
+        <v>14.8029680252075</v>
       </c>
       <c r="H450" t="n">
         <v>391347</v>
@@ -13622,7 +13622,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G457" t="n">
-        <v>16.0446338653564</v>
+        <v>16.0446319580078</v>
       </c>
       <c r="H457" t="n">
         <v>378598</v>
@@ -13680,7 +13680,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G459" t="n">
-        <v>15.9573268890381</v>
+        <v>15.9573278427124</v>
       </c>
       <c r="H459" t="n">
         <v>261224</v>
@@ -13796,7 +13796,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G463" t="n">
-        <v>16.0252304077148</v>
+        <v>16.0252323150635</v>
       </c>
       <c r="H463" t="n">
         <v>392686</v>
@@ -13825,7 +13825,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G464" t="n">
-        <v>15.6857128143311</v>
+        <v>15.6857137680054</v>
       </c>
       <c r="H464" t="n">
         <v>532461</v>
@@ -14028,7 +14028,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G471" t="n">
-        <v>15.870023727417</v>
+        <v>15.8700227737427</v>
       </c>
       <c r="H471" t="n">
         <v>880362</v>
@@ -14115,7 +14115,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G474" t="n">
-        <v>16.9273796081543</v>
+        <v>16.9273777008057</v>
       </c>
       <c r="H474" t="n">
         <v>620043</v>
@@ -14260,7 +14260,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G479" t="n">
-        <v>17.5870094299316</v>
+        <v>17.5870113372803</v>
       </c>
       <c r="H479" t="n">
         <v>473621</v>
@@ -14289,7 +14289,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G480" t="n">
-        <v>17.5870094299316</v>
+        <v>17.5870113372803</v>
       </c>
       <c r="H480" t="n">
         <v>417252</v>
@@ -14347,7 +14347,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G482" t="n">
-        <v>17.1601886749268</v>
+        <v>17.1601905822754</v>
       </c>
       <c r="H482" t="n">
         <v>353508</v>
@@ -14405,7 +14405,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G484" t="n">
-        <v>17.7519187927246</v>
+        <v>17.7519207000732</v>
       </c>
       <c r="H484" t="n">
         <v>342388</v>
@@ -14434,7 +14434,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G485" t="n">
-        <v>17.7422218322754</v>
+        <v>17.7422199249268</v>
       </c>
       <c r="H485" t="n">
         <v>271126</v>
@@ -14521,7 +14521,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G488" t="n">
-        <v>17.9071292877197</v>
+        <v>17.9071273803711</v>
       </c>
       <c r="H488" t="n">
         <v>372109</v>
@@ -14550,7 +14550,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G489" t="n">
-        <v>18.3727531433105</v>
+        <v>18.3727512359619</v>
       </c>
       <c r="H489" t="n">
         <v>455016</v>
@@ -14608,7 +14608,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G491" t="n">
-        <v>16.8303718566895</v>
+        <v>16.8303737640381</v>
       </c>
       <c r="H491" t="n">
         <v>1164243</v>
@@ -14695,7 +14695,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G494" t="n">
-        <v>17.1601886749268</v>
+        <v>17.1601905822754</v>
       </c>
       <c r="H494" t="n">
         <v>564420</v>
@@ -14898,7 +14898,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G501" t="n">
-        <v>18.8480777740479</v>
+        <v>18.8480758666992</v>
       </c>
       <c r="H501" t="n">
         <v>377971</v>
@@ -14927,7 +14927,7 @@
         <v>19.4699993133545</v>
       </c>
       <c r="G502" t="n">
-        <v>18.8868789672852</v>
+        <v>18.8868770599365</v>
       </c>
       <c r="H502" t="n">
         <v>436832</v>
@@ -14956,7 +14956,7 @@
         <v>19.6100006103516</v>
       </c>
       <c r="G503" t="n">
-        <v>19.0226860046387</v>
+        <v>19.0226879119873</v>
       </c>
       <c r="H503" t="n">
         <v>218294</v>
@@ -15014,7 +15014,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G505" t="n">
-        <v>19.478609085083</v>
+        <v>19.4786109924316</v>
       </c>
       <c r="H505" t="n">
         <v>375456</v>
@@ -15043,7 +15043,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G506" t="n">
-        <v>19.45920753479</v>
+        <v>19.4592094421387</v>
       </c>
       <c r="H506" t="n">
         <v>430857</v>
@@ -15072,7 +15072,7 @@
         <v>20.0400009155273</v>
       </c>
       <c r="G507" t="n">
-        <v>19.4398097991943</v>
+        <v>19.4398078918457</v>
       </c>
       <c r="H507" t="n">
         <v>573705</v>
@@ -15130,7 +15130,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G509" t="n">
-        <v>20.3128547668457</v>
+        <v>20.3128528594971</v>
       </c>
       <c r="H509" t="n">
         <v>845381</v>
@@ -15159,7 +15159,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G510" t="n">
-        <v>20.2352485656738</v>
+        <v>20.2352504730225</v>
       </c>
       <c r="H510" t="n">
         <v>628106</v>
@@ -15188,7 +15188,7 @@
         <v>20.5400009155273</v>
       </c>
       <c r="G511" t="n">
-        <v>19.9248352050781</v>
+        <v>19.9248332977295</v>
       </c>
       <c r="H511" t="n">
         <v>774008</v>
@@ -15217,7 +15217,7 @@
         <v>20</v>
       </c>
       <c r="G512" t="n">
-        <v>19.4010066986084</v>
+        <v>19.4010047912598</v>
       </c>
       <c r="H512" t="n">
         <v>769373</v>
@@ -15304,7 +15304,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>21.6321201324463</v>
+        <v>21.6321220397949</v>
       </c>
       <c r="H515" t="n">
         <v>2197577</v>
@@ -15362,7 +15362,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G517" t="n">
-        <v>22.1171474456787</v>
+        <v>22.1171455383301</v>
       </c>
       <c r="H517" t="n">
         <v>555528</v>
@@ -15391,7 +15391,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G518" t="n">
-        <v>21.9619369506836</v>
+        <v>21.9619388580322</v>
       </c>
       <c r="H518" t="n">
         <v>611058</v>
@@ -26127,6 +26127,35 @@
         <v>570269</v>
       </c>
       <c r="I888" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="s">
+        <v>9</v>
+      </c>
+      <c r="B889" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C889" t="n">
+        <v>25.4500007629395</v>
+      </c>
+      <c r="D889" t="n">
+        <v>25.9200000762939</v>
+      </c>
+      <c r="E889" t="n">
+        <v>25.3600006103516</v>
+      </c>
+      <c r="F889" t="n">
+        <v>25.9200000762939</v>
+      </c>
+      <c r="G889" t="n">
+        <v>25.9200000762939</v>
+      </c>
+      <c r="H889" t="n">
+        <v>738628</v>
+      </c>
+      <c r="I889" t="s">
         <v>9</v>
       </c>
     </row>
